--- a/Check-lists.xlsx
+++ b/Check-lists.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="167">
   <si>
     <t>№ проверки</t>
   </si>
@@ -123,9 +123,6 @@
   </si>
   <si>
     <t>Эндпоинт POST/login</t>
-  </si>
-  <si>
-    <t>Эндпоинт GET/me</t>
   </si>
   <si>
     <t>Эндпоинт GET/profile</t>
@@ -527,6 +524,12 @@
   </si>
   <si>
     <t>Пароль валидной длины,игнорирование требований сложности (ввод пароля без одного из обязательных значений поочерёдно. Логин валидный.</t>
+  </si>
+  <si>
+    <t>Пароль с пробелами. Логин валидный.</t>
+  </si>
+  <si>
+    <t>Эндпоинт GET/tasks</t>
   </si>
 </sst>
 </file>
@@ -1035,7 +1038,7 @@
   <sheetData>
     <row r="2" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2" s="26" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C2" s="27"/>
       <c r="D2" s="27"/>
@@ -1074,7 +1077,7 @@
         <v>19</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F4" s="12" t="s">
         <v>14</v>
@@ -1092,7 +1095,7 @@
         <v>19</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F5" s="12" t="s">
         <v>14</v>
@@ -1110,7 +1113,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F6" s="12" t="s">
         <v>14</v>
@@ -1128,7 +1131,7 @@
         <v>31</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F7" s="12" t="s">
         <v>14</v>
@@ -1146,7 +1149,7 @@
         <v>31</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F8" s="12" t="s">
         <v>14</v>
@@ -1158,13 +1161,13 @@
         <v>6</v>
       </c>
       <c r="C9" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" s="10" t="s">
         <v>104</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>105</v>
       </c>
       <c r="F9" s="12" t="s">
         <v>14</v>
@@ -1176,13 +1179,13 @@
         <v>7</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D10" s="12" t="s">
         <v>30</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F10" s="12" t="s">
         <v>14</v>
@@ -1200,7 +1203,7 @@
         <v>31</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F11" s="12" t="s">
         <v>14</v>
@@ -1212,13 +1215,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D12" s="12" t="s">
         <v>30</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F12" s="12" t="s">
         <v>14</v>
@@ -1236,7 +1239,7 @@
         <v>31</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F13" s="12" t="s">
         <v>14</v>
@@ -1254,7 +1257,7 @@
         <v>30</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F14" s="12" t="s">
         <v>14</v>
@@ -1272,7 +1275,7 @@
         <v>30</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F15" s="12" t="s">
         <v>14</v>
@@ -1284,19 +1287,19 @@
         <v>13</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D16" s="12" t="s">
         <v>31</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F16" s="12" t="s">
         <v>15</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="17" spans="2:7" ht="30" x14ac:dyDescent="0.25">
@@ -1304,13 +1307,13 @@
         <v>14</v>
       </c>
       <c r="C17" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E17" s="10" t="s">
         <v>101</v>
-      </c>
-      <c r="D17" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="E17" s="10" t="s">
-        <v>102</v>
       </c>
       <c r="F17" s="12" t="s">
         <v>14</v>
@@ -1322,13 +1325,13 @@
         <v>15</v>
       </c>
       <c r="C18" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="E18" s="14" t="s">
         <v>108</v>
-      </c>
-      <c r="D18" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="E18" s="14" t="s">
-        <v>109</v>
       </c>
       <c r="F18" s="12" t="s">
         <v>15</v>
@@ -1340,13 +1343,13 @@
         <v>16</v>
       </c>
       <c r="C19" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="E19" s="14" t="s">
         <v>118</v>
-      </c>
-      <c r="D19" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="E19" s="14" t="s">
-        <v>119</v>
       </c>
       <c r="F19" s="12" t="s">
         <v>14</v>
@@ -1356,7 +1359,7 @@
     <row r="20" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="21" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B21" s="26" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C21" s="27"/>
       <c r="D21" s="27"/>
@@ -1389,13 +1392,13 @@
         <v>1</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>14</v>
@@ -1407,13 +1410,13 @@
         <v>2</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>30</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>14</v>
@@ -1425,13 +1428,13 @@
         <v>3</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>30</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>14</v>
@@ -1443,13 +1446,13 @@
         <v>4</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>30</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>14</v>
@@ -1461,13 +1464,13 @@
         <v>5</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>30</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>14</v>
@@ -1479,13 +1482,13 @@
         <v>6</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>30</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>14</v>
@@ -1497,19 +1500,19 @@
         <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>30</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>15</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="30" spans="2:7" ht="30" x14ac:dyDescent="0.25">
@@ -1517,13 +1520,13 @@
         <v>8</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>30</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>14</v>
@@ -1535,13 +1538,13 @@
         <v>9</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>14</v>
@@ -1553,13 +1556,13 @@
         <v>10</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>14</v>
@@ -1571,13 +1574,13 @@
         <v>11</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>14</v>
@@ -1589,13 +1592,13 @@
         <v>12</v>
       </c>
       <c r="C34" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="D34" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="E34" s="15" t="s">
         <v>108</v>
-      </c>
-      <c r="D34" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="E34" s="15" t="s">
-        <v>109</v>
       </c>
       <c r="F34" s="12" t="s">
         <v>15</v>
@@ -1605,7 +1608,7 @@
     <row r="36" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B36" s="21"/>
       <c r="C36" s="27" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D36" s="27"/>
       <c r="E36" s="27"/>
@@ -1637,13 +1640,13 @@
         <v>1</v>
       </c>
       <c r="C38" s="18" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D38" s="18" t="s">
         <v>1</v>
       </c>
       <c r="E38" s="18" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F38" s="18" t="s">
         <v>14</v>
@@ -1653,7 +1656,7 @@
     <row r="39" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B39" s="11"/>
       <c r="C39" s="22" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D39" s="23"/>
       <c r="E39" s="23"/>
@@ -1665,13 +1668,13 @@
         <v>2</v>
       </c>
       <c r="C40" s="20" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D40" s="20" t="s">
         <v>1</v>
       </c>
       <c r="E40" s="20" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F40" s="20" t="s">
         <v>14</v>
@@ -1683,13 +1686,13 @@
         <v>3</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>14</v>
@@ -1701,19 +1704,19 @@
         <v>4</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>15</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="43" spans="2:7" ht="30" x14ac:dyDescent="0.25">
@@ -1721,13 +1724,13 @@
         <v>5</v>
       </c>
       <c r="C43" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E43" s="2" t="s">
         <v>130</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>131</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>14</v>
@@ -1737,7 +1740,7 @@
     <row r="44" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B44" s="11"/>
       <c r="C44" s="22" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D44" s="23"/>
       <c r="E44" s="23"/>
@@ -1749,13 +1752,13 @@
         <v>6</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>1</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>14</v>
@@ -1767,13 +1770,13 @@
         <v>7</v>
       </c>
       <c r="C46" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E46" s="2" t="s">
         <v>141</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>142</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>14</v>
@@ -1785,13 +1788,13 @@
         <v>8</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>1</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>14</v>
@@ -1803,13 +1806,13 @@
         <v>9</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>14</v>
@@ -1821,13 +1824,13 @@
         <v>10</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>1</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>14</v>
@@ -1839,13 +1842,13 @@
         <v>11</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>14</v>
@@ -1857,13 +1860,13 @@
         <v>12</v>
       </c>
       <c r="C51" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E51" s="2" t="s">
         <v>143</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>144</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>14</v>
@@ -1875,13 +1878,13 @@
         <v>13</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>14</v>
@@ -1893,13 +1896,13 @@
         <v>14</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>14</v>
@@ -1911,13 +1914,13 @@
         <v>15</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>1</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>14</v>
@@ -1929,13 +1932,13 @@
         <v>16</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>1</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>14</v>
@@ -1947,13 +1950,13 @@
         <v>17</v>
       </c>
       <c r="C56" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E56" s="15" t="s">
         <v>147</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E56" s="15" t="s">
-        <v>148</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>14</v>
@@ -1973,13 +1976,13 @@
         <v>18</v>
       </c>
       <c r="C58" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E58" s="15" t="s">
         <v>151</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E58" s="15" t="s">
-        <v>152</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>14</v>
@@ -2098,7 +2101,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>19</v>
@@ -2114,7 +2117,7 @@
         <v>1</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>1</v>
@@ -2132,7 +2135,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>19</v>
@@ -2148,7 +2151,7 @@
         <v>2</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>30</v>
@@ -2182,7 +2185,7 @@
         <v>3</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>30</v>
@@ -2200,7 +2203,7 @@
         <v>4</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>21</v>
@@ -2216,7 +2219,7 @@
         <v>4</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K7" s="1" t="s">
         <v>30</v>
@@ -2234,7 +2237,7 @@
         <v>5</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>21</v>
@@ -2250,7 +2253,7 @@
         <v>5</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K8" s="1" t="s">
         <v>30</v>
@@ -2268,7 +2271,7 @@
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>30</v>
@@ -2284,7 +2287,7 @@
         <v>7</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>30</v>
@@ -2302,7 +2305,7 @@
         <v>8</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>21</v>
@@ -2318,7 +2321,7 @@
         <v>8</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K10" s="1" t="s">
         <v>30</v>
@@ -2336,13 +2339,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>30</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>14</v>
@@ -2352,7 +2355,7 @@
         <v>9</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K11" s="1" t="s">
         <v>30</v>
@@ -2370,7 +2373,7 @@
         <v>10</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>21</v>
@@ -2386,7 +2389,7 @@
         <v>10</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>30</v>
@@ -2398,7 +2401,7 @@
         <v>14</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="13" spans="2:14" ht="30" x14ac:dyDescent="0.25">
@@ -2406,7 +2409,7 @@
         <v>11</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>24</v>
+        <v>165</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>30</v>
@@ -2422,7 +2425,7 @@
         <v>11</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K13" s="1" t="s">
         <v>30</v>
@@ -2440,7 +2443,7 @@
         <v>12</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>30</v>
@@ -2456,7 +2459,7 @@
         <v>12</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K14" s="1" t="s">
         <v>30</v>
@@ -2468,7 +2471,7 @@
         <v>14</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.25">
@@ -2521,7 +2524,7 @@
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B18" s="26" t="s">
-        <v>34</v>
+        <v>166</v>
       </c>
       <c r="C18" s="27"/>
       <c r="D18" s="27"/>
@@ -2529,7 +2532,7 @@
       <c r="F18" s="27"/>
       <c r="G18" s="28"/>
       <c r="I18" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J18" s="27"/>
       <c r="K18" s="27"/>
@@ -2580,7 +2583,7 @@
         <v>1</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>1</v>
@@ -2596,7 +2599,7 @@
         <v>1</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K20" s="1" t="s">
         <v>1</v>
@@ -2614,7 +2617,7 @@
         <v>2</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>30</v>
@@ -2630,7 +2633,7 @@
         <v>2</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K21" s="1" t="s">
         <v>30</v>
@@ -2648,7 +2651,7 @@
         <v>3</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>30</v>
@@ -2664,7 +2667,7 @@
         <v>3</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K22" s="1" t="s">
         <v>30</v>
@@ -2682,7 +2685,7 @@
         <v>4</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>30</v>
@@ -2698,7 +2701,7 @@
         <v>4</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K23" s="1" t="s">
         <v>30</v>
@@ -2716,7 +2719,7 @@
         <v>5</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>30</v>
@@ -2732,7 +2735,7 @@
         <v>5</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K24" s="1" t="s">
         <v>30</v>
@@ -2756,7 +2759,7 @@
         <v>6</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K25" s="1" t="s">
         <v>1</v>
@@ -2780,7 +2783,7 @@
         <v>7</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K26" s="1" t="s">
         <v>1</v>
@@ -2804,7 +2807,7 @@
         <v>8</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K27" s="1" t="s">
         <v>1</v>
@@ -2828,7 +2831,7 @@
         <v>9</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K28" s="1" t="s">
         <v>1</v>
@@ -2857,7 +2860,7 @@
     </row>
     <row r="30" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B30" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C30" s="27"/>
       <c r="D30" s="27"/>
@@ -2865,7 +2868,7 @@
       <c r="F30" s="27"/>
       <c r="G30" s="28"/>
       <c r="I30" s="29" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J30" s="29"/>
       <c r="K30" s="29"/>
@@ -2916,7 +2919,7 @@
         <v>1</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>1</v>
@@ -2932,7 +2935,7 @@
         <v>1</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K32" s="1" t="s">
         <v>1</v>
@@ -2950,7 +2953,7 @@
         <v>2</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>1</v>
@@ -2966,7 +2969,7 @@
         <v>2</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K33" s="1" t="s">
         <v>30</v>
@@ -2984,7 +2987,7 @@
         <v>3</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>30</v>
@@ -3000,7 +3003,7 @@
         <v>3</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K34" s="1" t="s">
         <v>1</v>
@@ -3018,7 +3021,7 @@
         <v>4</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>30</v>
@@ -3034,7 +3037,7 @@
         <v>4</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="K35" s="1" t="s">
         <v>30</v>
@@ -3046,7 +3049,7 @@
         <v>14</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="36" spans="2:14" x14ac:dyDescent="0.25">
@@ -3054,7 +3057,7 @@
         <v>5</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>30</v>
@@ -3070,7 +3073,7 @@
         <v>5</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K36" s="1" t="s">
         <v>1</v>
@@ -3088,7 +3091,7 @@
         <v>6</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>30</v>
@@ -3104,7 +3107,7 @@
         <v>6</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K37" s="1" t="s">
         <v>30</v>
@@ -3122,7 +3125,7 @@
         <v>7</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>30</v>
@@ -3138,7 +3141,7 @@
         <v>7</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K38" s="1" t="s">
         <v>1</v>
@@ -3156,7 +3159,7 @@
         <v>8</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>30</v>
@@ -3172,7 +3175,7 @@
         <v>8</v>
       </c>
       <c r="J39" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K39" s="1" t="s">
         <v>30</v>
@@ -3190,7 +3193,7 @@
         <v>9</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>30</v>
@@ -3206,7 +3209,7 @@
         <v>9</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K40" s="1" t="s">
         <v>30</v>
@@ -3224,7 +3227,7 @@
         <v>10</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>31</v>
@@ -3240,7 +3243,7 @@
         <v>10</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="K41" s="1" t="s">
         <v>30</v>
@@ -3258,7 +3261,7 @@
         <v>11</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>31</v>
@@ -3274,7 +3277,7 @@
         <v>11</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K42" s="1" t="s">
         <v>30</v>
@@ -3292,7 +3295,7 @@
         <v>12</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>30</v>
@@ -3304,13 +3307,13 @@
         <v>14</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I43" s="4">
         <v>12</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K43" s="1" t="s">
         <v>30</v>
@@ -3485,7 +3488,7 @@
         <v>13</v>
       </c>
       <c r="H1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" spans="2:8" x14ac:dyDescent="0.25">
@@ -3499,7 +3502,7 @@
         <v>14</v>
       </c>
       <c r="H2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
@@ -3541,12 +3544,12 @@
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>

--- a/Check-lists.xlsx
+++ b/Check-lists.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="166">
   <si>
     <t>№ проверки</t>
   </si>
@@ -273,12 +273,6 @@
   </si>
   <si>
     <t>409 Conflict</t>
-  </si>
-  <si>
-    <t>лучше пофиксить ввод пробела на границах</t>
-  </si>
-  <si>
-    <t>игнорирование лишних полей</t>
   </si>
   <si>
     <t>Лучше возвращать 400</t>
@@ -530,6 +524,9 @@
   </si>
   <si>
     <t>Эндпоинт GET/tasks</t>
+  </si>
+  <si>
+    <t>Автоматизировано</t>
   </si>
 </sst>
 </file>
@@ -1038,7 +1035,7 @@
   <sheetData>
     <row r="2" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2" s="26" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C2" s="27"/>
       <c r="D2" s="27"/>
@@ -1077,7 +1074,7 @@
         <v>19</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F4" s="12" t="s">
         <v>14</v>
@@ -1095,7 +1092,7 @@
         <v>19</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F5" s="12" t="s">
         <v>14</v>
@@ -1113,7 +1110,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F6" s="12" t="s">
         <v>14</v>
@@ -1131,7 +1128,7 @@
         <v>31</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F7" s="12" t="s">
         <v>14</v>
@@ -1149,7 +1146,7 @@
         <v>31</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F8" s="12" t="s">
         <v>14</v>
@@ -1161,13 +1158,13 @@
         <v>6</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D9" s="12" t="s">
         <v>30</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F9" s="12" t="s">
         <v>14</v>
@@ -1179,13 +1176,13 @@
         <v>7</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D10" s="12" t="s">
         <v>30</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F10" s="12" t="s">
         <v>14</v>
@@ -1203,7 +1200,7 @@
         <v>31</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F11" s="12" t="s">
         <v>14</v>
@@ -1221,7 +1218,7 @@
         <v>30</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F12" s="12" t="s">
         <v>14</v>
@@ -1239,7 +1236,7 @@
         <v>31</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F13" s="12" t="s">
         <v>14</v>
@@ -1257,7 +1254,7 @@
         <v>30</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F14" s="12" t="s">
         <v>14</v>
@@ -1275,7 +1272,7 @@
         <v>30</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F15" s="12" t="s">
         <v>14</v>
@@ -1287,19 +1284,19 @@
         <v>13</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D16" s="12" t="s">
         <v>31</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F16" s="12" t="s">
         <v>15</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="17" spans="2:7" ht="30" x14ac:dyDescent="0.25">
@@ -1307,13 +1304,13 @@
         <v>14</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D17" s="12" t="s">
         <v>30</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F17" s="12" t="s">
         <v>14</v>
@@ -1325,13 +1322,13 @@
         <v>15</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D18" s="12" t="s">
         <v>1</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F18" s="12" t="s">
         <v>15</v>
@@ -1343,13 +1340,13 @@
         <v>16</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D19" s="12" t="s">
         <v>1</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F19" s="12" t="s">
         <v>14</v>
@@ -1359,7 +1356,7 @@
     <row r="20" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="21" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B21" s="26" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C21" s="27"/>
       <c r="D21" s="27"/>
@@ -1398,7 +1395,7 @@
         <v>1</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>14</v>
@@ -1416,7 +1413,7 @@
         <v>30</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>14</v>
@@ -1434,7 +1431,7 @@
         <v>30</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>14</v>
@@ -1452,7 +1449,7 @@
         <v>30</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>14</v>
@@ -1464,13 +1461,13 @@
         <v>5</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>30</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>14</v>
@@ -1488,7 +1485,7 @@
         <v>30</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>14</v>
@@ -1506,13 +1503,13 @@
         <v>30</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>15</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="30" spans="2:7" ht="30" x14ac:dyDescent="0.25">
@@ -1526,7 +1523,7 @@
         <v>30</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>14</v>
@@ -1538,13 +1535,13 @@
         <v>9</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>14</v>
@@ -1556,13 +1553,13 @@
         <v>10</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>14</v>
@@ -1574,13 +1571,13 @@
         <v>11</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>14</v>
@@ -1592,13 +1589,13 @@
         <v>12</v>
       </c>
       <c r="C34" s="16" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D34" s="16" t="s">
         <v>1</v>
       </c>
       <c r="E34" s="15" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F34" s="12" t="s">
         <v>15</v>
@@ -1608,7 +1605,7 @@
     <row r="36" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B36" s="21"/>
       <c r="C36" s="27" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D36" s="27"/>
       <c r="E36" s="27"/>
@@ -1640,13 +1637,13 @@
         <v>1</v>
       </c>
       <c r="C38" s="18" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D38" s="18" t="s">
         <v>1</v>
       </c>
       <c r="E38" s="18" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F38" s="18" t="s">
         <v>14</v>
@@ -1656,7 +1653,7 @@
     <row r="39" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B39" s="11"/>
       <c r="C39" s="22" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D39" s="23"/>
       <c r="E39" s="23"/>
@@ -1668,13 +1665,13 @@
         <v>2</v>
       </c>
       <c r="C40" s="20" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D40" s="20" t="s">
         <v>1</v>
       </c>
       <c r="E40" s="20" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F40" s="20" t="s">
         <v>14</v>
@@ -1686,13 +1683,13 @@
         <v>3</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>14</v>
@@ -1704,19 +1701,19 @@
         <v>4</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>15</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="43" spans="2:7" ht="30" x14ac:dyDescent="0.25">
@@ -1724,13 +1721,13 @@
         <v>5</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>1</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>14</v>
@@ -1740,7 +1737,7 @@
     <row r="44" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B44" s="11"/>
       <c r="C44" s="22" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D44" s="23"/>
       <c r="E44" s="23"/>
@@ -1758,7 +1755,7 @@
         <v>1</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>14</v>
@@ -1770,13 +1767,13 @@
         <v>7</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>14</v>
@@ -1794,7 +1791,7 @@
         <v>1</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>14</v>
@@ -1812,7 +1809,7 @@
         <v>30</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>14</v>
@@ -1830,7 +1827,7 @@
         <v>1</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>14</v>
@@ -1848,7 +1845,7 @@
         <v>30</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>14</v>
@@ -1860,13 +1857,13 @@
         <v>12</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>14</v>
@@ -1878,13 +1875,13 @@
         <v>13</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>14</v>
@@ -1896,13 +1893,13 @@
         <v>14</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>14</v>
@@ -1914,13 +1911,13 @@
         <v>15</v>
       </c>
       <c r="C54" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E54" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>154</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>14</v>
@@ -1932,13 +1929,13 @@
         <v>16</v>
       </c>
       <c r="C55" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E55" s="2" t="s">
         <v>153</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>155</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>14</v>
@@ -1950,13 +1947,13 @@
         <v>17</v>
       </c>
       <c r="C56" s="15" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E56" s="15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>14</v>
@@ -1976,13 +1973,13 @@
         <v>18</v>
       </c>
       <c r="C58" s="15" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>1</v>
       </c>
       <c r="E58" s="15" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>14</v>
@@ -2101,7 +2098,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>19</v>
@@ -2112,7 +2109,9 @@
       <c r="F4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G4" s="1"/>
+      <c r="G4" s="1" t="s">
+        <v>165</v>
+      </c>
       <c r="I4" s="4">
         <v>1</v>
       </c>
@@ -2135,7 +2134,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>19</v>
@@ -2146,7 +2145,9 @@
       <c r="F5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="2"/>
+      <c r="G5" s="1" t="s">
+        <v>165</v>
+      </c>
       <c r="I5" s="4">
         <v>2</v>
       </c>
@@ -2180,7 +2181,9 @@
       <c r="F6" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G6" s="1"/>
+      <c r="G6" s="1" t="s">
+        <v>165</v>
+      </c>
       <c r="I6" s="4">
         <v>3</v>
       </c>
@@ -2203,7 +2206,7 @@
         <v>4</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>21</v>
@@ -2214,7 +2217,9 @@
       <c r="F7" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G7" s="1"/>
+      <c r="G7" s="1" t="s">
+        <v>165</v>
+      </c>
       <c r="I7" s="4">
         <v>4</v>
       </c>
@@ -2237,7 +2242,7 @@
         <v>5</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>21</v>
@@ -2248,7 +2253,9 @@
       <c r="F8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G8" s="1"/>
+      <c r="G8" s="1" t="s">
+        <v>165</v>
+      </c>
       <c r="I8" s="4">
         <v>5</v>
       </c>
@@ -2271,7 +2278,7 @@
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>30</v>
@@ -2282,7 +2289,9 @@
       <c r="F9" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G9" s="1"/>
+      <c r="G9" s="1" t="s">
+        <v>165</v>
+      </c>
       <c r="I9" s="4">
         <v>7</v>
       </c>
@@ -2305,7 +2314,7 @@
         <v>8</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>21</v>
@@ -2316,7 +2325,9 @@
       <c r="F10" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G10" s="1"/>
+      <c r="G10" s="1" t="s">
+        <v>165</v>
+      </c>
       <c r="I10" s="4">
         <v>8</v>
       </c>
@@ -2339,7 +2350,7 @@
         <v>9</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>30</v>
@@ -2350,7 +2361,9 @@
       <c r="F11" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G11" s="1"/>
+      <c r="G11" s="1" t="s">
+        <v>165</v>
+      </c>
       <c r="I11" s="4">
         <v>9</v>
       </c>
@@ -2373,7 +2386,7 @@
         <v>10</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>21</v>
@@ -2384,7 +2397,9 @@
       <c r="F12" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G12" s="2"/>
+      <c r="G12" s="1" t="s">
+        <v>165</v>
+      </c>
       <c r="I12" s="4">
         <v>10</v>
       </c>
@@ -2400,16 +2415,14 @@
       <c r="M12" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="N12" s="2" t="s">
-        <v>84</v>
-      </c>
+      <c r="N12" s="2"/>
     </row>
     <row r="13" spans="2:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B13" s="4">
         <v>11</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>30</v>
@@ -2443,7 +2456,7 @@
         <v>12</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>30</v>
@@ -2470,9 +2483,7 @@
       <c r="M14" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="N14" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="N14" s="1"/>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B15" s="4">
@@ -2524,7 +2535,7 @@
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B18" s="26" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C18" s="27"/>
       <c r="D18" s="27"/>
@@ -3049,7 +3060,7 @@
         <v>14</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="36" spans="2:14" x14ac:dyDescent="0.25">
@@ -3307,7 +3318,7 @@
         <v>14</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="I43" s="4">
         <v>12</v>
@@ -3488,7 +3499,7 @@
         <v>13</v>
       </c>
       <c r="H1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="2" spans="2:8" x14ac:dyDescent="0.25">
@@ -3502,7 +3513,7 @@
         <v>14</v>
       </c>
       <c r="H2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">

--- a/Check-lists.xlsx
+++ b/Check-lists.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="139">
   <si>
     <t>№ проверки</t>
   </si>
@@ -125,12 +125,6 @@
     <t>Эндпоинт POST/login</t>
   </si>
   <si>
-    <t>Эндпоинт GET/profile</t>
-  </si>
-  <si>
-    <t>Эндпоинт PUT /users/{id}/password</t>
-  </si>
-  <si>
     <t>Вход с валидным логином и паролем</t>
   </si>
   <si>
@@ -182,57 +176,9 @@
     <t>Запрос с невалидным токеном</t>
   </si>
   <si>
-    <t>Эндпоинт PUT /profile</t>
-  </si>
-  <si>
-    <t>Данные в GET /profile соответствуют данным, обновлённым через PUT /profile</t>
-  </si>
-  <si>
-    <t>Данные профиля соответствуют пользователю, авторизованному по токену</t>
-  </si>
-  <si>
-    <t>Не заполненные опциональные поля возвращаются как null</t>
-  </si>
-  <si>
-    <t>Смена пароля с несуществующим JWT</t>
-  </si>
-  <si>
-    <t>Смена пароля без Authorization</t>
-  </si>
-  <si>
-    <t>Смена пароля с истёкшим JWT</t>
-  </si>
-  <si>
-    <t>Смена  пароля пользователя с его активным JWT</t>
-  </si>
-  <si>
-    <t>Пустой Body</t>
-  </si>
-  <si>
-    <t>Новый Пароль невалидной длины,требования сложности соблюдены</t>
-  </si>
-  <si>
-    <t>Новый пароль = старый пароль</t>
-  </si>
-  <si>
-    <t>Успешный логин после смены пароля</t>
-  </si>
-  <si>
-    <t>Смена чужого пароля со своим JWT</t>
-  </si>
-  <si>
     <t>415 Unsupported media type</t>
   </si>
   <si>
-    <t>Смена пароля с валидным JWT другого пользователя</t>
-  </si>
-  <si>
-    <t>Body содержит дополнительные поля, не предусмотренные API</t>
-  </si>
-  <si>
-    <t>Пароль валидной длины, но не соответствует требованиям сложности и локализации</t>
-  </si>
-  <si>
     <t>Смена e-mail на валидный</t>
   </si>
   <si>
@@ -245,40 +191,10 @@
     <t>Смена номера телефона на невалидный (длина, буквы, спецсимволы)</t>
   </si>
   <si>
-    <t>Изменение данных без JWT</t>
-  </si>
-  <si>
-    <t>Изменение данных с истёкшим JWT</t>
-  </si>
-  <si>
-    <t>Указание неподдерживаемого поля в Body (в т.ч. Birth Date)</t>
-  </si>
-  <si>
-    <t>Опциональные поля заполнены, запрос с Body = {} → профиль очищается</t>
-  </si>
-  <si>
-    <t>Опциональные поля не заполнены, запрос с Body = {} → ошибка ""no changes to update""</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Смена e-mail - невалидный формат </t>
-  </si>
-  <si>
     <t xml:space="preserve">Смена имени - невалидный фомат </t>
   </si>
   <si>
-    <t>Попытка запроса без внесения изменений со всеми заполненными опциональными полями</t>
-  </si>
-  <si>
-    <t>PUT /profile очищает поля, отсутствующие в запросе</t>
-  </si>
-  <si>
     <t>409 Conflict</t>
-  </si>
-  <si>
-    <t>Лучше возвращать 400</t>
-  </si>
-  <si>
-    <t>допускает пробелы перед и в конце имени, обрезвает их</t>
   </si>
   <si>
     <t>Ожидаемый результат фронта</t>
@@ -527,6 +443,9 @@
   </si>
   <si>
     <t>Автоматизировано</t>
+  </si>
+  <si>
+    <t>Вход с верным логином и паролем</t>
   </si>
 </sst>
 </file>
@@ -1035,7 +954,7 @@
   <sheetData>
     <row r="2" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2" s="26" t="s">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="C2" s="27"/>
       <c r="D2" s="27"/>
@@ -1074,7 +993,7 @@
         <v>19</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="F4" s="12" t="s">
         <v>14</v>
@@ -1092,7 +1011,7 @@
         <v>19</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="F5" s="12" t="s">
         <v>14</v>
@@ -1110,7 +1029,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="F6" s="12" t="s">
         <v>14</v>
@@ -1128,7 +1047,7 @@
         <v>31</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="F7" s="12" t="s">
         <v>14</v>
@@ -1146,7 +1065,7 @@
         <v>31</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>89</v>
+        <v>61</v>
       </c>
       <c r="F8" s="12" t="s">
         <v>14</v>
@@ -1158,13 +1077,13 @@
         <v>6</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>101</v>
+        <v>73</v>
       </c>
       <c r="D9" s="12" t="s">
         <v>30</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>102</v>
+        <v>74</v>
       </c>
       <c r="F9" s="12" t="s">
         <v>14</v>
@@ -1176,13 +1095,13 @@
         <v>7</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="D10" s="12" t="s">
         <v>30</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>93</v>
+        <v>65</v>
       </c>
       <c r="F10" s="12" t="s">
         <v>14</v>
@@ -1200,7 +1119,7 @@
         <v>31</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>103</v>
+        <v>75</v>
       </c>
       <c r="F11" s="12" t="s">
         <v>14</v>
@@ -1212,13 +1131,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D12" s="12" t="s">
         <v>30</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="F12" s="12" t="s">
         <v>14</v>
@@ -1236,7 +1155,7 @@
         <v>31</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>92</v>
+        <v>64</v>
       </c>
       <c r="F13" s="12" t="s">
         <v>14</v>
@@ -1254,7 +1173,7 @@
         <v>30</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="F14" s="12" t="s">
         <v>14</v>
@@ -1272,7 +1191,7 @@
         <v>30</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>104</v>
+        <v>76</v>
       </c>
       <c r="F15" s="12" t="s">
         <v>14</v>
@@ -1284,19 +1203,19 @@
         <v>13</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>97</v>
+        <v>69</v>
       </c>
       <c r="D16" s="12" t="s">
         <v>31</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>96</v>
+        <v>68</v>
       </c>
       <c r="F16" s="12" t="s">
         <v>15</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>95</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17" spans="2:7" ht="30" x14ac:dyDescent="0.25">
@@ -1304,13 +1223,13 @@
         <v>14</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>98</v>
+        <v>70</v>
       </c>
       <c r="D17" s="12" t="s">
         <v>30</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>99</v>
+        <v>71</v>
       </c>
       <c r="F17" s="12" t="s">
         <v>14</v>
@@ -1322,13 +1241,13 @@
         <v>15</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="D18" s="12" t="s">
         <v>1</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="F18" s="12" t="s">
         <v>15</v>
@@ -1340,13 +1259,13 @@
         <v>16</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>115</v>
+        <v>87</v>
       </c>
       <c r="D19" s="12" t="s">
         <v>1</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>116</v>
+        <v>88</v>
       </c>
       <c r="F19" s="12" t="s">
         <v>14</v>
@@ -1356,7 +1275,7 @@
     <row r="20" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="21" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B21" s="26" t="s">
-        <v>107</v>
+        <v>79</v>
       </c>
       <c r="C21" s="27"/>
       <c r="D21" s="27"/>
@@ -1389,13 +1308,13 @@
         <v>1</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>108</v>
+        <v>80</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>14</v>
@@ -1407,13 +1326,13 @@
         <v>2</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>30</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>14</v>
@@ -1425,13 +1344,13 @@
         <v>3</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>30</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>14</v>
@@ -1443,13 +1362,13 @@
         <v>4</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>30</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>14</v>
@@ -1461,13 +1380,13 @@
         <v>5</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>111</v>
+        <v>83</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>30</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>14</v>
@@ -1479,13 +1398,13 @@
         <v>6</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>30</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>112</v>
+        <v>84</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>14</v>
@@ -1497,19 +1416,19 @@
         <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>30</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>15</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>121</v>
+        <v>93</v>
       </c>
     </row>
     <row r="30" spans="2:7" ht="30" x14ac:dyDescent="0.25">
@@ -1517,13 +1436,13 @@
         <v>8</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>30</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>93</v>
+        <v>65</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>14</v>
@@ -1535,13 +1454,13 @@
         <v>9</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>113</v>
+        <v>85</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>117</v>
+        <v>89</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>14</v>
@@ -1553,13 +1472,13 @@
         <v>10</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>119</v>
+        <v>91</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>118</v>
+        <v>90</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>14</v>
@@ -1571,13 +1490,13 @@
         <v>11</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>114</v>
+        <v>86</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>120</v>
+        <v>92</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>14</v>
@@ -1589,13 +1508,13 @@
         <v>12</v>
       </c>
       <c r="C34" s="16" t="s">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="D34" s="16" t="s">
         <v>1</v>
       </c>
       <c r="E34" s="15" t="s">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="F34" s="12" t="s">
         <v>15</v>
@@ -1605,7 +1524,7 @@
     <row r="36" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B36" s="21"/>
       <c r="C36" s="27" t="s">
-        <v>122</v>
+        <v>94</v>
       </c>
       <c r="D36" s="27"/>
       <c r="E36" s="27"/>
@@ -1637,13 +1556,13 @@
         <v>1</v>
       </c>
       <c r="C38" s="18" t="s">
-        <v>123</v>
+        <v>95</v>
       </c>
       <c r="D38" s="18" t="s">
         <v>1</v>
       </c>
       <c r="E38" s="18" t="s">
-        <v>129</v>
+        <v>101</v>
       </c>
       <c r="F38" s="18" t="s">
         <v>14</v>
@@ -1653,7 +1572,7 @@
     <row r="39" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B39" s="11"/>
       <c r="C39" s="22" t="s">
-        <v>130</v>
+        <v>102</v>
       </c>
       <c r="D39" s="23"/>
       <c r="E39" s="23"/>
@@ -1665,13 +1584,13 @@
         <v>2</v>
       </c>
       <c r="C40" s="20" t="s">
-        <v>131</v>
+        <v>103</v>
       </c>
       <c r="D40" s="20" t="s">
         <v>1</v>
       </c>
       <c r="E40" s="20" t="s">
-        <v>124</v>
+        <v>96</v>
       </c>
       <c r="F40" s="20" t="s">
         <v>14</v>
@@ -1683,13 +1602,13 @@
         <v>3</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>132</v>
+        <v>104</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>104</v>
+        <v>76</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>14</v>
@@ -1701,19 +1620,19 @@
         <v>4</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>133</v>
+        <v>105</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>125</v>
+        <v>97</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>15</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>126</v>
+        <v>98</v>
       </c>
     </row>
     <row r="43" spans="2:7" ht="30" x14ac:dyDescent="0.25">
@@ -1721,13 +1640,13 @@
         <v>5</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>127</v>
+        <v>99</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>1</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>128</v>
+        <v>100</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>14</v>
@@ -1737,7 +1656,7 @@
     <row r="44" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B44" s="11"/>
       <c r="C44" s="22" t="s">
-        <v>134</v>
+        <v>106</v>
       </c>
       <c r="D44" s="23"/>
       <c r="E44" s="23"/>
@@ -1749,13 +1668,13 @@
         <v>6</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>1</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>135</v>
+        <v>107</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>14</v>
@@ -1767,13 +1686,13 @@
         <v>7</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>138</v>
+        <v>110</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>139</v>
+        <v>111</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>14</v>
@@ -1785,13 +1704,13 @@
         <v>8</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>1</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>135</v>
+        <v>107</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>14</v>
@@ -1803,13 +1722,13 @@
         <v>9</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>80</v>
+        <v>56</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>137</v>
+        <v>109</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>14</v>
@@ -1821,13 +1740,13 @@
         <v>10</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>1</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>135</v>
+        <v>107</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>14</v>
@@ -1839,13 +1758,13 @@
         <v>11</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>136</v>
+        <v>108</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>14</v>
@@ -1857,13 +1776,13 @@
         <v>12</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>140</v>
+        <v>112</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>141</v>
+        <v>113</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>14</v>
@@ -1875,13 +1794,13 @@
         <v>13</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>142</v>
+        <v>114</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>14</v>
@@ -1893,13 +1812,13 @@
         <v>14</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>143</v>
+        <v>115</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>147</v>
+        <v>119</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>14</v>
@@ -1911,13 +1830,13 @@
         <v>15</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>150</v>
+        <v>122</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>1</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>152</v>
+        <v>124</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>14</v>
@@ -1929,13 +1848,13 @@
         <v>16</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>151</v>
+        <v>123</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>1</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>153</v>
+        <v>125</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>14</v>
@@ -1947,13 +1866,13 @@
         <v>17</v>
       </c>
       <c r="C56" s="15" t="s">
-        <v>144</v>
+        <v>116</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E56" s="15" t="s">
-        <v>145</v>
+        <v>117</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>14</v>
@@ -1973,13 +1892,13 @@
         <v>18</v>
       </c>
       <c r="C58" s="15" t="s">
-        <v>148</v>
+        <v>120</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>1</v>
       </c>
       <c r="E58" s="15" t="s">
-        <v>149</v>
+        <v>121</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>14</v>
@@ -2098,7 +2017,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>154</v>
+        <v>126</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>19</v>
@@ -2110,13 +2029,13 @@
         <v>14</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>165</v>
+        <v>137</v>
       </c>
       <c r="I4" s="4">
         <v>1</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>36</v>
+        <v>138</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>1</v>
@@ -2127,14 +2046,16 @@
       <c r="M4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="N4" s="1"/>
+      <c r="N4" s="1" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="5" spans="2:14" ht="45" x14ac:dyDescent="0.25">
       <c r="B5" s="4">
         <v>2</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>155</v>
+        <v>127</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>19</v>
@@ -2146,13 +2067,13 @@
         <v>15</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>165</v>
+        <v>137</v>
       </c>
       <c r="I5" s="4">
         <v>2</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>30</v>
@@ -2163,7 +2084,9 @@
       <c r="M5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="N5" s="1"/>
+      <c r="N5" s="1" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="6" spans="2:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B6" s="4">
@@ -2182,13 +2105,13 @@
         <v>14</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>165</v>
+        <v>137</v>
       </c>
       <c r="I6" s="4">
         <v>3</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>30</v>
@@ -2199,14 +2122,16 @@
       <c r="M6" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="N6" s="1"/>
+      <c r="N6" s="1" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="7" spans="2:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B7" s="4">
         <v>4</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>156</v>
+        <v>128</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>21</v>
@@ -2218,13 +2143,13 @@
         <v>14</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>165</v>
+        <v>137</v>
       </c>
       <c r="I7" s="4">
         <v>4</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K7" s="1" t="s">
         <v>30</v>
@@ -2235,14 +2160,16 @@
       <c r="M7" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="N7" s="1"/>
+      <c r="N7" s="1" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="8" spans="2:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B8" s="4">
         <v>5</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>157</v>
+        <v>129</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>21</v>
@@ -2254,13 +2181,13 @@
         <v>14</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>165</v>
+        <v>137</v>
       </c>
       <c r="I8" s="4">
         <v>5</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="K8" s="1" t="s">
         <v>30</v>
@@ -2271,14 +2198,16 @@
       <c r="M8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="N8" s="1"/>
+      <c r="N8" s="1" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="9" spans="2:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B9" s="4">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>159</v>
+        <v>131</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>30</v>
@@ -2290,13 +2219,13 @@
         <v>14</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>165</v>
+        <v>137</v>
       </c>
       <c r="I9" s="4">
         <v>7</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>30</v>
@@ -2307,14 +2236,16 @@
       <c r="M9" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="N9" s="1"/>
+      <c r="N9" s="1" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="10" spans="2:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B10" s="4">
         <v>8</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>158</v>
+        <v>130</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>21</v>
@@ -2326,13 +2257,13 @@
         <v>14</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>165</v>
+        <v>137</v>
       </c>
       <c r="I10" s="4">
         <v>8</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="K10" s="1" t="s">
         <v>30</v>
@@ -2343,32 +2274,34 @@
       <c r="M10" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="N10" s="1"/>
+      <c r="N10" s="1" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="11" spans="2:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B11" s="4">
         <v>9</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>160</v>
+        <v>132</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>30</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>83</v>
+        <v>57</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>14</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>165</v>
+        <v>137</v>
       </c>
       <c r="I11" s="4">
         <v>9</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="K11" s="1" t="s">
         <v>30</v>
@@ -2379,14 +2312,16 @@
       <c r="M11" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="N11" s="1"/>
+      <c r="N11" s="1" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="12" spans="2:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B12" s="4">
         <v>10</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>161</v>
+        <v>133</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>21</v>
@@ -2398,31 +2333,33 @@
         <v>15</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>165</v>
+        <v>137</v>
       </c>
       <c r="I12" s="4">
         <v>10</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>30</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M12" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="N12" s="2"/>
+      <c r="N12" s="1" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="13" spans="2:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B13" s="4">
         <v>11</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>163</v>
+        <v>135</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>30</v>
@@ -2433,12 +2370,14 @@
       <c r="F13" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G13" s="1"/>
+      <c r="G13" s="1" t="s">
+        <v>137</v>
+      </c>
       <c r="I13" s="4">
         <v>11</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K13" s="1" t="s">
         <v>30</v>
@@ -2449,14 +2388,16 @@
       <c r="M13" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="N13" s="1"/>
+      <c r="N13" s="1" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="14" spans="2:14" ht="75" x14ac:dyDescent="0.25">
       <c r="B14" s="4">
         <v>12</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>162</v>
+        <v>134</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>30</v>
@@ -2467,12 +2408,14 @@
       <c r="F14" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G14" s="1"/>
+      <c r="G14" s="1" t="s">
+        <v>137</v>
+      </c>
       <c r="I14" s="4">
         <v>12</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K14" s="1" t="s">
         <v>30</v>
@@ -2483,7 +2426,9 @@
       <c r="M14" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="N14" s="1"/>
+      <c r="N14" s="1" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B15" s="4">
@@ -2501,7 +2446,9 @@
       <c r="F15" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G15" s="1"/>
+      <c r="G15" s="1" t="s">
+        <v>137</v>
+      </c>
       <c r="I15" s="7"/>
       <c r="J15" s="8"/>
       <c r="K15" s="9"/>
@@ -2525,7 +2472,9 @@
       <c r="F16" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G16" s="1"/>
+      <c r="G16" s="1" t="s">
+        <v>137</v>
+      </c>
       <c r="I16" s="7"/>
       <c r="J16" s="8"/>
       <c r="K16" s="9"/>
@@ -2535,16 +2484,14 @@
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B18" s="26" t="s">
-        <v>164</v>
+        <v>136</v>
       </c>
       <c r="C18" s="27"/>
       <c r="D18" s="27"/>
       <c r="E18" s="27"/>
       <c r="F18" s="27"/>
       <c r="G18" s="28"/>
-      <c r="I18" s="26" t="s">
-        <v>34</v>
-      </c>
+      <c r="I18" s="26"/>
       <c r="J18" s="27"/>
       <c r="K18" s="27"/>
       <c r="L18" s="27"/>
@@ -2570,31 +2517,19 @@
       <c r="G19" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="I19" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K19" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="L19" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="M19" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="N19" s="3" t="s">
-        <v>20</v>
-      </c>
+      <c r="I19" s="3"/>
+      <c r="J19" s="3"/>
+      <c r="K19" s="3"/>
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+      <c r="N19" s="3"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B20" s="4">
         <v>1</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>1</v>
@@ -2606,21 +2541,11 @@
         <v>14</v>
       </c>
       <c r="G20" s="1"/>
-      <c r="I20" s="4">
-        <v>1</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="L20" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="M20" s="1" t="s">
-        <v>14</v>
-      </c>
+      <c r="I20" s="4"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
       <c r="N20" s="1"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.25">
@@ -2628,7 +2553,7 @@
         <v>2</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>30</v>
@@ -2640,21 +2565,11 @@
         <v>14</v>
       </c>
       <c r="G21" s="1"/>
-      <c r="I21" s="4">
-        <v>2</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="K21" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="L21" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="M21" s="1" t="s">
-        <v>14</v>
-      </c>
+      <c r="I21" s="4"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
+      <c r="M21" s="1"/>
       <c r="N21" s="1"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.25">
@@ -2662,7 +2577,7 @@
         <v>3</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>30</v>
@@ -2674,21 +2589,11 @@
         <v>14</v>
       </c>
       <c r="G22" s="1"/>
-      <c r="I22" s="4">
-        <v>3</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="K22" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="L22" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="M22" s="1" t="s">
-        <v>14</v>
-      </c>
+      <c r="I22" s="4"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1"/>
+      <c r="M22" s="1"/>
       <c r="N22" s="1"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.25">
@@ -2696,7 +2601,7 @@
         <v>4</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>30</v>
@@ -2708,21 +2613,11 @@
         <v>14</v>
       </c>
       <c r="G23" s="1"/>
-      <c r="I23" s="4">
-        <v>4</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="L23" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="M23" s="1" t="s">
-        <v>14</v>
-      </c>
+      <c r="I23" s="4"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1"/>
+      <c r="M23" s="1"/>
       <c r="N23" s="1"/>
     </row>
     <row r="24" spans="2:14" ht="30" x14ac:dyDescent="0.25">
@@ -2730,7 +2625,7 @@
         <v>5</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>30</v>
@@ -2742,117 +2637,67 @@
         <v>14</v>
       </c>
       <c r="G24" s="1"/>
-      <c r="I24" s="4">
-        <v>5</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="K24" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="L24" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="M24" s="1" t="s">
-        <v>14</v>
-      </c>
+      <c r="I24" s="4"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="1"/>
+      <c r="L24" s="1"/>
+      <c r="M24" s="1"/>
       <c r="N24" s="1"/>
     </row>
-    <row r="25" spans="2:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B25" s="7"/>
       <c r="C25" s="8"/>
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
       <c r="F25" s="9"/>
       <c r="G25" s="9"/>
-      <c r="I25" s="4">
-        <v>6</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="K25" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="L25" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="M25" s="1" t="s">
-        <v>14</v>
-      </c>
+      <c r="I25" s="4"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="1"/>
+      <c r="L25" s="1"/>
+      <c r="M25" s="1"/>
       <c r="N25" s="1"/>
     </row>
-    <row r="26" spans="2:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B26" s="7"/>
       <c r="C26" s="8"/>
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
       <c r="F26" s="9"/>
       <c r="G26" s="9"/>
-      <c r="I26" s="4">
-        <v>7</v>
-      </c>
-      <c r="J26" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="K26" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="L26" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="M26" s="1" t="s">
-        <v>14</v>
-      </c>
+      <c r="I26" s="4"/>
+      <c r="J26" s="6"/>
+      <c r="K26" s="1"/>
+      <c r="L26" s="1"/>
+      <c r="M26" s="1"/>
       <c r="N26" s="1"/>
     </row>
-    <row r="27" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B27" s="7"/>
       <c r="C27" s="8"/>
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
       <c r="F27" s="9"/>
       <c r="G27" s="9"/>
-      <c r="I27" s="4">
-        <v>8</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="K27" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="L27" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="M27" s="1" t="s">
-        <v>14</v>
-      </c>
+      <c r="I27" s="4"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="1"/>
+      <c r="L27" s="1"/>
+      <c r="M27" s="1"/>
       <c r="N27" s="1"/>
     </row>
-    <row r="28" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B28" s="7"/>
       <c r="C28" s="8"/>
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
       <c r="F28" s="9"/>
       <c r="G28" s="9"/>
-      <c r="I28" s="4">
-        <v>9</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="K28" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="L28" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="M28" s="1" t="s">
-        <v>14</v>
-      </c>
+      <c r="I28" s="4"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
+      <c r="M28" s="1"/>
       <c r="N28" s="1"/>
     </row>
     <row r="29" spans="2:14" x14ac:dyDescent="0.25">
@@ -2870,17 +2715,13 @@
       <c r="N29" s="9"/>
     </row>
     <row r="30" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B30" s="26" t="s">
-        <v>35</v>
-      </c>
+      <c r="B30" s="26"/>
       <c r="C30" s="27"/>
       <c r="D30" s="27"/>
       <c r="E30" s="27"/>
       <c r="F30" s="27"/>
       <c r="G30" s="28"/>
-      <c r="I30" s="29" t="s">
-        <v>53</v>
-      </c>
+      <c r="I30" s="29"/>
       <c r="J30" s="29"/>
       <c r="K30" s="29"/>
       <c r="L30" s="29"/>
@@ -2888,453 +2729,185 @@
       <c r="N30" s="29"/>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B31" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="I31" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="J31" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K31" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="L31" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="M31" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="N31" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="32" spans="2:14" ht="30" x14ac:dyDescent="0.25">
-      <c r="B32" s="4">
-        <v>1</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>14</v>
-      </c>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="I31" s="3"/>
+      <c r="J31" s="3"/>
+      <c r="K31" s="3"/>
+      <c r="L31" s="3"/>
+      <c r="M31" s="3"/>
+      <c r="N31" s="3"/>
+    </row>
+    <row r="32" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B32" s="4"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
       <c r="G32" s="1"/>
-      <c r="I32" s="4">
-        <v>1</v>
-      </c>
-      <c r="J32" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="K32" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="L32" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="M32" s="1" t="s">
-        <v>14</v>
-      </c>
+      <c r="I32" s="4"/>
+      <c r="J32" s="2"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
+      <c r="M32" s="1"/>
       <c r="N32" s="1"/>
     </row>
-    <row r="33" spans="2:14" ht="30" x14ac:dyDescent="0.25">
-      <c r="B33" s="4">
-        <v>2</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>14</v>
-      </c>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B33" s="4"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
       <c r="G33" s="1"/>
-      <c r="I33" s="4">
-        <v>2</v>
-      </c>
-      <c r="J33" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="K33" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="L33" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="M33" s="1" t="s">
-        <v>14</v>
-      </c>
+      <c r="I33" s="4"/>
+      <c r="J33" s="2"/>
+      <c r="K33" s="1"/>
+      <c r="L33" s="1"/>
+      <c r="M33" s="1"/>
       <c r="N33" s="1"/>
     </row>
     <row r="34" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B34" s="4">
-        <v>3</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>14</v>
-      </c>
+      <c r="B34" s="4"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
       <c r="G34" s="1"/>
-      <c r="I34" s="4">
-        <v>3</v>
-      </c>
-      <c r="J34" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="K34" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="L34" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="M34" s="1" t="s">
-        <v>14</v>
-      </c>
+      <c r="I34" s="4"/>
+      <c r="J34" s="2"/>
+      <c r="K34" s="1"/>
+      <c r="L34" s="1"/>
+      <c r="M34" s="1"/>
       <c r="N34" s="1"/>
     </row>
-    <row r="35" spans="2:14" ht="30" x14ac:dyDescent="0.25">
-      <c r="B35" s="4">
-        <v>4</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>14</v>
-      </c>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B35" s="4"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
       <c r="G35" s="1"/>
-      <c r="I35" s="4">
-        <v>4</v>
-      </c>
-      <c r="J35" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="K35" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="L35" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="M35" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="N35" s="2" t="s">
-        <v>85</v>
-      </c>
+      <c r="I35" s="4"/>
+      <c r="J35" s="2"/>
+      <c r="K35" s="1"/>
+      <c r="L35" s="1"/>
+      <c r="M35" s="1"/>
+      <c r="N35" s="2"/>
     </row>
     <row r="36" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B36" s="4">
-        <v>5</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>14</v>
-      </c>
+      <c r="B36" s="4"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
       <c r="G36" s="1"/>
-      <c r="I36" s="4">
-        <v>5</v>
-      </c>
-      <c r="J36" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="K36" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="L36" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="M36" s="1" t="s">
-        <v>14</v>
-      </c>
+      <c r="I36" s="4"/>
+      <c r="J36" s="2"/>
+      <c r="K36" s="1"/>
+      <c r="L36" s="1"/>
+      <c r="M36" s="1"/>
       <c r="N36" s="1"/>
     </row>
-    <row r="37" spans="2:14" ht="45" x14ac:dyDescent="0.25">
-      <c r="B37" s="4">
-        <v>6</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>14</v>
-      </c>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B37" s="4"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
       <c r="G37" s="1"/>
-      <c r="I37" s="4">
-        <v>6</v>
-      </c>
-      <c r="J37" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="K37" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="L37" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="M37" s="1" t="s">
-        <v>14</v>
-      </c>
+      <c r="I37" s="4"/>
+      <c r="J37" s="2"/>
+      <c r="K37" s="1"/>
+      <c r="L37" s="1"/>
+      <c r="M37" s="1"/>
       <c r="N37" s="1"/>
     </row>
-    <row r="38" spans="2:14" ht="45" x14ac:dyDescent="0.25">
-      <c r="B38" s="4">
-        <v>7</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>14</v>
-      </c>
+    <row r="38" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B38" s="4"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
       <c r="G38" s="1"/>
-      <c r="I38" s="4">
-        <v>7</v>
-      </c>
-      <c r="J38" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="K38" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="L38" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="M38" s="1" t="s">
-        <v>14</v>
-      </c>
+      <c r="I38" s="4"/>
+      <c r="J38" s="2"/>
+      <c r="K38" s="1"/>
+      <c r="L38" s="1"/>
+      <c r="M38" s="1"/>
       <c r="N38" s="1"/>
     </row>
-    <row r="39" spans="2:14" ht="45" x14ac:dyDescent="0.25">
-      <c r="B39" s="4">
-        <v>8</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>14</v>
-      </c>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B39" s="4"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1"/>
       <c r="G39" s="1"/>
-      <c r="I39" s="4">
-        <v>8</v>
-      </c>
-      <c r="J39" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="K39" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="L39" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="M39" s="1" t="s">
-        <v>14</v>
-      </c>
+      <c r="I39" s="4"/>
+      <c r="J39" s="5"/>
+      <c r="K39" s="1"/>
+      <c r="L39" s="1"/>
+      <c r="M39" s="1"/>
       <c r="N39" s="1"/>
     </row>
-    <row r="40" spans="2:14" ht="30" x14ac:dyDescent="0.25">
-      <c r="B40" s="4">
-        <v>9</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>14</v>
-      </c>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B40" s="4"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="1"/>
+      <c r="E40" s="1"/>
+      <c r="F40" s="1"/>
       <c r="G40" s="1"/>
-      <c r="I40" s="4">
-        <v>9</v>
-      </c>
-      <c r="J40" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="K40" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="L40" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="M40" s="1" t="s">
-        <v>14</v>
-      </c>
+      <c r="I40" s="4"/>
+      <c r="J40" s="2"/>
+      <c r="K40" s="1"/>
+      <c r="L40" s="1"/>
+      <c r="M40" s="1"/>
       <c r="N40" s="1"/>
     </row>
-    <row r="41" spans="2:14" ht="45" x14ac:dyDescent="0.25">
-      <c r="B41" s="4">
-        <v>10</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>14</v>
-      </c>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B41" s="4"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1"/>
       <c r="G41" s="1"/>
-      <c r="I41" s="4">
-        <v>10</v>
-      </c>
-      <c r="J41" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="K41" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="L41" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="M41" s="1" t="s">
-        <v>14</v>
-      </c>
+      <c r="I41" s="4"/>
+      <c r="J41" s="2"/>
+      <c r="K41" s="1"/>
+      <c r="L41" s="1"/>
+      <c r="M41" s="1"/>
       <c r="N41" s="1"/>
     </row>
-    <row r="42" spans="2:14" ht="45" x14ac:dyDescent="0.25">
-      <c r="B42" s="4">
-        <v>11</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>14</v>
-      </c>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B42" s="4"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="1"/>
+      <c r="E42" s="1"/>
+      <c r="F42" s="1"/>
       <c r="G42" s="1"/>
-      <c r="I42" s="4">
-        <v>11</v>
-      </c>
-      <c r="J42" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="K42" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="L42" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="M42" s="1" t="s">
-        <v>14</v>
-      </c>
+      <c r="I42" s="4"/>
+      <c r="J42" s="2"/>
+      <c r="K42" s="1"/>
+      <c r="L42" s="1"/>
+      <c r="M42" s="1"/>
       <c r="N42" s="1"/>
     </row>
-    <row r="43" spans="2:14" ht="45" x14ac:dyDescent="0.25">
-      <c r="B43" s="4">
-        <v>12</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F43" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="I43" s="4">
-        <v>12</v>
-      </c>
-      <c r="J43" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="K43" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="L43" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="M43" s="1" t="s">
-        <v>14</v>
-      </c>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B43" s="4"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="1"/>
+      <c r="E43" s="1"/>
+      <c r="F43" s="1"/>
+      <c r="G43" s="1"/>
+      <c r="I43" s="4"/>
+      <c r="J43" s="2"/>
+      <c r="K43" s="1"/>
+      <c r="L43" s="1"/>
+      <c r="M43" s="1"/>
       <c r="N43" s="1"/>
     </row>
     <row r="44" spans="2:14" x14ac:dyDescent="0.25">
@@ -3499,7 +3072,7 @@
         <v>13</v>
       </c>
       <c r="H1" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="2:8" x14ac:dyDescent="0.25">
@@ -3513,7 +3086,7 @@
         <v>14</v>
       </c>
       <c r="H2" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
@@ -3555,12 +3128,12 @@
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D8" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D9" t="s">
-        <v>83</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/Check-lists.xlsx
+++ b/Check-lists.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="156">
   <si>
     <t>№ проверки</t>
   </si>
@@ -159,9 +159,6 @@
   </si>
   <si>
     <t>Вход с неверным логином и валидным паролем</t>
-  </si>
-  <si>
-    <t>Запрос с валидным токеном</t>
   </si>
   <si>
     <t>Запрос с истёкшим токеном</t>
@@ -446,6 +443,60 @@
   </si>
   <si>
     <t>Вход с верным логином и паролем</t>
+  </si>
+  <si>
+    <t>Эндпоинт DELETE/tasks</t>
+  </si>
+  <si>
+    <t>Запрос с валидным токеном отображает все задачи/задачи по id</t>
+  </si>
+  <si>
+    <t>При отсутствии задач запрос выдаёт пустой список</t>
+  </si>
+  <si>
+    <t>Получение своей задачи по ID</t>
+  </si>
+  <si>
+    <t>Получение чужой задачи</t>
+  </si>
+  <si>
+    <t>Получение задачи с несуществующим ID</t>
+  </si>
+  <si>
+    <t>Получение своей задачи по несуществующему статусу</t>
+  </si>
+  <si>
+    <t>Получение задач по несуществующему ключевому слову возвращает пустой список</t>
+  </si>
+  <si>
+    <t>Получение задач по существующему ключевому слову возвращает список с соответствующими задачами</t>
+  </si>
+  <si>
+    <t>Получение своей задачи по корректному статусу</t>
+  </si>
+  <si>
+    <t>Удаление своей задачи</t>
+  </si>
+  <si>
+    <t>Удаление чужой задачи</t>
+  </si>
+  <si>
+    <t>Запрос с несещуствующим токеном</t>
+  </si>
+  <si>
+    <t>Удаление несуществующей задачи</t>
+  </si>
+  <si>
+    <t>Повторное удаление уже удалённой задачи</t>
+  </si>
+  <si>
+    <t>204 No Content</t>
+  </si>
+  <si>
+    <t>422 Unprocessable Entity</t>
+  </si>
+  <si>
+    <t>Запрос без Aurhorization header</t>
   </si>
 </sst>
 </file>
@@ -582,7 +633,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -661,6 +712,8 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -954,7 +1007,7 @@
   <sheetData>
     <row r="2" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C2" s="27"/>
       <c r="D2" s="27"/>
@@ -993,7 +1046,7 @@
         <v>19</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F4" s="12" t="s">
         <v>14</v>
@@ -1011,7 +1064,7 @@
         <v>19</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F5" s="12" t="s">
         <v>14</v>
@@ -1029,7 +1082,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F6" s="12" t="s">
         <v>14</v>
@@ -1047,7 +1100,7 @@
         <v>31</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F7" s="12" t="s">
         <v>14</v>
@@ -1065,7 +1118,7 @@
         <v>31</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F8" s="12" t="s">
         <v>14</v>
@@ -1077,13 +1130,13 @@
         <v>6</v>
       </c>
       <c r="C9" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" s="10" t="s">
         <v>73</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>74</v>
       </c>
       <c r="F9" s="12" t="s">
         <v>14</v>
@@ -1095,13 +1148,13 @@
         <v>7</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D10" s="12" t="s">
         <v>30</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F10" s="12" t="s">
         <v>14</v>
@@ -1119,7 +1172,7 @@
         <v>31</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F11" s="12" t="s">
         <v>14</v>
@@ -1137,7 +1190,7 @@
         <v>30</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F12" s="12" t="s">
         <v>14</v>
@@ -1155,7 +1208,7 @@
         <v>31</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F13" s="12" t="s">
         <v>14</v>
@@ -1173,7 +1226,7 @@
         <v>30</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F14" s="12" t="s">
         <v>14</v>
@@ -1191,7 +1244,7 @@
         <v>30</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F15" s="12" t="s">
         <v>14</v>
@@ -1203,19 +1256,19 @@
         <v>13</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D16" s="12" t="s">
         <v>31</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F16" s="12" t="s">
         <v>15</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17" spans="2:7" ht="30" x14ac:dyDescent="0.25">
@@ -1223,13 +1276,13 @@
         <v>14</v>
       </c>
       <c r="C17" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E17" s="10" t="s">
         <v>70</v>
-      </c>
-      <c r="D17" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="E17" s="10" t="s">
-        <v>71</v>
       </c>
       <c r="F17" s="12" t="s">
         <v>14</v>
@@ -1241,13 +1294,13 @@
         <v>15</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D18" s="12" t="s">
         <v>1</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F18" s="12" t="s">
         <v>15</v>
@@ -1259,13 +1312,13 @@
         <v>16</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D19" s="12" t="s">
         <v>1</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F19" s="12" t="s">
         <v>14</v>
@@ -1275,7 +1328,7 @@
     <row r="20" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="21" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B21" s="26" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C21" s="27"/>
       <c r="D21" s="27"/>
@@ -1314,7 +1367,7 @@
         <v>1</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>14</v>
@@ -1332,7 +1385,7 @@
         <v>30</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>14</v>
@@ -1350,7 +1403,7 @@
         <v>30</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>14</v>
@@ -1368,7 +1421,7 @@
         <v>30</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>14</v>
@@ -1380,13 +1433,13 @@
         <v>5</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>30</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>14</v>
@@ -1404,7 +1457,7 @@
         <v>30</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>14</v>
@@ -1422,13 +1475,13 @@
         <v>30</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>15</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="30" spans="2:7" ht="30" x14ac:dyDescent="0.25">
@@ -1442,7 +1495,7 @@
         <v>30</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>14</v>
@@ -1454,13 +1507,13 @@
         <v>9</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>14</v>
@@ -1472,13 +1525,13 @@
         <v>10</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>14</v>
@@ -1490,13 +1543,13 @@
         <v>11</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>14</v>
@@ -1508,13 +1561,13 @@
         <v>12</v>
       </c>
       <c r="C34" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D34" s="16" t="s">
         <v>1</v>
       </c>
       <c r="E34" s="15" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F34" s="12" t="s">
         <v>15</v>
@@ -1524,7 +1577,7 @@
     <row r="36" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B36" s="21"/>
       <c r="C36" s="27" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D36" s="27"/>
       <c r="E36" s="27"/>
@@ -1556,13 +1609,13 @@
         <v>1</v>
       </c>
       <c r="C38" s="18" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D38" s="18" t="s">
         <v>1</v>
       </c>
       <c r="E38" s="18" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F38" s="18" t="s">
         <v>14</v>
@@ -1572,7 +1625,7 @@
     <row r="39" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B39" s="11"/>
       <c r="C39" s="22" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D39" s="23"/>
       <c r="E39" s="23"/>
@@ -1584,13 +1637,13 @@
         <v>2</v>
       </c>
       <c r="C40" s="20" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D40" s="20" t="s">
         <v>1</v>
       </c>
       <c r="E40" s="20" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F40" s="20" t="s">
         <v>14</v>
@@ -1602,13 +1655,13 @@
         <v>3</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>14</v>
@@ -1620,19 +1673,19 @@
         <v>4</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>15</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="43" spans="2:7" ht="30" x14ac:dyDescent="0.25">
@@ -1640,13 +1693,13 @@
         <v>5</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>1</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>14</v>
@@ -1656,7 +1709,7 @@
     <row r="44" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B44" s="11"/>
       <c r="C44" s="22" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D44" s="23"/>
       <c r="E44" s="23"/>
@@ -1668,13 +1721,13 @@
         <v>6</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>1</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>14</v>
@@ -1686,13 +1739,13 @@
         <v>7</v>
       </c>
       <c r="C46" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E46" s="2" t="s">
         <v>110</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>111</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>14</v>
@@ -1704,13 +1757,13 @@
         <v>8</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>1</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>14</v>
@@ -1722,13 +1775,13 @@
         <v>9</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>14</v>
@@ -1740,13 +1793,13 @@
         <v>10</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>1</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>14</v>
@@ -1758,13 +1811,13 @@
         <v>11</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>14</v>
@@ -1776,13 +1829,13 @@
         <v>12</v>
       </c>
       <c r="C51" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E51" s="2" t="s">
         <v>112</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>113</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>14</v>
@@ -1794,13 +1847,13 @@
         <v>13</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>14</v>
@@ -1812,13 +1865,13 @@
         <v>14</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>14</v>
@@ -1830,13 +1883,13 @@
         <v>15</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>1</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>14</v>
@@ -1848,13 +1901,13 @@
         <v>16</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>1</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>14</v>
@@ -1866,13 +1919,13 @@
         <v>17</v>
       </c>
       <c r="C56" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E56" s="15" t="s">
         <v>116</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E56" s="15" t="s">
-        <v>117</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>14</v>
@@ -1892,13 +1945,13 @@
         <v>18</v>
       </c>
       <c r="C58" s="15" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>1</v>
       </c>
       <c r="E58" s="15" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>14</v>
@@ -1939,7 +1992,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:N49"/>
+  <dimension ref="B2:N50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="12.7109375" customWidth="1"/>
@@ -1951,7 +2004,7 @@
     <col min="9" max="9" width="12.42578125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="37.5703125" customWidth="1"/>
     <col min="11" max="11" width="12.85546875" customWidth="1"/>
-    <col min="12" max="12" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="24.42578125" customWidth="1"/>
     <col min="13" max="13" width="15.140625" customWidth="1"/>
     <col min="14" max="14" width="28" customWidth="1"/>
   </cols>
@@ -2017,7 +2070,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>19</v>
@@ -2029,13 +2082,13 @@
         <v>14</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I4" s="4">
         <v>1</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>1</v>
@@ -2047,7 +2100,7 @@
         <v>14</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5" spans="2:14" ht="45" x14ac:dyDescent="0.25">
@@ -2055,7 +2108,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>19</v>
@@ -2067,7 +2120,7 @@
         <v>15</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I5" s="4">
         <v>2</v>
@@ -2085,7 +2138,7 @@
         <v>14</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="6" spans="2:14" ht="30" x14ac:dyDescent="0.25">
@@ -2105,7 +2158,7 @@
         <v>14</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I6" s="4">
         <v>3</v>
@@ -2123,7 +2176,7 @@
         <v>14</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="7" spans="2:14" ht="30" x14ac:dyDescent="0.25">
@@ -2131,7 +2184,7 @@
         <v>4</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>21</v>
@@ -2143,7 +2196,7 @@
         <v>14</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I7" s="4">
         <v>4</v>
@@ -2161,7 +2214,7 @@
         <v>14</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="8" spans="2:14" ht="30" x14ac:dyDescent="0.25">
@@ -2169,7 +2222,7 @@
         <v>5</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>21</v>
@@ -2181,7 +2234,7 @@
         <v>14</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I8" s="4">
         <v>5</v>
@@ -2199,7 +2252,7 @@
         <v>14</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="9" spans="2:14" ht="30" x14ac:dyDescent="0.25">
@@ -2207,7 +2260,7 @@
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>30</v>
@@ -2219,7 +2272,7 @@
         <v>14</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I9" s="4">
         <v>7</v>
@@ -2237,7 +2290,7 @@
         <v>14</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="10" spans="2:14" ht="30" x14ac:dyDescent="0.25">
@@ -2245,7 +2298,7 @@
         <v>8</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>21</v>
@@ -2257,7 +2310,7 @@
         <v>14</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I10" s="4">
         <v>8</v>
@@ -2275,7 +2328,7 @@
         <v>14</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11" spans="2:14" ht="30" x14ac:dyDescent="0.25">
@@ -2283,19 +2336,19 @@
         <v>9</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>30</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>14</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I11" s="4">
         <v>9</v>
@@ -2313,7 +2366,7 @@
         <v>14</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12" spans="2:14" ht="30" x14ac:dyDescent="0.25">
@@ -2321,7 +2374,7 @@
         <v>10</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>21</v>
@@ -2333,7 +2386,7 @@
         <v>15</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I12" s="4">
         <v>10</v>
@@ -2351,7 +2404,7 @@
         <v>14</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13" spans="2:14" ht="30" x14ac:dyDescent="0.25">
@@ -2359,7 +2412,7 @@
         <v>11</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>30</v>
@@ -2371,7 +2424,7 @@
         <v>15</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I13" s="4">
         <v>11</v>
@@ -2389,7 +2442,7 @@
         <v>14</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="14" spans="2:14" ht="75" x14ac:dyDescent="0.25">
@@ -2397,7 +2450,7 @@
         <v>12</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>30</v>
@@ -2409,7 +2462,7 @@
         <v>14</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I14" s="4">
         <v>12</v>
@@ -2427,7 +2480,7 @@
         <v>14</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.25">
@@ -2447,7 +2500,7 @@
         <v>14</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I15" s="7"/>
       <c r="J15" s="8"/>
@@ -2473,7 +2526,7 @@
         <v>14</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I16" s="7"/>
       <c r="J16" s="8"/>
@@ -2483,15 +2536,17 @@
       <c r="N16" s="9"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B18" s="26" t="s">
-        <v>136</v>
-      </c>
-      <c r="C18" s="27"/>
-      <c r="D18" s="27"/>
-      <c r="E18" s="27"/>
-      <c r="F18" s="27"/>
-      <c r="G18" s="28"/>
-      <c r="I18" s="26"/>
+      <c r="B18" s="29" t="s">
+        <v>135</v>
+      </c>
+      <c r="C18" s="29"/>
+      <c r="D18" s="29"/>
+      <c r="E18" s="29"/>
+      <c r="F18" s="29"/>
+      <c r="G18" s="29"/>
+      <c r="I18" s="26" t="s">
+        <v>138</v>
+      </c>
       <c r="J18" s="27"/>
       <c r="K18" s="27"/>
       <c r="L18" s="27"/>
@@ -2524,12 +2579,12 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
     </row>
-    <row r="20" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B20" s="4">
         <v>1</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>46</v>
+        <v>139</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>1</v>
@@ -2541,43 +2596,67 @@
         <v>14</v>
       </c>
       <c r="G20" s="1"/>
-      <c r="I20" s="4"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="1"/>
-      <c r="L20" s="1"/>
-      <c r="M20" s="1"/>
-      <c r="N20" s="1"/>
-    </row>
-    <row r="21" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="I20" s="4">
+        <v>1</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="21" spans="2:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B21" s="4">
         <v>2</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>47</v>
+        <v>140</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>14</v>
       </c>
       <c r="G21" s="1"/>
-      <c r="I21" s="4"/>
-      <c r="J21" s="2"/>
-      <c r="K21" s="1"/>
-      <c r="L21" s="1"/>
-      <c r="M21" s="1"/>
-      <c r="N21" s="1"/>
+      <c r="I21" s="4">
+        <v>2</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="M21" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="N21" s="1" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B22" s="4">
         <v>3</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>30</v>
@@ -2589,19 +2668,31 @@
         <v>14</v>
       </c>
       <c r="G22" s="1"/>
-      <c r="I22" s="4"/>
-      <c r="J22" s="2"/>
-      <c r="K22" s="1"/>
-      <c r="L22" s="1"/>
-      <c r="M22" s="1"/>
-      <c r="N22" s="1"/>
+      <c r="I22" s="4">
+        <v>3</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M22" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="N22" s="1" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B23" s="4">
         <v>4</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>30</v>
@@ -2613,19 +2704,31 @@
         <v>14</v>
       </c>
       <c r="G23" s="1"/>
-      <c r="I23" s="4"/>
-      <c r="J23" s="2"/>
-      <c r="K23" s="1"/>
-      <c r="L23" s="1"/>
-      <c r="M23" s="1"/>
-      <c r="N23" s="1"/>
+      <c r="I23" s="4">
+        <v>4</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="M23" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="24" spans="2:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B24" s="4">
         <v>5</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>30</v>
@@ -2637,62 +2740,130 @@
         <v>14</v>
       </c>
       <c r="G24" s="1"/>
-      <c r="I24" s="4"/>
-      <c r="J24" s="2"/>
-      <c r="K24" s="1"/>
-      <c r="L24" s="1"/>
-      <c r="M24" s="1"/>
-      <c r="N24" s="1"/>
-    </row>
-    <row r="25" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B25" s="7"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9"/>
-      <c r="I25" s="4"/>
-      <c r="J25" s="2"/>
-      <c r="K25" s="1"/>
-      <c r="L25" s="1"/>
+      <c r="I24" s="4">
+        <v>5</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M24" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="N24" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="25" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="B25" s="4">
+        <v>6</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G25" s="1"/>
+      <c r="I25" s="4">
+        <v>6</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>9</v>
+      </c>
       <c r="M25" s="1"/>
       <c r="N25" s="1"/>
     </row>
-    <row r="26" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B26" s="7"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="9"/>
-      <c r="I26" s="4"/>
-      <c r="J26" s="6"/>
-      <c r="K26" s="1"/>
-      <c r="L26" s="1"/>
+    <row r="26" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="B26" s="4">
+        <v>7</v>
+      </c>
+      <c r="C26" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="D26" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="E26" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G26" s="30"/>
+      <c r="I26" s="4">
+        <v>7</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="L26" s="1" t="s">
+        <v>9</v>
+      </c>
       <c r="M26" s="1"/>
       <c r="N26" s="1"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B27" s="7"/>
-      <c r="C27" s="8"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="9"/>
+      <c r="B27" s="4">
+        <v>8</v>
+      </c>
+      <c r="C27" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="D27" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="E27" s="30" t="s">
+        <v>6</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G27" s="30"/>
       <c r="I27" s="4"/>
-      <c r="J27" s="2"/>
+      <c r="J27" s="6"/>
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
       <c r="N27" s="1"/>
     </row>
-    <row r="28" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B28" s="7"/>
-      <c r="C28" s="8"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="9"/>
+    <row r="28" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="B28" s="4">
+        <v>9</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="D28" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="E28" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G28" s="30"/>
       <c r="I28" s="4"/>
       <c r="J28" s="2"/>
       <c r="K28" s="1"/>
@@ -2700,69 +2871,109 @@
       <c r="M28" s="1"/>
       <c r="N28" s="1"/>
     </row>
-    <row r="29" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B29" s="7"/>
-      <c r="C29" s="8"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="9"/>
-      <c r="I29" s="7"/>
-      <c r="J29" s="8"/>
-      <c r="K29" s="9"/>
-      <c r="L29" s="9"/>
-      <c r="M29" s="9"/>
-      <c r="N29" s="9"/>
-    </row>
-    <row r="30" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B30" s="26"/>
-      <c r="C30" s="27"/>
-      <c r="D30" s="27"/>
-      <c r="E30" s="27"/>
-      <c r="F30" s="27"/>
-      <c r="G30" s="28"/>
-      <c r="I30" s="29"/>
-      <c r="J30" s="29"/>
-      <c r="K30" s="29"/>
-      <c r="L30" s="29"/>
-      <c r="M30" s="29"/>
-      <c r="N30" s="29"/>
-    </row>
-    <row r="31" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="3"/>
-      <c r="I31" s="3"/>
-      <c r="J31" s="3"/>
-      <c r="K31" s="3"/>
-      <c r="L31" s="3"/>
-      <c r="M31" s="3"/>
-      <c r="N31" s="3"/>
-    </row>
-    <row r="32" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B32" s="4"/>
-      <c r="C32" s="2"/>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
-      <c r="G32" s="1"/>
-      <c r="I32" s="4"/>
-      <c r="J32" s="2"/>
-      <c r="K32" s="1"/>
-      <c r="L32" s="1"/>
-      <c r="M32" s="1"/>
-      <c r="N32" s="1"/>
+    <row r="29" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="B29" s="4">
+        <v>10</v>
+      </c>
+      <c r="C29" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="D29" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="E29" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G29" s="30"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="2"/>
+      <c r="K29" s="1"/>
+      <c r="L29" s="1"/>
+      <c r="M29" s="1"/>
+      <c r="N29" s="1"/>
+    </row>
+    <row r="30" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="B30" s="4">
+        <v>11</v>
+      </c>
+      <c r="C30" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="D30" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="E30" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G30" s="30"/>
+      <c r="I30" s="7"/>
+      <c r="J30" s="8"/>
+      <c r="K30" s="9"/>
+      <c r="L30" s="9"/>
+      <c r="M30" s="9"/>
+      <c r="N30" s="9"/>
+    </row>
+    <row r="31" spans="2:14" ht="45" x14ac:dyDescent="0.25">
+      <c r="B31" s="4">
+        <v>12</v>
+      </c>
+      <c r="C31" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="D31" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="E31" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G31" s="31"/>
+      <c r="I31" s="29"/>
+      <c r="J31" s="29"/>
+      <c r="K31" s="29"/>
+      <c r="L31" s="29"/>
+      <c r="M31" s="29"/>
+      <c r="N31" s="29"/>
+    </row>
+    <row r="32" spans="2:14" ht="45" x14ac:dyDescent="0.25">
+      <c r="B32" s="4">
+        <v>13</v>
+      </c>
+      <c r="C32" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="D32" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="E32" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G32" s="30"/>
+      <c r="I32" s="3"/>
+      <c r="J32" s="3"/>
+      <c r="K32" s="3"/>
+      <c r="L32" s="3"/>
+      <c r="M32" s="3"/>
+      <c r="N32" s="3"/>
     </row>
     <row r="33" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B33" s="4"/>
-      <c r="C33" s="2"/>
-      <c r="D33" s="1"/>
-      <c r="E33" s="1"/>
-      <c r="F33" s="1"/>
-      <c r="G33" s="1"/>
+      <c r="B33" s="7"/>
+      <c r="C33" s="8"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="9"/>
+      <c r="F33" s="9"/>
+      <c r="G33" s="9"/>
       <c r="I33" s="4"/>
       <c r="J33" s="2"/>
       <c r="K33" s="1"/>
@@ -2771,12 +2982,12 @@
       <c r="N33" s="1"/>
     </row>
     <row r="34" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B34" s="4"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="1"/>
-      <c r="E34" s="1"/>
-      <c r="F34" s="1"/>
-      <c r="G34" s="1"/>
+      <c r="B34" s="7"/>
+      <c r="C34" s="8"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="9"/>
+      <c r="F34" s="9"/>
+      <c r="G34" s="9"/>
       <c r="I34" s="4"/>
       <c r="J34" s="2"/>
       <c r="K34" s="1"/>
@@ -2785,40 +2996,40 @@
       <c r="N34" s="1"/>
     </row>
     <row r="35" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B35" s="4"/>
-      <c r="C35" s="2"/>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
-      <c r="F35" s="1"/>
-      <c r="G35" s="1"/>
+      <c r="B35" s="7"/>
+      <c r="C35" s="8"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="9"/>
+      <c r="F35" s="9"/>
+      <c r="G35" s="9"/>
       <c r="I35" s="4"/>
       <c r="J35" s="2"/>
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
       <c r="M35" s="1"/>
-      <c r="N35" s="2"/>
+      <c r="N35" s="1"/>
     </row>
     <row r="36" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B36" s="4"/>
-      <c r="C36" s="2"/>
-      <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="1"/>
-      <c r="G36" s="1"/>
+      <c r="B36" s="7"/>
+      <c r="C36" s="8"/>
+      <c r="D36" s="9"/>
+      <c r="E36" s="9"/>
+      <c r="F36" s="9"/>
+      <c r="G36" s="9"/>
       <c r="I36" s="4"/>
       <c r="J36" s="2"/>
       <c r="K36" s="1"/>
       <c r="L36" s="1"/>
       <c r="M36" s="1"/>
-      <c r="N36" s="1"/>
+      <c r="N36" s="2"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B37" s="4"/>
-      <c r="C37" s="2"/>
-      <c r="D37" s="1"/>
-      <c r="E37" s="1"/>
-      <c r="F37" s="1"/>
-      <c r="G37" s="1"/>
+      <c r="B37" s="7"/>
+      <c r="C37" s="8"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="9"/>
+      <c r="F37" s="9"/>
+      <c r="G37" s="9"/>
       <c r="I37" s="4"/>
       <c r="J37" s="2"/>
       <c r="K37" s="1"/>
@@ -2827,12 +3038,12 @@
       <c r="N37" s="1"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B38" s="4"/>
-      <c r="C38" s="2"/>
-      <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
-      <c r="F38" s="1"/>
-      <c r="G38" s="1"/>
+      <c r="B38" s="7"/>
+      <c r="C38" s="8"/>
+      <c r="D38" s="9"/>
+      <c r="E38" s="9"/>
+      <c r="F38" s="9"/>
+      <c r="G38" s="9"/>
       <c r="I38" s="4"/>
       <c r="J38" s="2"/>
       <c r="K38" s="1"/>
@@ -2841,40 +3052,40 @@
       <c r="N38" s="1"/>
     </row>
     <row r="39" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B39" s="4"/>
-      <c r="C39" s="2"/>
-      <c r="D39" s="1"/>
-      <c r="E39" s="1"/>
-      <c r="F39" s="1"/>
-      <c r="G39" s="1"/>
+      <c r="B39" s="7"/>
+      <c r="C39" s="8"/>
+      <c r="D39" s="9"/>
+      <c r="E39" s="9"/>
+      <c r="F39" s="9"/>
+      <c r="G39" s="9"/>
       <c r="I39" s="4"/>
-      <c r="J39" s="5"/>
+      <c r="J39" s="2"/>
       <c r="K39" s="1"/>
       <c r="L39" s="1"/>
       <c r="M39" s="1"/>
       <c r="N39" s="1"/>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B40" s="4"/>
-      <c r="C40" s="2"/>
-      <c r="D40" s="1"/>
-      <c r="E40" s="1"/>
-      <c r="F40" s="1"/>
-      <c r="G40" s="1"/>
+      <c r="B40" s="7"/>
+      <c r="C40" s="8"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="9"/>
+      <c r="F40" s="9"/>
+      <c r="G40" s="9"/>
       <c r="I40" s="4"/>
-      <c r="J40" s="2"/>
+      <c r="J40" s="5"/>
       <c r="K40" s="1"/>
       <c r="L40" s="1"/>
       <c r="M40" s="1"/>
       <c r="N40" s="1"/>
     </row>
     <row r="41" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B41" s="4"/>
-      <c r="C41" s="2"/>
-      <c r="D41" s="1"/>
-      <c r="E41" s="1"/>
-      <c r="F41" s="1"/>
-      <c r="G41" s="1"/>
+      <c r="B41" s="7"/>
+      <c r="C41" s="8"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="9"/>
+      <c r="F41" s="9"/>
+      <c r="G41" s="9"/>
       <c r="I41" s="4"/>
       <c r="J41" s="2"/>
       <c r="K41" s="1"/>
@@ -2883,12 +3094,12 @@
       <c r="N41" s="1"/>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B42" s="4"/>
-      <c r="C42" s="2"/>
-      <c r="D42" s="1"/>
-      <c r="E42" s="1"/>
-      <c r="F42" s="1"/>
-      <c r="G42" s="1"/>
+      <c r="B42" s="7"/>
+      <c r="C42" s="8"/>
+      <c r="D42" s="9"/>
+      <c r="E42" s="9"/>
+      <c r="F42" s="9"/>
+      <c r="G42" s="9"/>
       <c r="I42" s="4"/>
       <c r="J42" s="2"/>
       <c r="K42" s="1"/>
@@ -2897,12 +3108,12 @@
       <c r="N42" s="1"/>
     </row>
     <row r="43" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B43" s="4"/>
-      <c r="C43" s="2"/>
-      <c r="D43" s="1"/>
-      <c r="E43" s="1"/>
-      <c r="F43" s="1"/>
-      <c r="G43" s="1"/>
+      <c r="B43" s="7"/>
+      <c r="C43" s="8"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="9"/>
+      <c r="F43" s="9"/>
+      <c r="G43" s="9"/>
       <c r="I43" s="4"/>
       <c r="J43" s="2"/>
       <c r="K43" s="1"/>
@@ -2912,18 +3123,17 @@
     </row>
     <row r="44" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B44" s="7"/>
-      <c r="C44" s="9"/>
+      <c r="C44" s="8"/>
       <c r="D44" s="9"/>
       <c r="E44" s="9"/>
       <c r="F44" s="9"/>
       <c r="G44" s="9"/>
-      <c r="H44" s="9"/>
-      <c r="I44" s="7"/>
-      <c r="J44" s="9"/>
-      <c r="K44" s="9"/>
-      <c r="L44" s="9"/>
-      <c r="M44" s="9"/>
-      <c r="N44" s="9"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="2"/>
+      <c r="K44" s="1"/>
+      <c r="L44" s="1"/>
+      <c r="M44" s="1"/>
+      <c r="N44" s="1"/>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B45" s="7"/>
@@ -3000,49 +3210,93 @@
       <c r="M49" s="9"/>
       <c r="N49" s="9"/>
     </row>
+    <row r="50" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B50" s="7"/>
+      <c r="C50" s="9"/>
+      <c r="D50" s="9"/>
+      <c r="E50" s="9"/>
+      <c r="F50" s="9"/>
+      <c r="G50" s="9"/>
+      <c r="H50" s="9"/>
+      <c r="I50" s="7"/>
+      <c r="J50" s="9"/>
+      <c r="K50" s="9"/>
+      <c r="L50" s="9"/>
+      <c r="M50" s="9"/>
+      <c r="N50" s="9"/>
+    </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="5">
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="I2:N2"/>
     <mergeCell ref="B18:G18"/>
     <mergeCell ref="I18:N18"/>
-    <mergeCell ref="B30:G30"/>
-    <mergeCell ref="I30:N30"/>
+    <mergeCell ref="I31:N31"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="5">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>'выпад списки'!$D$2:$D$7</xm:f>
-          </x14:formula1>
-          <xm:sqref>E20:E29 L32:L49 L20:L29 L4:L16</xm:sqref>
-        </x14:dataValidation>
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="10">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'выпад списки'!$F$2:$F$3</xm:f>
           </x14:formula1>
-          <xm:sqref>M20:M29 M32:M49 F32:F49 F20:F29 M4:M16 F4:F16</xm:sqref>
+          <xm:sqref>F20:F50 M33:M50 F4:F16 M4:M16 M20:M30</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'выпад списки'!$B$2:$B$5</xm:f>
           </x14:formula1>
-          <xm:sqref>D20:D29 D32:D49 K20:K29 K32:K49 D4:D17 K4:K16</xm:sqref>
+          <xm:sqref>K4:K16 K20:K30 K33:K50 D4:D17 D20:D50</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>'выпад списки'!$D$2:$D$11</xm:f>
+          </x14:formula1>
+          <xm:sqref>L20:L26</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'выпад списки'!$D$2:$D$8</xm:f>
           </x14:formula1>
-          <xm:sqref>E32:E49</xm:sqref>
+          <xm:sqref>L4:L16</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>'выпад списки'!$D$2:$D$8</xm:f>
+          </x14:formula1>
+          <xm:sqref>L33:L50</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>'выпад списки'!$D$2:$D$8</xm:f>
+          </x14:formula1>
+          <xm:sqref>L29:L30</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>'выпад списки'!$D$2:$D$8</xm:f>
+          </x14:formula1>
+          <xm:sqref>E20:E32</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'выпад списки'!$D$2:$D$9</xm:f>
           </x14:formula1>
+          <xm:sqref>E33:E50</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>'выпад списки'!$D$2:$D$10</xm:f>
+          </x14:formula1>
           <xm:sqref>E4:E16</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>'выпад списки'!$D$2:$D$10</xm:f>
+          </x14:formula1>
+          <xm:sqref>L27:L28</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -3052,7 +3306,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:H9"/>
+  <dimension ref="B1:H11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
@@ -3072,7 +3326,7 @@
         <v>13</v>
       </c>
       <c r="H1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="2:8" x14ac:dyDescent="0.25">
@@ -3086,7 +3340,7 @@
         <v>14</v>
       </c>
       <c r="H2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
@@ -3105,7 +3359,7 @@
         <v>19</v>
       </c>
       <c r="D4" t="s">
-        <v>4</v>
+        <v>153</v>
       </c>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.25">
@@ -3113,27 +3367,37 @@
         <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D7" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D8" t="s">
-        <v>51</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D9" t="s">
-        <v>57</v>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="D10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="D11" t="s">
+        <v>154</v>
       </c>
     </row>
   </sheetData>

--- a/Check-lists.xlsx
+++ b/Check-lists.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="163">
   <si>
     <t>№ проверки</t>
   </si>
@@ -96,12 +96,6 @@
   </si>
   <si>
     <t>Пароль с пробелами. Логин/ДР валидные.</t>
-  </si>
-  <si>
-    <t>Регистрация без поля логина</t>
-  </si>
-  <si>
-    <t>Регистрация без поля пароля</t>
   </si>
   <si>
     <t>Пароль валидной длины,игнорирование требований сложности (ввод пароля без одного из обязательных значений поочерёдно. Логин/ДР валидные.</t>
@@ -430,15 +424,9 @@
     <t>Пароль длиннее допустимых значений. Логин валидный.</t>
   </si>
   <si>
-    <t>Пароль валидной длины,игнорирование требований сложности (ввод пароля без одного из обязательных значений поочерёдно. Логин валидный.</t>
-  </si>
-  <si>
     <t>Пароль с пробелами. Логин валидный.</t>
   </si>
   <si>
-    <t>Эндпоинт GET/tasks</t>
-  </si>
-  <si>
     <t>Автоматизировано</t>
   </si>
   <si>
@@ -448,18 +436,12 @@
     <t>Эндпоинт DELETE/tasks</t>
   </si>
   <si>
-    <t>Запрос с валидным токеном отображает все задачи/задачи по id</t>
-  </si>
-  <si>
     <t>При отсутствии задач запрос выдаёт пустой список</t>
   </si>
   <si>
     <t>Получение своей задачи по ID</t>
   </si>
   <si>
-    <t>Получение чужой задачи</t>
-  </si>
-  <si>
     <t>Получение задачи с несуществующим ID</t>
   </si>
   <si>
@@ -497,6 +479,45 @@
   </si>
   <si>
     <t>Запрос без Aurhorization header</t>
+  </si>
+  <si>
+    <t>логин состоит только из цифр</t>
+  </si>
+  <si>
+    <t>логин содержит кириллицу</t>
+  </si>
+  <si>
+    <t>пароль содержит кириллицу</t>
+  </si>
+  <si>
+    <t>Логин из пробелов. Пароль валидный</t>
+  </si>
+  <si>
+    <t>Регистрация с пустым логином</t>
+  </si>
+  <si>
+    <t>Регистрация с пустым паролем</t>
+  </si>
+  <si>
+    <t>Пароль без цифры. Логин валидный</t>
+  </si>
+  <si>
+    <t>Пароль без латинского символа. Логин валидный</t>
+  </si>
+  <si>
+    <t>Вход без пароля</t>
+  </si>
+  <si>
+    <t>401 Unathorized</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Запрос с валидным токеном отображает все свои задачи </t>
+  </si>
+  <si>
+    <t>Получение чужой задачи по ID</t>
+  </si>
+  <si>
+    <t>GET /tasks и GET /tasks/&lt;id&gt;</t>
   </si>
 </sst>
 </file>
@@ -633,7 +654,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -688,6 +709,8 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -712,8 +735,10 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1006,14 +1031,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B2" s="26" t="s">
-        <v>71</v>
-      </c>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="28"/>
+      <c r="B2" s="28" t="s">
+        <v>69</v>
+      </c>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="30"/>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
@@ -1046,7 +1071,7 @@
         <v>19</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F4" s="12" t="s">
         <v>14</v>
@@ -1064,7 +1089,7 @@
         <v>19</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F5" s="12" t="s">
         <v>14</v>
@@ -1082,7 +1107,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F6" s="12" t="s">
         <v>14</v>
@@ -1094,13 +1119,13 @@
         <v>4</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F7" s="12" t="s">
         <v>14</v>
@@ -1112,13 +1137,13 @@
         <v>5</v>
       </c>
       <c r="C8" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="12" t="s">
-        <v>31</v>
-      </c>
       <c r="E8" s="10" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F8" s="12" t="s">
         <v>14</v>
@@ -1130,13 +1155,13 @@
         <v>6</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F9" s="12" t="s">
         <v>14</v>
@@ -1148,13 +1173,13 @@
         <v>7</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F10" s="12" t="s">
         <v>14</v>
@@ -1169,10 +1194,10 @@
         <v>22</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F11" s="12" t="s">
         <v>14</v>
@@ -1184,13 +1209,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F12" s="12" t="s">
         <v>14</v>
@@ -1205,10 +1230,10 @@
         <v>23</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F13" s="12" t="s">
         <v>14</v>
@@ -1223,10 +1248,10 @@
         <v>24</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F14" s="12" t="s">
         <v>14</v>
@@ -1238,13 +1263,13 @@
         <v>12</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F15" s="12" t="s">
         <v>14</v>
@@ -1256,19 +1281,19 @@
         <v>13</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F16" s="12" t="s">
         <v>15</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17" spans="2:7" ht="30" x14ac:dyDescent="0.25">
@@ -1276,13 +1301,13 @@
         <v>14</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F17" s="12" t="s">
         <v>14</v>
@@ -1294,13 +1319,13 @@
         <v>15</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D18" s="12" t="s">
         <v>1</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F18" s="12" t="s">
         <v>15</v>
@@ -1312,13 +1337,13 @@
         <v>16</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D19" s="12" t="s">
         <v>1</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F19" s="12" t="s">
         <v>14</v>
@@ -1327,14 +1352,14 @@
     </row>
     <row r="20" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="21" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B21" s="26" t="s">
-        <v>78</v>
-      </c>
-      <c r="C21" s="27"/>
-      <c r="D21" s="27"/>
-      <c r="E21" s="27"/>
-      <c r="F21" s="27"/>
-      <c r="G21" s="28"/>
+      <c r="B21" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="C21" s="29"/>
+      <c r="D21" s="29"/>
+      <c r="E21" s="29"/>
+      <c r="F21" s="29"/>
+      <c r="G21" s="30"/>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B22" s="3" t="s">
@@ -1361,13 +1386,13 @@
         <v>1</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>14</v>
@@ -1379,13 +1404,13 @@
         <v>2</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>14</v>
@@ -1397,13 +1422,13 @@
         <v>3</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>14</v>
@@ -1415,13 +1440,13 @@
         <v>4</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>14</v>
@@ -1433,13 +1458,13 @@
         <v>5</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>14</v>
@@ -1451,13 +1476,13 @@
         <v>6</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>14</v>
@@ -1469,19 +1494,19 @@
         <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>15</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="30" spans="2:7" ht="30" x14ac:dyDescent="0.25">
@@ -1489,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>14</v>
@@ -1507,13 +1532,13 @@
         <v>9</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>14</v>
@@ -1525,13 +1550,13 @@
         <v>10</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>14</v>
@@ -1543,13 +1568,13 @@
         <v>11</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>14</v>
@@ -1561,13 +1586,13 @@
         <v>12</v>
       </c>
       <c r="C34" s="16" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D34" s="16" t="s">
         <v>1</v>
       </c>
       <c r="E34" s="15" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F34" s="12" t="s">
         <v>15</v>
@@ -1576,13 +1601,13 @@
     </row>
     <row r="36" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B36" s="21"/>
-      <c r="C36" s="27" t="s">
-        <v>93</v>
-      </c>
-      <c r="D36" s="27"/>
-      <c r="E36" s="27"/>
-      <c r="F36" s="27"/>
-      <c r="G36" s="28"/>
+      <c r="C36" s="29" t="s">
+        <v>91</v>
+      </c>
+      <c r="D36" s="29"/>
+      <c r="E36" s="29"/>
+      <c r="F36" s="29"/>
+      <c r="G36" s="30"/>
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B37" s="3" t="s">
@@ -1609,13 +1634,13 @@
         <v>1</v>
       </c>
       <c r="C38" s="18" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D38" s="18" t="s">
         <v>1</v>
       </c>
       <c r="E38" s="18" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F38" s="18" t="s">
         <v>14</v>
@@ -1624,26 +1649,26 @@
     </row>
     <row r="39" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B39" s="11"/>
-      <c r="C39" s="22" t="s">
-        <v>101</v>
-      </c>
-      <c r="D39" s="23"/>
-      <c r="E39" s="23"/>
-      <c r="F39" s="23"/>
-      <c r="G39" s="24"/>
+      <c r="C39" s="24" t="s">
+        <v>99</v>
+      </c>
+      <c r="D39" s="25"/>
+      <c r="E39" s="25"/>
+      <c r="F39" s="25"/>
+      <c r="G39" s="26"/>
     </row>
     <row r="40" spans="2:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B40" s="19">
         <v>2</v>
       </c>
       <c r="C40" s="20" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D40" s="20" t="s">
         <v>1</v>
       </c>
       <c r="E40" s="20" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F40" s="20" t="s">
         <v>14</v>
@@ -1655,13 +1680,13 @@
         <v>3</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>14</v>
@@ -1673,19 +1698,19 @@
         <v>4</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>15</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="43" spans="2:7" ht="30" x14ac:dyDescent="0.25">
@@ -1693,13 +1718,13 @@
         <v>5</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>1</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>14</v>
@@ -1708,26 +1733,26 @@
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B44" s="11"/>
-      <c r="C44" s="22" t="s">
-        <v>105</v>
-      </c>
-      <c r="D44" s="23"/>
-      <c r="E44" s="23"/>
-      <c r="F44" s="23"/>
-      <c r="G44" s="24"/>
+      <c r="C44" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="D44" s="25"/>
+      <c r="E44" s="25"/>
+      <c r="F44" s="25"/>
+      <c r="G44" s="26"/>
     </row>
     <row r="45" spans="2:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B45" s="11">
         <v>6</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>1</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>14</v>
@@ -1739,13 +1764,13 @@
         <v>7</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>14</v>
@@ -1757,13 +1782,13 @@
         <v>8</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>1</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>14</v>
@@ -1775,13 +1800,13 @@
         <v>9</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>14</v>
@@ -1793,13 +1818,13 @@
         <v>10</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>1</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>14</v>
@@ -1811,13 +1836,13 @@
         <v>11</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>14</v>
@@ -1829,13 +1854,13 @@
         <v>12</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>14</v>
@@ -1847,13 +1872,13 @@
         <v>13</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>14</v>
@@ -1865,13 +1890,13 @@
         <v>14</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>14</v>
@@ -1883,13 +1908,13 @@
         <v>15</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>1</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>14</v>
@@ -1901,13 +1926,13 @@
         <v>16</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>1</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>14</v>
@@ -1919,13 +1944,13 @@
         <v>17</v>
       </c>
       <c r="C56" s="15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E56" s="15" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>14</v>
@@ -1933,25 +1958,25 @@
       <c r="G56" s="2"/>
     </row>
     <row r="57" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B57" s="25"/>
-      <c r="C57" s="25"/>
-      <c r="D57" s="25"/>
-      <c r="E57" s="25"/>
-      <c r="F57" s="25"/>
-      <c r="G57" s="25"/>
+      <c r="B57" s="27"/>
+      <c r="C57" s="27"/>
+      <c r="D57" s="27"/>
+      <c r="E57" s="27"/>
+      <c r="F57" s="27"/>
+      <c r="G57" s="27"/>
     </row>
     <row r="58" spans="2:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B58" s="11">
         <v>18</v>
       </c>
       <c r="C58" s="15" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>1</v>
       </c>
       <c r="E58" s="15" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>14</v>
@@ -1992,7 +2017,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:N50"/>
+  <dimension ref="B2:N56"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="12.7109375" customWidth="1"/>
@@ -2010,22 +2035,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:14" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="28"/>
-      <c r="I2" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="J2" s="27"/>
-      <c r="K2" s="27"/>
-      <c r="L2" s="27"/>
-      <c r="M2" s="27"/>
-      <c r="N2" s="28"/>
+      <c r="B2" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="30"/>
+      <c r="I2" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="J2" s="29"/>
+      <c r="K2" s="29"/>
+      <c r="L2" s="29"/>
+      <c r="M2" s="29"/>
+      <c r="N2" s="30"/>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
@@ -2070,7 +2095,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>19</v>
@@ -2082,13 +2107,13 @@
         <v>14</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="I4" s="4">
         <v>1</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>1</v>
@@ -2100,7 +2125,7 @@
         <v>14</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="5" spans="2:14" ht="45" x14ac:dyDescent="0.25">
@@ -2108,7 +2133,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>19</v>
@@ -2117,28 +2142,28 @@
         <v>3</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="I5" s="4">
         <v>2</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>5</v>
+        <v>159</v>
       </c>
       <c r="M5" s="1" t="s">
         <v>14</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="6" spans="2:14" ht="30" x14ac:dyDescent="0.25">
@@ -2158,25 +2183,25 @@
         <v>14</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="I6" s="4">
         <v>3</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>5</v>
+        <v>159</v>
       </c>
       <c r="M6" s="1" t="s">
         <v>14</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="7" spans="2:14" ht="30" x14ac:dyDescent="0.25">
@@ -2184,10 +2209,10 @@
         <v>4</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>4</v>
@@ -2196,36 +2221,36 @@
         <v>14</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="I7" s="4">
         <v>4</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>5</v>
+        <v>159</v>
       </c>
       <c r="M7" s="1" t="s">
         <v>14</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="8" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B8" s="4">
         <v>5</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>128</v>
+      <c r="C8" t="s">
+        <v>150</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>4</v>
@@ -2234,16 +2259,16 @@
         <v>14</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="I8" s="4">
         <v>5</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="L8" s="1" t="s">
         <v>4</v>
@@ -2252,18 +2277,18 @@
         <v>14</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="9" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B9" s="4">
-        <v>7</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>130</v>
+        <v>6</v>
+      </c>
+      <c r="C9" t="s">
+        <v>151</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>4</v>
@@ -2272,16 +2297,16 @@
         <v>14</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="I9" s="4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="L9" s="1" t="s">
         <v>4</v>
@@ -2290,18 +2315,18 @@
         <v>14</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="10" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B10" s="4">
-        <v>8</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>129</v>
+        <v>7</v>
+      </c>
+      <c r="C10" t="s">
+        <v>152</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>4</v>
@@ -2310,92 +2335,92 @@
         <v>14</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="I10" s="4">
-        <v>8</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>38</v>
+        <v>7</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>158</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M10" s="1" t="s">
         <v>14</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="11" spans="2:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B11" s="4">
-        <v>9</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>131</v>
+        <v>8</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>126</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>56</v>
+        <v>4</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>14</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="I11" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M11" s="1" t="s">
         <v>14</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="12" spans="2:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B12" s="4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="I12" s="4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="L12" s="1" t="s">
         <v>4</v>
@@ -2404,56 +2429,56 @@
         <v>14</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13" spans="2:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B13" s="4">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>134</v>
+        <v>153</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="I13" s="4">
+        <v>10</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="14" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="B14" s="4">
         <v>11</v>
       </c>
-      <c r="J13" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="L13" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="M13" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="N13" s="1" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="14" spans="2:14" ht="75" x14ac:dyDescent="0.25">
-      <c r="B14" s="4">
-        <v>12</v>
-      </c>
       <c r="C14" s="2" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>4</v>
@@ -2462,62 +2487,74 @@
         <v>14</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="I14" s="4">
+        <v>11</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="15" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="B15" s="4">
         <v>12</v>
       </c>
-      <c r="J14" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="L14" s="1" t="s">
+      <c r="C15" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="I15" s="4">
+        <v>12</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L15" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="M14" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="N14" s="1" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B15" s="4">
-        <v>16</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="I15" s="7"/>
-      <c r="J15" s="8"/>
-      <c r="K15" s="9"/>
-      <c r="L15" s="9"/>
-      <c r="M15" s="9"/>
-      <c r="N15" s="9"/>
-    </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="M15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="16" spans="2:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B16" s="4">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>26</v>
+        <v>130</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>4</v>
@@ -2526,468 +2563,464 @@
         <v>14</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="I16" s="7"/>
-      <c r="J16" s="8"/>
-      <c r="K16" s="9"/>
-      <c r="L16" s="9"/>
-      <c r="M16" s="9"/>
-      <c r="N16" s="9"/>
-    </row>
-    <row r="18" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B18" s="29" t="s">
-        <v>135</v>
-      </c>
-      <c r="C18" s="29"/>
-      <c r="D18" s="29"/>
-      <c r="E18" s="29"/>
-      <c r="F18" s="29"/>
-      <c r="G18" s="29"/>
-      <c r="I18" s="26" t="s">
-        <v>138</v>
-      </c>
-      <c r="J18" s="27"/>
-      <c r="K18" s="27"/>
-      <c r="L18" s="27"/>
-      <c r="M18" s="27"/>
-      <c r="N18" s="28"/>
+        <v>132</v>
+      </c>
+    </row>
+    <row r="17" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="B17" s="4">
+        <v>14</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="18" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="B18" s="4">
+        <v>15</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="4">
+        <v>16</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="I19" s="7"/>
+      <c r="J19" s="32"/>
+      <c r="K19" s="33"/>
+      <c r="L19" s="33"/>
+      <c r="M19" s="33"/>
+      <c r="N19" s="33"/>
+    </row>
+    <row r="20" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B20" s="4">
+        <v>17</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="I20" s="7"/>
+      <c r="J20" s="32"/>
+      <c r="K20" s="33"/>
+      <c r="L20" s="33"/>
+      <c r="M20" s="33"/>
+      <c r="N20" s="33"/>
+    </row>
+    <row r="21" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B21" s="4">
+        <v>18</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="I21" s="7"/>
+      <c r="J21" s="8"/>
+      <c r="K21" s="9"/>
+      <c r="L21" s="9"/>
+      <c r="M21" s="9"/>
+      <c r="N21" s="9"/>
+    </row>
+    <row r="22" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="I22" s="7"/>
+      <c r="J22" s="8"/>
+      <c r="K22" s="9"/>
+      <c r="L22" s="9"/>
+      <c r="M22" s="9"/>
+      <c r="N22" s="9"/>
+    </row>
+    <row r="24" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B24" s="31" t="s">
+        <v>162</v>
+      </c>
+      <c r="C24" s="31"/>
+      <c r="D24" s="31"/>
+      <c r="E24" s="31"/>
+      <c r="F24" s="31"/>
+      <c r="G24" s="31"/>
+      <c r="I24" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="J24" s="29"/>
+      <c r="K24" s="29"/>
+      <c r="L24" s="29"/>
+      <c r="M24" s="29"/>
+      <c r="N24" s="30"/>
+    </row>
+    <row r="25" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B25" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C25" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="D25" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="E25" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F19" s="3" t="s">
+      <c r="F25" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G19" s="3" t="s">
+      <c r="G25" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="I19" s="3"/>
-      <c r="J19" s="3"/>
-      <c r="K19" s="3"/>
-      <c r="L19" s="3"/>
-      <c r="M19" s="3"/>
-      <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="2:14" ht="30" x14ac:dyDescent="0.25">
-      <c r="B20" s="4">
-        <v>1</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G20" s="1"/>
-      <c r="I20" s="4">
-        <v>1</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="L20" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="M20" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="N20" s="1" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="21" spans="2:14" ht="30" x14ac:dyDescent="0.25">
-      <c r="B21" s="4">
-        <v>2</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G21" s="1"/>
-      <c r="I21" s="4">
-        <v>2</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="K21" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="L21" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="M21" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="N21" s="1" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="22" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B22" s="4">
-        <v>3</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G22" s="1"/>
-      <c r="I22" s="4">
-        <v>3</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="K22" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="L22" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="M22" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="N22" s="1" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="23" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B23" s="4">
-        <v>4</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G23" s="1"/>
-      <c r="I23" s="4">
-        <v>4</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="L23" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="M23" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="N23" s="1" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="24" spans="2:14" ht="30" x14ac:dyDescent="0.25">
-      <c r="B24" s="4">
-        <v>5</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G24" s="1"/>
-      <c r="I24" s="4">
-        <v>5</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="K24" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="L24" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="M24" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="N24" s="1" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="25" spans="2:14" ht="30" x14ac:dyDescent="0.25">
-      <c r="B25" s="4">
-        <v>6</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G25" s="1"/>
-      <c r="I25" s="4">
-        <v>6</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="K25" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="L25" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="M25" s="1"/>
-      <c r="N25" s="1"/>
+      <c r="I25" s="3"/>
+      <c r="J25" s="3"/>
+      <c r="K25" s="3"/>
+      <c r="L25" s="3"/>
+      <c r="M25" s="3"/>
+      <c r="N25" s="3"/>
     </row>
     <row r="26" spans="2:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B26" s="4">
-        <v>7</v>
-      </c>
-      <c r="C26" s="15" t="s">
-        <v>141</v>
-      </c>
-      <c r="D26" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="E26" s="30" t="s">
+      <c r="C26" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E26" s="1" t="s">
         <v>2</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G26" s="30"/>
+      <c r="G26" s="1"/>
       <c r="I26" s="4">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="M26" s="1"/>
-      <c r="N26" s="1"/>
-    </row>
-    <row r="27" spans="2:14" x14ac:dyDescent="0.25">
+        <v>147</v>
+      </c>
+      <c r="M26" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="N26" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="27" spans="2:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B27" s="4">
-        <v>8</v>
-      </c>
-      <c r="C27" s="15" t="s">
-        <v>142</v>
-      </c>
-      <c r="D27" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="E27" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G27" s="1"/>
+      <c r="I27" s="4">
+        <v>2</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L27" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F27" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G27" s="30"/>
-      <c r="I27" s="4"/>
-      <c r="J27" s="6"/>
-      <c r="K27" s="1"/>
-      <c r="L27" s="1"/>
-      <c r="M27" s="1"/>
-      <c r="N27" s="1"/>
-    </row>
-    <row r="28" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="M27" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="N27" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="28" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B28" s="4">
-        <v>9</v>
-      </c>
-      <c r="C28" s="15" t="s">
-        <v>143</v>
-      </c>
-      <c r="D28" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="E28" s="30" t="s">
-        <v>9</v>
+        <v>3</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>159</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G28" s="30"/>
-      <c r="I28" s="4"/>
-      <c r="J28" s="2"/>
-      <c r="K28" s="1"/>
-      <c r="L28" s="1"/>
-      <c r="M28" s="1"/>
-      <c r="N28" s="1"/>
-    </row>
-    <row r="29" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="G28" s="1"/>
+      <c r="I28" s="4">
+        <v>3</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L28" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M28" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="N28" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="29" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B29" s="4">
-        <v>10</v>
-      </c>
-      <c r="C29" s="15" t="s">
-        <v>147</v>
-      </c>
-      <c r="D29" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="E29" s="30" t="s">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>159</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G29" s="30"/>
-      <c r="I29" s="4"/>
-      <c r="J29" s="2"/>
-      <c r="K29" s="1"/>
-      <c r="L29" s="1"/>
-      <c r="M29" s="1"/>
-      <c r="N29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="I29" s="4">
+        <v>4</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L29" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="M29" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="N29" s="1" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="30" spans="2:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B30" s="4">
-        <v>11</v>
-      </c>
-      <c r="C30" s="15" t="s">
-        <v>144</v>
-      </c>
-      <c r="D30" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="E30" s="30" t="s">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>159</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G30" s="30"/>
-      <c r="I30" s="7"/>
-      <c r="J30" s="8"/>
-      <c r="K30" s="9"/>
-      <c r="L30" s="9"/>
-      <c r="M30" s="9"/>
-      <c r="N30" s="9"/>
-    </row>
-    <row r="31" spans="2:14" ht="45" x14ac:dyDescent="0.25">
+      <c r="G30" s="1"/>
+      <c r="I30" s="4">
+        <v>5</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L30" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="M30" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="N30" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="31" spans="2:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B31" s="4">
-        <v>12</v>
-      </c>
-      <c r="C31" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G31" s="1"/>
+      <c r="I31" s="4">
+        <v>6</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L31" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="M31" s="1"/>
+      <c r="N31" s="1"/>
+    </row>
+    <row r="32" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="B32" s="4">
+        <v>7</v>
+      </c>
+      <c r="C32" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="D32" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="E32" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G32" s="22"/>
+      <c r="I32" s="4">
+        <v>7</v>
+      </c>
+      <c r="J32" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="D31" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="E31" s="30" t="s">
-        <v>2</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G31" s="31"/>
-      <c r="I31" s="29"/>
-      <c r="J31" s="29"/>
-      <c r="K31" s="29"/>
-      <c r="L31" s="29"/>
-      <c r="M31" s="29"/>
-      <c r="N31" s="29"/>
-    </row>
-    <row r="32" spans="2:14" ht="45" x14ac:dyDescent="0.25">
-      <c r="B32" s="4">
-        <v>13</v>
-      </c>
-      <c r="C32" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="D32" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="E32" s="30" t="s">
-        <v>2</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G32" s="30"/>
-      <c r="I32" s="3"/>
-      <c r="J32" s="3"/>
-      <c r="K32" s="3"/>
-      <c r="L32" s="3"/>
-      <c r="M32" s="3"/>
-      <c r="N32" s="3"/>
+      <c r="K32" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L32" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="M32" s="1"/>
+      <c r="N32" s="1"/>
     </row>
     <row r="33" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B33" s="7"/>
-      <c r="C33" s="8"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="9"/>
+      <c r="B33" s="4">
+        <v>8</v>
+      </c>
+      <c r="C33" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="D33" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="E33" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G33" s="22"/>
       <c r="I33" s="4"/>
-      <c r="J33" s="2"/>
+      <c r="J33" s="6"/>
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
       <c r="M33" s="1"/>
       <c r="N33" s="1"/>
     </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B34" s="7"/>
-      <c r="C34" s="8"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="9"/>
+    <row r="34" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="B34" s="4">
+        <v>9</v>
+      </c>
+      <c r="C34" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="D34" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="E34" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G34" s="22"/>
       <c r="I34" s="4"/>
       <c r="J34" s="2"/>
       <c r="K34" s="1"/>
@@ -2995,13 +3028,23 @@
       <c r="M34" s="1"/>
       <c r="N34" s="1"/>
     </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B35" s="7"/>
-      <c r="C35" s="8"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="9"/>
+    <row r="35" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="B35" s="4">
+        <v>10</v>
+      </c>
+      <c r="C35" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="D35" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="E35" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G35" s="22"/>
       <c r="I35" s="4"/>
       <c r="J35" s="2"/>
       <c r="K35" s="1"/>
@@ -3009,47 +3052,77 @@
       <c r="M35" s="1"/>
       <c r="N35" s="1"/>
     </row>
-    <row r="36" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B36" s="7"/>
-      <c r="C36" s="8"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="9"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="9"/>
-      <c r="I36" s="4"/>
-      <c r="J36" s="2"/>
-      <c r="K36" s="1"/>
-      <c r="L36" s="1"/>
-      <c r="M36" s="1"/>
-      <c r="N36" s="2"/>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B37" s="7"/>
-      <c r="C37" s="8"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="9"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="9"/>
-      <c r="I37" s="4"/>
-      <c r="J37" s="2"/>
-      <c r="K37" s="1"/>
-      <c r="L37" s="1"/>
-      <c r="M37" s="1"/>
-      <c r="N37" s="1"/>
-    </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B38" s="7"/>
-      <c r="C38" s="8"/>
-      <c r="D38" s="9"/>
-      <c r="E38" s="9"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="9"/>
-      <c r="I38" s="4"/>
-      <c r="J38" s="2"/>
-      <c r="K38" s="1"/>
-      <c r="L38" s="1"/>
-      <c r="M38" s="1"/>
-      <c r="N38" s="1"/>
+    <row r="36" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="B36" s="4">
+        <v>11</v>
+      </c>
+      <c r="C36" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="D36" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="E36" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G36" s="22"/>
+      <c r="I36" s="7"/>
+      <c r="J36" s="8"/>
+      <c r="K36" s="9"/>
+      <c r="L36" s="9"/>
+      <c r="M36" s="9"/>
+      <c r="N36" s="9"/>
+    </row>
+    <row r="37" spans="2:14" ht="45" x14ac:dyDescent="0.25">
+      <c r="B37" s="4">
+        <v>12</v>
+      </c>
+      <c r="C37" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="D37" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="E37" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G37" s="23"/>
+      <c r="I37" s="31"/>
+      <c r="J37" s="31"/>
+      <c r="K37" s="31"/>
+      <c r="L37" s="31"/>
+      <c r="M37" s="31"/>
+      <c r="N37" s="31"/>
+    </row>
+    <row r="38" spans="2:14" ht="45" x14ac:dyDescent="0.25">
+      <c r="B38" s="4">
+        <v>13</v>
+      </c>
+      <c r="C38" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="D38" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="E38" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G38" s="22"/>
+      <c r="I38" s="3"/>
+      <c r="J38" s="3"/>
+      <c r="K38" s="3"/>
+      <c r="L38" s="3"/>
+      <c r="M38" s="3"/>
+      <c r="N38" s="3"/>
     </row>
     <row r="39" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B39" s="7"/>
@@ -3073,7 +3146,7 @@
       <c r="F40" s="9"/>
       <c r="G40" s="9"/>
       <c r="I40" s="4"/>
-      <c r="J40" s="5"/>
+      <c r="J40" s="2"/>
       <c r="K40" s="1"/>
       <c r="L40" s="1"/>
       <c r="M40" s="1"/>
@@ -3105,7 +3178,7 @@
       <c r="K42" s="1"/>
       <c r="L42" s="1"/>
       <c r="M42" s="1"/>
-      <c r="N42" s="1"/>
+      <c r="N42" s="2"/>
     </row>
     <row r="43" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B43" s="7"/>
@@ -3137,166 +3210,226 @@
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B45" s="7"/>
-      <c r="C45" s="9"/>
+      <c r="C45" s="8"/>
       <c r="D45" s="9"/>
       <c r="E45" s="9"/>
       <c r="F45" s="9"/>
       <c r="G45" s="9"/>
-      <c r="H45" s="9"/>
-      <c r="I45" s="7"/>
-      <c r="J45" s="9"/>
-      <c r="K45" s="9"/>
-      <c r="L45" s="9"/>
-      <c r="M45" s="9"/>
-      <c r="N45" s="9"/>
+      <c r="I45" s="4"/>
+      <c r="J45" s="2"/>
+      <c r="K45" s="1"/>
+      <c r="L45" s="1"/>
+      <c r="M45" s="1"/>
+      <c r="N45" s="1"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B46" s="7"/>
-      <c r="C46" s="9"/>
+      <c r="C46" s="8"/>
       <c r="D46" s="9"/>
       <c r="E46" s="9"/>
       <c r="F46" s="9"/>
       <c r="G46" s="9"/>
-      <c r="H46" s="9"/>
-      <c r="I46" s="7"/>
-      <c r="J46" s="9"/>
-      <c r="K46" s="9"/>
-      <c r="L46" s="9"/>
-      <c r="M46" s="9"/>
-      <c r="N46" s="9"/>
+      <c r="I46" s="4"/>
+      <c r="J46" s="5"/>
+      <c r="K46" s="1"/>
+      <c r="L46" s="1"/>
+      <c r="M46" s="1"/>
+      <c r="N46" s="1"/>
     </row>
     <row r="47" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B47" s="7"/>
-      <c r="C47" s="9"/>
+      <c r="C47" s="8"/>
       <c r="D47" s="9"/>
       <c r="E47" s="9"/>
       <c r="F47" s="9"/>
       <c r="G47" s="9"/>
-      <c r="H47" s="9"/>
-      <c r="I47" s="7"/>
-      <c r="J47" s="9"/>
-      <c r="K47" s="9"/>
-      <c r="L47" s="9"/>
-      <c r="M47" s="9"/>
-      <c r="N47" s="9"/>
+      <c r="I47" s="4"/>
+      <c r="J47" s="2"/>
+      <c r="K47" s="1"/>
+      <c r="L47" s="1"/>
+      <c r="M47" s="1"/>
+      <c r="N47" s="1"/>
     </row>
     <row r="48" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B48" s="7"/>
-      <c r="C48" s="9"/>
+      <c r="C48" s="8"/>
       <c r="D48" s="9"/>
       <c r="E48" s="9"/>
       <c r="F48" s="9"/>
       <c r="G48" s="9"/>
-      <c r="H48" s="9"/>
-      <c r="I48" s="7"/>
-      <c r="J48" s="9"/>
-      <c r="K48" s="9"/>
-      <c r="L48" s="9"/>
-      <c r="M48" s="9"/>
-      <c r="N48" s="9"/>
+      <c r="I48" s="4"/>
+      <c r="J48" s="2"/>
+      <c r="K48" s="1"/>
+      <c r="L48" s="1"/>
+      <c r="M48" s="1"/>
+      <c r="N48" s="1"/>
     </row>
     <row r="49" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B49" s="7"/>
-      <c r="C49" s="9"/>
+      <c r="C49" s="8"/>
       <c r="D49" s="9"/>
       <c r="E49" s="9"/>
       <c r="F49" s="9"/>
       <c r="G49" s="9"/>
-      <c r="H49" s="9"/>
-      <c r="I49" s="7"/>
-      <c r="J49" s="9"/>
-      <c r="K49" s="9"/>
-      <c r="L49" s="9"/>
-      <c r="M49" s="9"/>
-      <c r="N49" s="9"/>
+      <c r="I49" s="4"/>
+      <c r="J49" s="2"/>
+      <c r="K49" s="1"/>
+      <c r="L49" s="1"/>
+      <c r="M49" s="1"/>
+      <c r="N49" s="1"/>
     </row>
     <row r="50" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B50" s="7"/>
-      <c r="C50" s="9"/>
+      <c r="C50" s="8"/>
       <c r="D50" s="9"/>
       <c r="E50" s="9"/>
       <c r="F50" s="9"/>
       <c r="G50" s="9"/>
-      <c r="H50" s="9"/>
-      <c r="I50" s="7"/>
-      <c r="J50" s="9"/>
-      <c r="K50" s="9"/>
-      <c r="L50" s="9"/>
-      <c r="M50" s="9"/>
-      <c r="N50" s="9"/>
+      <c r="I50" s="4"/>
+      <c r="J50" s="2"/>
+      <c r="K50" s="1"/>
+      <c r="L50" s="1"/>
+      <c r="M50" s="1"/>
+      <c r="N50" s="1"/>
+    </row>
+    <row r="51" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B51" s="7"/>
+      <c r="C51" s="9"/>
+      <c r="D51" s="9"/>
+      <c r="E51" s="9"/>
+      <c r="F51" s="9"/>
+      <c r="G51" s="9"/>
+      <c r="H51" s="9"/>
+      <c r="I51" s="7"/>
+      <c r="J51" s="9"/>
+      <c r="K51" s="9"/>
+      <c r="L51" s="9"/>
+      <c r="M51" s="9"/>
+      <c r="N51" s="9"/>
+    </row>
+    <row r="52" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B52" s="7"/>
+      <c r="C52" s="9"/>
+      <c r="D52" s="9"/>
+      <c r="E52" s="9"/>
+      <c r="F52" s="9"/>
+      <c r="G52" s="9"/>
+      <c r="H52" s="9"/>
+      <c r="I52" s="7"/>
+      <c r="J52" s="9"/>
+      <c r="K52" s="9"/>
+      <c r="L52" s="9"/>
+      <c r="M52" s="9"/>
+      <c r="N52" s="9"/>
+    </row>
+    <row r="53" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B53" s="7"/>
+      <c r="C53" s="9"/>
+      <c r="D53" s="9"/>
+      <c r="E53" s="9"/>
+      <c r="F53" s="9"/>
+      <c r="G53" s="9"/>
+      <c r="H53" s="9"/>
+      <c r="I53" s="7"/>
+      <c r="J53" s="9"/>
+      <c r="K53" s="9"/>
+      <c r="L53" s="9"/>
+      <c r="M53" s="9"/>
+      <c r="N53" s="9"/>
+    </row>
+    <row r="54" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B54" s="7"/>
+      <c r="C54" s="9"/>
+      <c r="D54" s="9"/>
+      <c r="E54" s="9"/>
+      <c r="F54" s="9"/>
+      <c r="G54" s="9"/>
+      <c r="H54" s="9"/>
+      <c r="I54" s="7"/>
+      <c r="J54" s="9"/>
+      <c r="K54" s="9"/>
+      <c r="L54" s="9"/>
+      <c r="M54" s="9"/>
+      <c r="N54" s="9"/>
+    </row>
+    <row r="55" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B55" s="7"/>
+      <c r="C55" s="9"/>
+      <c r="D55" s="9"/>
+      <c r="E55" s="9"/>
+      <c r="F55" s="9"/>
+      <c r="G55" s="9"/>
+      <c r="H55" s="9"/>
+      <c r="I55" s="7"/>
+      <c r="J55" s="9"/>
+      <c r="K55" s="9"/>
+      <c r="L55" s="9"/>
+      <c r="M55" s="9"/>
+      <c r="N55" s="9"/>
+    </row>
+    <row r="56" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B56" s="7"/>
+      <c r="C56" s="9"/>
+      <c r="D56" s="9"/>
+      <c r="E56" s="9"/>
+      <c r="F56" s="9"/>
+      <c r="G56" s="9"/>
+      <c r="H56" s="9"/>
+      <c r="I56" s="7"/>
+      <c r="J56" s="9"/>
+      <c r="K56" s="9"/>
+      <c r="L56" s="9"/>
+      <c r="M56" s="9"/>
+      <c r="N56" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="I2:N2"/>
-    <mergeCell ref="B18:G18"/>
-    <mergeCell ref="I18:N18"/>
-    <mergeCell ref="I31:N31"/>
+    <mergeCell ref="B24:G24"/>
+    <mergeCell ref="I24:N24"/>
+    <mergeCell ref="I37:N37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="10">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="6">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'выпад списки'!$F$2:$F$3</xm:f>
           </x14:formula1>
-          <xm:sqref>F20:F50 M33:M50 F4:F16 M4:M16 M20:M30</xm:sqref>
+          <xm:sqref>F26:F56 M39:M56 M26:M36 F4:F21 M19:M22 M4:M15</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'выпад списки'!$B$2:$B$5</xm:f>
           </x14:formula1>
-          <xm:sqref>K4:K16 K20:K30 K33:K50 D4:D17 D20:D50</xm:sqref>
+          <xm:sqref>K26:K36 K39:K56 D26:D56 D23 D4:D21 K19:K22 K4:K15</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'выпад списки'!$D$2:$D$11</xm:f>
           </x14:formula1>
-          <xm:sqref>L20:L26</xm:sqref>
+          <xm:sqref>L4:L15 L26:L32 E28:E31</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'выпад списки'!$D$2:$D$8</xm:f>
           </x14:formula1>
-          <xm:sqref>L4:L16</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>'выпад списки'!$D$2:$D$8</xm:f>
-          </x14:formula1>
-          <xm:sqref>L33:L50</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>'выпад списки'!$D$2:$D$8</xm:f>
-          </x14:formula1>
-          <xm:sqref>L29:L30</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>'выпад списки'!$D$2:$D$8</xm:f>
-          </x14:formula1>
-          <xm:sqref>E20:E32</xm:sqref>
+          <xm:sqref>L19:L22 L35:L36 L39:L56 E32:E38 E26:E27</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'выпад списки'!$D$2:$D$9</xm:f>
           </x14:formula1>
-          <xm:sqref>E33:E50</xm:sqref>
+          <xm:sqref>E39:E56</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'выпад списки'!$D$2:$D$10</xm:f>
           </x14:formula1>
-          <xm:sqref>E4:E16</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>'выпад списки'!$D$2:$D$10</xm:f>
-          </x14:formula1>
-          <xm:sqref>L27:L28</xm:sqref>
+          <xm:sqref>L33:L34 E4:E21</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -3326,7 +3459,7 @@
         <v>13</v>
       </c>
       <c r="H1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="2:8" x14ac:dyDescent="0.25">
@@ -3340,12 +3473,12 @@
         <v>14</v>
       </c>
       <c r="H2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D3" t="s">
         <v>3</v>
@@ -3359,12 +3492,12 @@
         <v>19</v>
       </c>
       <c r="D4" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D5" t="s">
         <v>4</v>
@@ -3372,7 +3505,7 @@
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D6" t="s">
-        <v>5</v>
+        <v>159</v>
       </c>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.25">
@@ -3387,17 +3520,17 @@
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D9" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D10" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D11" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
     </row>
   </sheetData>

--- a/Check-lists.xlsx
+++ b/Check-lists.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="172">
   <si>
     <t>№ проверки</t>
   </si>
@@ -36,9 +36,6 @@
   </si>
   <si>
     <t>400 Bad Request</t>
-  </si>
-  <si>
-    <t>401 Unathourized</t>
   </si>
   <si>
     <t>403 Forbidden</t>
@@ -433,9 +430,6 @@
     <t>Вход с верным логином и паролем</t>
   </si>
   <si>
-    <t>Эндпоинт DELETE/tasks</t>
-  </si>
-  <si>
     <t>При отсутствии задач запрос выдаёт пустой список</t>
   </si>
   <si>
@@ -463,9 +457,6 @@
     <t>Удаление чужой задачи</t>
   </si>
   <si>
-    <t>Запрос с несещуствующим токеном</t>
-  </si>
-  <si>
     <t>Удаление несуществующей задачи</t>
   </si>
   <si>
@@ -478,9 +469,6 @@
     <t>422 Unprocessable Entity</t>
   </si>
   <si>
-    <t>Запрос без Aurhorization header</t>
-  </si>
-  <si>
     <t>логин состоит только из цифр</t>
   </si>
   <si>
@@ -518,6 +506,45 @@
   </si>
   <si>
     <t>GET /tasks и GET /tasks/&lt;id&gt;</t>
+  </si>
+  <si>
+    <t>Эндпоинт DELETE/tasks/&lt;id&gt;</t>
+  </si>
+  <si>
+    <t>Запрос без Authorization header</t>
+  </si>
+  <si>
+    <t>Смена статуса на другой валидный</t>
+  </si>
+  <si>
+    <t>Смена статуса на тот же валидный</t>
+  </si>
+  <si>
+    <t>Смена статуса чужой задачи</t>
+  </si>
+  <si>
+    <t>Попытка сменить другие поля задачи обновляет только статус задачи</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Смена статуса на несуществующий </t>
+  </si>
+  <si>
+    <t>Смена статуса несуществующей задачи</t>
+  </si>
+  <si>
+    <t>Эндпоинт PATCH/tasks/&lt;id&gt;/status</t>
+  </si>
+  <si>
+    <t>Запрос без поля Status</t>
+  </si>
+  <si>
+    <t>Запрос с пустым Status</t>
+  </si>
+  <si>
+    <t>Фактическое поведение текущей реализации: Flask-JWT-Extended возвращает 422 для malformed token</t>
+  </si>
+  <si>
+    <t>Эндпоинт PATCH/tasks/&lt;id&gt;</t>
   </si>
 </sst>
 </file>
@@ -711,6 +738,10 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -735,10 +766,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1031,33 +1058,33 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B2" s="28" t="s">
-        <v>69</v>
-      </c>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="30"/>
+      <c r="B2" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="32"/>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>13</v>
-      </c>
       <c r="G3" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="2:7" ht="30" x14ac:dyDescent="0.25">
@@ -1065,16 +1092,16 @@
         <v>1</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G4" s="12"/>
     </row>
@@ -1083,16 +1110,16 @@
         <v>2</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G5" s="10"/>
     </row>
@@ -1101,16 +1128,16 @@
         <v>3</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D6" s="12" t="s">
         <v>1</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G6" s="12"/>
     </row>
@@ -1119,16 +1146,16 @@
         <v>4</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G7" s="12"/>
     </row>
@@ -1137,16 +1164,16 @@
         <v>5</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G8" s="12"/>
     </row>
@@ -1155,16 +1182,16 @@
         <v>6</v>
       </c>
       <c r="C9" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="D9" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>71</v>
-      </c>
       <c r="F9" s="12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G9" s="12"/>
     </row>
@@ -1173,16 +1200,16 @@
         <v>7</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G10" s="12"/>
     </row>
@@ -1191,16 +1218,16 @@
         <v>8</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G11" s="12"/>
     </row>
@@ -1209,16 +1236,16 @@
         <v>9</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G12" s="12"/>
     </row>
@@ -1227,16 +1254,16 @@
         <v>10</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G13" s="10"/>
     </row>
@@ -1245,16 +1272,16 @@
         <v>11</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G14" s="12"/>
     </row>
@@ -1263,16 +1290,16 @@
         <v>12</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G15" s="12"/>
     </row>
@@ -1281,19 +1308,19 @@
         <v>13</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17" spans="2:7" ht="30" x14ac:dyDescent="0.25">
@@ -1301,16 +1328,16 @@
         <v>14</v>
       </c>
       <c r="C17" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="E17" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="D17" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="E17" s="10" t="s">
-        <v>68</v>
-      </c>
       <c r="F17" s="12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G17" s="12"/>
     </row>
@@ -1319,16 +1346,16 @@
         <v>15</v>
       </c>
       <c r="C18" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="E18" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="D18" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="E18" s="14" t="s">
-        <v>75</v>
-      </c>
       <c r="F18" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G18" s="1"/>
     </row>
@@ -1337,48 +1364,48 @@
         <v>16</v>
       </c>
       <c r="C19" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="E19" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="D19" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="E19" s="14" t="s">
-        <v>85</v>
-      </c>
       <c r="F19" s="12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G19" s="1"/>
     </row>
     <row r="20" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="21" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B21" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="C21" s="29"/>
-      <c r="D21" s="29"/>
-      <c r="E21" s="29"/>
-      <c r="F21" s="29"/>
-      <c r="G21" s="30"/>
+      <c r="B21" s="30" t="s">
+        <v>75</v>
+      </c>
+      <c r="C21" s="31"/>
+      <c r="D21" s="31"/>
+      <c r="E21" s="31"/>
+      <c r="F21" s="31"/>
+      <c r="G21" s="32"/>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B22" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C22" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="E22" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E22" s="3" t="s">
+      <c r="F22" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>13</v>
-      </c>
       <c r="G22" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.25">
@@ -1386,16 +1413,16 @@
         <v>1</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G23" s="1"/>
     </row>
@@ -1404,16 +1431,16 @@
         <v>2</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G24" s="1"/>
     </row>
@@ -1422,16 +1449,16 @@
         <v>3</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G25" s="1"/>
     </row>
@@ -1440,16 +1467,16 @@
         <v>4</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G26" s="1"/>
     </row>
@@ -1458,16 +1485,16 @@
         <v>5</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G27" s="1"/>
     </row>
@@ -1476,16 +1503,16 @@
         <v>6</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G28" s="1"/>
     </row>
@@ -1494,19 +1521,19 @@
         <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="30" spans="2:7" ht="30" x14ac:dyDescent="0.25">
@@ -1514,16 +1541,16 @@
         <v>8</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G30" s="1"/>
     </row>
@@ -1532,16 +1559,16 @@
         <v>9</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G31" s="1"/>
     </row>
@@ -1550,16 +1577,16 @@
         <v>10</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G32" s="1"/>
     </row>
@@ -1568,16 +1595,16 @@
         <v>11</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G33" s="1"/>
     </row>
@@ -1586,47 +1613,47 @@
         <v>12</v>
       </c>
       <c r="C34" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="D34" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="E34" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="D34" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="E34" s="15" t="s">
-        <v>75</v>
-      </c>
       <c r="F34" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G34" s="1"/>
     </row>
     <row r="36" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B36" s="21"/>
-      <c r="C36" s="29" t="s">
-        <v>91</v>
-      </c>
-      <c r="D36" s="29"/>
-      <c r="E36" s="29"/>
-      <c r="F36" s="29"/>
-      <c r="G36" s="30"/>
+      <c r="C36" s="31" t="s">
+        <v>90</v>
+      </c>
+      <c r="D36" s="31"/>
+      <c r="E36" s="31"/>
+      <c r="F36" s="31"/>
+      <c r="G36" s="32"/>
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B37" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C37" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D37" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D37" s="3" t="s">
+      <c r="E37" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E37" s="3" t="s">
+      <c r="F37" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F37" s="3" t="s">
-        <v>13</v>
-      </c>
       <c r="G37" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="38" spans="2:7" ht="30" x14ac:dyDescent="0.25">
@@ -1634,44 +1661,44 @@
         <v>1</v>
       </c>
       <c r="C38" s="18" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D38" s="18" t="s">
         <v>1</v>
       </c>
       <c r="E38" s="18" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F38" s="18" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G38" s="18"/>
     </row>
     <row r="39" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B39" s="11"/>
-      <c r="C39" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="D39" s="25"/>
-      <c r="E39" s="25"/>
-      <c r="F39" s="25"/>
-      <c r="G39" s="26"/>
+      <c r="C39" s="26" t="s">
+        <v>98</v>
+      </c>
+      <c r="D39" s="27"/>
+      <c r="E39" s="27"/>
+      <c r="F39" s="27"/>
+      <c r="G39" s="28"/>
     </row>
     <row r="40" spans="2:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B40" s="19">
         <v>2</v>
       </c>
       <c r="C40" s="20" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D40" s="20" t="s">
         <v>1</v>
       </c>
       <c r="E40" s="20" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F40" s="20" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G40" s="20"/>
     </row>
@@ -1680,16 +1707,16 @@
         <v>3</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G41" s="2"/>
     </row>
@@ -1698,19 +1725,19 @@
         <v>4</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E42" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G42" s="2" t="s">
         <v>94</v>
-      </c>
-      <c r="F42" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G42" s="2" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="43" spans="2:7" ht="30" x14ac:dyDescent="0.25">
@@ -1718,44 +1745,44 @@
         <v>5</v>
       </c>
       <c r="C43" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E43" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D43" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>97</v>
-      </c>
       <c r="F43" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G43" s="2"/>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B44" s="11"/>
-      <c r="C44" s="24" t="s">
-        <v>103</v>
-      </c>
-      <c r="D44" s="25"/>
-      <c r="E44" s="25"/>
-      <c r="F44" s="25"/>
-      <c r="G44" s="26"/>
+      <c r="C44" s="26" t="s">
+        <v>102</v>
+      </c>
+      <c r="D44" s="27"/>
+      <c r="E44" s="27"/>
+      <c r="F44" s="27"/>
+      <c r="G44" s="28"/>
     </row>
     <row r="45" spans="2:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B45" s="11">
         <v>6</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>1</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G45" s="2"/>
     </row>
@@ -1764,16 +1791,16 @@
         <v>7</v>
       </c>
       <c r="C46" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E46" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="D46" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>108</v>
-      </c>
       <c r="F46" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G46" s="2"/>
     </row>
@@ -1782,16 +1809,16 @@
         <v>8</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>1</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G47" s="2"/>
     </row>
@@ -1800,16 +1827,16 @@
         <v>9</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G48" s="2"/>
     </row>
@@ -1818,16 +1845,16 @@
         <v>10</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>1</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G49" s="2"/>
     </row>
@@ -1836,16 +1863,16 @@
         <v>11</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G50" s="2"/>
     </row>
@@ -1854,16 +1881,16 @@
         <v>12</v>
       </c>
       <c r="C51" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E51" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="D51" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>110</v>
-      </c>
       <c r="F51" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G51" s="2"/>
     </row>
@@ -1872,16 +1899,16 @@
         <v>13</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G52" s="2"/>
     </row>
@@ -1890,16 +1917,16 @@
         <v>14</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G53" s="2"/>
     </row>
@@ -1908,16 +1935,16 @@
         <v>15</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>1</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G54" s="2"/>
     </row>
@@ -1926,16 +1953,16 @@
         <v>16</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>1</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G55" s="2"/>
     </row>
@@ -1944,42 +1971,42 @@
         <v>17</v>
       </c>
       <c r="C56" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E56" s="15" t="s">
         <v>113</v>
       </c>
-      <c r="D56" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E56" s="15" t="s">
-        <v>114</v>
-      </c>
       <c r="F56" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G56" s="2"/>
     </row>
     <row r="57" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B57" s="27"/>
-      <c r="C57" s="27"/>
-      <c r="D57" s="27"/>
-      <c r="E57" s="27"/>
-      <c r="F57" s="27"/>
-      <c r="G57" s="27"/>
+      <c r="B57" s="29"/>
+      <c r="C57" s="29"/>
+      <c r="D57" s="29"/>
+      <c r="E57" s="29"/>
+      <c r="F57" s="29"/>
+      <c r="G57" s="29"/>
     </row>
     <row r="58" spans="2:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B58" s="11">
         <v>18</v>
       </c>
       <c r="C58" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E58" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="D58" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E58" s="15" t="s">
-        <v>118</v>
-      </c>
       <c r="F58" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G58" s="1"/>
     </row>
@@ -2035,59 +2062,59 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:14" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="32"/>
+      <c r="I2" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="30"/>
-      <c r="I2" s="28" t="s">
-        <v>31</v>
-      </c>
-      <c r="J2" s="29"/>
-      <c r="K2" s="29"/>
-      <c r="L2" s="29"/>
-      <c r="M2" s="29"/>
-      <c r="N2" s="30"/>
+      <c r="J2" s="31"/>
+      <c r="K2" s="31"/>
+      <c r="L2" s="31"/>
+      <c r="M2" s="31"/>
+      <c r="N2" s="32"/>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>13</v>
-      </c>
       <c r="G3" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="J3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="L3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="M3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M3" s="3" t="s">
-        <v>13</v>
-      </c>
       <c r="N3" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="2:14" ht="45" x14ac:dyDescent="0.25">
@@ -2095,25 +2122,25 @@
         <v>1</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G4" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="I4" s="4">
+        <v>1</v>
+      </c>
+      <c r="J4" s="2" t="s">
         <v>132</v>
-      </c>
-      <c r="I4" s="4">
-        <v>1</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>133</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>1</v>
@@ -2122,10 +2149,10 @@
         <v>2</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="5" spans="2:14" ht="45" x14ac:dyDescent="0.25">
@@ -2133,37 +2160,37 @@
         <v>2</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I5" s="4">
         <v>2</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="6" spans="2:14" ht="30" x14ac:dyDescent="0.25">
@@ -2171,7 +2198,7 @@
         <v>3</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>1</v>
@@ -2180,28 +2207,28 @@
         <v>3</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I6" s="4">
         <v>3</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="7" spans="2:14" ht="30" x14ac:dyDescent="0.25">
@@ -2209,37 +2236,37 @@
         <v>4</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I7" s="4">
         <v>4</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.25">
@@ -2247,37 +2274,37 @@
         <v>5</v>
       </c>
       <c r="C8" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I8" s="4">
         <v>5</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.25">
@@ -2285,37 +2312,37 @@
         <v>6</v>
       </c>
       <c r="C9" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I9" s="4">
         <v>6</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.25">
@@ -2323,37 +2350,37 @@
         <v>7</v>
       </c>
       <c r="C10" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I10" s="4">
         <v>7</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L10" s="1" t="s">
         <v>4</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="11" spans="2:14" ht="30" x14ac:dyDescent="0.25">
@@ -2361,37 +2388,37 @@
         <v>8</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I11" s="4">
         <v>8</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L11" s="1" t="s">
         <v>4</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="12" spans="2:14" ht="30" x14ac:dyDescent="0.25">
@@ -2399,37 +2426,37 @@
         <v>9</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I12" s="4">
         <v>9</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L12" s="1" t="s">
         <v>4</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13" spans="2:14" ht="30" x14ac:dyDescent="0.25">
@@ -2437,37 +2464,37 @@
         <v>10</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I13" s="4">
         <v>10</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L13" s="1" t="s">
         <v>4</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="14" spans="2:14" ht="30" x14ac:dyDescent="0.25">
@@ -2475,37 +2502,37 @@
         <v>11</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I14" s="4">
         <v>11</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L14" s="1" t="s">
         <v>4</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="15" spans="2:14" ht="30" x14ac:dyDescent="0.25">
@@ -2513,37 +2540,37 @@
         <v>12</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I15" s="4">
         <v>12</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L15" s="1" t="s">
         <v>2</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="16" spans="2:14" ht="30" x14ac:dyDescent="0.25">
@@ -2551,19 +2578,19 @@
         <v>13</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="17" spans="2:14" ht="30" x14ac:dyDescent="0.25">
@@ -2571,19 +2598,19 @@
         <v>14</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="18" spans="2:14" ht="30" x14ac:dyDescent="0.25">
@@ -2591,19 +2618,19 @@
         <v>15</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.25">
@@ -2611,71 +2638,71 @@
         <v>16</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I19" s="7"/>
-      <c r="J19" s="32"/>
-      <c r="K19" s="33"/>
-      <c r="L19" s="33"/>
-      <c r="M19" s="33"/>
-      <c r="N19" s="33"/>
+      <c r="J19" s="24"/>
+      <c r="K19" s="25"/>
+      <c r="L19" s="25"/>
+      <c r="M19" s="25"/>
+      <c r="N19" s="25"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B20" s="4">
         <v>17</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I20" s="7"/>
-      <c r="J20" s="32"/>
-      <c r="K20" s="33"/>
-      <c r="L20" s="33"/>
-      <c r="M20" s="33"/>
-      <c r="N20" s="33"/>
+      <c r="J20" s="24"/>
+      <c r="K20" s="25"/>
+      <c r="L20" s="25"/>
+      <c r="M20" s="25"/>
+      <c r="N20" s="25"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B21" s="4">
         <v>18</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I21" s="7"/>
       <c r="J21" s="8"/>
@@ -2693,55 +2720,67 @@
       <c r="N22" s="9"/>
     </row>
     <row r="24" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B24" s="31" t="s">
-        <v>162</v>
-      </c>
-      <c r="C24" s="31"/>
-      <c r="D24" s="31"/>
-      <c r="E24" s="31"/>
-      <c r="F24" s="31"/>
-      <c r="G24" s="31"/>
-      <c r="I24" s="28" t="s">
-        <v>134</v>
-      </c>
-      <c r="J24" s="29"/>
-      <c r="K24" s="29"/>
-      <c r="L24" s="29"/>
-      <c r="M24" s="29"/>
-      <c r="N24" s="30"/>
+      <c r="B24" s="33" t="s">
+        <v>158</v>
+      </c>
+      <c r="C24" s="33"/>
+      <c r="D24" s="33"/>
+      <c r="E24" s="33"/>
+      <c r="F24" s="33"/>
+      <c r="G24" s="33"/>
+      <c r="I24" s="30" t="s">
+        <v>159</v>
+      </c>
+      <c r="J24" s="31"/>
+      <c r="K24" s="31"/>
+      <c r="L24" s="31"/>
+      <c r="M24" s="31"/>
+      <c r="N24" s="32"/>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B25" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C25" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="E25" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E25" s="3" t="s">
+      <c r="F25" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F25" s="3" t="s">
-        <v>13</v>
-      </c>
       <c r="G25" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="I25" s="3"/>
-      <c r="J25" s="3"/>
-      <c r="K25" s="3"/>
-      <c r="L25" s="3"/>
-      <c r="M25" s="3"/>
-      <c r="N25" s="3"/>
+        <v>19</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L25" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M25" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="N25" s="3" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="26" spans="2:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B26" s="4">
         <v>1</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>1</v>
@@ -2750,26 +2789,26 @@
         <v>2</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G26" s="1"/>
       <c r="I26" s="4">
         <v>1</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="K26" s="1" t="s">
         <v>1</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="27" spans="2:14" ht="30" x14ac:dyDescent="0.25">
@@ -2777,7 +2816,7 @@
         <v>2</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>1</v>
@@ -2786,26 +2825,26 @@
         <v>2</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G27" s="1"/>
       <c r="I27" s="4">
         <v>2</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.25">
@@ -2813,35 +2852,35 @@
         <v>3</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G28" s="1"/>
       <c r="I28" s="4">
         <v>3</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>5</v>
+        <v>155</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N28" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="29" spans="2:14" x14ac:dyDescent="0.25">
@@ -2849,35 +2888,35 @@
         <v>4</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G29" s="1"/>
       <c r="I29" s="4">
         <v>4</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>144</v>
+        <v>46</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="30" spans="2:14" ht="30" x14ac:dyDescent="0.25">
@@ -2885,35 +2924,35 @@
         <v>5</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G30" s="1"/>
       <c r="I30" s="4">
         <v>5</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="31" spans="2:14" ht="30" x14ac:dyDescent="0.25">
@@ -2921,39 +2960,43 @@
         <v>6</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G31" s="1"/>
       <c r="I31" s="4">
         <v>6</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="M31" s="1"/>
-      <c r="N31" s="1"/>
+        <v>8</v>
+      </c>
+      <c r="M31" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N31" s="1" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="32" spans="2:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B32" s="4">
         <v>7</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D32" s="22" t="s">
         <v>1</v>
@@ -2962,39 +3005,43 @@
         <v>2</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G32" s="22"/>
       <c r="I32" s="4">
         <v>7</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="M32" s="1"/>
-      <c r="N32" s="1"/>
+        <v>8</v>
+      </c>
+      <c r="M32" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N32" s="1" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="33" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B33" s="4">
         <v>8</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="D33" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E33" s="22" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G33" s="22"/>
       <c r="I33" s="4"/>
@@ -3009,16 +3056,16 @@
         <v>9</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D34" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E34" s="22" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G34" s="22"/>
       <c r="I34" s="4"/>
@@ -3033,7 +3080,7 @@
         <v>10</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D35" s="22" t="s">
         <v>1</v>
@@ -3042,7 +3089,7 @@
         <v>2</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G35" s="22"/>
       <c r="I35" s="4"/>
@@ -3057,16 +3104,16 @@
         <v>11</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D36" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E36" s="22" t="s">
         <v>4</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G36" s="22"/>
       <c r="I36" s="7"/>
@@ -3081,7 +3128,7 @@
         <v>12</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D37" s="22" t="s">
         <v>1</v>
@@ -3090,22 +3137,16 @@
         <v>2</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G37" s="23"/>
-      <c r="I37" s="31"/>
-      <c r="J37" s="31"/>
-      <c r="K37" s="31"/>
-      <c r="L37" s="31"/>
-      <c r="M37" s="31"/>
-      <c r="N37" s="31"/>
     </row>
     <row r="38" spans="2:14" ht="45" x14ac:dyDescent="0.25">
       <c r="B38" s="4">
         <v>13</v>
       </c>
       <c r="C38" s="15" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D38" s="22" t="s">
         <v>1</v>
@@ -3114,15 +3155,9 @@
         <v>2</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G38" s="22"/>
-      <c r="I38" s="3"/>
-      <c r="J38" s="3"/>
-      <c r="K38" s="3"/>
-      <c r="L38" s="3"/>
-      <c r="M38" s="3"/>
-      <c r="N38" s="3"/>
     </row>
     <row r="39" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B39" s="7"/>
@@ -3131,196 +3166,358 @@
       <c r="E39" s="9"/>
       <c r="F39" s="9"/>
       <c r="G39" s="9"/>
-      <c r="I39" s="4"/>
-      <c r="J39" s="2"/>
-      <c r="K39" s="1"/>
-      <c r="L39" s="1"/>
-      <c r="M39" s="1"/>
-      <c r="N39" s="1"/>
+      <c r="I39" s="33" t="s">
+        <v>167</v>
+      </c>
+      <c r="J39" s="33"/>
+      <c r="K39" s="33"/>
+      <c r="L39" s="33"/>
+      <c r="M39" s="33"/>
+      <c r="N39" s="33"/>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B40" s="7"/>
-      <c r="C40" s="8"/>
-      <c r="D40" s="9"/>
-      <c r="E40" s="9"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="9"/>
-      <c r="I40" s="4"/>
-      <c r="J40" s="2"/>
-      <c r="K40" s="1"/>
-      <c r="L40" s="1"/>
-      <c r="M40" s="1"/>
-      <c r="N40" s="1"/>
+      <c r="B40" s="33" t="s">
+        <v>171</v>
+      </c>
+      <c r="C40" s="33"/>
+      <c r="D40" s="33"/>
+      <c r="E40" s="33"/>
+      <c r="F40" s="33"/>
+      <c r="G40" s="33"/>
+      <c r="I40" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="J40" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K40" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L40" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M40" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="N40" s="3" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="41" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B41" s="7"/>
-      <c r="C41" s="8"/>
-      <c r="D41" s="9"/>
-      <c r="E41" s="9"/>
-      <c r="F41" s="9"/>
-      <c r="G41" s="9"/>
-      <c r="I41" s="4"/>
-      <c r="J41" s="2"/>
-      <c r="K41" s="1"/>
-      <c r="L41" s="1"/>
-      <c r="M41" s="1"/>
+      <c r="B41" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I41" s="4">
+        <v>1</v>
+      </c>
+      <c r="J41" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="K41" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L41" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="M41" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="N41" s="1"/>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B42" s="7"/>
-      <c r="C42" s="8"/>
-      <c r="D42" s="9"/>
-      <c r="E42" s="9"/>
-      <c r="F42" s="9"/>
-      <c r="G42" s="9"/>
-      <c r="I42" s="4"/>
-      <c r="J42" s="2"/>
-      <c r="K42" s="1"/>
-      <c r="L42" s="1"/>
-      <c r="M42" s="1"/>
-      <c r="N42" s="2"/>
+      <c r="B42" s="4">
+        <v>1</v>
+      </c>
+      <c r="C42" s="2"/>
+      <c r="D42" s="1"/>
+      <c r="E42" s="1"/>
+      <c r="F42" s="1"/>
+      <c r="G42" s="1"/>
+      <c r="I42" s="4">
+        <v>2</v>
+      </c>
+      <c r="J42" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="K42" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L42" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="M42" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N42" s="1"/>
     </row>
     <row r="43" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B43" s="7"/>
-      <c r="C43" s="8"/>
-      <c r="D43" s="9"/>
-      <c r="E43" s="9"/>
-      <c r="F43" s="9"/>
-      <c r="G43" s="9"/>
-      <c r="I43" s="4"/>
-      <c r="J43" s="2"/>
-      <c r="K43" s="1"/>
-      <c r="L43" s="1"/>
-      <c r="M43" s="1"/>
+      <c r="B43" s="4">
+        <v>2</v>
+      </c>
+      <c r="C43" s="2"/>
+      <c r="D43" s="1"/>
+      <c r="E43" s="1"/>
+      <c r="F43" s="1"/>
+      <c r="G43" s="1"/>
+      <c r="I43" s="4">
+        <v>3</v>
+      </c>
+      <c r="J43" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="K43" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L43" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M43" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="N43" s="1"/>
     </row>
     <row r="44" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B44" s="7"/>
-      <c r="C44" s="8"/>
-      <c r="D44" s="9"/>
-      <c r="E44" s="9"/>
-      <c r="F44" s="9"/>
-      <c r="G44" s="9"/>
-      <c r="I44" s="4"/>
-      <c r="J44" s="2"/>
-      <c r="K44" s="1"/>
-      <c r="L44" s="1"/>
-      <c r="M44" s="1"/>
-      <c r="N44" s="1"/>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B45" s="7"/>
-      <c r="C45" s="8"/>
-      <c r="D45" s="9"/>
-      <c r="E45" s="9"/>
-      <c r="F45" s="9"/>
-      <c r="G45" s="9"/>
-      <c r="I45" s="4"/>
-      <c r="J45" s="2"/>
-      <c r="K45" s="1"/>
-      <c r="L45" s="1"/>
-      <c r="M45" s="1"/>
-      <c r="N45" s="1"/>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="7"/>
-      <c r="C46" s="8"/>
-      <c r="D46" s="9"/>
-      <c r="E46" s="9"/>
-      <c r="F46" s="9"/>
-      <c r="G46" s="9"/>
-      <c r="I46" s="4"/>
-      <c r="J46" s="5"/>
-      <c r="K46" s="1"/>
-      <c r="L46" s="1"/>
-      <c r="M46" s="1"/>
+      <c r="B44" s="4">
+        <v>3</v>
+      </c>
+      <c r="C44" s="2"/>
+      <c r="D44" s="1"/>
+      <c r="E44" s="1"/>
+      <c r="F44" s="1"/>
+      <c r="G44" s="1"/>
+      <c r="I44" s="4">
+        <v>4</v>
+      </c>
+      <c r="J44" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="K44" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L44" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="M44" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N44" s="2"/>
+    </row>
+    <row r="45" spans="2:14" ht="60" x14ac:dyDescent="0.25">
+      <c r="B45" s="4">
+        <v>4</v>
+      </c>
+      <c r="C45" s="2"/>
+      <c r="D45" s="1"/>
+      <c r="E45" s="1"/>
+      <c r="F45" s="1"/>
+      <c r="G45" s="2"/>
+      <c r="I45" s="4">
+        <v>5</v>
+      </c>
+      <c r="J45" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="K45" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L45" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="M45" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N45" s="6" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="46" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="B46" s="4">
+        <v>5</v>
+      </c>
+      <c r="C46" s="2"/>
+      <c r="D46" s="1"/>
+      <c r="E46" s="1"/>
+      <c r="F46" s="1"/>
+      <c r="G46" s="6"/>
+      <c r="I46" s="4">
+        <v>6</v>
+      </c>
+      <c r="J46" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="K46" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L46" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="M46" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="N46" s="1"/>
     </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B47" s="7"/>
-      <c r="C47" s="8"/>
-      <c r="D47" s="9"/>
-      <c r="E47" s="9"/>
-      <c r="F47" s="9"/>
-      <c r="G47" s="9"/>
-      <c r="I47" s="4"/>
-      <c r="J47" s="2"/>
-      <c r="K47" s="1"/>
-      <c r="L47" s="1"/>
-      <c r="M47" s="1"/>
+    <row r="47" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="B47" s="4">
+        <v>6</v>
+      </c>
+      <c r="C47" s="2"/>
+      <c r="D47" s="1"/>
+      <c r="E47" s="1"/>
+      <c r="F47" s="1"/>
+      <c r="G47" s="1"/>
+      <c r="I47" s="4">
+        <v>7</v>
+      </c>
+      <c r="J47" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="K47" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L47" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="M47" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="N47" s="1"/>
     </row>
     <row r="48" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B48" s="7"/>
-      <c r="C48" s="8"/>
-      <c r="D48" s="9"/>
-      <c r="E48" s="9"/>
-      <c r="F48" s="9"/>
-      <c r="G48" s="9"/>
-      <c r="I48" s="4"/>
-      <c r="J48" s="2"/>
-      <c r="K48" s="1"/>
-      <c r="L48" s="1"/>
-      <c r="M48" s="1"/>
+      <c r="B48" s="4">
+        <v>7</v>
+      </c>
+      <c r="C48" s="2"/>
+      <c r="D48" s="1"/>
+      <c r="E48" s="1"/>
+      <c r="F48" s="1"/>
+      <c r="G48" s="1"/>
+      <c r="I48" s="4">
+        <v>8</v>
+      </c>
+      <c r="J48" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="K48" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L48" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="M48" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="N48" s="1"/>
     </row>
     <row r="49" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B49" s="7"/>
-      <c r="C49" s="8"/>
-      <c r="D49" s="9"/>
-      <c r="E49" s="9"/>
-      <c r="F49" s="9"/>
-      <c r="G49" s="9"/>
-      <c r="I49" s="4"/>
-      <c r="J49" s="2"/>
-      <c r="K49" s="1"/>
-      <c r="L49" s="1"/>
-      <c r="M49" s="1"/>
+      <c r="B49" s="4">
+        <v>8</v>
+      </c>
+      <c r="C49" s="5"/>
+      <c r="D49" s="1"/>
+      <c r="E49" s="1"/>
+      <c r="F49" s="1"/>
+      <c r="G49" s="1"/>
+      <c r="I49" s="4">
+        <v>9</v>
+      </c>
+      <c r="J49" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="K49" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L49" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M49" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="N49" s="1"/>
     </row>
     <row r="50" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B50" s="7"/>
-      <c r="C50" s="8"/>
-      <c r="D50" s="9"/>
-      <c r="E50" s="9"/>
-      <c r="F50" s="9"/>
-      <c r="G50" s="9"/>
-      <c r="I50" s="4"/>
-      <c r="J50" s="2"/>
-      <c r="K50" s="1"/>
-      <c r="L50" s="1"/>
-      <c r="M50" s="1"/>
+      <c r="B50" s="4">
+        <v>9</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" s="1"/>
+      <c r="E50" s="1"/>
+      <c r="F50" s="1"/>
+      <c r="G50" s="1"/>
+      <c r="I50" s="4">
+        <v>10</v>
+      </c>
+      <c r="J50" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="K50" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L50" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="M50" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="N50" s="1"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B51" s="7"/>
-      <c r="C51" s="9"/>
-      <c r="D51" s="9"/>
-      <c r="E51" s="9"/>
-      <c r="F51" s="9"/>
-      <c r="G51" s="9"/>
+      <c r="B51" s="4">
+        <v>10</v>
+      </c>
+      <c r="C51" s="2"/>
+      <c r="D51" s="1"/>
+      <c r="E51" s="1"/>
+      <c r="F51" s="1"/>
+      <c r="G51" s="1"/>
       <c r="H51" s="9"/>
-      <c r="I51" s="7"/>
-      <c r="J51" s="9"/>
-      <c r="K51" s="9"/>
-      <c r="L51" s="9"/>
-      <c r="M51" s="9"/>
-      <c r="N51" s="9"/>
+      <c r="I51" s="4">
+        <v>11</v>
+      </c>
+      <c r="J51" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="K51" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L51" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="M51" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N51" s="1"/>
     </row>
     <row r="52" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B52" s="7"/>
-      <c r="C52" s="9"/>
-      <c r="D52" s="9"/>
-      <c r="E52" s="9"/>
-      <c r="F52" s="9"/>
-      <c r="G52" s="9"/>
+      <c r="B52" s="4">
+        <v>11</v>
+      </c>
+      <c r="C52" s="2"/>
+      <c r="D52" s="1"/>
+      <c r="E52" s="1"/>
+      <c r="F52" s="1"/>
+      <c r="G52" s="1"/>
       <c r="H52" s="9"/>
-      <c r="I52" s="7"/>
-      <c r="J52" s="9"/>
-      <c r="K52" s="9"/>
-      <c r="L52" s="9"/>
-      <c r="M52" s="9"/>
-      <c r="N52" s="9"/>
+      <c r="I52" s="4"/>
+      <c r="J52" s="2"/>
+      <c r="K52" s="1"/>
+      <c r="L52" s="1"/>
+      <c r="M52" s="1"/>
+      <c r="N52" s="1"/>
     </row>
     <row r="53" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B53" s="7"/>
@@ -3383,12 +3580,13 @@
       <c r="N56" s="9"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
+    <mergeCell ref="B40:G40"/>
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="I2:N2"/>
     <mergeCell ref="B24:G24"/>
     <mergeCell ref="I24:N24"/>
-    <mergeCell ref="I37:N37"/>
+    <mergeCell ref="I39:N39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3399,31 +3597,31 @@
           <x14:formula1>
             <xm:f>'выпад списки'!$F$2:$F$3</xm:f>
           </x14:formula1>
-          <xm:sqref>F26:F56 M39:M56 M26:M36 F4:F21 M19:M22 M4:M15</xm:sqref>
+          <xm:sqref>F42:F56 M4:M15 M26:M36 F4:F21 M19:M22 F26:F39 M41:M52 M53:M56</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'выпад списки'!$B$2:$B$5</xm:f>
           </x14:formula1>
-          <xm:sqref>K26:K36 K39:K56 D26:D56 D23 D4:D21 K19:K22 K4:K15</xm:sqref>
+          <xm:sqref>K26:K36 K4:K15 D42:D56 D23 D4:D21 K19:K22 D26:D39 K41:K52 K53:K56</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'выпад списки'!$D$2:$D$11</xm:f>
           </x14:formula1>
-          <xm:sqref>L4:L15 L26:L32 E28:E31</xm:sqref>
+          <xm:sqref>L4:L15 L26:L32 E28:E31 L45:L46 E46:E47</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'выпад списки'!$D$2:$D$8</xm:f>
           </x14:formula1>
-          <xm:sqref>L19:L22 L35:L36 L39:L56 E32:E38 E26:E27</xm:sqref>
+          <xm:sqref>L19:L22 L35:L36 E26:E27 E32:E38 L41:L44 E48:E52 E42:E45 L47:L52 L53:L56</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'выпад списки'!$D$2:$D$9</xm:f>
           </x14:formula1>
-          <xm:sqref>E39:E56</xm:sqref>
+          <xm:sqref>E39 E53:E56</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -3450,16 +3648,16 @@
   <sheetData>
     <row r="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" t="s">
         <v>7</v>
       </c>
-      <c r="D1" t="s">
-        <v>8</v>
-      </c>
       <c r="F1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" spans="2:8" x14ac:dyDescent="0.25">
@@ -3470,34 +3668,34 @@
         <v>2</v>
       </c>
       <c r="F2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D3" t="s">
         <v>3</v>
       </c>
       <c r="F3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D4" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D5" t="s">
         <v>4</v>
@@ -3505,32 +3703,32 @@
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D6" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D11" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>

--- a/Check-lists.xlsx
+++ b/Check-lists.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="213">
   <si>
     <t>№ проверки</t>
   </si>
@@ -545,6 +545,134 @@
   </si>
   <si>
     <t>Эндпоинт PATCH/tasks/&lt;id&gt;</t>
+  </si>
+  <si>
+    <t>Изменение заголовка на другой валидный</t>
+  </si>
+  <si>
+    <t>Пустой заголовок</t>
+  </si>
+  <si>
+    <t>Дедлайн - прошлое</t>
+  </si>
+  <si>
+    <t>Дедлайн - null удаляет дедлайн</t>
+  </si>
+  <si>
+    <t>Заголовок только из пробелов</t>
+  </si>
+  <si>
+    <t>Попытка сменить ID, статус и дату создания не изменяет данные</t>
+  </si>
+  <si>
+    <t>Смена задачи без токена</t>
+  </si>
+  <si>
+    <t>Смена задачи с невалидным токеном</t>
+  </si>
+  <si>
+    <t>Смена задачи с некорректным форматом Authorization header</t>
+  </si>
+  <si>
+    <t>Заголовок больше допустимой длины</t>
+  </si>
+  <si>
+    <t>Заголовок макисмальной длины</t>
+  </si>
+  <si>
+    <t>Смена описания на другое валидное</t>
+  </si>
+  <si>
+    <t>Пустое описание</t>
+  </si>
+  <si>
+    <t>Описание больше допустимой длины</t>
+  </si>
+  <si>
+    <t>Описание максимальной длины</t>
+  </si>
+  <si>
+    <t>Описание короче максимальной длины на 1 символ</t>
+  </si>
+  <si>
+    <t>Смена приоритета на другой валидный</t>
+  </si>
+  <si>
+    <t>Смена приоритета на невалидный</t>
+  </si>
+  <si>
+    <t>Пустой приоритет</t>
+  </si>
+  <si>
+    <t>Изменение несуществующей задачи</t>
+  </si>
+  <si>
+    <t>Дедлайн &lt;30мин</t>
+  </si>
+  <si>
+    <t>Дедлайн невалидного формата</t>
+  </si>
+  <si>
+    <t>Смена дедлайна на валидный &gt;30мин</t>
+  </si>
+  <si>
+    <t>Изменение чужой задачи</t>
+  </si>
+  <si>
+    <t>Заголовок короче максимальной длины на 1 символ</t>
+  </si>
+  <si>
+    <t>401 Unauthorized</t>
+  </si>
+  <si>
+    <t>Запрос без поля title не изменяет заголовок</t>
+  </si>
+  <si>
+    <t>Эндпоинт POST/tasks</t>
+  </si>
+  <si>
+    <t>В задаче пустой заголовок</t>
+  </si>
+  <si>
+    <t>Невалидный приоритет</t>
+  </si>
+  <si>
+    <t>Создание задачи без приоритета выставляет medium по умолчанию</t>
+  </si>
+  <si>
+    <t>Дедлайн - null создаёт задачу без дедлайна</t>
+  </si>
+  <si>
+    <t>Пустое поле дедлайна создаёт задачу без дедлайна</t>
+  </si>
+  <si>
+    <t>Создание задачи со всеми допустимыми полями</t>
+  </si>
+  <si>
+    <t>Создание задачи без токена</t>
+  </si>
+  <si>
+    <t>Создание задачи с невалидным токеном</t>
+  </si>
+  <si>
+    <t>Создание задачи с некорректным форматом Authorization header</t>
+  </si>
+  <si>
+    <t>Создание задачи с истёкшим токеном</t>
+  </si>
+  <si>
+    <t>Запрос без заголовка</t>
+  </si>
+  <si>
+    <t>Любые поля, кроме:
+1) title
+2) description
+3) priority
+4) deadline
+Игнорируются</t>
+  </si>
+  <si>
+    <t>Заголовок максимальной длины</t>
   </si>
 </sst>
 </file>
@@ -681,7 +809,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -692,9 +820,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -738,10 +863,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1058,14 +1179,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="27" t="s">
         <v>68</v>
       </c>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="32"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="29"/>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
@@ -1088,305 +1209,305 @@
       </c>
     </row>
     <row r="4" spans="2:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="B4" s="11">
-        <v>1</v>
-      </c>
-      <c r="C4" s="10" t="s">
+      <c r="B4" s="10">
+        <v>1</v>
+      </c>
+      <c r="C4" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="F4" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" s="12"/>
+      <c r="F4" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" s="11"/>
     </row>
     <row r="5" spans="2:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="B5" s="11">
+      <c r="B5" s="10">
         <v>2</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="E5" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="F5" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5" s="10"/>
+      <c r="F5" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="9"/>
     </row>
     <row r="6" spans="2:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="B6" s="11">
+      <c r="B6" s="10">
         <v>3</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="E6" s="10" t="s">
+      <c r="D6" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="E6" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="F6" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6" s="12"/>
+      <c r="F6" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" s="11"/>
     </row>
     <row r="7" spans="2:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="B7" s="11">
-        <v>4</v>
-      </c>
-      <c r="C7" s="10" t="s">
+      <c r="B7" s="10">
+        <v>4</v>
+      </c>
+      <c r="C7" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="E7" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="F7" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7" s="12"/>
+      <c r="F7" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" s="11"/>
     </row>
     <row r="8" spans="2:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="B8" s="11">
+      <c r="B8" s="10">
         <v>5</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="E8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="F8" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8" s="12"/>
+      <c r="F8" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" s="11"/>
     </row>
     <row r="9" spans="2:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="B9" s="11">
+      <c r="B9" s="10">
         <v>6</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="D9" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="E9" s="10" t="s">
+      <c r="D9" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="F9" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9" s="12"/>
+      <c r="F9" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" s="11"/>
     </row>
     <row r="10" spans="2:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="B10" s="11">
+      <c r="B10" s="10">
         <v>7</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="D10" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="E10" s="10" t="s">
+      <c r="D10" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="F10" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10" s="12"/>
+      <c r="F10" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" s="11"/>
     </row>
     <row r="11" spans="2:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="B11" s="11">
+      <c r="B11" s="10">
         <v>8</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D11" s="12" t="s">
+      <c r="D11" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="E11" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="F11" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G11" s="12"/>
+      <c r="F11" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11" s="11"/>
     </row>
     <row r="12" spans="2:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="B12" s="11">
+      <c r="B12" s="10">
         <v>9</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C12" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="E12" s="10" t="s">
+      <c r="D12" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="F12" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G12" s="12"/>
+      <c r="F12" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12" s="11"/>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="11">
+      <c r="B13" s="10">
         <v>10</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="D13" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="E13" s="10" t="s">
+      <c r="E13" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="F13" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G13" s="10"/>
+      <c r="F13" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13" s="9"/>
     </row>
     <row r="14" spans="2:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="B14" s="11">
+      <c r="B14" s="10">
         <v>11</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D14" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="E14" s="10" t="s">
+      <c r="D14" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="E14" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="F14" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G14" s="12"/>
+      <c r="F14" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14" s="11"/>
     </row>
     <row r="15" spans="2:7" ht="105" x14ac:dyDescent="0.25">
-      <c r="B15" s="11">
+      <c r="B15" s="10">
         <v>12</v>
       </c>
-      <c r="C15" s="10" t="s">
+      <c r="C15" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="D15" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="E15" s="10" t="s">
+      <c r="D15" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="E15" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="F15" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G15" s="12"/>
+      <c r="F15" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15" s="11"/>
     </row>
     <row r="16" spans="2:7" ht="81.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="11">
-        <v>13</v>
-      </c>
-      <c r="C16" s="10" t="s">
+      <c r="B16" s="10">
+        <v>13</v>
+      </c>
+      <c r="C16" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D16" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="E16" s="10" t="s">
+      <c r="E16" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="F16" s="12" t="s">
+      <c r="F16" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="G16" s="10" t="s">
+      <c r="G16" s="9" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="17" spans="2:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="B17" s="11">
+      <c r="B17" s="10">
         <v>14</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="C17" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="D17" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="E17" s="10" t="s">
+      <c r="D17" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="E17" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="F17" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G17" s="12"/>
+      <c r="F17" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G17" s="11"/>
     </row>
     <row r="18" spans="2:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="B18" s="11">
+      <c r="B18" s="10">
         <v>15</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="D18" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="E18" s="14" t="s">
+      <c r="D18" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="E18" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="F18" s="12" t="s">
+      <c r="F18" s="11" t="s">
         <v>14</v>
       </c>
       <c r="G18" s="1"/>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="11">
+      <c r="B19" s="10">
         <v>16</v>
       </c>
-      <c r="C19" s="14" t="s">
+      <c r="C19" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="D19" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="E19" s="14" t="s">
+      <c r="D19" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="E19" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="F19" s="12" t="s">
+      <c r="F19" s="11" t="s">
         <v>13</v>
       </c>
       <c r="G19" s="1"/>
     </row>
     <row r="20" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="21" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B21" s="30" t="s">
+      <c r="B21" s="27" t="s">
         <v>75</v>
       </c>
-      <c r="C21" s="31"/>
-      <c r="D21" s="31"/>
-      <c r="E21" s="31"/>
-      <c r="F21" s="31"/>
-      <c r="G21" s="32"/>
+      <c r="C21" s="28"/>
+      <c r="D21" s="28"/>
+      <c r="E21" s="28"/>
+      <c r="F21" s="28"/>
+      <c r="G21" s="29"/>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B22" s="3" t="s">
@@ -1409,7 +1530,7 @@
       </c>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B23" s="11">
+      <c r="B23" s="10">
         <v>1</v>
       </c>
       <c r="C23" s="1" t="s">
@@ -1427,7 +1548,7 @@
       <c r="G23" s="1"/>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B24" s="11">
+      <c r="B24" s="10">
         <v>2</v>
       </c>
       <c r="C24" s="2" t="s">
@@ -1445,7 +1566,7 @@
       <c r="G24" s="1"/>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B25" s="11">
+      <c r="B25" s="10">
         <v>3</v>
       </c>
       <c r="C25" s="2" t="s">
@@ -1463,10 +1584,10 @@
       <c r="G25" s="1"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B26" s="11">
-        <v>4</v>
-      </c>
-      <c r="C26" s="15" t="s">
+      <c r="B26" s="10">
+        <v>4</v>
+      </c>
+      <c r="C26" s="14" t="s">
         <v>39</v>
       </c>
       <c r="D26" s="1" t="s">
@@ -1481,7 +1602,7 @@
       <c r="G26" s="1"/>
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B27" s="11">
+      <c r="B27" s="10">
         <v>5</v>
       </c>
       <c r="C27" s="2" t="s">
@@ -1499,10 +1620,10 @@
       <c r="G27" s="1"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B28" s="11">
+      <c r="B28" s="10">
         <v>6</v>
       </c>
-      <c r="C28" s="15" t="s">
+      <c r="C28" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D28" s="1" t="s">
@@ -1517,7 +1638,7 @@
       <c r="G28" s="1"/>
     </row>
     <row r="29" spans="2:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="B29" s="11">
+      <c r="B29" s="10">
         <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
@@ -1526,7 +1647,7 @@
       <c r="D29" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E29" s="10" t="s">
+      <c r="E29" s="9" t="s">
         <v>62</v>
       </c>
       <c r="F29" s="1" t="s">
@@ -1537,7 +1658,7 @@
       </c>
     </row>
     <row r="30" spans="2:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="B30" s="11">
+      <c r="B30" s="10">
         <v>8</v>
       </c>
       <c r="C30" s="2" t="s">
@@ -1546,7 +1667,7 @@
       <c r="D30" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E30" s="10" t="s">
+      <c r="E30" s="9" t="s">
         <v>61</v>
       </c>
       <c r="F30" s="1" t="s">
@@ -1555,7 +1676,7 @@
       <c r="G30" s="1"/>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B31" s="11">
+      <c r="B31" s="10">
         <v>9</v>
       </c>
       <c r="C31" s="1" t="s">
@@ -1573,10 +1694,10 @@
       <c r="G31" s="1"/>
     </row>
     <row r="32" spans="2:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="B32" s="11">
+      <c r="B32" s="10">
         <v>10</v>
       </c>
-      <c r="C32" s="15" t="s">
+      <c r="C32" s="14" t="s">
         <v>87</v>
       </c>
       <c r="D32" s="1" t="s">
@@ -1591,10 +1712,10 @@
       <c r="G32" s="1"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B33" s="11">
+      <c r="B33" s="10">
         <v>11</v>
       </c>
-      <c r="C33" s="15" t="s">
+      <c r="C33" s="14" t="s">
         <v>82</v>
       </c>
       <c r="D33" s="1" t="s">
@@ -1609,32 +1730,32 @@
       <c r="G33" s="1"/>
     </row>
     <row r="34" spans="2:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="B34" s="11">
+      <c r="B34" s="10">
         <v>12</v>
       </c>
-      <c r="C34" s="16" t="s">
+      <c r="C34" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="D34" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="E34" s="15" t="s">
+      <c r="D34" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="E34" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="F34" s="12" t="s">
+      <c r="F34" s="11" t="s">
         <v>14</v>
       </c>
       <c r="G34" s="1"/>
     </row>
     <row r="36" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B36" s="21"/>
-      <c r="C36" s="31" t="s">
+      <c r="B36" s="20"/>
+      <c r="C36" s="28" t="s">
         <v>90</v>
       </c>
-      <c r="D36" s="31"/>
-      <c r="E36" s="31"/>
-      <c r="F36" s="31"/>
-      <c r="G36" s="32"/>
+      <c r="D36" s="28"/>
+      <c r="E36" s="28"/>
+      <c r="F36" s="28"/>
+      <c r="G36" s="29"/>
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B37" s="3" t="s">
@@ -1657,53 +1778,53 @@
       </c>
     </row>
     <row r="38" spans="2:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="B38" s="17">
-        <v>1</v>
-      </c>
-      <c r="C38" s="18" t="s">
+      <c r="B38" s="16">
+        <v>1</v>
+      </c>
+      <c r="C38" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="D38" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="E38" s="18" t="s">
+      <c r="D38" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="E38" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="F38" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G38" s="18"/>
+      <c r="F38" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G38" s="17"/>
     </row>
     <row r="39" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B39" s="11"/>
-      <c r="C39" s="26" t="s">
+      <c r="B39" s="10"/>
+      <c r="C39" s="23" t="s">
         <v>98</v>
       </c>
-      <c r="D39" s="27"/>
-      <c r="E39" s="27"/>
-      <c r="F39" s="27"/>
-      <c r="G39" s="28"/>
+      <c r="D39" s="24"/>
+      <c r="E39" s="24"/>
+      <c r="F39" s="24"/>
+      <c r="G39" s="25"/>
     </row>
     <row r="40" spans="2:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="B40" s="19">
+      <c r="B40" s="18">
         <v>2</v>
       </c>
-      <c r="C40" s="20" t="s">
+      <c r="C40" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="D40" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="E40" s="20" t="s">
+      <c r="D40" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="E40" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="F40" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="G40" s="20"/>
+      <c r="F40" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G40" s="19"/>
     </row>
     <row r="41" spans="2:7" ht="105" x14ac:dyDescent="0.25">
-      <c r="B41" s="11">
+      <c r="B41" s="10">
         <v>3</v>
       </c>
       <c r="C41" s="2" t="s">
@@ -1712,7 +1833,7 @@
       <c r="D41" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="E41" s="10" t="s">
+      <c r="E41" s="9" t="s">
         <v>72</v>
       </c>
       <c r="F41" s="2" t="s">
@@ -1721,7 +1842,7 @@
       <c r="G41" s="2"/>
     </row>
     <row r="42" spans="2:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="B42" s="11">
+      <c r="B42" s="10">
         <v>4</v>
       </c>
       <c r="C42" s="2" t="s">
@@ -1741,7 +1862,7 @@
       </c>
     </row>
     <row r="43" spans="2:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="B43" s="11">
+      <c r="B43" s="10">
         <v>5</v>
       </c>
       <c r="C43" s="2" t="s">
@@ -1759,17 +1880,17 @@
       <c r="G43" s="2"/>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B44" s="11"/>
-      <c r="C44" s="26" t="s">
+      <c r="B44" s="10"/>
+      <c r="C44" s="23" t="s">
         <v>102</v>
       </c>
-      <c r="D44" s="27"/>
-      <c r="E44" s="27"/>
-      <c r="F44" s="27"/>
-      <c r="G44" s="28"/>
+      <c r="D44" s="24"/>
+      <c r="E44" s="24"/>
+      <c r="F44" s="24"/>
+      <c r="G44" s="25"/>
     </row>
     <row r="45" spans="2:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="B45" s="11">
+      <c r="B45" s="10">
         <v>6</v>
       </c>
       <c r="C45" s="2" t="s">
@@ -1787,7 +1908,7 @@
       <c r="G45" s="2"/>
     </row>
     <row r="46" spans="2:7" ht="120" x14ac:dyDescent="0.25">
-      <c r="B46" s="11">
+      <c r="B46" s="10">
         <v>7</v>
       </c>
       <c r="C46" s="2" t="s">
@@ -1805,7 +1926,7 @@
       <c r="G46" s="2"/>
     </row>
     <row r="47" spans="2:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="B47" s="11">
+      <c r="B47" s="10">
         <v>8</v>
       </c>
       <c r="C47" s="2" t="s">
@@ -1823,7 +1944,7 @@
       <c r="G47" s="2"/>
     </row>
     <row r="48" spans="2:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="B48" s="11">
+      <c r="B48" s="10">
         <v>9</v>
       </c>
       <c r="C48" s="2" t="s">
@@ -1841,7 +1962,7 @@
       <c r="G48" s="2"/>
     </row>
     <row r="49" spans="2:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="B49" s="11">
+      <c r="B49" s="10">
         <v>10</v>
       </c>
       <c r="C49" s="2" t="s">
@@ -1859,7 +1980,7 @@
       <c r="G49" s="2"/>
     </row>
     <row r="50" spans="2:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="B50" s="11">
+      <c r="B50" s="10">
         <v>11</v>
       </c>
       <c r="C50" s="2" t="s">
@@ -1877,7 +1998,7 @@
       <c r="G50" s="2"/>
     </row>
     <row r="51" spans="2:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="B51" s="11">
+      <c r="B51" s="10">
         <v>12</v>
       </c>
       <c r="C51" s="2" t="s">
@@ -1895,7 +2016,7 @@
       <c r="G51" s="2"/>
     </row>
     <row r="52" spans="2:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="B52" s="11">
+      <c r="B52" s="10">
         <v>13</v>
       </c>
       <c r="C52" s="2" t="s">
@@ -1913,7 +2034,7 @@
       <c r="G52" s="2"/>
     </row>
     <row r="53" spans="2:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="B53" s="11">
+      <c r="B53" s="10">
         <v>14</v>
       </c>
       <c r="C53" s="2" t="s">
@@ -1931,7 +2052,7 @@
       <c r="G53" s="2"/>
     </row>
     <row r="54" spans="2:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="B54" s="11">
+      <c r="B54" s="10">
         <v>15</v>
       </c>
       <c r="C54" s="2" t="s">
@@ -1949,7 +2070,7 @@
       <c r="G54" s="2"/>
     </row>
     <row r="55" spans="2:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="B55" s="11">
+      <c r="B55" s="10">
         <v>16</v>
       </c>
       <c r="C55" s="2" t="s">
@@ -1967,16 +2088,16 @@
       <c r="G55" s="2"/>
     </row>
     <row r="56" spans="2:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="B56" s="11">
+      <c r="B56" s="10">
         <v>17</v>
       </c>
-      <c r="C56" s="15" t="s">
+      <c r="C56" s="14" t="s">
         <v>112</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="E56" s="15" t="s">
+      <c r="E56" s="14" t="s">
         <v>113</v>
       </c>
       <c r="F56" s="2" t="s">
@@ -1985,24 +2106,24 @@
       <c r="G56" s="2"/>
     </row>
     <row r="57" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B57" s="29"/>
-      <c r="C57" s="29"/>
-      <c r="D57" s="29"/>
-      <c r="E57" s="29"/>
-      <c r="F57" s="29"/>
-      <c r="G57" s="29"/>
+      <c r="B57" s="26"/>
+      <c r="C57" s="26"/>
+      <c r="D57" s="26"/>
+      <c r="E57" s="26"/>
+      <c r="F57" s="26"/>
+      <c r="G57" s="26"/>
     </row>
     <row r="58" spans="2:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="B58" s="11">
+      <c r="B58" s="10">
         <v>18</v>
       </c>
-      <c r="C58" s="15" t="s">
+      <c r="C58" s="14" t="s">
         <v>116</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="E58" s="15" t="s">
+      <c r="E58" s="14" t="s">
         <v>117</v>
       </c>
       <c r="F58" s="2" t="s">
@@ -2044,7 +2165,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:N56"/>
+  <dimension ref="B2:N72"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="12.7109375" customWidth="1"/>
@@ -2055,29 +2176,29 @@
     <col min="7" max="7" width="32" customWidth="1"/>
     <col min="9" max="9" width="12.42578125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="37.5703125" customWidth="1"/>
-    <col min="11" max="11" width="12.85546875" customWidth="1"/>
+    <col min="11" max="11" width="19.28515625" customWidth="1"/>
     <col min="12" max="12" width="24.42578125" customWidth="1"/>
     <col min="13" max="13" width="15.140625" customWidth="1"/>
     <col min="14" max="14" width="28" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:14" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="32"/>
-      <c r="I2" s="30" t="s">
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="29"/>
+      <c r="I2" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="J2" s="31"/>
-      <c r="K2" s="31"/>
-      <c r="L2" s="31"/>
-      <c r="M2" s="31"/>
-      <c r="N2" s="32"/>
+      <c r="J2" s="28"/>
+      <c r="K2" s="28"/>
+      <c r="L2" s="28"/>
+      <c r="M2" s="28"/>
+      <c r="N2" s="29"/>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
@@ -2183,8 +2304,8 @@
       <c r="K5" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="L5" s="1" t="s">
-        <v>155</v>
+      <c r="L5" t="s">
+        <v>197</v>
       </c>
       <c r="M5" s="1" t="s">
         <v>13</v>
@@ -2221,8 +2342,8 @@
       <c r="K6" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="L6" s="1" t="s">
-        <v>155</v>
+      <c r="L6" t="s">
+        <v>197</v>
       </c>
       <c r="M6" s="1" t="s">
         <v>13</v>
@@ -2612,6 +2733,14 @@
       <c r="G17" s="1" t="s">
         <v>131</v>
       </c>
+      <c r="I17" s="27" t="s">
+        <v>199</v>
+      </c>
+      <c r="J17" s="28"/>
+      <c r="K17" s="28"/>
+      <c r="L17" s="28"/>
+      <c r="M17" s="28"/>
+      <c r="N17" s="29"/>
     </row>
     <row r="18" spans="2:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B18" s="4">
@@ -2632,8 +2761,26 @@
       <c r="G18" s="1" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="19" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="I18" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" spans="2:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B19" s="4">
         <v>16</v>
       </c>
@@ -2652,12 +2799,22 @@
       <c r="G19" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="I19" s="7"/>
-      <c r="J19" s="24"/>
-      <c r="K19" s="25"/>
-      <c r="L19" s="25"/>
-      <c r="M19" s="25"/>
-      <c r="N19" s="25"/>
+      <c r="I19" s="4">
+        <v>1</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N19" s="1"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B20" s="4">
@@ -2678,12 +2835,22 @@
       <c r="G20" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="I20" s="7"/>
-      <c r="J20" s="24"/>
-      <c r="K20" s="25"/>
-      <c r="L20" s="25"/>
-      <c r="M20" s="25"/>
-      <c r="N20" s="25"/>
+      <c r="I20" s="4">
+        <v>2</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N20" s="1"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B21" s="4">
@@ -2704,40 +2871,86 @@
       <c r="G21" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="I21" s="7"/>
-      <c r="J21" s="8"/>
-      <c r="K21" s="9"/>
-      <c r="L21" s="9"/>
-      <c r="M21" s="9"/>
-      <c r="N21" s="9"/>
+      <c r="I21" s="4">
+        <v>3</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="M21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N21" s="1"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="I22" s="7"/>
-      <c r="J22" s="8"/>
-      <c r="K22" s="9"/>
-      <c r="L22" s="9"/>
-      <c r="M22" s="9"/>
-      <c r="N22" s="9"/>
+      <c r="I22" s="4">
+        <v>4</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="M22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N22" s="1"/>
+    </row>
+    <row r="23" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="I23" s="4">
+        <v>5</v>
+      </c>
+      <c r="J23" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="M23" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N23" s="1"/>
     </row>
     <row r="24" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B24" s="33" t="s">
+      <c r="B24" s="30" t="s">
         <v>158</v>
       </c>
-      <c r="C24" s="33"/>
-      <c r="D24" s="33"/>
-      <c r="E24" s="33"/>
-      <c r="F24" s="33"/>
-      <c r="G24" s="33"/>
-      <c r="I24" s="30" t="s">
-        <v>159</v>
-      </c>
-      <c r="J24" s="31"/>
-      <c r="K24" s="31"/>
-      <c r="L24" s="31"/>
-      <c r="M24" s="31"/>
-      <c r="N24" s="32"/>
-    </row>
-    <row r="25" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="C24" s="30"/>
+      <c r="D24" s="30"/>
+      <c r="E24" s="30"/>
+      <c r="F24" s="30"/>
+      <c r="G24" s="30"/>
+      <c r="I24" s="4">
+        <v>6</v>
+      </c>
+      <c r="J24" s="14" t="s">
+        <v>212</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M24" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N24" s="1"/>
+    </row>
+    <row r="25" spans="2:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B25" s="3" t="s">
         <v>0</v>
       </c>
@@ -2756,24 +2969,22 @@
       <c r="G25" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="I25" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="K25" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="L25" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="M25" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="N25" s="3" t="s">
-        <v>19</v>
-      </c>
+      <c r="I25" s="4">
+        <v>7</v>
+      </c>
+      <c r="J25" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M25" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N25" s="1"/>
     </row>
     <row r="26" spans="2:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B26" s="4">
@@ -2793,23 +3004,21 @@
       </c>
       <c r="G26" s="1"/>
       <c r="I26" s="4">
-        <v>1</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>140</v>
+        <v>8</v>
+      </c>
+      <c r="J26" s="14" t="s">
+        <v>184</v>
       </c>
       <c r="K26" s="1" t="s">
         <v>1</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>144</v>
+        <v>3</v>
       </c>
       <c r="M26" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="N26" s="1" t="s">
-        <v>131</v>
-      </c>
+      <c r="N26" s="1"/>
     </row>
     <row r="27" spans="2:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B27" s="4">
@@ -2829,23 +3038,21 @@
       </c>
       <c r="G27" s="1"/>
       <c r="I27" s="4">
-        <v>2</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>141</v>
+        <v>9</v>
+      </c>
+      <c r="J27" s="14" t="s">
+        <v>185</v>
       </c>
       <c r="K27" s="1" t="s">
         <v>27</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M27" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="N27" s="1" t="s">
-        <v>131</v>
-      </c>
+      <c r="N27" s="1"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B28" s="4">
@@ -2857,33 +3064,31 @@
       <c r="D28" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E28" s="1" t="s">
-        <v>155</v>
+      <c r="E28" t="s">
+        <v>197</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G28" s="1"/>
       <c r="I28" s="4">
+        <v>10</v>
+      </c>
+      <c r="J28" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L28" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="J28" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="K28" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="L28" s="1" t="s">
-        <v>155</v>
-      </c>
       <c r="M28" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="N28" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="29" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="N28" s="1"/>
+    </row>
+    <row r="29" spans="2:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B29" s="4">
         <v>4</v>
       </c>
@@ -2893,33 +3098,31 @@
       <c r="D29" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E29" s="1" t="s">
-        <v>155</v>
+      <c r="E29" t="s">
+        <v>197</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G29" s="1"/>
       <c r="I29" s="4">
-        <v>4</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="K29" s="1" t="s">
-        <v>27</v>
+        <v>11</v>
+      </c>
+      <c r="J29" s="14" t="s">
+        <v>187</v>
+      </c>
+      <c r="K29" s="21" t="s">
+        <v>18</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>145</v>
+        <v>3</v>
       </c>
       <c r="M29" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="N29" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="30" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="N29" s="1"/>
+    </row>
+    <row r="30" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B30" s="4">
         <v>5</v>
       </c>
@@ -2929,31 +3132,29 @@
       <c r="D30" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E30" s="1" t="s">
-        <v>155</v>
+      <c r="E30" t="s">
+        <v>197</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G30" s="1"/>
       <c r="I30" s="4">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>45</v>
+        <v>201</v>
       </c>
       <c r="K30" s="1" t="s">
         <v>27</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>155</v>
+        <v>4</v>
       </c>
       <c r="M30" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="N30" s="1" t="s">
-        <v>131</v>
-      </c>
+      <c r="N30" s="1"/>
     </row>
     <row r="31" spans="2:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B31" s="4">
@@ -2965,628 +3166,1203 @@
       <c r="D31" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E31" s="1" t="s">
-        <v>155</v>
+      <c r="E31" t="s">
+        <v>197</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G31" s="1"/>
       <c r="I31" s="4">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>142</v>
+        <v>202</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="M31" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="N31" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="32" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="N31" s="1"/>
+    </row>
+    <row r="32" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B32" s="4">
         <v>7</v>
       </c>
-      <c r="C32" s="15" t="s">
+      <c r="C32" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="D32" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E32" s="22" t="s">
+      <c r="D32" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="E32" s="21" t="s">
         <v>2</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G32" s="22"/>
+      <c r="G32" s="21"/>
       <c r="I32" s="4">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="K32" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="L32" s="1" t="s">
-        <v>8</v>
+        <v>174</v>
+      </c>
+      <c r="K32" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="L32" s="21" t="s">
+        <v>4</v>
       </c>
       <c r="M32" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="N32" s="1" t="s">
-        <v>131</v>
-      </c>
+      <c r="N32" s="1"/>
     </row>
     <row r="33" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B33" s="4">
         <v>8</v>
       </c>
-      <c r="C33" s="15" t="s">
+      <c r="C33" s="14" t="s">
         <v>157</v>
       </c>
-      <c r="D33" s="22" t="s">
-        <v>27</v>
-      </c>
-      <c r="E33" s="22" t="s">
+      <c r="D33" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="E33" s="21" t="s">
         <v>5</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G33" s="22"/>
-      <c r="I33" s="4"/>
-      <c r="J33" s="6"/>
-      <c r="K33" s="1"/>
-      <c r="L33" s="1"/>
-      <c r="M33" s="1"/>
+      <c r="G33" s="21"/>
+      <c r="I33" s="4">
+        <v>15</v>
+      </c>
+      <c r="J33" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="K33" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="L33" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="M33" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="N33" s="1"/>
     </row>
     <row r="34" spans="2:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B34" s="4">
         <v>9</v>
       </c>
-      <c r="C34" s="15" t="s">
+      <c r="C34" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="D34" s="22" t="s">
-        <v>27</v>
-      </c>
-      <c r="E34" s="22" t="s">
+      <c r="D34" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="E34" s="21" t="s">
         <v>8</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G34" s="22"/>
-      <c r="I34" s="4"/>
-      <c r="J34" s="2"/>
-      <c r="K34" s="1"/>
-      <c r="L34" s="1"/>
-      <c r="M34" s="1"/>
+      <c r="G34" s="21"/>
+      <c r="I34" s="4">
+        <v>16</v>
+      </c>
+      <c r="J34" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L34" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M34" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="N34" s="1"/>
     </row>
     <row r="35" spans="2:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B35" s="4">
         <v>10</v>
       </c>
-      <c r="C35" s="15" t="s">
+      <c r="C35" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="D35" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E35" s="22" t="s">
+      <c r="D35" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="E35" s="21" t="s">
         <v>2</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G35" s="22"/>
-      <c r="I35" s="4"/>
-      <c r="J35" s="2"/>
-      <c r="K35" s="1"/>
-      <c r="L35" s="1"/>
-      <c r="M35" s="1"/>
+      <c r="G35" s="21"/>
+      <c r="I35" s="4">
+        <v>17</v>
+      </c>
+      <c r="J35" s="14" t="s">
+        <v>204</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L35" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M35" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="N35" s="1"/>
     </row>
     <row r="36" spans="2:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B36" s="4">
         <v>11</v>
       </c>
-      <c r="C36" s="15" t="s">
+      <c r="C36" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="D36" s="22" t="s">
-        <v>27</v>
-      </c>
-      <c r="E36" s="22" t="s">
+      <c r="D36" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="E36" s="21" t="s">
         <v>4</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G36" s="22"/>
-      <c r="I36" s="7"/>
-      <c r="J36" s="8"/>
-      <c r="K36" s="9"/>
-      <c r="L36" s="9"/>
-      <c r="M36" s="9"/>
-      <c r="N36" s="9"/>
-    </row>
-    <row r="37" spans="2:14" ht="45" x14ac:dyDescent="0.25">
+      <c r="G36" s="21"/>
+      <c r="I36" s="4">
+        <v>18</v>
+      </c>
+      <c r="J36" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="K36" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="L36" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="M36" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N36" s="1"/>
+    </row>
+    <row r="37" spans="2:14" ht="90" x14ac:dyDescent="0.25">
       <c r="B37" s="4">
         <v>12</v>
       </c>
-      <c r="C37" s="15" t="s">
+      <c r="C37" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="D37" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E37" s="22" t="s">
+      <c r="D37" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="E37" s="21" t="s">
         <v>2</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G37" s="23"/>
+      <c r="G37" s="22"/>
+      <c r="I37" s="4">
+        <v>19</v>
+      </c>
+      <c r="J37" s="14" t="s">
+        <v>211</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L37" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M37" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N37" s="1"/>
     </row>
     <row r="38" spans="2:14" ht="45" x14ac:dyDescent="0.25">
       <c r="B38" s="4">
         <v>13</v>
       </c>
-      <c r="C38" s="15" t="s">
+      <c r="C38" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="D38" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E38" s="22" t="s">
+      <c r="D38" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="E38" s="21" t="s">
         <v>2</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G38" s="22"/>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B39" s="7"/>
-      <c r="C39" s="8"/>
-      <c r="D39" s="9"/>
-      <c r="E39" s="9"/>
-      <c r="F39" s="9"/>
-      <c r="G39" s="9"/>
-      <c r="I39" s="33" t="s">
-        <v>167</v>
-      </c>
-      <c r="J39" s="33"/>
-      <c r="K39" s="33"/>
-      <c r="L39" s="33"/>
-      <c r="M39" s="33"/>
-      <c r="N39" s="33"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B40" s="33" t="s">
+      <c r="G38" s="21"/>
+      <c r="I38" s="4">
+        <v>20</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="K38" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="L38" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="M38" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N38" s="1"/>
+    </row>
+    <row r="39" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="B39" s="6"/>
+      <c r="C39" s="7"/>
+      <c r="D39" s="8"/>
+      <c r="E39" s="8"/>
+      <c r="F39" s="8"/>
+      <c r="G39" s="8"/>
+      <c r="I39" s="4">
+        <v>21</v>
+      </c>
+      <c r="J39" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="K39" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="L39" s="21" t="s">
+        <v>145</v>
+      </c>
+      <c r="M39" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N39" s="1"/>
+    </row>
+    <row r="40" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="I40" s="4">
+        <v>22</v>
+      </c>
+      <c r="J40" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="K40" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="L40" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="M40" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N40" s="1"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="I41" s="4">
+        <v>23</v>
+      </c>
+      <c r="J41" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="K41" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="L41" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="M41" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N41" s="1"/>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B45" s="30" t="s">
         <v>171</v>
       </c>
-      <c r="C40" s="33"/>
-      <c r="D40" s="33"/>
-      <c r="E40" s="33"/>
-      <c r="F40" s="33"/>
-      <c r="G40" s="33"/>
-      <c r="I40" s="3" t="s">
+      <c r="C45" s="30"/>
+      <c r="D45" s="30"/>
+      <c r="E45" s="30"/>
+      <c r="F45" s="30"/>
+      <c r="G45" s="30"/>
+      <c r="I45" s="27" t="s">
+        <v>159</v>
+      </c>
+      <c r="J45" s="28"/>
+      <c r="K45" s="28"/>
+      <c r="L45" s="28"/>
+      <c r="M45" s="28"/>
+      <c r="N45" s="29"/>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B46" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="J40" s="3" t="s">
+      <c r="C46" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K40" s="3" t="s">
+      <c r="D46" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L40" s="3" t="s">
+      <c r="E46" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M40" s="3" t="s">
+      <c r="F46" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N40" s="3" t="s">
+      <c r="G46" s="3" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B41" s="3" t="s">
+      <c r="I46" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="J46" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D41" s="3" t="s">
+      <c r="K46" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E41" s="3" t="s">
+      <c r="L46" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F41" s="3" t="s">
+      <c r="M46" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G41" s="3" t="s">
+      <c r="N46" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="I41" s="4">
-        <v>1</v>
-      </c>
-      <c r="J41" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="K41" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="L41" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="M41" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="N41" s="1"/>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B42" s="4">
-        <v>1</v>
-      </c>
-      <c r="C42" s="2"/>
-      <c r="D42" s="1"/>
-      <c r="E42" s="1"/>
-      <c r="F42" s="1"/>
-      <c r="G42" s="1"/>
-      <c r="I42" s="4">
-        <v>2</v>
-      </c>
-      <c r="J42" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="K42" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="L42" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="M42" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="N42" s="1"/>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B43" s="4">
-        <v>2</v>
-      </c>
-      <c r="C43" s="2"/>
-      <c r="D43" s="1"/>
-      <c r="E43" s="1"/>
-      <c r="F43" s="1"/>
-      <c r="G43" s="1"/>
-      <c r="I43" s="4">
-        <v>3</v>
-      </c>
-      <c r="J43" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="K43" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="L43" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="M43" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="N43" s="1"/>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B44" s="4">
-        <v>3</v>
-      </c>
-      <c r="C44" s="2"/>
-      <c r="D44" s="1"/>
-      <c r="E44" s="1"/>
-      <c r="F44" s="1"/>
-      <c r="G44" s="1"/>
-      <c r="I44" s="4">
-        <v>4</v>
-      </c>
-      <c r="J44" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="K44" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="L44" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="M44" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="N44" s="2"/>
-    </row>
-    <row r="45" spans="2:14" ht="60" x14ac:dyDescent="0.25">
-      <c r="B45" s="4">
-        <v>4</v>
-      </c>
-      <c r="C45" s="2"/>
-      <c r="D45" s="1"/>
-      <c r="E45" s="1"/>
-      <c r="F45" s="1"/>
-      <c r="G45" s="2"/>
-      <c r="I45" s="4">
-        <v>5</v>
-      </c>
-      <c r="J45" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="K45" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="L45" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="M45" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="N45" s="6" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="46" spans="2:14" ht="30" x14ac:dyDescent="0.25">
-      <c r="B46" s="4">
-        <v>5</v>
-      </c>
-      <c r="C46" s="2"/>
-      <c r="D46" s="1"/>
-      <c r="E46" s="1"/>
-      <c r="F46" s="1"/>
-      <c r="G46" s="6"/>
-      <c r="I46" s="4">
-        <v>6</v>
-      </c>
-      <c r="J46" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="K46" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="L46" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="M46" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="N46" s="1"/>
     </row>
     <row r="47" spans="2:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B47" s="4">
-        <v>6</v>
-      </c>
-      <c r="C47" s="2"/>
-      <c r="D47" s="1"/>
-      <c r="E47" s="1"/>
-      <c r="F47" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="G47" s="1"/>
       <c r="I47" s="4">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="K47" s="1" t="s">
         <v>1</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>2</v>
+        <v>144</v>
       </c>
       <c r="M47" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="N47" s="1"/>
+      <c r="N47" s="1" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="48" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B48" s="4">
-        <v>7</v>
-      </c>
-      <c r="C48" s="2"/>
-      <c r="D48" s="1"/>
-      <c r="E48" s="1"/>
-      <c r="F48" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="G48" s="1"/>
       <c r="I48" s="4">
-        <v>8</v>
-      </c>
-      <c r="J48" s="5" t="s">
-        <v>165</v>
+        <v>2</v>
+      </c>
+      <c r="J48" s="2" t="s">
+        <v>141</v>
       </c>
       <c r="K48" s="1" t="s">
         <v>27</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M48" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="N48" s="1"/>
+      <c r="N48" s="1" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="49" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B49" s="4">
-        <v>8</v>
-      </c>
-      <c r="C49" s="5"/>
-      <c r="D49" s="1"/>
-      <c r="E49" s="1"/>
-      <c r="F49" s="1"/>
+        <v>3</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="G49" s="1"/>
       <c r="I49" s="4">
+        <v>3</v>
+      </c>
+      <c r="J49" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="K49" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L49" t="s">
+        <v>197</v>
+      </c>
+      <c r="M49" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N49" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="50" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="B50" s="4">
+        <v>4</v>
+      </c>
+      <c r="C50" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G50" s="2"/>
+      <c r="I50" s="4">
+        <v>4</v>
+      </c>
+      <c r="J50" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="K50" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L50" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="M50" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N50" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="51" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="B51" s="4">
+        <v>5</v>
+      </c>
+      <c r="C51" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G51" s="2"/>
+      <c r="I51" s="4">
+        <v>5</v>
+      </c>
+      <c r="J51" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="K51" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L51" t="s">
+        <v>197</v>
+      </c>
+      <c r="M51" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N51" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="52" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="B52" s="4">
+        <v>6</v>
+      </c>
+      <c r="C52" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G52" s="1"/>
+      <c r="I52" s="4">
+        <v>6</v>
+      </c>
+      <c r="J52" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="K52" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L52" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M52" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N52" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="53" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="B53" s="4">
+        <v>7</v>
+      </c>
+      <c r="C53" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G53" s="1"/>
+      <c r="I53" s="4">
+        <v>7</v>
+      </c>
+      <c r="J53" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="K53" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L53" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M53" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N53" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="54" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B54" s="4">
+        <v>8</v>
+      </c>
+      <c r="C54" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G54" s="1"/>
+      <c r="I54" s="6"/>
+      <c r="J54" s="7"/>
+      <c r="K54" s="8"/>
+      <c r="L54" s="8"/>
+      <c r="M54" s="8"/>
+      <c r="N54" s="8"/>
+    </row>
+    <row r="55" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B55" s="4">
         <v>9</v>
       </c>
-      <c r="J49" s="2" t="s">
+      <c r="C55" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G55" s="1"/>
+    </row>
+    <row r="56" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B56" s="4">
+        <v>10</v>
+      </c>
+      <c r="C56" s="14" t="s">
+        <v>185</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G56" s="1"/>
+      <c r="H56" s="8"/>
+    </row>
+    <row r="57" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B57" s="4">
+        <v>11</v>
+      </c>
+      <c r="C57" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G57" s="1"/>
+      <c r="H57" s="8"/>
+    </row>
+    <row r="58" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="B58" s="4">
+        <v>12</v>
+      </c>
+      <c r="C58" s="14" t="s">
+        <v>187</v>
+      </c>
+      <c r="D58" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="E58" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G58" s="21"/>
+      <c r="H58" s="8"/>
+    </row>
+    <row r="59" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="B59" s="4">
+        <v>13</v>
+      </c>
+      <c r="C59" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="D59" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="E59" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G59" s="21"/>
+      <c r="H59" s="8"/>
+    </row>
+    <row r="60" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B60" s="4">
+        <v>14</v>
+      </c>
+      <c r="C60" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="D60" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="E60" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G60" s="21"/>
+      <c r="H60" s="8"/>
+      <c r="I60" s="27" t="s">
+        <v>167</v>
+      </c>
+      <c r="J60" s="28"/>
+      <c r="K60" s="28"/>
+      <c r="L60" s="28"/>
+      <c r="M60" s="28"/>
+      <c r="N60" s="29"/>
+    </row>
+    <row r="61" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B61" s="4">
+        <v>15</v>
+      </c>
+      <c r="C61" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="D61" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="E61" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G61" s="21"/>
+      <c r="H61" s="8"/>
+      <c r="I61" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K61" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L61" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M61" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="N61" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="62" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B62" s="4">
+        <v>16</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D62" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="E62" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G62" s="1"/>
+      <c r="I62" s="4">
+        <v>1</v>
+      </c>
+      <c r="J62" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="K62" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L62" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="M62" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N62" s="1"/>
+    </row>
+    <row r="63" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B63" s="4">
+        <v>17</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="D63" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="E63" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G63" s="1"/>
+      <c r="I63" s="4">
+        <v>2</v>
+      </c>
+      <c r="J63" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="K63" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L63" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="M63" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N63" s="1"/>
+    </row>
+    <row r="64" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B64" s="4">
+        <v>18</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D64" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="E64" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G64" s="1"/>
+      <c r="I64" s="4">
+        <v>3</v>
+      </c>
+      <c r="J64" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="K64" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L64" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M64" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N64" s="1"/>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B65" s="4">
+        <v>19</v>
+      </c>
+      <c r="C65" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="D65" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="E65" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G65" s="1"/>
+      <c r="I65" s="4">
+        <v>4</v>
+      </c>
+      <c r="J65" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="K65" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L65" t="s">
+        <v>197</v>
+      </c>
+      <c r="M65" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N65" s="2"/>
+    </row>
+    <row r="66" spans="2:14" ht="60" x14ac:dyDescent="0.25">
+      <c r="B66" s="4">
+        <v>20</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="D66" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="E66" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G66" s="1"/>
+      <c r="I66" s="4">
+        <v>5</v>
+      </c>
+      <c r="J66" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="K66" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L66" t="s">
+        <v>197</v>
+      </c>
+      <c r="M66" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N66" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="67" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="B67" s="4">
+        <v>21</v>
+      </c>
+      <c r="C67" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="D67" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="E67" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G67" s="1"/>
+      <c r="I67" s="4">
+        <v>6</v>
+      </c>
+      <c r="J67" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="K67" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L67" t="s">
+        <v>197</v>
+      </c>
+      <c r="M67" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N67" s="1"/>
+    </row>
+    <row r="68" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="B68" s="4">
+        <v>22</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="D68" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="E68" t="s">
+        <v>197</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G68" s="1"/>
+      <c r="I68" s="4">
+        <v>7</v>
+      </c>
+      <c r="J68" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="K68" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L68" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="M68" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N68" s="1"/>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B69" s="4">
+        <v>23</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D69" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="E69" s="21" t="s">
+        <v>145</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G69" s="1"/>
+      <c r="I69" s="4">
+        <v>8</v>
+      </c>
+      <c r="J69" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="K69" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L69" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="M69" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N69" s="1"/>
+    </row>
+    <row r="70" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="B70" s="4">
+        <v>24</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D70" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="E70" t="s">
+        <v>197</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G70" s="1"/>
+      <c r="I70" s="4">
+        <v>9</v>
+      </c>
+      <c r="J70" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="K49" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="L49" s="1" t="s">
+      <c r="K70" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L70" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="M49" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="N49" s="1"/>
-    </row>
-    <row r="50" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B50" s="4">
-        <v>9</v>
-      </c>
-      <c r="C50" s="2"/>
-      <c r="D50" s="1"/>
-      <c r="E50" s="1"/>
-      <c r="F50" s="1"/>
-      <c r="G50" s="1"/>
-      <c r="I50" s="4">
+      <c r="M70" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N70" s="1"/>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B71" s="4">
+        <v>25</v>
+      </c>
+      <c r="C71" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="D71" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="E71" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G71" s="1"/>
+      <c r="I71" s="4">
         <v>10</v>
       </c>
-      <c r="J50" s="2" t="s">
+      <c r="J71" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="K50" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="L50" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="M50" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="N50" s="1"/>
-    </row>
-    <row r="51" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B51" s="4">
-        <v>10</v>
-      </c>
-      <c r="C51" s="2"/>
-      <c r="D51" s="1"/>
-      <c r="E51" s="1"/>
-      <c r="F51" s="1"/>
-      <c r="G51" s="1"/>
-      <c r="H51" s="9"/>
-      <c r="I51" s="4">
+      <c r="K71" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L71" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="M71" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N71" s="1"/>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B72" s="4">
+        <v>26</v>
+      </c>
+      <c r="C72" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="D72" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="E72" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G72" s="1"/>
+      <c r="I72" s="4">
         <v>11</v>
       </c>
-      <c r="J51" s="2" t="s">
+      <c r="J72" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="K51" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="L51" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="M51" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="N51" s="1"/>
-    </row>
-    <row r="52" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B52" s="4">
-        <v>11</v>
-      </c>
-      <c r="C52" s="2"/>
-      <c r="D52" s="1"/>
-      <c r="E52" s="1"/>
-      <c r="F52" s="1"/>
-      <c r="G52" s="1"/>
-      <c r="H52" s="9"/>
-      <c r="I52" s="4"/>
-      <c r="J52" s="2"/>
-      <c r="K52" s="1"/>
-      <c r="L52" s="1"/>
-      <c r="M52" s="1"/>
-      <c r="N52" s="1"/>
-    </row>
-    <row r="53" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B53" s="7"/>
-      <c r="C53" s="9"/>
-      <c r="D53" s="9"/>
-      <c r="E53" s="9"/>
-      <c r="F53" s="9"/>
-      <c r="G53" s="9"/>
-      <c r="H53" s="9"/>
-      <c r="I53" s="7"/>
-      <c r="J53" s="9"/>
-      <c r="K53" s="9"/>
-      <c r="L53" s="9"/>
-      <c r="M53" s="9"/>
-      <c r="N53" s="9"/>
-    </row>
-    <row r="54" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B54" s="7"/>
-      <c r="C54" s="9"/>
-      <c r="D54" s="9"/>
-      <c r="E54" s="9"/>
-      <c r="F54" s="9"/>
-      <c r="G54" s="9"/>
-      <c r="H54" s="9"/>
-      <c r="I54" s="7"/>
-      <c r="J54" s="9"/>
-      <c r="K54" s="9"/>
-      <c r="L54" s="9"/>
-      <c r="M54" s="9"/>
-      <c r="N54" s="9"/>
-    </row>
-    <row r="55" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B55" s="7"/>
-      <c r="C55" s="9"/>
-      <c r="D55" s="9"/>
-      <c r="E55" s="9"/>
-      <c r="F55" s="9"/>
-      <c r="G55" s="9"/>
-      <c r="H55" s="9"/>
-      <c r="I55" s="7"/>
-      <c r="J55" s="9"/>
-      <c r="K55" s="9"/>
-      <c r="L55" s="9"/>
-      <c r="M55" s="9"/>
-      <c r="N55" s="9"/>
-    </row>
-    <row r="56" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B56" s="7"/>
-      <c r="C56" s="9"/>
-      <c r="D56" s="9"/>
-      <c r="E56" s="9"/>
-      <c r="F56" s="9"/>
-      <c r="G56" s="9"/>
-      <c r="H56" s="9"/>
-      <c r="I56" s="7"/>
-      <c r="J56" s="9"/>
-      <c r="K56" s="9"/>
-      <c r="L56" s="9"/>
-      <c r="M56" s="9"/>
-      <c r="N56" s="9"/>
+      <c r="K72" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L72" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="M72" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N72" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="B40:G40"/>
+  <mergeCells count="7">
+    <mergeCell ref="I17:N17"/>
+    <mergeCell ref="I60:N60"/>
+    <mergeCell ref="B45:G45"/>
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="I2:N2"/>
     <mergeCell ref="B24:G24"/>
-    <mergeCell ref="I24:N24"/>
-    <mergeCell ref="I39:N39"/>
+    <mergeCell ref="I45:N45"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3597,37 +4373,37 @@
           <x14:formula1>
             <xm:f>'выпад списки'!$F$2:$F$3</xm:f>
           </x14:formula1>
-          <xm:sqref>F42:F56 M4:M15 M26:M36 F4:F21 M19:M22 F26:F39 M41:M52 M53:M56</xm:sqref>
+          <xm:sqref>F47:F72 M4:M15 M62:M72 F4:F21 F26:F39 M47:M53 M19:M41</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'выпад списки'!$B$2:$B$5</xm:f>
           </x14:formula1>
-          <xm:sqref>K26:K36 K4:K15 D42:D56 D23 D4:D21 K19:K22 D26:D39 K41:K52 K53:K56</xm:sqref>
+          <xm:sqref>K62:K72 K4:K15 D23 D4:D21 D26:D39 D47:D72 K47:K53 K19:K41</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'выпад списки'!$D$2:$D$11</xm:f>
           </x14:formula1>
-          <xm:sqref>L4:L15 L26:L32 E28:E31 L45:L46 E46:E47</xm:sqref>
+          <xm:sqref>E28:E31 L65:L67 L47:L53 E47:E72 L4:L15 L19:L41</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'выпад списки'!$D$2:$D$8</xm:f>
           </x14:formula1>
-          <xm:sqref>L19:L22 L35:L36 E26:E27 E32:E38 L41:L44 E48:E52 E42:E45 L47:L52 L53:L56</xm:sqref>
+          <xm:sqref>L62:L64 L68:L72 E26:E27 E32:E38</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'выпад списки'!$D$2:$D$9</xm:f>
           </x14:formula1>
-          <xm:sqref>E39 E53:E56</xm:sqref>
+          <xm:sqref>E39</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'выпад списки'!$D$2:$D$10</xm:f>
           </x14:formula1>
-          <xm:sqref>L33:L34 E4:E21</xm:sqref>
+          <xm:sqref>E4:E21</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -3703,7 +4479,7 @@
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D6" t="s">
-        <v>155</v>
+        <v>197</v>
       </c>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.25">

--- a/Check-lists.xlsx
+++ b/Check-lists.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="764" uniqueCount="213">
   <si>
     <t>№ проверки</t>
   </si>
@@ -4010,7 +4010,9 @@
       <c r="M62" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="N62" s="1"/>
+      <c r="N62" s="1" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="63" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B63" s="4">
@@ -4044,7 +4046,9 @@
       <c r="M63" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="N63" s="1"/>
+      <c r="N63" s="1" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="64" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B64" s="4">
@@ -4078,7 +4082,9 @@
       <c r="M64" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="N64" s="1"/>
+      <c r="N64" s="1" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="65" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B65" s="4">
@@ -4112,7 +4118,9 @@
       <c r="M65" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="N65" s="2"/>
+      <c r="N65" s="1" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="66" spans="2:14" ht="60" x14ac:dyDescent="0.25">
       <c r="B66" s="4">
@@ -4250,7 +4258,9 @@
       <c r="M69" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="N69" s="1"/>
+      <c r="N69" s="1" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="70" spans="2:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B70" s="4">
@@ -4318,7 +4328,9 @@
       <c r="M71" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="N71" s="1"/>
+      <c r="N71" s="1" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="72" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B72" s="4">

--- a/Check-lists.xlsx
+++ b/Check-lists.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="764" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="781" uniqueCount="213">
   <si>
     <t>№ проверки</t>
   </si>
@@ -539,9 +539,6 @@
   </si>
   <si>
     <t>Запрос с пустым Status</t>
-  </si>
-  <si>
-    <t>Фактическое поведение текущей реализации: Flask-JWT-Extended возвращает 422 для malformed token</t>
   </si>
   <si>
     <t>Эндпоинт PATCH/tasks/&lt;id&gt;</t>
@@ -673,6 +670,9 @@
   </si>
   <si>
     <t>Заголовок максимальной длины</t>
+  </si>
+  <si>
+    <t>Автоматизировано. Фактическое поведение текущей реализации: Flask-JWT-Extended возвращает 422 для malformed token</t>
   </si>
 </sst>
 </file>
@@ -2305,7 +2305,7 @@
         <v>27</v>
       </c>
       <c r="L5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="M5" s="1" t="s">
         <v>13</v>
@@ -2343,7 +2343,7 @@
         <v>27</v>
       </c>
       <c r="L6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="M6" s="1" t="s">
         <v>13</v>
@@ -2734,7 +2734,7 @@
         <v>131</v>
       </c>
       <c r="I17" s="27" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="J17" s="28"/>
       <c r="K17" s="28"/>
@@ -2803,7 +2803,7 @@
         <v>1</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="K19" s="1" t="s">
         <v>1</v>
@@ -2814,7 +2814,9 @@
       <c r="M19" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="N19" s="1"/>
+      <c r="N19" s="1" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B20" s="4">
@@ -2839,7 +2841,7 @@
         <v>2</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="K20" s="1" t="s">
         <v>27</v>
@@ -2850,7 +2852,9 @@
       <c r="M20" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="N20" s="1"/>
+      <c r="N20" s="1" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B21" s="4">
@@ -2875,7 +2879,7 @@
         <v>3</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="K21" s="1" t="s">
         <v>27</v>
@@ -2886,14 +2890,16 @@
       <c r="M21" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="N21" s="1"/>
+      <c r="N21" s="1" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.25">
       <c r="I22" s="4">
         <v>4</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="K22" s="1" t="s">
         <v>27</v>
@@ -2904,14 +2910,16 @@
       <c r="M22" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="N22" s="1"/>
+      <c r="N22" s="1" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.25">
       <c r="I23" s="4">
         <v>5</v>
       </c>
       <c r="J23" s="14" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="K23" s="1" t="s">
         <v>28</v>
@@ -2922,7 +2930,9 @@
       <c r="M23" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="N23" s="1"/>
+      <c r="N23" s="1" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="24" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B24" s="30" t="s">
@@ -2937,7 +2947,7 @@
         <v>6</v>
       </c>
       <c r="J24" s="14" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K24" s="1" t="s">
         <v>18</v>
@@ -2948,7 +2958,9 @@
       <c r="M24" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="N24" s="1"/>
+      <c r="N24" s="1" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="25" spans="2:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B25" s="3" t="s">
@@ -2973,7 +2985,7 @@
         <v>7</v>
       </c>
       <c r="J25" s="14" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="K25" s="1" t="s">
         <v>18</v>
@@ -2984,7 +2996,9 @@
       <c r="M25" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="N25" s="1"/>
+      <c r="N25" s="1" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="26" spans="2:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B26" s="4">
@@ -3007,7 +3021,7 @@
         <v>8</v>
       </c>
       <c r="J26" s="14" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="K26" s="1" t="s">
         <v>1</v>
@@ -3018,7 +3032,9 @@
       <c r="M26" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="N26" s="1"/>
+      <c r="N26" s="1" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="27" spans="2:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B27" s="4">
@@ -3041,7 +3057,7 @@
         <v>9</v>
       </c>
       <c r="J27" s="14" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="K27" s="1" t="s">
         <v>27</v>
@@ -3052,7 +3068,9 @@
       <c r="M27" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="N27" s="1"/>
+      <c r="N27" s="1" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B28" s="4">
@@ -3065,7 +3083,7 @@
         <v>27</v>
       </c>
       <c r="E28" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>13</v>
@@ -3075,7 +3093,7 @@
         <v>10</v>
       </c>
       <c r="J28" s="14" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="K28" s="1" t="s">
         <v>18</v>
@@ -3086,7 +3104,9 @@
       <c r="M28" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="N28" s="1"/>
+      <c r="N28" s="1" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="29" spans="2:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B29" s="4">
@@ -3099,7 +3119,7 @@
         <v>27</v>
       </c>
       <c r="E29" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>13</v>
@@ -3109,7 +3129,7 @@
         <v>11</v>
       </c>
       <c r="J29" s="14" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="K29" s="21" t="s">
         <v>18</v>
@@ -3120,7 +3140,9 @@
       <c r="M29" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="N29" s="1"/>
+      <c r="N29" s="1" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="30" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B30" s="4">
@@ -3133,7 +3155,7 @@
         <v>27</v>
       </c>
       <c r="E30" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>13</v>
@@ -3143,7 +3165,7 @@
         <v>12</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="K30" s="1" t="s">
         <v>27</v>
@@ -3154,7 +3176,9 @@
       <c r="M30" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="N30" s="1"/>
+      <c r="N30" s="1" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="31" spans="2:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B31" s="4">
@@ -3167,7 +3191,7 @@
         <v>27</v>
       </c>
       <c r="E31" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>13</v>
@@ -3177,7 +3201,7 @@
         <v>13</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="K31" s="1" t="s">
         <v>1</v>
@@ -3188,7 +3212,9 @@
       <c r="M31" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="N31" s="1"/>
+      <c r="N31" s="1" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B32" s="4">
@@ -3211,7 +3237,7 @@
         <v>14</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K32" s="21" t="s">
         <v>27</v>
@@ -3245,7 +3271,7 @@
         <v>15</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="K33" s="21" t="s">
         <v>27</v>
@@ -3279,7 +3305,7 @@
         <v>16</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="K34" s="1" t="s">
         <v>1</v>
@@ -3313,7 +3339,7 @@
         <v>17</v>
       </c>
       <c r="J35" s="14" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="K35" s="1" t="s">
         <v>1</v>
@@ -3347,7 +3373,7 @@
         <v>18</v>
       </c>
       <c r="J36" s="14" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K36" s="21" t="s">
         <v>27</v>
@@ -3381,7 +3407,7 @@
         <v>19</v>
       </c>
       <c r="J37" s="14" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="K37" s="1" t="s">
         <v>1</v>
@@ -3415,13 +3441,13 @@
         <v>20</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="K38" s="21" t="s">
         <v>27</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="M38" s="1" t="s">
         <v>13</v>
@@ -3439,7 +3465,7 @@
         <v>21</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="K39" s="21" t="s">
         <v>27</v>
@@ -3457,13 +3483,13 @@
         <v>22</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="K40" s="21" t="s">
         <v>27</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="M40" s="1" t="s">
         <v>13</v>
@@ -3475,13 +3501,13 @@
         <v>23</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K41" s="21" t="s">
         <v>27</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="M41" s="1" t="s">
         <v>13</v>
@@ -3490,7 +3516,7 @@
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B45" s="30" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C45" s="30"/>
       <c r="D45" s="30"/>
@@ -3549,7 +3575,7 @@
         <v>1</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>1</v>
@@ -3585,7 +3611,7 @@
         <v>2</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>27</v>
@@ -3621,7 +3647,7 @@
         <v>3</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>27</v>
@@ -3643,7 +3669,7 @@
         <v>27</v>
       </c>
       <c r="L49" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="M49" s="1" t="s">
         <v>13</v>
@@ -3657,7 +3683,7 @@
         <v>4</v>
       </c>
       <c r="C50" s="14" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>28</v>
@@ -3693,7 +3719,7 @@
         <v>5</v>
       </c>
       <c r="C51" s="14" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>18</v>
@@ -3715,7 +3741,7 @@
         <v>27</v>
       </c>
       <c r="L51" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="M51" s="1" t="s">
         <v>13</v>
@@ -3729,7 +3755,7 @@
         <v>6</v>
       </c>
       <c r="C52" s="14" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>18</v>
@@ -3765,7 +3791,7 @@
         <v>7</v>
       </c>
       <c r="C53" s="14" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>1</v>
@@ -3801,7 +3827,7 @@
         <v>8</v>
       </c>
       <c r="C54" s="14" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>1</v>
@@ -3825,7 +3851,7 @@
         <v>9</v>
       </c>
       <c r="C55" s="14" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>1</v>
@@ -3843,7 +3869,7 @@
         <v>10</v>
       </c>
       <c r="C56" s="14" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>27</v>
@@ -3862,7 +3888,7 @@
         <v>11</v>
       </c>
       <c r="C57" s="14" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>18</v>
@@ -3881,7 +3907,7 @@
         <v>12</v>
       </c>
       <c r="C58" s="14" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D58" s="21" t="s">
         <v>18</v>
@@ -3900,7 +3926,7 @@
         <v>13</v>
       </c>
       <c r="C59" s="14" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D59" s="21" t="s">
         <v>1</v>
@@ -3919,7 +3945,7 @@
         <v>14</v>
       </c>
       <c r="C60" s="14" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D60" s="21" t="s">
         <v>27</v>
@@ -3946,7 +3972,7 @@
         <v>15</v>
       </c>
       <c r="C61" s="14" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D61" s="21" t="s">
         <v>27</v>
@@ -3983,7 +4009,7 @@
         <v>16</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D62" s="21" t="s">
         <v>27</v>
@@ -4019,7 +4045,7 @@
         <v>17</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D63" s="21" t="s">
         <v>27</v>
@@ -4055,7 +4081,7 @@
         <v>18</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D64" s="21" t="s">
         <v>1</v>
@@ -4091,7 +4117,7 @@
         <v>19</v>
       </c>
       <c r="C65" s="14" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D65" s="21" t="s">
         <v>27</v>
@@ -4113,7 +4139,7 @@
         <v>27</v>
       </c>
       <c r="L65" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="M65" s="1" t="s">
         <v>13</v>
@@ -4122,12 +4148,12 @@
         <v>131</v>
       </c>
     </row>
-    <row r="66" spans="2:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:14" ht="75" x14ac:dyDescent="0.25">
       <c r="B66" s="4">
         <v>20</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D66" s="21" t="s">
         <v>1</v>
@@ -4149,13 +4175,13 @@
         <v>27</v>
       </c>
       <c r="L66" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="M66" s="1" t="s">
         <v>13</v>
       </c>
       <c r="N66" s="2" t="s">
-        <v>170</v>
+        <v>212</v>
       </c>
     </row>
     <row r="67" spans="2:14" ht="30" x14ac:dyDescent="0.25">
@@ -4163,7 +4189,7 @@
         <v>21</v>
       </c>
       <c r="C67" s="14" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D67" s="21" t="s">
         <v>1</v>
@@ -4185,25 +4211,27 @@
         <v>27</v>
       </c>
       <c r="L67" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="M67" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="N67" s="1"/>
+      <c r="N67" s="1" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="68" spans="2:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B68" s="4">
         <v>22</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D68" s="21" t="s">
         <v>27</v>
       </c>
       <c r="E68" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>13</v>
@@ -4224,14 +4252,16 @@
       <c r="M68" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="N68" s="1"/>
+      <c r="N68" s="1" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="69" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B69" s="4">
         <v>23</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D69" s="21" t="s">
         <v>27</v>
@@ -4267,13 +4297,13 @@
         <v>24</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D70" s="21" t="s">
         <v>27</v>
       </c>
       <c r="E70" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>13</v>
@@ -4294,14 +4324,16 @@
       <c r="M70" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="N70" s="1"/>
+      <c r="N70" s="1" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="71" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B71" s="4">
         <v>25</v>
       </c>
       <c r="C71" s="14" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D71" s="21" t="s">
         <v>27</v>
@@ -4337,7 +4369,7 @@
         <v>26</v>
       </c>
       <c r="C72" s="14" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D72" s="21" t="s">
         <v>27</v>
@@ -4364,7 +4396,9 @@
       <c r="M72" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="N72" s="1"/>
+      <c r="N72" s="1" t="s">
+        <v>131</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -4491,7 +4525,7 @@
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.25">

--- a/Check-lists.xlsx
+++ b/Check-lists.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="781" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="801" uniqueCount="213">
   <si>
     <t>№ проверки</t>
   </si>
@@ -638,9 +638,6 @@
   </si>
   <si>
     <t>Дедлайн - null создаёт задачу без дедлайна</t>
-  </si>
-  <si>
-    <t>Пустое поле дедлайна создаёт задачу без дедлайна</t>
   </si>
   <si>
     <t>Создание задачи со всеми допустимыми полями</t>
@@ -673,6 +670,9 @@
   </si>
   <si>
     <t>Автоматизировано. Фактическое поведение текущей реализации: Flask-JWT-Extended возвращает 422 для malformed token</t>
+  </si>
+  <si>
+    <t>Отсутствие поля дедлайна создаёт задачу без дедлайна</t>
   </si>
 </sst>
 </file>
@@ -2803,7 +2803,7 @@
         <v>1</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="K19" s="1" t="s">
         <v>1</v>
@@ -2879,7 +2879,7 @@
         <v>3</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K21" s="1" t="s">
         <v>27</v>
@@ -2947,7 +2947,7 @@
         <v>6</v>
       </c>
       <c r="J24" s="14" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="K24" s="1" t="s">
         <v>18</v>
@@ -3016,7 +3016,9 @@
       <c r="F26" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G26" s="1"/>
+      <c r="G26" s="1" t="s">
+        <v>131</v>
+      </c>
       <c r="I26" s="4">
         <v>8</v>
       </c>
@@ -3052,7 +3054,9 @@
       <c r="F27" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G27" s="1"/>
+      <c r="G27" s="1" t="s">
+        <v>131</v>
+      </c>
       <c r="I27" s="4">
         <v>9</v>
       </c>
@@ -3088,7 +3092,9 @@
       <c r="F28" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G28" s="1"/>
+      <c r="G28" s="1" t="s">
+        <v>131</v>
+      </c>
       <c r="I28" s="4">
         <v>10</v>
       </c>
@@ -3124,7 +3130,9 @@
       <c r="F29" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G29" s="1"/>
+      <c r="G29" s="1" t="s">
+        <v>131</v>
+      </c>
       <c r="I29" s="4">
         <v>11</v>
       </c>
@@ -3160,7 +3168,9 @@
       <c r="F30" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G30" s="1"/>
+      <c r="G30" s="1" t="s">
+        <v>131</v>
+      </c>
       <c r="I30" s="4">
         <v>12</v>
       </c>
@@ -3196,7 +3206,9 @@
       <c r="F31" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G31" s="1"/>
+      <c r="G31" s="1" t="s">
+        <v>131</v>
+      </c>
       <c r="I31" s="4">
         <v>13</v>
       </c>
@@ -3232,7 +3244,9 @@
       <c r="F32" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G32" s="21"/>
+      <c r="G32" s="1" t="s">
+        <v>131</v>
+      </c>
       <c r="I32" s="4">
         <v>14</v>
       </c>
@@ -3248,7 +3262,9 @@
       <c r="M32" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="N32" s="1"/>
+      <c r="N32" s="1" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="33" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B33" s="4">
@@ -3266,7 +3282,9 @@
       <c r="F33" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G33" s="21"/>
+      <c r="G33" s="1" t="s">
+        <v>131</v>
+      </c>
       <c r="I33" s="4">
         <v>15</v>
       </c>
@@ -3282,7 +3300,9 @@
       <c r="M33" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="N33" s="1"/>
+      <c r="N33" s="1" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="34" spans="2:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B34" s="4">
@@ -3300,7 +3320,9 @@
       <c r="F34" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G34" s="21"/>
+      <c r="G34" s="1" t="s">
+        <v>131</v>
+      </c>
       <c r="I34" s="4">
         <v>16</v>
       </c>
@@ -3316,7 +3338,9 @@
       <c r="M34" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="N34" s="1"/>
+      <c r="N34" s="1" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="35" spans="2:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B35" s="4">
@@ -3334,12 +3358,14 @@
       <c r="F35" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G35" s="21"/>
+      <c r="G35" s="1" t="s">
+        <v>131</v>
+      </c>
       <c r="I35" s="4">
         <v>17</v>
       </c>
       <c r="J35" s="14" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="K35" s="1" t="s">
         <v>1</v>
@@ -3350,7 +3376,9 @@
       <c r="M35" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="N35" s="1"/>
+      <c r="N35" s="1" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="36" spans="2:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B36" s="4">
@@ -3368,7 +3396,9 @@
       <c r="F36" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G36" s="21"/>
+      <c r="G36" s="1" t="s">
+        <v>131</v>
+      </c>
       <c r="I36" s="4">
         <v>18</v>
       </c>
@@ -3384,7 +3414,9 @@
       <c r="M36" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="N36" s="1"/>
+      <c r="N36" s="1" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="37" spans="2:14" ht="90" x14ac:dyDescent="0.25">
       <c r="B37" s="4">
@@ -3407,7 +3439,7 @@
         <v>19</v>
       </c>
       <c r="J37" s="14" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="K37" s="1" t="s">
         <v>1</v>
@@ -3418,7 +3450,9 @@
       <c r="M37" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="N37" s="1"/>
+      <c r="N37" s="1" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="38" spans="2:14" ht="45" x14ac:dyDescent="0.25">
       <c r="B38" s="4">
@@ -3441,7 +3475,7 @@
         <v>20</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="K38" s="21" t="s">
         <v>27</v>
@@ -3452,7 +3486,9 @@
       <c r="M38" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="N38" s="1"/>
+      <c r="N38" s="1" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="39" spans="2:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B39" s="6"/>
@@ -3465,7 +3501,7 @@
         <v>21</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="K39" s="21" t="s">
         <v>27</v>
@@ -3476,14 +3512,16 @@
       <c r="M39" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="N39" s="1"/>
+      <c r="N39" s="1" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="40" spans="2:14" ht="30" x14ac:dyDescent="0.25">
       <c r="I40" s="4">
         <v>22</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="K40" s="21" t="s">
         <v>27</v>
@@ -3494,14 +3532,16 @@
       <c r="M40" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="N40" s="1"/>
+      <c r="N40" s="1" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="41" spans="2:14" x14ac:dyDescent="0.25">
       <c r="I41" s="4">
         <v>23</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="K41" s="21" t="s">
         <v>27</v>
@@ -4181,7 +4221,7 @@
         <v>13</v>
       </c>
       <c r="N66" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="67" spans="2:14" ht="30" x14ac:dyDescent="0.25">

--- a/Check-lists.xlsx
+++ b/Check-lists.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="801" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="213">
   <si>
     <t>№ проверки</t>
   </si>
@@ -3626,7 +3626,9 @@
       <c r="F47" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G47" s="1"/>
+      <c r="G47" s="1" t="s">
+        <v>131</v>
+      </c>
       <c r="I47" s="4">
         <v>1</v>
       </c>
@@ -3662,7 +3664,9 @@
       <c r="F48" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G48" s="1"/>
+      <c r="G48" s="1" t="s">
+        <v>131</v>
+      </c>
       <c r="I48" s="4">
         <v>2</v>
       </c>
@@ -3698,7 +3702,9 @@
       <c r="F49" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G49" s="1"/>
+      <c r="G49" s="1" t="s">
+        <v>131</v>
+      </c>
       <c r="I49" s="4">
         <v>3</v>
       </c>
@@ -3734,7 +3740,9 @@
       <c r="F50" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G50" s="2"/>
+      <c r="G50" s="1" t="s">
+        <v>131</v>
+      </c>
       <c r="I50" s="4">
         <v>4</v>
       </c>
@@ -3770,7 +3778,9 @@
       <c r="F51" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G51" s="2"/>
+      <c r="G51" s="1" t="s">
+        <v>131</v>
+      </c>
       <c r="I51" s="4">
         <v>5</v>
       </c>
@@ -3806,7 +3816,9 @@
       <c r="F52" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G52" s="1"/>
+      <c r="G52" s="1" t="s">
+        <v>131</v>
+      </c>
       <c r="I52" s="4">
         <v>6</v>
       </c>
@@ -3842,7 +3854,9 @@
       <c r="F53" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G53" s="1"/>
+      <c r="G53" s="1" t="s">
+        <v>131</v>
+      </c>
       <c r="I53" s="4">
         <v>7</v>
       </c>
@@ -3878,7 +3892,9 @@
       <c r="F54" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G54" s="1"/>
+      <c r="G54" s="1" t="s">
+        <v>131</v>
+      </c>
       <c r="I54" s="6"/>
       <c r="J54" s="7"/>
       <c r="K54" s="8"/>
@@ -3902,7 +3918,9 @@
       <c r="F55" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G55" s="1"/>
+      <c r="G55" s="1" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="56" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B56" s="4">
@@ -3920,7 +3938,9 @@
       <c r="F56" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G56" s="1"/>
+      <c r="G56" s="1" t="s">
+        <v>131</v>
+      </c>
       <c r="H56" s="8"/>
     </row>
     <row r="57" spans="2:14" x14ac:dyDescent="0.25">
@@ -3939,7 +3959,9 @@
       <c r="F57" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G57" s="1"/>
+      <c r="G57" s="1" t="s">
+        <v>131</v>
+      </c>
       <c r="H57" s="8"/>
     </row>
     <row r="58" spans="2:14" ht="30" x14ac:dyDescent="0.25">
@@ -3958,7 +3980,9 @@
       <c r="F58" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G58" s="21"/>
+      <c r="G58" s="1" t="s">
+        <v>131</v>
+      </c>
       <c r="H58" s="8"/>
     </row>
     <row r="59" spans="2:14" ht="30" x14ac:dyDescent="0.25">
@@ -3977,7 +4001,9 @@
       <c r="F59" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G59" s="21"/>
+      <c r="G59" s="1" t="s">
+        <v>131</v>
+      </c>
       <c r="H59" s="8"/>
     </row>
     <row r="60" spans="2:14" x14ac:dyDescent="0.25">
@@ -3996,7 +4022,9 @@
       <c r="F60" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G60" s="21"/>
+      <c r="G60" s="1" t="s">
+        <v>131</v>
+      </c>
       <c r="H60" s="8"/>
       <c r="I60" s="27" t="s">
         <v>167</v>
@@ -4023,7 +4051,9 @@
       <c r="F61" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G61" s="21"/>
+      <c r="G61" s="1" t="s">
+        <v>131</v>
+      </c>
       <c r="H61" s="8"/>
       <c r="I61" s="3" t="s">
         <v>0</v>

--- a/Check-lists.xlsx
+++ b/Check-lists.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="829" uniqueCount="213">
   <si>
     <t>№ проверки</t>
   </si>
@@ -809,7 +809,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -862,7 +862,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1179,14 +1178,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B2" s="27" t="s">
+      <c r="B2" s="26" t="s">
         <v>68</v>
       </c>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="29"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="28"/>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
@@ -1500,14 +1499,14 @@
     </row>
     <row r="20" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="21" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B21" s="27" t="s">
+      <c r="B21" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="C21" s="28"/>
-      <c r="D21" s="28"/>
-      <c r="E21" s="28"/>
-      <c r="F21" s="28"/>
-      <c r="G21" s="29"/>
+      <c r="C21" s="27"/>
+      <c r="D21" s="27"/>
+      <c r="E21" s="27"/>
+      <c r="F21" s="27"/>
+      <c r="G21" s="28"/>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B22" s="3" t="s">
@@ -1749,13 +1748,13 @@
     </row>
     <row r="36" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B36" s="20"/>
-      <c r="C36" s="28" t="s">
+      <c r="C36" s="27" t="s">
         <v>90</v>
       </c>
-      <c r="D36" s="28"/>
-      <c r="E36" s="28"/>
-      <c r="F36" s="28"/>
-      <c r="G36" s="29"/>
+      <c r="D36" s="27"/>
+      <c r="E36" s="27"/>
+      <c r="F36" s="27"/>
+      <c r="G36" s="28"/>
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B37" s="3" t="s">
@@ -1797,13 +1796,13 @@
     </row>
     <row r="39" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B39" s="10"/>
-      <c r="C39" s="23" t="s">
+      <c r="C39" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="D39" s="24"/>
-      <c r="E39" s="24"/>
-      <c r="F39" s="24"/>
-      <c r="G39" s="25"/>
+      <c r="D39" s="23"/>
+      <c r="E39" s="23"/>
+      <c r="F39" s="23"/>
+      <c r="G39" s="24"/>
     </row>
     <row r="40" spans="2:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B40" s="18">
@@ -1881,13 +1880,13 @@
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B44" s="10"/>
-      <c r="C44" s="23" t="s">
+      <c r="C44" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="D44" s="24"/>
-      <c r="E44" s="24"/>
-      <c r="F44" s="24"/>
-      <c r="G44" s="25"/>
+      <c r="D44" s="23"/>
+      <c r="E44" s="23"/>
+      <c r="F44" s="23"/>
+      <c r="G44" s="24"/>
     </row>
     <row r="45" spans="2:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B45" s="10">
@@ -2106,12 +2105,12 @@
       <c r="G56" s="2"/>
     </row>
     <row r="57" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B57" s="26"/>
-      <c r="C57" s="26"/>
-      <c r="D57" s="26"/>
-      <c r="E57" s="26"/>
-      <c r="F57" s="26"/>
-      <c r="G57" s="26"/>
+      <c r="B57" s="25"/>
+      <c r="C57" s="25"/>
+      <c r="D57" s="25"/>
+      <c r="E57" s="25"/>
+      <c r="F57" s="25"/>
+      <c r="G57" s="25"/>
     </row>
     <row r="58" spans="2:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B58" s="10">
@@ -2183,22 +2182,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:14" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="27" t="s">
+      <c r="B2" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="29"/>
-      <c r="I2" s="27" t="s">
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="28"/>
+      <c r="I2" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="J2" s="28"/>
-      <c r="K2" s="28"/>
-      <c r="L2" s="28"/>
-      <c r="M2" s="28"/>
-      <c r="N2" s="29"/>
+      <c r="J2" s="27"/>
+      <c r="K2" s="27"/>
+      <c r="L2" s="27"/>
+      <c r="M2" s="27"/>
+      <c r="N2" s="28"/>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
@@ -2733,14 +2732,14 @@
       <c r="G17" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="I17" s="27" t="s">
+      <c r="I17" s="26" t="s">
         <v>198</v>
       </c>
-      <c r="J17" s="28"/>
-      <c r="K17" s="28"/>
-      <c r="L17" s="28"/>
-      <c r="M17" s="28"/>
-      <c r="N17" s="29"/>
+      <c r="J17" s="27"/>
+      <c r="K17" s="27"/>
+      <c r="L17" s="27"/>
+      <c r="M17" s="27"/>
+      <c r="N17" s="28"/>
     </row>
     <row r="18" spans="2:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B18" s="4">
@@ -2935,14 +2934,14 @@
       </c>
     </row>
     <row r="24" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B24" s="30" t="s">
+      <c r="B24" s="29" t="s">
         <v>158</v>
       </c>
-      <c r="C24" s="30"/>
-      <c r="D24" s="30"/>
-      <c r="E24" s="30"/>
-      <c r="F24" s="30"/>
-      <c r="G24" s="30"/>
+      <c r="C24" s="29"/>
+      <c r="D24" s="29"/>
+      <c r="E24" s="29"/>
+      <c r="F24" s="29"/>
+      <c r="G24" s="29"/>
       <c r="I24" s="4">
         <v>6</v>
       </c>
@@ -3434,7 +3433,9 @@
       <c r="F37" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G37" s="22"/>
+      <c r="G37" s="1" t="s">
+        <v>131</v>
+      </c>
       <c r="I37" s="4">
         <v>19</v>
       </c>
@@ -3470,7 +3471,9 @@
       <c r="F38" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G38" s="21"/>
+      <c r="G38" s="1" t="s">
+        <v>131</v>
+      </c>
       <c r="I38" s="4">
         <v>20</v>
       </c>
@@ -3555,22 +3558,22 @@
       <c r="N41" s="1"/>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B45" s="30" t="s">
+      <c r="B45" s="29" t="s">
         <v>170</v>
       </c>
-      <c r="C45" s="30"/>
-      <c r="D45" s="30"/>
-      <c r="E45" s="30"/>
-      <c r="F45" s="30"/>
-      <c r="G45" s="30"/>
-      <c r="I45" s="27" t="s">
+      <c r="C45" s="29"/>
+      <c r="D45" s="29"/>
+      <c r="E45" s="29"/>
+      <c r="F45" s="29"/>
+      <c r="G45" s="29"/>
+      <c r="I45" s="26" t="s">
         <v>159</v>
       </c>
-      <c r="J45" s="28"/>
-      <c r="K45" s="28"/>
-      <c r="L45" s="28"/>
-      <c r="M45" s="28"/>
-      <c r="N45" s="29"/>
+      <c r="J45" s="27"/>
+      <c r="K45" s="27"/>
+      <c r="L45" s="27"/>
+      <c r="M45" s="27"/>
+      <c r="N45" s="28"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B46" s="3" t="s">
@@ -4026,14 +4029,14 @@
         <v>131</v>
       </c>
       <c r="H60" s="8"/>
-      <c r="I60" s="27" t="s">
+      <c r="I60" s="26" t="s">
         <v>167</v>
       </c>
-      <c r="J60" s="28"/>
-      <c r="K60" s="28"/>
-      <c r="L60" s="28"/>
-      <c r="M60" s="28"/>
-      <c r="N60" s="29"/>
+      <c r="J60" s="27"/>
+      <c r="K60" s="27"/>
+      <c r="L60" s="27"/>
+      <c r="M60" s="27"/>
+      <c r="N60" s="28"/>
     </row>
     <row r="61" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B61" s="4">
@@ -4090,7 +4093,9 @@
       <c r="F62" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G62" s="1"/>
+      <c r="G62" s="1" t="s">
+        <v>131</v>
+      </c>
       <c r="I62" s="4">
         <v>1</v>
       </c>
@@ -4126,7 +4131,9 @@
       <c r="F63" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G63" s="1"/>
+      <c r="G63" s="1" t="s">
+        <v>131</v>
+      </c>
       <c r="I63" s="4">
         <v>2</v>
       </c>
@@ -4162,7 +4169,9 @@
       <c r="F64" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G64" s="1"/>
+      <c r="G64" s="1" t="s">
+        <v>131</v>
+      </c>
       <c r="I64" s="4">
         <v>3</v>
       </c>
@@ -4198,7 +4207,9 @@
       <c r="F65" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G65" s="1"/>
+      <c r="G65" s="1" t="s">
+        <v>131</v>
+      </c>
       <c r="I65" s="4">
         <v>4</v>
       </c>
@@ -4234,7 +4245,9 @@
       <c r="F66" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G66" s="1"/>
+      <c r="G66" s="1" t="s">
+        <v>131</v>
+      </c>
       <c r="I66" s="4">
         <v>5</v>
       </c>
@@ -4270,7 +4283,9 @@
       <c r="F67" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G67" s="1"/>
+      <c r="G67" s="1" t="s">
+        <v>131</v>
+      </c>
       <c r="I67" s="4">
         <v>6</v>
       </c>
@@ -4306,7 +4321,9 @@
       <c r="F68" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G68" s="1"/>
+      <c r="G68" s="1" t="s">
+        <v>131</v>
+      </c>
       <c r="I68" s="4">
         <v>7</v>
       </c>
@@ -4342,7 +4359,9 @@
       <c r="F69" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G69" s="1"/>
+      <c r="G69" s="1" t="s">
+        <v>131</v>
+      </c>
       <c r="I69" s="4">
         <v>8</v>
       </c>
@@ -4378,7 +4397,9 @@
       <c r="F70" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G70" s="1"/>
+      <c r="G70" s="1" t="s">
+        <v>131</v>
+      </c>
       <c r="I70" s="4">
         <v>9</v>
       </c>
@@ -4414,7 +4435,9 @@
       <c r="F71" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G71" s="1"/>
+      <c r="G71" s="1" t="s">
+        <v>131</v>
+      </c>
       <c r="I71" s="4">
         <v>10</v>
       </c>
@@ -4450,7 +4473,9 @@
       <c r="F72" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G72" s="1"/>
+      <c r="G72" s="1" t="s">
+        <v>131</v>
+      </c>
       <c r="I72" s="4">
         <v>11</v>
       </c>

--- a/Check-lists.xlsx
+++ b/Check-lists.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
   </bookViews>
   <sheets>
     <sheet name="Фронт" sheetId="3" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="829" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="756" uniqueCount="169">
   <si>
     <t>№ проверки</t>
   </si>
@@ -68,12 +68,6 @@
     <t>Failed</t>
   </si>
   <si>
-    <t>Регистрация с валидным логином/паролем минимальной длины, минимальный возраст</t>
-  </si>
-  <si>
-    <t>Регистрация с валидным логином/паролем максимальной длины, максимально допустимый возраст</t>
-  </si>
-  <si>
     <t>Регистрация с валидными данными со средними значениями</t>
   </si>
   <si>
@@ -86,24 +80,6 @@
     <t>Negtive (Boundary)</t>
   </si>
   <si>
-    <t>Пароль короче допустимых значений. Логин/ДР валидные.</t>
-  </si>
-  <si>
-    <t>Пароль длиннее допустимых значений. Логин/ДР валидные.</t>
-  </si>
-  <si>
-    <t>Пароль с пробелами. Логин/ДР валидные.</t>
-  </si>
-  <si>
-    <t>Пароль валидной длины,игнорирование требований сложности (ввод пароля без одного из обязательных значений поочерёдно. Логин/ДР валидные.</t>
-  </si>
-  <si>
-    <t>Логин длиной меньше допустимых значений. ДР/пароль валидные</t>
-  </si>
-  <si>
-    <t>Логин длиной больше допустимых значений. ДР/пароль валидные</t>
-  </si>
-  <si>
     <t>Negаtive</t>
   </si>
   <si>
@@ -119,9 +95,6 @@
     <t>Вход с валидным логином и паролем</t>
   </si>
   <si>
-    <t>Регистрация с не уникальным логином. Пароль/ДР Валидные</t>
-  </si>
-  <si>
     <t>Вход с верным логином и неверным паролем</t>
   </si>
   <si>
@@ -167,21 +140,6 @@
     <t>415 Unsupported media type</t>
   </si>
   <si>
-    <t>Смена e-mail на валидный</t>
-  </si>
-  <si>
-    <t>Смена имени на валидное</t>
-  </si>
-  <si>
-    <t>Смена номера телефона на валидный</t>
-  </si>
-  <si>
-    <t>Смена номера телефона на невалидный (длина, буквы, спецсимволы)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Смена имени - невалидный фомат </t>
-  </si>
-  <si>
     <t>409 Conflict</t>
   </si>
   <si>
@@ -191,88 +149,15 @@
     <t>Переход на страницу профиля с данными зарегистрированного пользователя</t>
   </si>
   <si>
-    <t>Ошибка "Логин должен содержать минимум 3 символа"</t>
-  </si>
-  <si>
-    <t>Ошибка "Логин должен содержать максимум 32 символа"</t>
-  </si>
-  <si>
-    <t>Ввод логина с пробелами. ДР/пароль валидные</t>
-  </si>
-  <si>
-    <t>При регистрации ошибка "Пользователь с этим логином уже существует"</t>
-  </si>
-  <si>
-    <t>Ошибка "Пароль должен содержать не более 72 символов"</t>
-  </si>
-  <si>
-    <t>Блокировка ввода пробелов, выходит ошибка "Логин не может содержать пробелы" и уходит через 3с</t>
-  </si>
-  <si>
-    <t>Блокировка ввода пробелов, выходит ошибка "Пароль не может содержать пробелы" и уходит через 3с</t>
-  </si>
-  <si>
-    <t>При выборе в календаре самой старой даты из доступных выходит ошибка недопустимого возраста. Валидация пропускает только +1 день от самой минимальной даты рождения в календаре</t>
-  </si>
-  <si>
-    <t>Ввод через клавиатуру позволяет ввести невалидный возраст, при регистрации выдаёт ошибку "Допустимый возраст 14-120 лет". 
-При выборе даты через кнопку календаря доступен выбор только валидной даты рождения</t>
-  </si>
-  <si>
-    <t>Дата рождения - будущее/старше/младше допустимого. Логин/Пароль валидные</t>
-  </si>
-  <si>
-    <t>Регистрация поочерёдно без одного из обязательных полей, регистрация со всеми пустыми полями</t>
-  </si>
-  <si>
-    <t>Не заполненное поле выделяется красным цветом, ошибка "Все поля должны быть заполнены"</t>
-  </si>
-  <si>
     <t>Форма регистрации пользователя</t>
   </si>
   <si>
-    <t>Ввод логина с кириллицей. ДР/пароль валидные</t>
-  </si>
-  <si>
-    <t>Блокировка ввода кириллицы, выходит ошибка "Ввод доступен только на латинице" и уходит через 3с</t>
-  </si>
-  <si>
-    <t>Строка надёжности пароля не заполнена/заполнена не полностью, при попытке регистрации ошибка "Пароль должен содержать не менее 12 символов"</t>
-  </si>
-  <si>
-    <t>При отсутствии одного из обязательных требований сложности отображается соответствующая ошибка:
-1) Пароль должен содержать как минимум одну заглавную букву; 
-2) Пароль должен содержать как минимум одну цифру;
-3) Пароль должен содержать как минимум один специальный символ</t>
-  </si>
-  <si>
-    <t>Проверка исчезновения сообщения об ошибке через 3 секунды</t>
-  </si>
-  <si>
-    <t>Отображаемое сообщение об ошибке автоматически исчезает через 3 секунды</t>
-  </si>
-  <si>
     <t>Форма Логина пользователя</t>
   </si>
   <si>
-    <t>Открывается окно профиля пользователя</t>
-  </si>
-  <si>
     <t>Ошибка "Неверный логин или пароль", оба поля подсвечиваются красным.</t>
   </si>
   <si>
-    <t>Ошибка "Оба поля должны быть заполнены", не заполненное поле выделяется красным цветом</t>
-  </si>
-  <si>
-    <t>Вход без логина/пароля</t>
-  </si>
-  <si>
-    <t>Ошибка "Оба поля должны быть заполнены", не заполненные поля выделяются красным цветом</t>
-  </si>
-  <si>
-    <t>Кнопка "Глазок" скрывает и показывает введённый пароль</t>
-  </si>
-  <si>
     <t>Переход с окна авторизации в окно регистрации</t>
   </si>
   <si>
@@ -282,119 +167,7 @@
     <t>Переход в окно авторизации совершён</t>
   </si>
   <si>
-    <t>При переключении пароль скрывается под * и обратно</t>
-  </si>
-  <si>
-    <t>Уведомление о включённом CapsLock отображается/исчезает</t>
-  </si>
-  <si>
-    <t>Отображение уведомления о включённом CapsLock под паролем</t>
-  </si>
-  <si>
     <t>Переход в окно регистрации совершён</t>
-  </si>
-  <si>
-    <t>Форма принимает пробелы</t>
-  </si>
-  <si>
-    <t>Форма Профиля пользователя</t>
-  </si>
-  <si>
-    <t>Кнопка "Посмотреть логин и ID"</t>
-  </si>
-  <si>
-    <t>Уведомление о смене "Пароль успешно изменён", поле ввода очищается</t>
-  </si>
-  <si>
-    <t>Ошибка "Вы не внесли изменений"</t>
-  </si>
-  <si>
-    <t>При вводе прежнего пароля выходит уведомление об успешности смены</t>
-  </si>
-  <si>
-    <t>индикатор надёжности пароля</t>
-  </si>
-  <si>
-    <t>при вводе пароля заполняется индикатор надёжности пароля</t>
-  </si>
-  <si>
-    <t>При нажатии отображается ID и логин клиента, исчезает через 3 секунды</t>
-  </si>
-  <si>
-    <t>Окно смены пароля</t>
-  </si>
-  <si>
-    <t>смена пароля на другой валидный пароль</t>
-  </si>
-  <si>
-    <t>смена пароля на невалидный пароль (длина, сложность)</t>
-  </si>
-  <si>
-    <t>смена пароля на прежний пароль</t>
-  </si>
-  <si>
-    <t>Окно детали профиля/изменение деталей профиля (кнопка "Сохранить профиль")</t>
-  </si>
-  <si>
-    <t>Профиль обновляется, уведомление "Изменения сохранены" уходит спустя 3 секунды</t>
-  </si>
-  <si>
-    <t>Поле не принимает символы кроме цифр, при вводе номера недостаточной длины ошибка "Номер телфона должен быть в формате +7(XXX)XXX-XX-XX" появляется и уходит через 3 секунды</t>
-  </si>
-  <si>
-    <t>При вводе цифр и спецсимволов/невалидной длины ошибка "ФИО может состоять только из букв и содержать не более 40 символов"</t>
-  </si>
-  <si>
-    <t>Смена e-mail на невалидный</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Варианты ошибок:
-1) При вводе слишком короткой почты: "Минимальная длина электронной почты — 6 символов"
-2) При вводе слишком длинной почты: "Длина электронной почты должна быть не более 256 символов"
-3) Почта невалидного формата: "Некорректный формат email (пример: a@b.cd)"
-</t>
-  </si>
-  <si>
-    <t>Смена даты рождения</t>
-  </si>
-  <si>
-    <t>Поле даты рождения неактивно, доступ к редактированию запрещён</t>
-  </si>
-  <si>
-    <t>Попытка сохранить профиль без изменений</t>
-  </si>
-  <si>
-    <t>Попытка сохранить профиль с истёкшим токеном</t>
-  </si>
-  <si>
-    <t>Изменения полей профиля без сохранения с последующей перезагрузкой страницы</t>
-  </si>
-  <si>
-    <t>Несохранённые изменения очищаются, поля остаются в исходном состоянии</t>
-  </si>
-  <si>
-    <t>Ошибка "Вы не внесли изменений" появляется и уходит через 3 секунды</t>
-  </si>
-  <si>
-    <t>Пользователя переводят на окно авторизации с ошибкой "Сессия истекла. Пожалуйста, войдите заново". Окна ввода логина и пароля пустые</t>
-  </si>
-  <si>
-    <t>Кнопка Выйти</t>
-  </si>
-  <si>
-    <t>Пользователя возвращает в окно авторизации, поля ввода пустые</t>
-  </si>
-  <si>
-    <t>Очистка всех заполненных опциональных полей</t>
-  </si>
-  <si>
-    <t>Внесённые изменения остаются после Выхода и повторной авторизации, консистенстность данных</t>
-  </si>
-  <si>
-    <t>Опциональные поля очищаются и в последующем остаются доступными для изменений</t>
-  </si>
-  <si>
-    <t>Повторный логин отображает актуальные данные, данные в БД сходятся</t>
   </si>
   <si>
     <t>Регистрация с валидным логином/паролем минимальной длины</t>
@@ -673,6 +446,95 @@
   </si>
   <si>
     <t>Отсутствие поля дедлайна создаёт задачу без дедлайна</t>
+  </si>
+  <si>
+    <t>Форма Создания задачи</t>
+  </si>
+  <si>
+    <t>Переход на страницу с задачами</t>
+  </si>
+  <si>
+    <t>Логин длиной меньше допустимых значений. пароль валидный</t>
+  </si>
+  <si>
+    <t>Логин длиной больше допустимых значений. пароль валидный</t>
+  </si>
+  <si>
+    <t>Ввод логина с кириллицей. пароль валидный</t>
+  </si>
+  <si>
+    <t>Ввод логина с пробелами. пароль валидный</t>
+  </si>
+  <si>
+    <t>Пароль длиннее допустимых значений. Логин валидный</t>
+  </si>
+  <si>
+    <t>Регисрация без пароля</t>
+  </si>
+  <si>
+    <t>Регистрация без логина</t>
+  </si>
+  <si>
+    <t>In-line валидация выдаёт ошибку "Логин должен быть от 3 до 30 символов."</t>
+  </si>
+  <si>
+    <t>In-line валидация выдаёт ошибку "Логин не должен содержать кириллицу."</t>
+  </si>
+  <si>
+    <t>In-line валидация выдаёт ошибку "Логин не должен содержать пробелы."</t>
+  </si>
+  <si>
+    <t>выдаёт ошибку "Такой логин уже существует"</t>
+  </si>
+  <si>
+    <t>In-line валидация выдаёт ошибку "Пароль должен быть от 8 до 32 символов."</t>
+  </si>
+  <si>
+    <t>In-line валидация выдаёт ошибку "Пароль должен содержать хотя бы одну латинскую букву."</t>
+  </si>
+  <si>
+    <t>In-line валидация выдаёт ошибку "Пароль должен содержать хотя бы одну цифру."</t>
+  </si>
+  <si>
+    <t>In-line валидация выдаёт ошибку "Пароль не должен содержать пробелы."</t>
+  </si>
+  <si>
+    <t>Пароль валидной длины только из цифр. Логин валидный</t>
+  </si>
+  <si>
+    <t>Пароль валидной длины только из букв. Логин валидный</t>
+  </si>
+  <si>
+    <t>Пароль валидной длины с кириллицей. Пароль валидный</t>
+  </si>
+  <si>
+    <t>In-line валидация выдаёт ошибку "Пароль не должен содержать кириллицу."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In-line валидация выдаёт ошибку "Логин обязателен."
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In-line валидация выдаёт ошибку "Пароль обязателен."
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Смена темы с светлой на тёмную и наоборот. </t>
+  </si>
+  <si>
+    <t>Тема меняется, поля логина и пароля не очищаются</t>
+  </si>
+  <si>
+    <t>подсветка только формы пароля</t>
+  </si>
+  <si>
+    <t>In-line валидация выдаёт ошибку "Логин обязателен."</t>
+  </si>
+  <si>
+    <t>In-line валидация выдаёт ошибку "Пароль обязателен."</t>
+  </si>
+  <si>
+    <t>In-line валидация выдаёт ошибку "Пароль обязателен." и "Логин обязателен."</t>
   </si>
 </sst>
 </file>
@@ -708,7 +570,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -779,37 +641,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -848,32 +684,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1166,7 +977,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:G58"/>
+  <dimension ref="B2:G49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
@@ -1178,14 +989,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B2" s="26" t="s">
-        <v>68</v>
-      </c>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="28"/>
+      <c r="B2" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="19"/>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
@@ -1204,7 +1015,7 @@
         <v>12</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="2:7" ht="30" x14ac:dyDescent="0.25">
@@ -1212,13 +1023,13 @@
         <v>1</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>55</v>
+        <v>141</v>
       </c>
       <c r="F4" s="11" t="s">
         <v>13</v>
@@ -1230,31 +1041,31 @@
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D5" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="11" t="s">
-        <v>18</v>
-      </c>
       <c r="E5" s="9" t="s">
-        <v>55</v>
+        <v>141</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>13</v>
       </c>
       <c r="G5" s="9"/>
     </row>
-    <row r="6" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="10">
         <v>3</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D6" s="11" t="s">
         <v>1</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>55</v>
+        <v>141</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>13</v>
@@ -1266,13 +1077,13 @@
         <v>4</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>25</v>
+        <v>142</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>56</v>
+        <v>149</v>
       </c>
       <c r="F7" s="11" t="s">
         <v>13</v>
@@ -1284,13 +1095,13 @@
         <v>5</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>26</v>
+        <v>143</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>57</v>
+        <v>149</v>
       </c>
       <c r="F8" s="11" t="s">
         <v>13</v>
@@ -1302,13 +1113,13 @@
         <v>6</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>69</v>
+        <v>144</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="F9" s="11" t="s">
         <v>13</v>
@@ -1320,31 +1131,31 @@
         <v>7</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>58</v>
+        <v>145</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>61</v>
+        <v>151</v>
       </c>
       <c r="F10" s="11" t="s">
         <v>13</v>
       </c>
       <c r="G10" s="11"/>
     </row>
-    <row r="11" spans="2:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B11" s="10">
         <v>8</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>71</v>
+        <v>153</v>
       </c>
       <c r="F11" s="11" t="s">
         <v>13</v>
@@ -1355,14 +1166,14 @@
       <c r="B12" s="10">
         <v>9</v>
       </c>
-      <c r="C12" s="12" t="s">
-        <v>32</v>
+      <c r="C12" s="9" t="s">
+        <v>146</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>59</v>
+        <v>153</v>
       </c>
       <c r="F12" s="11" t="s">
         <v>13</v>
@@ -1373,88 +1184,86 @@
       <c r="B13" s="10">
         <v>10</v>
       </c>
-      <c r="C13" s="9" t="s">
-        <v>22</v>
+      <c r="C13" s="12" t="s">
+        <v>55</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>60</v>
+        <v>152</v>
       </c>
       <c r="F13" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="G13" s="9"/>
+      <c r="G13" s="11"/>
     </row>
     <row r="14" spans="2:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B14" s="10">
         <v>11</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>62</v>
+        <v>156</v>
       </c>
       <c r="F14" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="G14" s="11"/>
-    </row>
-    <row r="15" spans="2:7" ht="105" x14ac:dyDescent="0.25">
+      <c r="G14" s="9"/>
+    </row>
+    <row r="15" spans="2:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B15" s="10">
         <v>12</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>24</v>
+        <v>157</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>72</v>
+        <v>154</v>
       </c>
       <c r="F15" s="11" t="s">
         <v>13</v>
       </c>
       <c r="G15" s="11"/>
     </row>
-    <row r="16" spans="2:7" ht="81.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B16" s="10">
         <v>13</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>65</v>
+        <v>158</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>64</v>
+        <v>155</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="G16" s="9" t="s">
-        <v>63</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="G16" s="11"/>
     </row>
     <row r="17" spans="2:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B17" s="10">
         <v>14</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>66</v>
+        <v>159</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>67</v>
+        <v>160</v>
       </c>
       <c r="F17" s="11" t="s">
         <v>13</v>
@@ -1465,117 +1274,117 @@
       <c r="B18" s="10">
         <v>15</v>
       </c>
-      <c r="C18" s="1" t="s">
-        <v>73</v>
+      <c r="C18" s="9" t="s">
+        <v>148</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>74</v>
+        <v>19</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>161</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="G18" s="1"/>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="G18" s="11"/>
+    </row>
+    <row r="19" spans="2:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B19" s="10">
         <v>16</v>
       </c>
-      <c r="C19" s="13" t="s">
-        <v>83</v>
+      <c r="C19" s="9" t="s">
+        <v>147</v>
       </c>
       <c r="D19" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19" s="11"/>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B20" s="10">
+        <v>17</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="D20" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="E19" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="F19" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="G19" s="1"/>
-    </row>
-    <row r="20" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="E20" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G20" s="11"/>
+    </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B21" s="26" t="s">
-        <v>75</v>
-      </c>
-      <c r="C21" s="27"/>
-      <c r="D21" s="27"/>
-      <c r="E21" s="27"/>
-      <c r="F21" s="27"/>
-      <c r="G21" s="28"/>
-    </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="3" t="s">
+      <c r="B21" s="10">
+        <v>18</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="E21" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G21" s="1"/>
+    </row>
+    <row r="22" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B23" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="C23" s="20"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="20"/>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B24" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C24" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="D24" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E22" s="3" t="s">
+      <c r="E24" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F22" s="3" t="s">
+      <c r="F24" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B23" s="10">
-        <v>1</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G23" s="1"/>
-    </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B24" s="10">
-        <v>2</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G24" s="1"/>
+      <c r="G24" s="3" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B25" s="10">
-        <v>3</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>42</v>
+        <v>1</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>77</v>
+        <v>1</v>
+      </c>
+      <c r="E25" s="9" t="s">
+        <v>141</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>13</v>
@@ -1584,108 +1393,112 @@
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B26" s="10">
-        <v>4</v>
-      </c>
-      <c r="C26" s="14" t="s">
-        <v>39</v>
+        <v>2</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>77</v>
+        <v>44</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G26" s="1"/>
+        <v>14</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>165</v>
+      </c>
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B27" s="10">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>79</v>
+        <v>33</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G27" s="1"/>
+        <v>14</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>165</v>
+      </c>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B28" s="10">
+        <v>4</v>
+      </c>
+      <c r="C28" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B29" s="10">
+        <v>5</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G29" s="1"/>
+    </row>
+    <row r="30" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B30" s="10">
         <v>6</v>
       </c>
-      <c r="C28" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G28" s="1"/>
-    </row>
-    <row r="29" spans="2:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="B29" s="10">
+      <c r="C30" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G30" s="1"/>
+    </row>
+    <row r="31" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="B31" s="10">
         <v>7</v>
       </c>
-      <c r="C29" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E29" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="30" spans="2:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="B30" s="10">
-        <v>8</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E30" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G30" s="1"/>
-    </row>
-    <row r="31" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B31" s="10">
-        <v>9</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>81</v>
+      <c r="C31" s="14" t="s">
+        <v>32</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>85</v>
+        <v>19</v>
+      </c>
+      <c r="E31" s="9" t="s">
+        <v>168</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>13</v>
@@ -1694,67 +1507,67 @@
     </row>
     <row r="32" spans="2:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B32" s="10">
+        <v>8</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E32" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G32" s="1"/>
+    </row>
+    <row r="33" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="B33" s="10">
+        <v>9</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E33" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G33" s="1"/>
+    </row>
+    <row r="34" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B34" s="10">
         <v>10</v>
       </c>
-      <c r="C32" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="D32" s="1" t="s">
+      <c r="C34" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="D34" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E32" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G32" s="1"/>
-    </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B33" s="10">
-        <v>11</v>
-      </c>
-      <c r="C33" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G33" s="1"/>
-    </row>
-    <row r="34" spans="2:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="B34" s="10">
-        <v>12</v>
-      </c>
-      <c r="C34" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="D34" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="E34" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="F34" s="11" t="s">
-        <v>14</v>
+      <c r="E34" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="G34" s="1"/>
     </row>
     <row r="36" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B36" s="20"/>
-      <c r="C36" s="27" t="s">
-        <v>90</v>
-      </c>
-      <c r="D36" s="27"/>
-      <c r="E36" s="27"/>
-      <c r="F36" s="27"/>
-      <c r="G36" s="28"/>
+      <c r="B36" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="C36" s="18"/>
+      <c r="D36" s="18"/>
+      <c r="E36" s="18"/>
+      <c r="F36" s="18"/>
+      <c r="G36" s="19"/>
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B37" s="3" t="s">
@@ -1773,371 +1586,134 @@
         <v>12</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="38" spans="2:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="B38" s="16">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B38" s="10">
         <v>1</v>
       </c>
-      <c r="C38" s="17" t="s">
-        <v>91</v>
-      </c>
-      <c r="D38" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="E38" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="F38" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="G38" s="17"/>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
     </row>
     <row r="39" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B39" s="10"/>
-      <c r="C39" s="22" t="s">
-        <v>98</v>
-      </c>
-      <c r="D39" s="23"/>
-      <c r="E39" s="23"/>
-      <c r="F39" s="23"/>
-      <c r="G39" s="24"/>
-    </row>
-    <row r="40" spans="2:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="B40" s="18">
+      <c r="B39" s="10">
         <v>2</v>
       </c>
-      <c r="C40" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="D40" s="19" t="s">
-        <v>1</v>
-      </c>
-      <c r="E40" s="19" t="s">
-        <v>92</v>
-      </c>
-      <c r="F40" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G40" s="19"/>
-    </row>
-    <row r="41" spans="2:7" ht="105" x14ac:dyDescent="0.25">
+      <c r="C39" s="2"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
+    </row>
+    <row r="40" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B40" s="10">
+        <v>3</v>
+      </c>
+      <c r="C40" s="2"/>
+      <c r="D40" s="1"/>
+      <c r="E40" s="1"/>
+      <c r="F40" s="1"/>
+      <c r="G40" s="1"/>
+    </row>
+    <row r="41" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B41" s="10">
-        <v>3</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E41" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="F41" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G41" s="2"/>
-    </row>
-    <row r="42" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="C41" s="14"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1"/>
+      <c r="G41" s="1"/>
+    </row>
+    <row r="42" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B42" s="10">
-        <v>4</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="F42" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G42" s="2" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="43" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+      <c r="C42" s="2"/>
+      <c r="D42" s="1"/>
+      <c r="E42" s="1"/>
+      <c r="F42" s="1"/>
+      <c r="G42" s="1"/>
+    </row>
+    <row r="43" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B43" s="10">
-        <v>5</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G43" s="2"/>
+        <v>6</v>
+      </c>
+      <c r="C43" s="14"/>
+      <c r="D43" s="1"/>
+      <c r="E43" s="1"/>
+      <c r="F43" s="1"/>
+      <c r="G43" s="1"/>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B44" s="10"/>
-      <c r="C44" s="22" t="s">
-        <v>102</v>
-      </c>
-      <c r="D44" s="23"/>
-      <c r="E44" s="23"/>
-      <c r="F44" s="23"/>
-      <c r="G44" s="24"/>
-    </row>
-    <row r="45" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="B44" s="10">
+        <v>7</v>
+      </c>
+      <c r="C44" s="2"/>
+      <c r="D44" s="1"/>
+      <c r="E44" s="9"/>
+      <c r="F44" s="1"/>
+      <c r="G44" s="1"/>
+    </row>
+    <row r="45" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B45" s="10">
-        <v>6</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="F45" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G45" s="2"/>
-    </row>
-    <row r="46" spans="2:7" ht="120" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="C45" s="2"/>
+      <c r="D45" s="1"/>
+      <c r="E45" s="9"/>
+      <c r="F45" s="1"/>
+      <c r="G45" s="1"/>
+    </row>
+    <row r="46" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B46" s="10">
-        <v>7</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G46" s="2"/>
-    </row>
-    <row r="47" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="C46" s="1"/>
+      <c r="D46" s="1"/>
+      <c r="E46" s="1"/>
+      <c r="F46" s="1"/>
+      <c r="G46" s="1"/>
+    </row>
+    <row r="47" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B47" s="10">
-        <v>8</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="F47" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G47" s="2"/>
-    </row>
-    <row r="48" spans="2:7" ht="45" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="C47" s="14"/>
+      <c r="D47" s="1"/>
+      <c r="E47" s="1"/>
+      <c r="F47" s="1"/>
+      <c r="G47" s="1"/>
+    </row>
+    <row r="48" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B48" s="10">
-        <v>9</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="F48" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G48" s="2"/>
-    </row>
-    <row r="49" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="C48" s="14"/>
+      <c r="D48" s="1"/>
+      <c r="E48" s="1"/>
+      <c r="F48" s="1"/>
+      <c r="G48" s="1"/>
+    </row>
+    <row r="49" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B49" s="10">
-        <v>10</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="F49" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G49" s="2"/>
-    </row>
-    <row r="50" spans="2:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="B50" s="10">
-        <v>11</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="F50" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G50" s="2"/>
-    </row>
-    <row r="51" spans="2:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="B51" s="10">
         <v>12</v>
       </c>
-      <c r="C51" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G51" s="2"/>
-    </row>
-    <row r="52" spans="2:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="B52" s="10">
-        <v>13</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="F52" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G52" s="2"/>
-    </row>
-    <row r="53" spans="2:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="B53" s="10">
-        <v>14</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F53" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G53" s="2"/>
-    </row>
-    <row r="54" spans="2:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="B54" s="10">
-        <v>15</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="F54" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G54" s="2"/>
-    </row>
-    <row r="55" spans="2:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="B55" s="10">
-        <v>16</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="F55" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G55" s="2"/>
-    </row>
-    <row r="56" spans="2:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="B56" s="10">
-        <v>17</v>
-      </c>
-      <c r="C56" s="14" t="s">
-        <v>112</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E56" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="F56" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G56" s="2"/>
-    </row>
-    <row r="57" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B57" s="25"/>
-      <c r="C57" s="25"/>
-      <c r="D57" s="25"/>
-      <c r="E57" s="25"/>
-      <c r="F57" s="25"/>
-      <c r="G57" s="25"/>
-    </row>
-    <row r="58" spans="2:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="B58" s="10">
-        <v>18</v>
-      </c>
-      <c r="C58" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E58" s="14" t="s">
-        <v>117</v>
-      </c>
-      <c r="F58" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G58" s="1"/>
+      <c r="C49" s="15"/>
+      <c r="D49" s="15"/>
+      <c r="E49" s="14"/>
+      <c r="F49" s="11"/>
+      <c r="G49" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="C44:G44"/>
-    <mergeCell ref="B57:G57"/>
+  <mergeCells count="3">
     <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B21:G21"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="B23:G23"/>
+    <mergeCell ref="B36:G36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2148,13 +1724,13 @@
           <x14:formula1>
             <xm:f>'выпад списки'!$B$2:$B$5</xm:f>
           </x14:formula1>
-          <xm:sqref>D4:D19 D23:D34 D38 D40:D43 D45:D56 D58</xm:sqref>
+          <xm:sqref>D4:D21 D38:D49 D25:D34</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'выпад списки'!$F$2:$F$3</xm:f>
           </x14:formula1>
-          <xm:sqref>F4:F19 F23:F34 F38 F40:F43 F58 F45:F56</xm:sqref>
+          <xm:sqref>F38:F49 F4:F21 F25:F34</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -2182,22 +1758,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:14" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="26" t="s">
-        <v>29</v>
-      </c>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="28"/>
-      <c r="I2" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="J2" s="27"/>
-      <c r="K2" s="27"/>
-      <c r="L2" s="27"/>
-      <c r="M2" s="27"/>
-      <c r="N2" s="28"/>
+      <c r="B2" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="19"/>
+      <c r="I2" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2" s="18"/>
+      <c r="K2" s="18"/>
+      <c r="L2" s="18"/>
+      <c r="M2" s="18"/>
+      <c r="N2" s="19"/>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
@@ -2216,7 +1792,7 @@
         <v>12</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>0</v>
@@ -2234,7 +1810,7 @@
         <v>12</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="2:14" ht="45" x14ac:dyDescent="0.25">
@@ -2242,10 +1818,10 @@
         <v>1</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>3</v>
@@ -2254,13 +1830,13 @@
         <v>13</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
       <c r="I4" s="4">
         <v>1</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>132</v>
+        <v>59</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>1</v>
@@ -2272,7 +1848,7 @@
         <v>13</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="2:14" ht="45" x14ac:dyDescent="0.25">
@@ -2280,10 +1856,10 @@
         <v>2</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>123</v>
+        <v>50</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>3</v>
@@ -2292,25 +1868,25 @@
         <v>13</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
       <c r="I5" s="4">
         <v>2</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="L5" t="s">
-        <v>196</v>
+        <v>123</v>
       </c>
       <c r="M5" s="1" t="s">
         <v>13</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="2:14" ht="30" x14ac:dyDescent="0.25">
@@ -2318,7 +1894,7 @@
         <v>3</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>1</v>
@@ -2330,25 +1906,25 @@
         <v>13</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
       <c r="I6" s="4">
         <v>3</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="L6" t="s">
-        <v>196</v>
+        <v>123</v>
       </c>
       <c r="M6" s="1" t="s">
         <v>13</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="2:14" ht="30" x14ac:dyDescent="0.25">
@@ -2356,10 +1932,10 @@
         <v>4</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>124</v>
+        <v>51</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>4</v>
@@ -2368,25 +1944,25 @@
         <v>13</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
       <c r="I7" s="4">
         <v>4</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="M7" s="1" t="s">
         <v>13</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.25">
@@ -2394,10 +1970,10 @@
         <v>5</v>
       </c>
       <c r="C8" t="s">
-        <v>146</v>
+        <v>73</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>4</v>
@@ -2406,16 +1982,16 @@
         <v>13</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
       <c r="I8" s="4">
         <v>5</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="L8" s="1" t="s">
         <v>4</v>
@@ -2424,7 +2000,7 @@
         <v>13</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.25">
@@ -2432,10 +2008,10 @@
         <v>6</v>
       </c>
       <c r="C9" t="s">
-        <v>147</v>
+        <v>74</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>4</v>
@@ -2444,16 +2020,16 @@
         <v>13</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
       <c r="I9" s="4">
         <v>6</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="L9" s="1" t="s">
         <v>4</v>
@@ -2462,7 +2038,7 @@
         <v>13</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.25">
@@ -2470,10 +2046,10 @@
         <v>7</v>
       </c>
       <c r="C10" t="s">
-        <v>148</v>
+        <v>75</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>4</v>
@@ -2482,16 +2058,16 @@
         <v>13</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
       <c r="I10" s="4">
         <v>7</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>154</v>
+        <v>81</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="L10" s="1" t="s">
         <v>4</v>
@@ -2500,7 +2076,7 @@
         <v>13</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11" spans="2:14" ht="30" x14ac:dyDescent="0.25">
@@ -2508,10 +2084,10 @@
         <v>8</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>125</v>
+        <v>52</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>4</v>
@@ -2520,16 +2096,16 @@
         <v>13</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
       <c r="I11" s="4">
         <v>8</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="L11" s="1" t="s">
         <v>4</v>
@@ -2538,7 +2114,7 @@
         <v>13</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12" spans="2:14" ht="30" x14ac:dyDescent="0.25">
@@ -2546,10 +2122,10 @@
         <v>9</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>127</v>
+        <v>54</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>4</v>
@@ -2558,16 +2134,16 @@
         <v>13</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
       <c r="I12" s="4">
         <v>9</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="L12" s="1" t="s">
         <v>4</v>
@@ -2576,7 +2152,7 @@
         <v>13</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13" spans="2:14" ht="30" x14ac:dyDescent="0.25">
@@ -2584,10 +2160,10 @@
         <v>10</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>149</v>
+        <v>76</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>4</v>
@@ -2596,16 +2172,16 @@
         <v>13</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
       <c r="I13" s="4">
         <v>10</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="L13" s="1" t="s">
         <v>4</v>
@@ -2614,7 +2190,7 @@
         <v>13</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14" spans="2:14" ht="30" x14ac:dyDescent="0.25">
@@ -2622,10 +2198,10 @@
         <v>11</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>126</v>
+        <v>53</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>4</v>
@@ -2634,16 +2210,16 @@
         <v>13</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
       <c r="I14" s="4">
         <v>11</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="L14" s="1" t="s">
         <v>4</v>
@@ -2652,7 +2228,7 @@
         <v>13</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" spans="2:14" ht="30" x14ac:dyDescent="0.25">
@@ -2660,28 +2236,28 @@
         <v>12</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>128</v>
+        <v>55</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
       <c r="I15" s="4">
         <v>12</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="L15" s="1" t="s">
         <v>2</v>
@@ -2690,7 +2266,7 @@
         <v>13</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
     </row>
     <row r="16" spans="2:14" ht="30" x14ac:dyDescent="0.25">
@@ -2698,10 +2274,10 @@
         <v>13</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>129</v>
+        <v>56</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>4</v>
@@ -2710,7 +2286,7 @@
         <v>13</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
     </row>
     <row r="17" spans="2:14" ht="30" x14ac:dyDescent="0.25">
@@ -2718,10 +2294,10 @@
         <v>14</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>130</v>
+        <v>57</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>4</v>
@@ -2730,26 +2306,26 @@
         <v>13</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="I17" s="26" t="s">
-        <v>198</v>
-      </c>
-      <c r="J17" s="27"/>
-      <c r="K17" s="27"/>
-      <c r="L17" s="27"/>
-      <c r="M17" s="27"/>
-      <c r="N17" s="28"/>
+        <v>58</v>
+      </c>
+      <c r="I17" s="17" t="s">
+        <v>125</v>
+      </c>
+      <c r="J17" s="18"/>
+      <c r="K17" s="18"/>
+      <c r="L17" s="18"/>
+      <c r="M17" s="18"/>
+      <c r="N17" s="19"/>
     </row>
     <row r="18" spans="2:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B18" s="4">
         <v>15</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>153</v>
+        <v>80</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>4</v>
@@ -2758,7 +2334,7 @@
         <v>13</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>0</v>
@@ -2776,7 +2352,7 @@
         <v>12</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19" spans="2:14" ht="30" x14ac:dyDescent="0.25">
@@ -2784,10 +2360,10 @@
         <v>16</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>152</v>
+        <v>79</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>4</v>
@@ -2796,13 +2372,13 @@
         <v>13</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
       <c r="I19" s="4">
         <v>1</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>203</v>
+        <v>130</v>
       </c>
       <c r="K19" s="1" t="s">
         <v>1</v>
@@ -2814,7 +2390,7 @@
         <v>13</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.25">
@@ -2822,10 +2398,10 @@
         <v>17</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>150</v>
+        <v>77</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>4</v>
@@ -2834,16 +2410,16 @@
         <v>13</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
       <c r="I20" s="4">
         <v>2</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>199</v>
+        <v>126</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="L20" s="1" t="s">
         <v>4</v>
@@ -2852,7 +2428,7 @@
         <v>13</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.25">
@@ -2860,10 +2436,10 @@
         <v>18</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>151</v>
+        <v>78</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>4</v>
@@ -2872,16 +2448,16 @@
         <v>13</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
       <c r="I21" s="4">
         <v>3</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>208</v>
+        <v>135</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="L21" s="1" t="s">
         <v>4</v>
@@ -2890,7 +2466,7 @@
         <v>13</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.25">
@@ -2898,10 +2474,10 @@
         <v>4</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>175</v>
+        <v>102</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="L22" s="1" t="s">
         <v>4</v>
@@ -2910,7 +2486,7 @@
         <v>13</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.25">
@@ -2918,10 +2494,10 @@
         <v>5</v>
       </c>
       <c r="J23" s="14" t="s">
-        <v>180</v>
+        <v>107</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="L23" s="1" t="s">
         <v>4</v>
@@ -2930,26 +2506,26 @@
         <v>13</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
     </row>
     <row r="24" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B24" s="29" t="s">
-        <v>158</v>
-      </c>
-      <c r="C24" s="29"/>
-      <c r="D24" s="29"/>
-      <c r="E24" s="29"/>
-      <c r="F24" s="29"/>
-      <c r="G24" s="29"/>
+      <c r="B24" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="C24" s="20"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="20"/>
+      <c r="G24" s="20"/>
       <c r="I24" s="4">
         <v>6</v>
       </c>
       <c r="J24" s="14" t="s">
-        <v>210</v>
+        <v>137</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L24" s="1" t="s">
         <v>3</v>
@@ -2958,7 +2534,7 @@
         <v>13</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
     </row>
     <row r="25" spans="2:14" ht="30" x14ac:dyDescent="0.25">
@@ -2978,16 +2554,16 @@
         <v>12</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I25" s="4">
         <v>7</v>
       </c>
       <c r="J25" s="14" t="s">
-        <v>195</v>
+        <v>122</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L25" s="1" t="s">
         <v>3</v>
@@ -2996,7 +2572,7 @@
         <v>13</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
     </row>
     <row r="26" spans="2:14" ht="30" x14ac:dyDescent="0.25">
@@ -3004,7 +2580,7 @@
         <v>1</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>156</v>
+        <v>83</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>1</v>
@@ -3016,13 +2592,13 @@
         <v>13</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
       <c r="I26" s="4">
         <v>8</v>
       </c>
       <c r="J26" s="14" t="s">
-        <v>183</v>
+        <v>110</v>
       </c>
       <c r="K26" s="1" t="s">
         <v>1</v>
@@ -3034,7 +2610,7 @@
         <v>13</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
     </row>
     <row r="27" spans="2:14" ht="30" x14ac:dyDescent="0.25">
@@ -3042,7 +2618,7 @@
         <v>2</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>133</v>
+        <v>60</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>1</v>
@@ -3054,16 +2630,16 @@
         <v>13</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
       <c r="I27" s="4">
         <v>9</v>
       </c>
       <c r="J27" s="14" t="s">
-        <v>184</v>
+        <v>111</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="L27" s="1" t="s">
         <v>4</v>
@@ -3072,7 +2648,7 @@
         <v>13</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.25">
@@ -3080,28 +2656,28 @@
         <v>3</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E28" t="s">
-        <v>196</v>
+        <v>123</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
       <c r="I28" s="4">
         <v>10</v>
       </c>
       <c r="J28" s="14" t="s">
-        <v>185</v>
+        <v>112</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L28" s="1" t="s">
         <v>3</v>
@@ -3110,7 +2686,7 @@
         <v>13</v>
       </c>
       <c r="N28" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
     </row>
     <row r="29" spans="2:14" ht="30" x14ac:dyDescent="0.25">
@@ -3118,28 +2694,28 @@
         <v>4</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E29" t="s">
-        <v>196</v>
+        <v>123</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
       <c r="I29" s="4">
         <v>11</v>
       </c>
       <c r="J29" s="14" t="s">
-        <v>186</v>
-      </c>
-      <c r="K29" s="21" t="s">
-        <v>18</v>
+        <v>113</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>16</v>
       </c>
       <c r="L29" s="1" t="s">
         <v>3</v>
@@ -3148,7 +2724,7 @@
         <v>13</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
     </row>
     <row r="30" spans="2:14" x14ac:dyDescent="0.25">
@@ -3156,28 +2732,28 @@
         <v>5</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E30" t="s">
-        <v>196</v>
+        <v>123</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
       <c r="I30" s="4">
         <v>12</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>200</v>
+        <v>127</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="L30" s="1" t="s">
         <v>4</v>
@@ -3186,7 +2762,7 @@
         <v>13</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
     </row>
     <row r="31" spans="2:14" ht="30" x14ac:dyDescent="0.25">
@@ -3194,25 +2770,25 @@
         <v>6</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E31" t="s">
-        <v>196</v>
+        <v>123</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
       <c r="I31" s="4">
         <v>13</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>201</v>
+        <v>128</v>
       </c>
       <c r="K31" s="1" t="s">
         <v>1</v>
@@ -3224,7 +2800,7 @@
         <v>13</v>
       </c>
       <c r="N31" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.25">
@@ -3232,37 +2808,37 @@
         <v>7</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>134</v>
-      </c>
-      <c r="D32" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="D32" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="E32" s="21" t="s">
+      <c r="E32" s="16" t="s">
         <v>2</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
       <c r="I32" s="4">
         <v>14</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="K32" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="L32" s="21" t="s">
+        <v>100</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="L32" s="16" t="s">
         <v>4</v>
       </c>
       <c r="M32" s="1" t="s">
         <v>13</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
     </row>
     <row r="33" spans="2:14" x14ac:dyDescent="0.25">
@@ -3270,37 +2846,37 @@
         <v>8</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>157</v>
-      </c>
-      <c r="D33" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="E33" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="D33" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="E33" s="16" t="s">
         <v>5</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
       <c r="I33" s="4">
         <v>15</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="K33" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="L33" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="L33" s="16" t="s">
         <v>4</v>
       </c>
       <c r="M33" s="1" t="s">
         <v>13</v>
       </c>
       <c r="N33" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
     </row>
     <row r="34" spans="2:14" ht="30" x14ac:dyDescent="0.25">
@@ -3308,25 +2884,25 @@
         <v>9</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>135</v>
-      </c>
-      <c r="D34" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="E34" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="D34" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="E34" s="16" t="s">
         <v>8</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
       <c r="I34" s="4">
         <v>16</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>202</v>
+        <v>129</v>
       </c>
       <c r="K34" s="1" t="s">
         <v>1</v>
@@ -3338,7 +2914,7 @@
         <v>13</v>
       </c>
       <c r="N34" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
     </row>
     <row r="35" spans="2:14" ht="30" x14ac:dyDescent="0.25">
@@ -3346,25 +2922,25 @@
         <v>10</v>
       </c>
       <c r="C35" s="14" t="s">
-        <v>139</v>
-      </c>
-      <c r="D35" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="D35" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="E35" s="21" t="s">
+      <c r="E35" s="16" t="s">
         <v>2</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
       <c r="I35" s="4">
         <v>17</v>
       </c>
       <c r="J35" s="14" t="s">
-        <v>212</v>
+        <v>139</v>
       </c>
       <c r="K35" s="1" t="s">
         <v>1</v>
@@ -3376,7 +2952,7 @@
         <v>13</v>
       </c>
       <c r="N35" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
     </row>
     <row r="36" spans="2:14" ht="30" x14ac:dyDescent="0.25">
@@ -3384,37 +2960,37 @@
         <v>11</v>
       </c>
       <c r="C36" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="D36" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="E36" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="D36" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="E36" s="16" t="s">
         <v>4</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
       <c r="I36" s="4">
         <v>18</v>
       </c>
       <c r="J36" s="14" t="s">
-        <v>192</v>
-      </c>
-      <c r="K36" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="L36" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="K36" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="L36" s="16" t="s">
         <v>4</v>
       </c>
       <c r="M36" s="1" t="s">
         <v>13</v>
       </c>
       <c r="N36" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
     </row>
     <row r="37" spans="2:14" ht="90" x14ac:dyDescent="0.25">
@@ -3422,25 +2998,25 @@
         <v>12</v>
       </c>
       <c r="C37" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="D37" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="D37" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="E37" s="21" t="s">
+      <c r="E37" s="16" t="s">
         <v>2</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
       <c r="I37" s="4">
         <v>19</v>
       </c>
       <c r="J37" s="14" t="s">
-        <v>209</v>
+        <v>136</v>
       </c>
       <c r="K37" s="1" t="s">
         <v>1</v>
@@ -3452,7 +3028,7 @@
         <v>13</v>
       </c>
       <c r="N37" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
     </row>
     <row r="38" spans="2:14" ht="45" x14ac:dyDescent="0.25">
@@ -3460,37 +3036,37 @@
         <v>13</v>
       </c>
       <c r="C38" s="14" t="s">
-        <v>137</v>
-      </c>
-      <c r="D38" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="D38" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="E38" s="21" t="s">
+      <c r="E38" s="16" t="s">
         <v>2</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
       <c r="I38" s="4">
         <v>20</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="K38" s="21" t="s">
-        <v>27</v>
+        <v>131</v>
+      </c>
+      <c r="K38" s="16" t="s">
+        <v>19</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>196</v>
+        <v>123</v>
       </c>
       <c r="M38" s="1" t="s">
         <v>13</v>
       </c>
       <c r="N38" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
     </row>
     <row r="39" spans="2:14" ht="30" x14ac:dyDescent="0.25">
@@ -3504,19 +3080,19 @@
         <v>21</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="K39" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="L39" s="21" t="s">
-        <v>145</v>
+        <v>132</v>
+      </c>
+      <c r="K39" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="L39" s="16" t="s">
+        <v>72</v>
       </c>
       <c r="M39" s="1" t="s">
         <v>13</v>
       </c>
       <c r="N39" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
     </row>
     <row r="40" spans="2:14" ht="30" x14ac:dyDescent="0.25">
@@ -3524,19 +3100,19 @@
         <v>22</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="K40" s="21" t="s">
-        <v>27</v>
+        <v>133</v>
+      </c>
+      <c r="K40" s="16" t="s">
+        <v>19</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>196</v>
+        <v>123</v>
       </c>
       <c r="M40" s="1" t="s">
         <v>13</v>
       </c>
       <c r="N40" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
     </row>
     <row r="41" spans="2:14" x14ac:dyDescent="0.25">
@@ -3544,36 +3120,38 @@
         <v>23</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="K41" s="21" t="s">
-        <v>27</v>
+        <v>134</v>
+      </c>
+      <c r="K41" s="16" t="s">
+        <v>19</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>196</v>
+        <v>123</v>
       </c>
       <c r="M41" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="N41" s="1"/>
+      <c r="N41" s="1" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B45" s="29" t="s">
-        <v>170</v>
-      </c>
-      <c r="C45" s="29"/>
-      <c r="D45" s="29"/>
-      <c r="E45" s="29"/>
-      <c r="F45" s="29"/>
-      <c r="G45" s="29"/>
-      <c r="I45" s="26" t="s">
-        <v>159</v>
-      </c>
-      <c r="J45" s="27"/>
-      <c r="K45" s="27"/>
-      <c r="L45" s="27"/>
-      <c r="M45" s="27"/>
-      <c r="N45" s="28"/>
+      <c r="B45" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="C45" s="20"/>
+      <c r="D45" s="20"/>
+      <c r="E45" s="20"/>
+      <c r="F45" s="20"/>
+      <c r="G45" s="20"/>
+      <c r="I45" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="J45" s="18"/>
+      <c r="K45" s="18"/>
+      <c r="L45" s="18"/>
+      <c r="M45" s="18"/>
+      <c r="N45" s="19"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B46" s="3" t="s">
@@ -3592,7 +3170,7 @@
         <v>12</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I46" s="3" t="s">
         <v>0</v>
@@ -3610,7 +3188,7 @@
         <v>12</v>
       </c>
       <c r="N46" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="47" spans="2:14" ht="30" x14ac:dyDescent="0.25">
@@ -3618,7 +3196,7 @@
         <v>1</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>171</v>
+        <v>98</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>1</v>
@@ -3630,25 +3208,25 @@
         <v>13</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
       <c r="I47" s="4">
         <v>1</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>140</v>
+        <v>67</v>
       </c>
       <c r="K47" s="1" t="s">
         <v>1</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>144</v>
+        <v>71</v>
       </c>
       <c r="M47" s="1" t="s">
         <v>13</v>
       </c>
       <c r="N47" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
     </row>
     <row r="48" spans="2:14" x14ac:dyDescent="0.25">
@@ -3656,10 +3234,10 @@
         <v>2</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>175</v>
+        <v>102</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>4</v>
@@ -3668,16 +3246,16 @@
         <v>13</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
       <c r="I48" s="4">
         <v>2</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>141</v>
+        <v>68</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="L48" s="1" t="s">
         <v>5</v>
@@ -3686,7 +3264,7 @@
         <v>13</v>
       </c>
       <c r="N48" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
     </row>
     <row r="49" spans="2:14" x14ac:dyDescent="0.25">
@@ -3694,10 +3272,10 @@
         <v>3</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>172</v>
+        <v>99</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>4</v>
@@ -3706,25 +3284,25 @@
         <v>13</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
       <c r="I49" s="4">
         <v>3</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>160</v>
+        <v>87</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="L49" t="s">
-        <v>196</v>
+        <v>123</v>
       </c>
       <c r="M49" s="1" t="s">
         <v>13</v>
       </c>
       <c r="N49" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="30" x14ac:dyDescent="0.25">
@@ -3732,10 +3310,10 @@
         <v>4</v>
       </c>
       <c r="C50" s="14" t="s">
-        <v>180</v>
+        <v>107</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>4</v>
@@ -3744,25 +3322,25 @@
         <v>13</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
       <c r="I50" s="4">
         <v>4</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>145</v>
+        <v>72</v>
       </c>
       <c r="M50" s="1" t="s">
         <v>13</v>
       </c>
       <c r="N50" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
     </row>
     <row r="51" spans="2:14" ht="30" x14ac:dyDescent="0.25">
@@ -3770,10 +3348,10 @@
         <v>5</v>
       </c>
       <c r="C51" s="14" t="s">
-        <v>181</v>
+        <v>108</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>2</v>
@@ -3782,25 +3360,25 @@
         <v>13</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
       <c r="I51" s="4">
         <v>5</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="L51" t="s">
-        <v>196</v>
+        <v>123</v>
       </c>
       <c r="M51" s="1" t="s">
         <v>13</v>
       </c>
       <c r="N51" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
     </row>
     <row r="52" spans="2:14" ht="30" x14ac:dyDescent="0.25">
@@ -3808,10 +3386,10 @@
         <v>6</v>
       </c>
       <c r="C52" s="14" t="s">
-        <v>195</v>
+        <v>122</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>2</v>
@@ -3820,16 +3398,16 @@
         <v>13</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
       <c r="I52" s="4">
         <v>6</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>142</v>
+        <v>69</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="L52" s="1" t="s">
         <v>8</v>
@@ -3838,7 +3416,7 @@
         <v>13</v>
       </c>
       <c r="N52" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
     </row>
     <row r="53" spans="2:14" ht="30" x14ac:dyDescent="0.25">
@@ -3846,7 +3424,7 @@
         <v>7</v>
       </c>
       <c r="C53" s="14" t="s">
-        <v>197</v>
+        <v>124</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>1</v>
@@ -3858,16 +3436,16 @@
         <v>13</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
       <c r="I53" s="4">
         <v>7</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>143</v>
+        <v>70</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="L53" s="1" t="s">
         <v>8</v>
@@ -3876,7 +3454,7 @@
         <v>13</v>
       </c>
       <c r="N53" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
     </row>
     <row r="54" spans="2:14" x14ac:dyDescent="0.25">
@@ -3884,7 +3462,7 @@
         <v>8</v>
       </c>
       <c r="C54" s="14" t="s">
-        <v>182</v>
+        <v>109</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>1</v>
@@ -3896,7 +3474,7 @@
         <v>13</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
       <c r="I54" s="6"/>
       <c r="J54" s="7"/>
@@ -3910,7 +3488,7 @@
         <v>9</v>
       </c>
       <c r="C55" s="14" t="s">
-        <v>183</v>
+        <v>110</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>1</v>
@@ -3922,7 +3500,7 @@
         <v>13</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
     </row>
     <row r="56" spans="2:14" x14ac:dyDescent="0.25">
@@ -3930,10 +3508,10 @@
         <v>10</v>
       </c>
       <c r="C56" s="14" t="s">
-        <v>184</v>
+        <v>111</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>4</v>
@@ -3942,7 +3520,7 @@
         <v>13</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
       <c r="H56" s="8"/>
     </row>
@@ -3951,10 +3529,10 @@
         <v>11</v>
       </c>
       <c r="C57" s="14" t="s">
-        <v>185</v>
+        <v>112</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>2</v>
@@ -3963,7 +3541,7 @@
         <v>13</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
       <c r="H57" s="8"/>
     </row>
@@ -3972,19 +3550,19 @@
         <v>12</v>
       </c>
       <c r="C58" s="14" t="s">
-        <v>186</v>
-      </c>
-      <c r="D58" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="E58" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="D58" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="E58" s="16" t="s">
         <v>2</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
       <c r="H58" s="8"/>
     </row>
@@ -3993,19 +3571,19 @@
         <v>13</v>
       </c>
       <c r="C59" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="D59" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="D59" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="E59" s="21" t="s">
+      <c r="E59" s="16" t="s">
         <v>2</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
       <c r="H59" s="8"/>
     </row>
@@ -4014,48 +3592,48 @@
         <v>14</v>
       </c>
       <c r="C60" s="14" t="s">
-        <v>188</v>
-      </c>
-      <c r="D60" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="E60" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="D60" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="E60" s="16" t="s">
         <v>4</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
       <c r="H60" s="8"/>
-      <c r="I60" s="26" t="s">
-        <v>167</v>
-      </c>
-      <c r="J60" s="27"/>
-      <c r="K60" s="27"/>
-      <c r="L60" s="27"/>
-      <c r="M60" s="27"/>
-      <c r="N60" s="28"/>
+      <c r="I60" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="J60" s="18"/>
+      <c r="K60" s="18"/>
+      <c r="L60" s="18"/>
+      <c r="M60" s="18"/>
+      <c r="N60" s="19"/>
     </row>
     <row r="61" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B61" s="4">
         <v>15</v>
       </c>
       <c r="C61" s="14" t="s">
-        <v>189</v>
-      </c>
-      <c r="D61" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="E61" s="21" t="s">
+        <v>116</v>
+      </c>
+      <c r="D61" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="E61" s="16" t="s">
         <v>4</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
       <c r="H61" s="8"/>
       <c r="I61" s="3" t="s">
@@ -4074,7 +3652,7 @@
         <v>12</v>
       </c>
       <c r="N61" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="62" spans="2:14" x14ac:dyDescent="0.25">
@@ -4082,25 +3660,25 @@
         <v>16</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="D62" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="E62" s="21" t="s">
+        <v>100</v>
+      </c>
+      <c r="D62" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="E62" s="16" t="s">
         <v>4</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
       <c r="I62" s="4">
         <v>1</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>161</v>
+        <v>88</v>
       </c>
       <c r="K62" s="1" t="s">
         <v>1</v>
@@ -4112,7 +3690,7 @@
         <v>13</v>
       </c>
       <c r="N62" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
     </row>
     <row r="63" spans="2:14" x14ac:dyDescent="0.25">
@@ -4120,25 +3698,25 @@
         <v>17</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="D63" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="E63" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="D63" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="E63" s="16" t="s">
         <v>4</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
       <c r="I63" s="4">
         <v>2</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>162</v>
+        <v>89</v>
       </c>
       <c r="K63" s="1" t="s">
         <v>1</v>
@@ -4150,7 +3728,7 @@
         <v>13</v>
       </c>
       <c r="N63" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
     </row>
     <row r="64" spans="2:14" x14ac:dyDescent="0.25">
@@ -4158,28 +3736,28 @@
         <v>18</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="D64" s="21" t="s">
+        <v>101</v>
+      </c>
+      <c r="D64" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="E64" s="21" t="s">
+      <c r="E64" s="16" t="s">
         <v>2</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
       <c r="I64" s="4">
         <v>3</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>163</v>
+        <v>90</v>
       </c>
       <c r="K64" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="L64" s="1" t="s">
         <v>5</v>
@@ -4188,7 +3766,7 @@
         <v>13</v>
       </c>
       <c r="N64" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
     </row>
     <row r="65" spans="2:14" x14ac:dyDescent="0.25">
@@ -4196,37 +3774,37 @@
         <v>19</v>
       </c>
       <c r="C65" s="14" t="s">
-        <v>192</v>
-      </c>
-      <c r="D65" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="E65" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="D65" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="E65" s="16" t="s">
         <v>4</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
       <c r="I65" s="4">
         <v>4</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>160</v>
+        <v>87</v>
       </c>
       <c r="K65" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="L65" t="s">
-        <v>196</v>
+        <v>123</v>
       </c>
       <c r="M65" s="1" t="s">
         <v>13</v>
       </c>
       <c r="N65" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
     </row>
     <row r="66" spans="2:14" ht="75" x14ac:dyDescent="0.25">
@@ -4234,37 +3812,37 @@
         <v>20</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="D66" s="21" t="s">
+        <v>120</v>
+      </c>
+      <c r="D66" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="E66" s="21" t="s">
+      <c r="E66" s="16" t="s">
         <v>2</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
       <c r="I66" s="4">
         <v>5</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="K66" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="L66" t="s">
-        <v>196</v>
+        <v>123</v>
       </c>
       <c r="M66" s="1" t="s">
         <v>13</v>
       </c>
       <c r="N66" s="2" t="s">
-        <v>211</v>
+        <v>138</v>
       </c>
     </row>
     <row r="67" spans="2:14" ht="30" x14ac:dyDescent="0.25">
@@ -4272,37 +3850,37 @@
         <v>21</v>
       </c>
       <c r="C67" s="14" t="s">
-        <v>176</v>
-      </c>
-      <c r="D67" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="D67" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="E67" s="21" t="s">
+      <c r="E67" s="16" t="s">
         <v>2</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
       <c r="I67" s="4">
         <v>6</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="K67" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="L67" t="s">
-        <v>196</v>
+        <v>123</v>
       </c>
       <c r="M67" s="1" t="s">
         <v>13</v>
       </c>
       <c r="N67" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
     </row>
     <row r="68" spans="2:14" ht="30" x14ac:dyDescent="0.25">
@@ -4310,25 +3888,25 @@
         <v>22</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="D68" s="21" t="s">
-        <v>27</v>
+        <v>104</v>
+      </c>
+      <c r="D68" s="16" t="s">
+        <v>19</v>
       </c>
       <c r="E68" t="s">
-        <v>196</v>
+        <v>123</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
       <c r="I68" s="4">
         <v>7</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>164</v>
+        <v>91</v>
       </c>
       <c r="K68" s="1" t="s">
         <v>1</v>
@@ -4340,7 +3918,7 @@
         <v>13</v>
       </c>
       <c r="N68" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
     </row>
     <row r="69" spans="2:14" x14ac:dyDescent="0.25">
@@ -4348,28 +3926,28 @@
         <v>23</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="D69" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="E69" s="21" t="s">
-        <v>145</v>
+        <v>105</v>
+      </c>
+      <c r="D69" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="E69" s="16" t="s">
+        <v>72</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
       <c r="I69" s="4">
         <v>8</v>
       </c>
       <c r="J69" s="5" t="s">
-        <v>165</v>
+        <v>92</v>
       </c>
       <c r="K69" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="L69" s="1" t="s">
         <v>4</v>
@@ -4378,7 +3956,7 @@
         <v>13</v>
       </c>
       <c r="N69" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
     </row>
     <row r="70" spans="2:14" ht="30" x14ac:dyDescent="0.25">
@@ -4386,28 +3964,28 @@
         <v>24</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="D70" s="21" t="s">
-        <v>27</v>
+        <v>106</v>
+      </c>
+      <c r="D70" s="16" t="s">
+        <v>19</v>
       </c>
       <c r="E70" t="s">
-        <v>196</v>
+        <v>123</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
       <c r="I70" s="4">
         <v>9</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>166</v>
+        <v>93</v>
       </c>
       <c r="K70" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="L70" s="1" t="s">
         <v>8</v>
@@ -4416,7 +3994,7 @@
         <v>13</v>
       </c>
       <c r="N70" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
     </row>
     <row r="71" spans="2:14" x14ac:dyDescent="0.25">
@@ -4424,28 +4002,28 @@
         <v>25</v>
       </c>
       <c r="C71" s="14" t="s">
-        <v>194</v>
-      </c>
-      <c r="D71" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="E71" s="21" t="s">
+        <v>121</v>
+      </c>
+      <c r="D71" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="E71" s="16" t="s">
         <v>5</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
       <c r="I71" s="4">
         <v>10</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>168</v>
+        <v>95</v>
       </c>
       <c r="K71" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="L71" s="1" t="s">
         <v>4</v>
@@ -4454,7 +4032,7 @@
         <v>13</v>
       </c>
       <c r="N71" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
     </row>
     <row r="72" spans="2:14" x14ac:dyDescent="0.25">
@@ -4462,28 +4040,28 @@
         <v>26</v>
       </c>
       <c r="C72" s="14" t="s">
-        <v>190</v>
-      </c>
-      <c r="D72" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="E72" s="21" t="s">
+        <v>117</v>
+      </c>
+      <c r="D72" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="E72" s="16" t="s">
         <v>8</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
       <c r="I72" s="4">
         <v>11</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>169</v>
+        <v>96</v>
       </c>
       <c r="K72" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="L72" s="1" t="s">
         <v>4</v>
@@ -4492,7 +4070,7 @@
         <v>13</v>
       </c>
       <c r="N72" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -4574,7 +4152,7 @@
         <v>12</v>
       </c>
       <c r="H1" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="2:8" x14ac:dyDescent="0.25">
@@ -4588,12 +4166,12 @@
         <v>13</v>
       </c>
       <c r="H2" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
         <v>3</v>
@@ -4604,15 +4182,15 @@
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D4" t="s">
-        <v>144</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D5" t="s">
         <v>4</v>
@@ -4620,7 +4198,7 @@
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D6" t="s">
-        <v>196</v>
+        <v>123</v>
       </c>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.25">
@@ -4635,17 +4213,17 @@
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D9" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D10" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D11" t="s">
-        <v>145</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>

--- a/Check-lists.xlsx
+++ b/Check-lists.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="756" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="767" uniqueCount="166">
   <si>
     <t>№ проверки</t>
   </si>
@@ -511,21 +511,10 @@
     <t>In-line валидация выдаёт ошибку "Пароль не должен содержать кириллицу."</t>
   </si>
   <si>
-    <t xml:space="preserve">In-line валидация выдаёт ошибку "Логин обязателен."
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">In-line валидация выдаёт ошибку "Пароль обязателен."
-</t>
-  </si>
-  <si>
     <t xml:space="preserve">Смена темы с светлой на тёмную и наоборот. </t>
   </si>
   <si>
     <t>Тема меняется, поля логина и пароля не очищаются</t>
-  </si>
-  <si>
-    <t>подсветка только формы пароля</t>
   </si>
   <si>
     <t>In-line валидация выдаёт ошибку "Логин обязателен."</t>
@@ -977,7 +966,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:G49"/>
+  <dimension ref="B2:G50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
@@ -1034,7 +1023,9 @@
       <c r="F4" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="11"/>
+      <c r="G4" s="11" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="5" spans="2:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B5" s="10">
@@ -1052,7 +1043,9 @@
       <c r="F5" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="G5" s="9"/>
+      <c r="G5" s="11" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="10">
@@ -1070,7 +1063,9 @@
       <c r="F6" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="G6" s="11"/>
+      <c r="G6" s="11" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="7" spans="2:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B7" s="10">
@@ -1088,7 +1083,9 @@
       <c r="F7" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="G7" s="11"/>
+      <c r="G7" s="11" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="8" spans="2:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B8" s="10">
@@ -1106,7 +1103,9 @@
       <c r="F8" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="G8" s="11"/>
+      <c r="G8" s="11" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="9" spans="2:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B9" s="10">
@@ -1124,7 +1123,9 @@
       <c r="F9" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="G9" s="11"/>
+      <c r="G9" s="11" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="10" spans="2:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B10" s="10">
@@ -1142,7 +1143,9 @@
       <c r="F10" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="G10" s="11"/>
+      <c r="G10" s="11" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="11" spans="2:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B11" s="10">
@@ -1196,7 +1199,9 @@
       <c r="F13" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="G13" s="11"/>
+      <c r="G13" s="11" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="14" spans="2:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B14" s="10">
@@ -1270,7 +1275,7 @@
       </c>
       <c r="G17" s="11"/>
     </row>
-    <row r="18" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B18" s="10">
         <v>15</v>
       </c>
@@ -1281,14 +1286,16 @@
         <v>19</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F18" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="G18" s="11"/>
-    </row>
-    <row r="19" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="G18" s="11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="10">
         <v>16</v>
       </c>
@@ -1299,12 +1306,14 @@
         <v>19</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F19" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="G19" s="11"/>
+      <c r="G19" s="11" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B20" s="10">
@@ -1329,13 +1338,13 @@
         <v>18</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D21" s="11" t="s">
         <v>1</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F21" s="11" t="s">
         <v>13</v>
@@ -1405,11 +1414,9 @@
         <v>44</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>165</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="G26" s="1"/>
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B27" s="10">
@@ -1425,11 +1432,9 @@
         <v>44</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>165</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="G27" s="1"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B28" s="10">
@@ -1445,11 +1450,9 @@
         <v>44</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>165</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="G28" s="1"/>
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B29" s="10">
@@ -1462,7 +1465,7 @@
         <v>19</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>13</v>
@@ -1480,7 +1483,7 @@
         <v>19</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>13</v>
@@ -1498,7 +1501,7 @@
         <v>19</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>13</v>
@@ -1559,51 +1562,59 @@
       </c>
       <c r="G34" s="1"/>
     </row>
-    <row r="36" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B36" s="17" t="s">
+    <row r="35" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B35" s="10">
+        <v>11</v>
+      </c>
+      <c r="C35" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="D35" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="E35" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="F35" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G35" s="1"/>
+    </row>
+    <row r="37" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B37" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="C36" s="18"/>
-      <c r="D36" s="18"/>
-      <c r="E36" s="18"/>
-      <c r="F36" s="18"/>
-      <c r="G36" s="19"/>
-    </row>
-    <row r="37" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B37" s="3" t="s">
+      <c r="C37" s="18"/>
+      <c r="D37" s="18"/>
+      <c r="E37" s="18"/>
+      <c r="F37" s="18"/>
+      <c r="G37" s="19"/>
+    </row>
+    <row r="38" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B38" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="C38" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D37" s="3" t="s">
+      <c r="D38" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E37" s="3" t="s">
+      <c r="E38" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F37" s="3" t="s">
+      <c r="F38" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G37" s="3" t="s">
+      <c r="G38" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="38" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B38" s="10">
-        <v>1</v>
-      </c>
-      <c r="C38" s="1"/>
-      <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
-      <c r="F38" s="1"/>
-      <c r="G38" s="1"/>
     </row>
     <row r="39" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B39" s="10">
-        <v>2</v>
-      </c>
-      <c r="C39" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="C39" s="1"/>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
       <c r="F39" s="1"/>
@@ -1611,7 +1622,7 @@
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B40" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" s="1"/>
@@ -1621,9 +1632,9 @@
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B41" s="10">
-        <v>4</v>
-      </c>
-      <c r="C41" s="14"/>
+        <v>3</v>
+      </c>
+      <c r="C41" s="2"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
       <c r="F41" s="1"/>
@@ -1631,9 +1642,9 @@
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B42" s="10">
-        <v>5</v>
-      </c>
-      <c r="C42" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="C42" s="14"/>
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
       <c r="F42" s="1"/>
@@ -1641,9 +1652,9 @@
     </row>
     <row r="43" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B43" s="10">
-        <v>6</v>
-      </c>
-      <c r="C43" s="14"/>
+        <v>5</v>
+      </c>
+      <c r="C43" s="2"/>
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
       <c r="F43" s="1"/>
@@ -1651,17 +1662,17 @@
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B44" s="10">
-        <v>7</v>
-      </c>
-      <c r="C44" s="2"/>
+        <v>6</v>
+      </c>
+      <c r="C44" s="14"/>
       <c r="D44" s="1"/>
-      <c r="E44" s="9"/>
+      <c r="E44" s="1"/>
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
     </row>
     <row r="45" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B45" s="10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" s="1"/>
@@ -1671,19 +1682,19 @@
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B46" s="10">
-        <v>9</v>
-      </c>
-      <c r="C46" s="1"/>
+        <v>8</v>
+      </c>
+      <c r="C46" s="2"/>
       <c r="D46" s="1"/>
-      <c r="E46" s="1"/>
+      <c r="E46" s="9"/>
       <c r="F46" s="1"/>
       <c r="G46" s="1"/>
     </row>
     <row r="47" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B47" s="10">
-        <v>10</v>
-      </c>
-      <c r="C47" s="14"/>
+        <v>9</v>
+      </c>
+      <c r="C47" s="1"/>
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
       <c r="F47" s="1"/>
@@ -1691,7 +1702,7 @@
     </row>
     <row r="48" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B48" s="10">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C48" s="14"/>
       <c r="D48" s="1"/>
@@ -1701,19 +1712,29 @@
     </row>
     <row r="49" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B49" s="10">
+        <v>11</v>
+      </c>
+      <c r="C49" s="14"/>
+      <c r="D49" s="1"/>
+      <c r="E49" s="1"/>
+      <c r="F49" s="1"/>
+      <c r="G49" s="1"/>
+    </row>
+    <row r="50" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B50" s="10">
         <v>12</v>
       </c>
-      <c r="C49" s="15"/>
-      <c r="D49" s="15"/>
-      <c r="E49" s="14"/>
-      <c r="F49" s="11"/>
-      <c r="G49" s="1"/>
+      <c r="C50" s="15"/>
+      <c r="D50" s="15"/>
+      <c r="E50" s="14"/>
+      <c r="F50" s="11"/>
+      <c r="G50" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="B23:G23"/>
-    <mergeCell ref="B36:G36"/>
+    <mergeCell ref="B37:G37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -1724,13 +1745,13 @@
           <x14:formula1>
             <xm:f>'выпад списки'!$B$2:$B$5</xm:f>
           </x14:formula1>
-          <xm:sqref>D4:D21 D38:D49 D25:D34</xm:sqref>
+          <xm:sqref>D4:D21 D39:D50 D25:D35</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'выпад списки'!$F$2:$F$3</xm:f>
           </x14:formula1>
-          <xm:sqref>F38:F49 F4:F21 F25:F34</xm:sqref>
+          <xm:sqref>F39:F50 F4:F21 F25:F35</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/Check-lists.xlsx
+++ b/Check-lists.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="767" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="856" uniqueCount="176">
   <si>
     <t>№ проверки</t>
   </si>
@@ -505,9 +505,6 @@
     <t>Пароль валидной длины только из букв. Логин валидный</t>
   </si>
   <si>
-    <t>Пароль валидной длины с кириллицей. Пароль валидный</t>
-  </si>
-  <si>
     <t>In-line валидация выдаёт ошибку "Пароль не должен содержать кириллицу."</t>
   </si>
   <si>
@@ -524,18 +521,72 @@
   </si>
   <si>
     <t>In-line валидация выдаёт ошибку "Пароль обязателен." и "Логин обязателен."</t>
+  </si>
+  <si>
+    <t>Пароль валидной длины с кириллицей. Логин валидный</t>
+  </si>
+  <si>
+    <t>Очищение поля дедлайна через кнопку "Очистить"</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Задача создаётся и </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>появляется в списке задач после создания, форма очищается, уведомление о создании задачи выходит</t>
+    </r>
+  </si>
+  <si>
+    <t>Задача не создастся, In-line валидация выдаст ошибку "Название задачи обязательно."</t>
+  </si>
+  <si>
+    <t>Задача не создастся, In-line валидация выдаст ошибку "Название должно быть не длиннее 80 символов."</t>
+  </si>
+  <si>
+    <t>Задача не создаётся, in line валидация выдаст ошибку "Описание должно быть не длиннее 500 символов."</t>
+  </si>
+  <si>
+    <t>Задача создаётся, при создании автоматически приоритет выставляется средний, если не выбирать иной</t>
+  </si>
+  <si>
+    <t>При создании задачи предустановлен средний приоритет</t>
+  </si>
+  <si>
+    <t>Задача создаётся, в списке задач в поле дедлайна стоит прочерк и тег "без дедлайна"</t>
+  </si>
+  <si>
+    <t>Задача не создаётся, выходит ошибка "Не удалось создать задачу."</t>
+  </si>
+  <si>
+    <t>Поле дедлайна очищается</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -634,7 +685,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -686,6 +737,10 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -966,7 +1021,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:G50"/>
+  <dimension ref="B2:G60"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
@@ -1163,7 +1218,9 @@
       <c r="F11" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="G11" s="11"/>
+      <c r="G11" s="11" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="12" spans="2:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B12" s="10">
@@ -1181,7 +1238,9 @@
       <c r="F12" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="G12" s="11"/>
+      <c r="G12" s="11" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="10">
@@ -1219,7 +1278,9 @@
       <c r="F14" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="G14" s="9"/>
+      <c r="G14" s="11" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="15" spans="2:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B15" s="10">
@@ -1237,7 +1298,9 @@
       <c r="F15" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="G15" s="11"/>
+      <c r="G15" s="11" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="16" spans="2:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B16" s="10">
@@ -1255,25 +1318,29 @@
       <c r="F16" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="G16" s="11"/>
+      <c r="G16" s="11" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="17" spans="2:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B17" s="10">
         <v>14</v>
       </c>
       <c r="C17" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="E17" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="D17" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>160</v>
-      </c>
       <c r="F17" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="G17" s="11"/>
+      <c r="G17" s="11" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B18" s="10">
@@ -1286,7 +1353,7 @@
         <v>19</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F18" s="11" t="s">
         <v>13</v>
@@ -1306,7 +1373,7 @@
         <v>19</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F19" s="11" t="s">
         <v>13</v>
@@ -1331,25 +1398,29 @@
       <c r="F20" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="G20" s="11"/>
+      <c r="G20" s="11" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B21" s="10">
         <v>18</v>
       </c>
       <c r="C21" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="E21" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="D21" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="E21" s="13" t="s">
-        <v>162</v>
-      </c>
       <c r="F21" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="G21" s="1"/>
+      <c r="G21" s="11" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="22" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="23" spans="2:7" x14ac:dyDescent="0.25">
@@ -1398,7 +1469,9 @@
       <c r="F25" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G25" s="1"/>
+      <c r="G25" s="11" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B26" s="10">
@@ -1416,7 +1489,9 @@
       <c r="F26" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G26" s="1"/>
+      <c r="G26" s="11" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B27" s="10">
@@ -1434,7 +1509,9 @@
       <c r="F27" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G27" s="1"/>
+      <c r="G27" s="11" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B28" s="10">
@@ -1452,7 +1529,9 @@
       <c r="F28" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G28" s="1"/>
+      <c r="G28" s="11" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B29" s="10">
@@ -1465,12 +1544,14 @@
         <v>19</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G29" s="1"/>
+      <c r="G29" s="11" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B30" s="10">
@@ -1483,12 +1564,14 @@
         <v>19</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G30" s="1"/>
+      <c r="G30" s="11" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="31" spans="2:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B31" s="10">
@@ -1501,12 +1584,14 @@
         <v>19</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G31" s="1"/>
+      <c r="G31" s="11" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="32" spans="2:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B32" s="10">
@@ -1524,7 +1609,9 @@
       <c r="F32" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G32" s="1"/>
+      <c r="G32" s="11" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="33" spans="2:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B33" s="10">
@@ -1542,7 +1629,9 @@
       <c r="F33" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G33" s="1"/>
+      <c r="G33" s="11" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B34" s="10">
@@ -1560,25 +1649,29 @@
       <c r="F34" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G34" s="1"/>
+      <c r="G34" s="11" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B35" s="10">
         <v>11</v>
       </c>
       <c r="C35" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="D35" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="E35" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="D35" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="E35" s="13" t="s">
-        <v>162</v>
-      </c>
       <c r="F35" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="G35" s="1"/>
+      <c r="G35" s="11" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B37" s="17" t="s">
@@ -1610,125 +1703,309 @@
         <v>17</v>
       </c>
     </row>
-    <row r="39" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:7" ht="45" x14ac:dyDescent="0.25">
       <c r="B39" s="10">
         <v>1</v>
       </c>
-      <c r="C39" s="1"/>
-      <c r="D39" s="1"/>
-      <c r="E39" s="1"/>
-      <c r="F39" s="1"/>
-      <c r="G39" s="1"/>
+      <c r="C39" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G39" s="11" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B40" s="10">
         <v>2</v>
       </c>
-      <c r="C40" s="2"/>
-      <c r="D40" s="1"/>
-      <c r="E40" s="1"/>
-      <c r="F40" s="1"/>
-      <c r="G40" s="1"/>
+      <c r="C40" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G40" s="11" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B41" s="10">
         <v>3</v>
       </c>
-      <c r="C41" s="2"/>
-      <c r="D41" s="1"/>
-      <c r="E41" s="1"/>
-      <c r="F41" s="1"/>
-      <c r="G41" s="1"/>
+      <c r="C41" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G41" s="11" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B42" s="10">
         <v>4</v>
       </c>
-      <c r="C42" s="14"/>
-      <c r="D42" s="1"/>
-      <c r="E42" s="1"/>
-      <c r="F42" s="1"/>
-      <c r="G42" s="1"/>
-    </row>
-    <row r="43" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C42" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G42" s="11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="43" spans="2:7" ht="45" x14ac:dyDescent="0.25">
       <c r="B43" s="10">
         <v>5</v>
       </c>
-      <c r="C43" s="2"/>
-      <c r="D43" s="1"/>
-      <c r="E43" s="1"/>
-      <c r="F43" s="1"/>
-      <c r="G43" s="1"/>
-    </row>
-    <row r="44" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C43" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G43" s="11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="44" spans="2:7" ht="45" x14ac:dyDescent="0.25">
       <c r="B44" s="10">
         <v>6</v>
       </c>
-      <c r="C44" s="14"/>
-      <c r="D44" s="1"/>
-      <c r="E44" s="1"/>
-      <c r="F44" s="1"/>
-      <c r="G44" s="1"/>
-    </row>
-    <row r="45" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C44" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G44" s="11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="45" spans="2:7" ht="45" x14ac:dyDescent="0.25">
       <c r="B45" s="10">
         <v>7</v>
       </c>
-      <c r="C45" s="2"/>
-      <c r="D45" s="1"/>
-      <c r="E45" s="9"/>
-      <c r="F45" s="1"/>
-      <c r="G45" s="1"/>
-    </row>
-    <row r="46" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C45" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G45" s="11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="46" spans="2:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B46" s="10">
         <v>8</v>
       </c>
-      <c r="C46" s="2"/>
-      <c r="D46" s="1"/>
-      <c r="E46" s="9"/>
-      <c r="F46" s="1"/>
-      <c r="G46" s="1"/>
-    </row>
-    <row r="47" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C46" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E46" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G46" s="11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="47" spans="2:7" ht="45" x14ac:dyDescent="0.25">
       <c r="B47" s="10">
         <v>9</v>
       </c>
-      <c r="C47" s="1"/>
-      <c r="D47" s="1"/>
-      <c r="E47" s="1"/>
-      <c r="F47" s="1"/>
-      <c r="G47" s="1"/>
-    </row>
-    <row r="48" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C47" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G47" s="11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="48" spans="2:7" ht="45" x14ac:dyDescent="0.25">
       <c r="B48" s="10">
         <v>10</v>
       </c>
-      <c r="C48" s="14"/>
-      <c r="D48" s="1"/>
-      <c r="E48" s="1"/>
-      <c r="F48" s="1"/>
-      <c r="G48" s="1"/>
+      <c r="C48" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G48" s="11" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="49" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B49" s="10">
         <v>11</v>
       </c>
-      <c r="C49" s="14"/>
-      <c r="D49" s="1"/>
-      <c r="E49" s="1"/>
-      <c r="F49" s="1"/>
-      <c r="G49" s="1"/>
-    </row>
-    <row r="50" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C49" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G49" s="11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="50" spans="2:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B50" s="10">
         <v>12</v>
       </c>
-      <c r="C50" s="15"/>
-      <c r="D50" s="15"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="11"/>
-      <c r="G50" s="1"/>
+      <c r="C50" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="D50" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="E50" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G50" s="11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="51" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B51" s="10">
+        <v>13</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="D51" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G51" s="11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="52" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B52" s="10">
+        <v>14</v>
+      </c>
+      <c r="C52" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="D52" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G52" s="11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="53" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C53" s="21"/>
+    </row>
+    <row r="54" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C54" s="22"/>
+    </row>
+    <row r="55" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C55" s="22"/>
+    </row>
+    <row r="56" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C56" s="7"/>
+    </row>
+    <row r="57" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C57" s="21"/>
+    </row>
+    <row r="58" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C58" s="21"/>
+    </row>
+    <row r="59" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C59" s="21"/>
+    </row>
+    <row r="60" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C60" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1745,13 +2022,13 @@
           <x14:formula1>
             <xm:f>'выпад списки'!$B$2:$B$5</xm:f>
           </x14:formula1>
-          <xm:sqref>D4:D21 D39:D50 D25:D35</xm:sqref>
+          <xm:sqref>D4:D21 D25:D35 D39:D52</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'выпад списки'!$F$2:$F$3</xm:f>
           </x14:formula1>
-          <xm:sqref>F39:F50 F4:F21 F25:F35</xm:sqref>
+          <xm:sqref>F25:F35 F4:F21 F39:F52</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/Check-lists.xlsx
+++ b/Check-lists.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="856" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="963" uniqueCount="203">
   <si>
     <t>№ проверки</t>
   </si>
@@ -567,6 +567,87 @@
   </si>
   <si>
     <t>Поле дедлайна очищается</t>
+  </si>
+  <si>
+    <t>Форма Редактирования задачи</t>
+  </si>
+  <si>
+    <t>Невозможность выбрать дедлайн &lt;30 минут</t>
+  </si>
+  <si>
+    <t>Очистка дедлайна</t>
+  </si>
+  <si>
+    <t>Смена приоритета на другой</t>
+  </si>
+  <si>
+    <t>Заголовок больше допустимой длины на 1 символ</t>
+  </si>
+  <si>
+    <t>Редактирование задачи без внесения изменений</t>
+  </si>
+  <si>
+    <t>Редактирование задачи с истёкшим токеном</t>
+  </si>
+  <si>
+    <t>Смена статуса задачи</t>
+  </si>
+  <si>
+    <t>Нажатие кнопки "Отмена"</t>
+  </si>
+  <si>
+    <t>Закрытие редактирование через Escape</t>
+  </si>
+  <si>
+    <t>Закрытие редактирование через "x"</t>
+  </si>
+  <si>
+    <t>Закрытие редактирование по клику на backdrop</t>
+  </si>
+  <si>
+    <t>При неуспешном сохранении задача в карточке не меняется</t>
+  </si>
+  <si>
+    <t>Успешное редактирование закрывает модалку, показывает success-message и обновляет карточку задачи в списке</t>
+  </si>
+  <si>
+    <t>Открытие модалки редактирования</t>
+  </si>
+  <si>
+    <t>Модалка содержит данные, которые были созданы ранее</t>
+  </si>
+  <si>
+    <t>Дедлайн очищается,при сохранении в списке задач появляется тег "без дедлайна"</t>
+  </si>
+  <si>
+    <t>Модалка открывается с пустым дедлайном</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Редактирование задачи без дедлайна </t>
+  </si>
+  <si>
+    <t>Модалка закрывается, пользователь попадает на основную страницу</t>
+  </si>
+  <si>
+    <t>Модалка закрывается, показывается уведомление "Вы не внесли изменений."</t>
+  </si>
+  <si>
+    <t>Данные задачи не изменяются</t>
+  </si>
+  <si>
+    <t>Данные задачи не изменяются, показывается уведомление "Не удалось загрузить задачи."</t>
+  </si>
+  <si>
+    <t>UI не позволяет выбрать дедлайн &lt;30 минут. Если на границах времени система онлайн выставит дедлайн &lt;30 минут, при отправке запроса выйдет ошибка "Дедлайн должен быть минимум на 30 минут позже текущего времени."</t>
+  </si>
+  <si>
+    <t>Задача не обновляется, inline валидация выдает ошибку "Описание должно быть не длиннее 500 символов.", запрос не уходит</t>
+  </si>
+  <si>
+    <t>Задача не обновляется, inline валидация выдает ошибку "Название должно быть не длиннее 80 символов.", запрос не уходит</t>
+  </si>
+  <si>
+    <t>Задача не обновляется, inline валидация выдает ошибку "Название задачи обязательно.", запрос не уходит</t>
   </si>
 </sst>
 </file>
@@ -725,6 +806,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -737,10 +821,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1021,26 +1102,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:G60"/>
+  <dimension ref="B2:G81"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="59.42578125" customWidth="1"/>
-    <col min="4" max="4" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.28515625" customWidth="1"/>
     <col min="5" max="5" width="57.85546875" customWidth="1"/>
     <col min="6" max="6" width="19.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="40.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="20"/>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
@@ -1424,14 +1505,14 @@
     </row>
     <row r="22" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="23" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B23" s="20" t="s">
+      <c r="B23" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="C23" s="20"/>
-      <c r="D23" s="20"/>
-      <c r="E23" s="20"/>
-      <c r="F23" s="20"/>
-      <c r="G23" s="20"/>
+      <c r="C23" s="21"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="21"/>
+      <c r="F23" s="21"/>
+      <c r="G23" s="21"/>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B24" s="3" t="s">
@@ -1674,14 +1755,14 @@
       </c>
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B37" s="17" t="s">
+      <c r="B37" s="18" t="s">
         <v>140</v>
       </c>
-      <c r="C37" s="18"/>
-      <c r="D37" s="18"/>
-      <c r="E37" s="18"/>
-      <c r="F37" s="18"/>
-      <c r="G37" s="19"/>
+      <c r="C37" s="19"/>
+      <c r="D37" s="19"/>
+      <c r="E37" s="19"/>
+      <c r="F37" s="19"/>
+      <c r="G37" s="20"/>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B38" s="3" t="s">
@@ -1984,51 +2065,527 @@
       </c>
     </row>
     <row r="53" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C53" s="21"/>
+      <c r="C53" s="17"/>
     </row>
     <row r="54" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C54" s="22"/>
+      <c r="B54" s="18" t="s">
+        <v>176</v>
+      </c>
+      <c r="C54" s="19"/>
+      <c r="D54" s="19"/>
+      <c r="E54" s="19"/>
+      <c r="F54" s="19"/>
+      <c r="G54" s="20"/>
     </row>
     <row r="55" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C55" s="22"/>
+      <c r="B55" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="56" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C56" s="7"/>
+      <c r="B56" s="10">
+        <v>1</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E56" t="s">
+        <v>189</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G56" s="1"/>
     </row>
     <row r="57" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C57" s="21"/>
+      <c r="B57" s="10">
+        <v>2</v>
+      </c>
+      <c r="C57" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G57" s="1"/>
     </row>
     <row r="58" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C58" s="21"/>
+      <c r="B58" s="10">
+        <v>3</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G58" s="1"/>
     </row>
     <row r="59" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C59" s="21"/>
+      <c r="B59" s="10">
+        <v>4</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G59" s="1"/>
     </row>
     <row r="60" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C60" s="22"/>
+      <c r="B60" s="10">
+        <v>5</v>
+      </c>
+      <c r="C60" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G60" s="1"/>
+    </row>
+    <row r="61" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B61" s="10">
+        <v>6</v>
+      </c>
+      <c r="C61" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G61" s="1"/>
+    </row>
+    <row r="62" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B62" s="10">
+        <v>7</v>
+      </c>
+      <c r="C62" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G62" s="1"/>
+    </row>
+    <row r="63" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B63" s="10">
+        <v>8</v>
+      </c>
+      <c r="C63" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G63" s="1"/>
+    </row>
+    <row r="64" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B64" s="10">
+        <v>9</v>
+      </c>
+      <c r="C64" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G64" s="1"/>
+    </row>
+    <row r="65" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B65" s="10">
+        <v>10</v>
+      </c>
+      <c r="C65" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G65" s="1"/>
+    </row>
+    <row r="66" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B66" s="10">
+        <v>11</v>
+      </c>
+      <c r="C66" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E66" t="s">
+        <v>189</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G66" s="1"/>
+    </row>
+    <row r="67" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B67" s="10">
+        <v>12</v>
+      </c>
+      <c r="C67" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="D67" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="E67" t="s">
+        <v>189</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G67" s="1"/>
+    </row>
+    <row r="68" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B68" s="10">
+        <v>13</v>
+      </c>
+      <c r="C68" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="D68" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="E68" t="s">
+        <v>189</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G68" s="1"/>
+    </row>
+    <row r="69" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B69" s="10">
+        <v>14</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D69" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="E69" s="16" t="s">
+        <v>199</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G69" s="1"/>
+    </row>
+    <row r="70" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B70" s="10">
+        <v>15</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="D70" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="E70" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G70" s="1"/>
+    </row>
+    <row r="71" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B71" s="10">
+        <v>16</v>
+      </c>
+      <c r="C71" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="D71" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="E71" t="s">
+        <v>189</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G71" s="1"/>
+    </row>
+    <row r="72" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B72" s="10">
+        <v>17</v>
+      </c>
+      <c r="C72" s="14" t="s">
+        <v>194</v>
+      </c>
+      <c r="D72" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="E72" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G72" s="1"/>
+    </row>
+    <row r="73" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B73" s="10">
+        <v>18</v>
+      </c>
+      <c r="C73" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="D73" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="E73" t="s">
+        <v>189</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G73" s="1"/>
+    </row>
+    <row r="74" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B74" s="10">
+        <v>19</v>
+      </c>
+      <c r="C74" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="D74" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="E74" s="16" t="s">
+        <v>195</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G74" s="1"/>
+    </row>
+    <row r="75" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B75" s="10">
+        <v>20</v>
+      </c>
+      <c r="C75" s="14" t="s">
+        <v>185</v>
+      </c>
+      <c r="D75" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="E75" s="16" t="s">
+        <v>195</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G75" s="1"/>
+    </row>
+    <row r="76" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B76" s="10">
+        <v>21</v>
+      </c>
+      <c r="C76" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="D76" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="E76" s="16" t="s">
+        <v>195</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G76" s="1"/>
+    </row>
+    <row r="77" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B77" s="10">
+        <v>22</v>
+      </c>
+      <c r="C77" s="14" t="s">
+        <v>187</v>
+      </c>
+      <c r="D77" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="E77" s="16" t="s">
+        <v>195</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G77" s="1"/>
+    </row>
+    <row r="78" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B78" s="10">
+        <v>23</v>
+      </c>
+      <c r="C78" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="D78" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G78" s="1"/>
+    </row>
+    <row r="79" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B79" s="10">
+        <v>24</v>
+      </c>
+      <c r="C79" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="D79" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="E79" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G79" s="1"/>
+    </row>
+    <row r="80" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B80" s="10">
+        <v>25</v>
+      </c>
+      <c r="C80" s="22" t="s">
+        <v>188</v>
+      </c>
+      <c r="D80" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="E80" s="16" t="s">
+        <v>198</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G80" s="1"/>
+    </row>
+    <row r="81" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B81" s="10">
+        <v>26</v>
+      </c>
+      <c r="C81" s="14"/>
+      <c r="D81" s="16"/>
+      <c r="E81" s="16"/>
+      <c r="F81" s="1"/>
+      <c r="G81" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="B23:G23"/>
     <mergeCell ref="B37:G37"/>
+    <mergeCell ref="B54:G54"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'выпад списки'!$B$2:$B$5</xm:f>
           </x14:formula1>
-          <xm:sqref>D4:D21 D25:D35 D39:D52</xm:sqref>
+          <xm:sqref>D4:D21 D25:D35 D39:D52 D56:D81</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'выпад списки'!$F$2:$F$3</xm:f>
           </x14:formula1>
-          <xm:sqref>F25:F35 F4:F21 F39:F52</xm:sqref>
+          <xm:sqref>F25:F35 F4:F21 F39:F52 F56:F81</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>'выпад списки'!$D$2:$D$11</xm:f>
+          </x14:formula1>
+          <xm:sqref>E81</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -2056,22 +2613,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:14" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="19"/>
-      <c r="I2" s="17" t="s">
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="20"/>
+      <c r="I2" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="J2" s="18"/>
-      <c r="K2" s="18"/>
-      <c r="L2" s="18"/>
-      <c r="M2" s="18"/>
-      <c r="N2" s="19"/>
+      <c r="J2" s="19"/>
+      <c r="K2" s="19"/>
+      <c r="L2" s="19"/>
+      <c r="M2" s="19"/>
+      <c r="N2" s="20"/>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
@@ -2606,14 +3163,14 @@
       <c r="G17" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="I17" s="17" t="s">
+      <c r="I17" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="J17" s="18"/>
-      <c r="K17" s="18"/>
-      <c r="L17" s="18"/>
-      <c r="M17" s="18"/>
-      <c r="N17" s="19"/>
+      <c r="J17" s="19"/>
+      <c r="K17" s="19"/>
+      <c r="L17" s="19"/>
+      <c r="M17" s="19"/>
+      <c r="N17" s="20"/>
     </row>
     <row r="18" spans="2:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B18" s="4">
@@ -2808,14 +3365,14 @@
       </c>
     </row>
     <row r="24" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B24" s="20" t="s">
+      <c r="B24" s="21" t="s">
         <v>85</v>
       </c>
-      <c r="C24" s="20"/>
-      <c r="D24" s="20"/>
-      <c r="E24" s="20"/>
-      <c r="F24" s="20"/>
-      <c r="G24" s="20"/>
+      <c r="C24" s="21"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="21"/>
+      <c r="F24" s="21"/>
+      <c r="G24" s="21"/>
       <c r="I24" s="4">
         <v>6</v>
       </c>
@@ -3434,22 +3991,22 @@
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B45" s="20" t="s">
+      <c r="B45" s="21" t="s">
         <v>97</v>
       </c>
-      <c r="C45" s="20"/>
-      <c r="D45" s="20"/>
-      <c r="E45" s="20"/>
-      <c r="F45" s="20"/>
-      <c r="G45" s="20"/>
-      <c r="I45" s="17" t="s">
+      <c r="C45" s="21"/>
+      <c r="D45" s="21"/>
+      <c r="E45" s="21"/>
+      <c r="F45" s="21"/>
+      <c r="G45" s="21"/>
+      <c r="I45" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="J45" s="18"/>
-      <c r="K45" s="18"/>
-      <c r="L45" s="18"/>
-      <c r="M45" s="18"/>
-      <c r="N45" s="19"/>
+      <c r="J45" s="19"/>
+      <c r="K45" s="19"/>
+      <c r="L45" s="19"/>
+      <c r="M45" s="19"/>
+      <c r="N45" s="20"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B46" s="3" t="s">
@@ -3905,14 +4462,14 @@
         <v>58</v>
       </c>
       <c r="H60" s="8"/>
-      <c r="I60" s="17" t="s">
+      <c r="I60" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="J60" s="18"/>
-      <c r="K60" s="18"/>
-      <c r="L60" s="18"/>
-      <c r="M60" s="18"/>
-      <c r="N60" s="19"/>
+      <c r="J60" s="19"/>
+      <c r="K60" s="19"/>
+      <c r="L60" s="19"/>
+      <c r="M60" s="19"/>
+      <c r="N60" s="20"/>
     </row>
     <row r="61" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B61" s="4">

--- a/Check-lists.xlsx
+++ b/Check-lists.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="963" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="999" uniqueCount="208">
   <si>
     <t>№ проверки</t>
   </si>
@@ -590,21 +590,9 @@
     <t>Редактирование задачи с истёкшим токеном</t>
   </si>
   <si>
-    <t>Смена статуса задачи</t>
-  </si>
-  <si>
     <t>Нажатие кнопки "Отмена"</t>
   </si>
   <si>
-    <t>Закрытие редактирование через Escape</t>
-  </si>
-  <si>
-    <t>Закрытие редактирование через "x"</t>
-  </si>
-  <si>
-    <t>Закрытие редактирование по клику на backdrop</t>
-  </si>
-  <si>
     <t>При неуспешном сохранении задача в карточке не меняется</t>
   </si>
   <si>
@@ -614,9 +602,6 @@
     <t>Открытие модалки редактирования</t>
   </si>
   <si>
-    <t>Модалка содержит данные, которые были созданы ранее</t>
-  </si>
-  <si>
     <t>Дедлайн очищается,при сохранении в списке задач появляется тег "без дедлайна"</t>
   </si>
   <si>
@@ -626,18 +611,6 @@
     <t xml:space="preserve">Редактирование задачи без дедлайна </t>
   </si>
   <si>
-    <t>Модалка закрывается, пользователь попадает на основную страницу</t>
-  </si>
-  <si>
-    <t>Модалка закрывается, показывается уведомление "Вы не внесли изменений."</t>
-  </si>
-  <si>
-    <t>Данные задачи не изменяются</t>
-  </si>
-  <si>
-    <t>Данные задачи не изменяются, показывается уведомление "Не удалось загрузить задачи."</t>
-  </si>
-  <si>
     <t>UI не позволяет выбрать дедлайн &lt;30 минут. Если на границах времени система онлайн выставит дедлайн &lt;30 минут, при отправке запроса выйдет ошибка "Дедлайн должен быть минимум на 30 минут позже текущего времени."</t>
   </si>
   <si>
@@ -648,18 +621,68 @@
   </si>
   <si>
     <t>Задача не обновляется, inline валидация выдает ошибку "Название задачи обязательно.", запрос не уходит</t>
+  </si>
+  <si>
+    <t>Модалка закрывается, показывается уведомление "Изменений нет."</t>
+  </si>
+  <si>
+    <t>Данные задачи не изменяются, показывается уведомление "Не удалось сохранить изменения."</t>
+  </si>
+  <si>
+    <t>Модалка закрывается, пользователь остаётся на экране задач.</t>
+  </si>
+  <si>
+    <t>Модалка открывается с ранее сохранёнными title / description / priority / deadline текущей задачи.</t>
+  </si>
+  <si>
+    <t>Закрытие редактирования через Escape</t>
+  </si>
+  <si>
+    <t>Закрытие редактирования через "x"</t>
+  </si>
+  <si>
+    <t>Закрытие редактирования по клику на backdrop</t>
+  </si>
+  <si>
+    <t>Изменение статуса задачи</t>
+  </si>
+  <si>
+    <t>Смена статуса задачи на другой</t>
+  </si>
+  <si>
+    <t>Смена статуса на тот же</t>
+  </si>
+  <si>
+    <t>Смена статуса с истёкшим токеном</t>
+  </si>
+  <si>
+    <t>Статус меняется, выходит уведомление "статус обновлён", у карточки меняется badge статуса, активной становится новая кнопка статуса, старая перестаёт быть текущей</t>
+  </si>
+  <si>
+    <t>Статус остаётся прежним, выходит уведомление "статус обновлён", статус</t>
+  </si>
+  <si>
+    <t>Показывается "Не удалось изменить статус." ,badge и активная кнопка статуса не меняются.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -766,7 +789,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -809,6 +832,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -821,7 +845,15 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1102,7 +1134,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:G81"/>
+  <dimension ref="B2:G83"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
@@ -1114,14 +1146,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="21"/>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
@@ -1505,14 +1537,14 @@
     </row>
     <row r="22" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="23" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B23" s="21" t="s">
+      <c r="B23" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="C23" s="21"/>
-      <c r="D23" s="21"/>
-      <c r="E23" s="21"/>
-      <c r="F23" s="21"/>
-      <c r="G23" s="21"/>
+      <c r="C23" s="22"/>
+      <c r="D23" s="22"/>
+      <c r="E23" s="22"/>
+      <c r="F23" s="22"/>
+      <c r="G23" s="22"/>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B24" s="3" t="s">
@@ -1755,14 +1787,14 @@
       </c>
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B37" s="18" t="s">
+      <c r="B37" s="19" t="s">
         <v>140</v>
       </c>
-      <c r="C37" s="19"/>
-      <c r="D37" s="19"/>
-      <c r="E37" s="19"/>
-      <c r="F37" s="19"/>
-      <c r="G37" s="20"/>
+      <c r="C37" s="20"/>
+      <c r="D37" s="20"/>
+      <c r="E37" s="20"/>
+      <c r="F37" s="20"/>
+      <c r="G37" s="21"/>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B38" s="3" t="s">
@@ -2068,14 +2100,14 @@
       <c r="C53" s="17"/>
     </row>
     <row r="54" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B54" s="18" t="s">
+      <c r="B54" s="19" t="s">
         <v>176</v>
       </c>
-      <c r="C54" s="19"/>
-      <c r="D54" s="19"/>
-      <c r="E54" s="19"/>
-      <c r="F54" s="19"/>
-      <c r="G54" s="20"/>
+      <c r="C54" s="20"/>
+      <c r="D54" s="20"/>
+      <c r="E54" s="20"/>
+      <c r="F54" s="20"/>
+      <c r="G54" s="21"/>
     </row>
     <row r="55" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B55" s="3" t="s">
@@ -2097,7 +2129,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="56" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B56" s="10">
         <v>1</v>
       </c>
@@ -2107,33 +2139,37 @@
       <c r="D56" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E56" t="s">
-        <v>189</v>
+      <c r="E56" s="2" t="s">
+        <v>185</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G56" s="1"/>
+      <c r="G56" s="11" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="57" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B57" s="10">
         <v>2</v>
       </c>
       <c r="C57" s="14" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G57" s="1"/>
-    </row>
-    <row r="58" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="G57" s="11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="58" spans="2:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B58" s="10">
         <v>3</v>
       </c>
@@ -2143,15 +2179,17 @@
       <c r="D58" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E58" s="1" t="s">
-        <v>202</v>
+      <c r="E58" s="2" t="s">
+        <v>193</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G58" s="1"/>
-    </row>
-    <row r="59" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="G58" s="11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="59" spans="2:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B59" s="10">
         <v>4</v>
       </c>
@@ -2161,15 +2199,17 @@
       <c r="D59" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E59" s="1" t="s">
-        <v>202</v>
+      <c r="E59" s="2" t="s">
+        <v>193</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G59" s="1"/>
-    </row>
-    <row r="60" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="G59" s="11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="60" spans="2:7" ht="45" x14ac:dyDescent="0.25">
       <c r="B60" s="10">
         <v>5</v>
       </c>
@@ -2179,33 +2219,37 @@
       <c r="D60" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E60" s="1" t="s">
-        <v>201</v>
+      <c r="E60" s="2" t="s">
+        <v>192</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G60" s="1"/>
-    </row>
-    <row r="61" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="G60" s="11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="61" spans="2:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B61" s="10">
         <v>6</v>
       </c>
       <c r="C61" s="14" t="s">
-        <v>108</v>
+        <v>137</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E61" s="1" t="s">
-        <v>189</v>
+      <c r="E61" s="2" t="s">
+        <v>185</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G61" s="1"/>
-    </row>
-    <row r="62" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="G61" s="11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="62" spans="2:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B62" s="10">
         <v>7</v>
       </c>
@@ -2215,15 +2259,17 @@
       <c r="D62" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E62" s="1" t="s">
-        <v>189</v>
+      <c r="E62" s="2" t="s">
+        <v>185</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G62" s="1"/>
-    </row>
-    <row r="63" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="G62" s="11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="63" spans="2:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B63" s="10">
         <v>8</v>
       </c>
@@ -2233,15 +2279,17 @@
       <c r="D63" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E63" s="1" t="s">
-        <v>189</v>
+      <c r="E63" s="2" t="s">
+        <v>185</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G63" s="1"/>
-    </row>
-    <row r="64" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="G63" s="11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="64" spans="2:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B64" s="10">
         <v>9</v>
       </c>
@@ -2251,15 +2299,17 @@
       <c r="D64" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E64" s="1" t="s">
-        <v>189</v>
+      <c r="E64" s="2" t="s">
+        <v>185</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G64" s="1"/>
-    </row>
-    <row r="65" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="G64" s="11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="65" spans="2:7" ht="45" x14ac:dyDescent="0.25">
       <c r="B65" s="10">
         <v>10</v>
       </c>
@@ -2269,15 +2319,17 @@
       <c r="D65" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E65" s="1" t="s">
-        <v>200</v>
+      <c r="E65" s="2" t="s">
+        <v>191</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G65" s="1"/>
-    </row>
-    <row r="66" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="G65" s="11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="66" spans="2:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B66" s="10">
         <v>11</v>
       </c>
@@ -2287,15 +2339,17 @@
       <c r="D66" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E66" t="s">
-        <v>189</v>
+      <c r="E66" s="2" t="s">
+        <v>185</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G66" s="1"/>
-    </row>
-    <row r="67" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="G66" s="11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="67" spans="2:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B67" s="10">
         <v>12</v>
       </c>
@@ -2305,15 +2359,17 @@
       <c r="D67" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="E67" t="s">
-        <v>189</v>
+      <c r="E67" s="2" t="s">
+        <v>185</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G67" s="1"/>
-    </row>
-    <row r="68" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="G67" s="11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="68" spans="2:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B68" s="10">
         <v>13</v>
       </c>
@@ -2323,15 +2379,17 @@
       <c r="D68" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="E68" t="s">
-        <v>189</v>
+      <c r="E68" s="2" t="s">
+        <v>185</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G68" s="1"/>
-    </row>
-    <row r="69" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="G68" s="11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="69" spans="2:7" ht="75" x14ac:dyDescent="0.25">
       <c r="B69" s="10">
         <v>14</v>
       </c>
@@ -2341,15 +2399,17 @@
       <c r="D69" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="E69" s="16" t="s">
-        <v>199</v>
+      <c r="E69" s="14" t="s">
+        <v>190</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G69" s="1"/>
-    </row>
-    <row r="70" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="G69" s="11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="70" spans="2:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B70" s="10">
         <v>15</v>
       </c>
@@ -2359,15 +2419,17 @@
       <c r="D70" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="E70" s="16" t="s">
-        <v>192</v>
+      <c r="E70" s="14" t="s">
+        <v>187</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G70" s="1"/>
-    </row>
-    <row r="71" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="G70" s="11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="71" spans="2:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B71" s="10">
         <v>16</v>
       </c>
@@ -2377,33 +2439,37 @@
       <c r="D71" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="E71" t="s">
-        <v>189</v>
+      <c r="E71" s="2" t="s">
+        <v>185</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G71" s="1"/>
+      <c r="G71" s="11" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="72" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B72" s="10">
         <v>17</v>
       </c>
       <c r="C72" s="14" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="D72" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="E72" s="16" t="s">
-        <v>193</v>
+      <c r="E72" s="14" t="s">
+        <v>188</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G72" s="1"/>
-    </row>
-    <row r="73" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="G72" s="11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="73" spans="2:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B73" s="10">
         <v>18</v>
       </c>
@@ -2413,179 +2479,230 @@
       <c r="D73" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="E73" t="s">
-        <v>189</v>
+      <c r="E73" s="2" t="s">
+        <v>196</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G73" s="1"/>
-    </row>
-    <row r="74" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="G73" s="11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="74" spans="2:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B74" s="10">
         <v>19</v>
       </c>
       <c r="C74" s="14" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="D74" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="E74" s="16" t="s">
-        <v>195</v>
+      <c r="E74" s="2" t="s">
+        <v>196</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G74" s="1"/>
-    </row>
-    <row r="75" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="G74" s="11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="75" spans="2:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B75" s="10">
         <v>20</v>
       </c>
       <c r="C75" s="14" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="D75" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="E75" s="16" t="s">
-        <v>195</v>
+      <c r="E75" s="2" t="s">
+        <v>196</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G75" s="1"/>
-    </row>
-    <row r="76" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="G75" s="11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="76" spans="2:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B76" s="10">
         <v>21</v>
       </c>
       <c r="C76" s="14" t="s">
-        <v>186</v>
+        <v>200</v>
       </c>
       <c r="D76" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="E76" s="16" t="s">
-        <v>195</v>
+      <c r="E76" s="2" t="s">
+        <v>196</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G76" s="1"/>
-    </row>
-    <row r="77" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="G76" s="11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="77" spans="2:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B77" s="10">
         <v>22</v>
       </c>
       <c r="C77" s="14" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="D77" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="E77" s="16" t="s">
-        <v>195</v>
+      <c r="E77" s="2" t="s">
+        <v>194</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G77" s="1"/>
-    </row>
-    <row r="78" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="G77" s="11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="78" spans="2:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B78" s="10">
         <v>23</v>
       </c>
       <c r="C78" s="14" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D78" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="E78" s="1" t="s">
-        <v>196</v>
+        <v>19</v>
+      </c>
+      <c r="E78" s="14" t="s">
+        <v>195</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G78" s="1"/>
-    </row>
-    <row r="79" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="G78" s="11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="79" spans="2:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B79" s="10">
         <v>24</v>
       </c>
-      <c r="C79" s="14" t="s">
-        <v>182</v>
+      <c r="C79" s="18" t="s">
+        <v>184</v>
       </c>
       <c r="D79" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="E79" s="16" t="s">
-        <v>197</v>
+      <c r="E79" s="14" t="s">
+        <v>195</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G79" s="1"/>
+      <c r="G79" s="11" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="80" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B80" s="10">
-        <v>25</v>
-      </c>
-      <c r="C80" s="22" t="s">
-        <v>188</v>
-      </c>
-      <c r="D80" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="E80" s="16" t="s">
-        <v>198</v>
-      </c>
-      <c r="F80" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G80" s="1"/>
+      <c r="B80" s="23" t="s">
+        <v>201</v>
+      </c>
+      <c r="C80" s="24"/>
+      <c r="D80" s="24"/>
+      <c r="E80" s="24"/>
+      <c r="F80" s="24"/>
+      <c r="G80" s="25"/>
     </row>
     <row r="81" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B81" s="10">
+        <v>25</v>
+      </c>
+      <c r="C81" s="14" t="s">
+        <v>202</v>
+      </c>
+      <c r="D81" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="E81" s="16" t="s">
+        <v>205</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G81" s="11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="82" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B82" s="10">
         <v>26</v>
       </c>
-      <c r="C81" s="14"/>
-      <c r="D81" s="16"/>
-      <c r="E81" s="16"/>
-      <c r="F81" s="1"/>
-      <c r="G81" s="1"/>
+      <c r="C82" s="14" t="s">
+        <v>203</v>
+      </c>
+      <c r="D82" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="E82" s="16" t="s">
+        <v>206</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G82" s="11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="83" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B83" s="10">
+        <v>27</v>
+      </c>
+      <c r="C83" s="14" t="s">
+        <v>204</v>
+      </c>
+      <c r="D83" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G83" s="11" t="s">
+        <v>58</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="B23:G23"/>
     <mergeCell ref="B37:G37"/>
     <mergeCell ref="B54:G54"/>
+    <mergeCell ref="B80:G80"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'выпад списки'!$B$2:$B$5</xm:f>
           </x14:formula1>
-          <xm:sqref>D4:D21 D25:D35 D39:D52 D56:D81</xm:sqref>
+          <xm:sqref>D4:D21 D25:D35 D39:D52 D56:D79 D81:D83</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'выпад списки'!$F$2:$F$3</xm:f>
           </x14:formula1>
-          <xm:sqref>F25:F35 F4:F21 F39:F52 F56:F81</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>'выпад списки'!$D$2:$D$11</xm:f>
-          </x14:formula1>
-          <xm:sqref>E81</xm:sqref>
+          <xm:sqref>F25:F35 F4:F21 F39:F52 F56:F79 F81:F83</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -2613,22 +2730,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:14" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="20"/>
-      <c r="I2" s="18" t="s">
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="21"/>
+      <c r="I2" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="J2" s="19"/>
-      <c r="K2" s="19"/>
-      <c r="L2" s="19"/>
-      <c r="M2" s="19"/>
-      <c r="N2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="21"/>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
@@ -3163,14 +3280,14 @@
       <c r="G17" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="I17" s="18" t="s">
+      <c r="I17" s="19" t="s">
         <v>125</v>
       </c>
-      <c r="J17" s="19"/>
-      <c r="K17" s="19"/>
-      <c r="L17" s="19"/>
-      <c r="M17" s="19"/>
-      <c r="N17" s="20"/>
+      <c r="J17" s="20"/>
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+      <c r="M17" s="20"/>
+      <c r="N17" s="21"/>
     </row>
     <row r="18" spans="2:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B18" s="4">
@@ -3365,14 +3482,14 @@
       </c>
     </row>
     <row r="24" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B24" s="21" t="s">
+      <c r="B24" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="C24" s="21"/>
-      <c r="D24" s="21"/>
-      <c r="E24" s="21"/>
-      <c r="F24" s="21"/>
-      <c r="G24" s="21"/>
+      <c r="C24" s="22"/>
+      <c r="D24" s="22"/>
+      <c r="E24" s="22"/>
+      <c r="F24" s="22"/>
+      <c r="G24" s="22"/>
       <c r="I24" s="4">
         <v>6</v>
       </c>
@@ -3991,22 +4108,22 @@
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B45" s="21" t="s">
+      <c r="B45" s="22" t="s">
         <v>97</v>
       </c>
-      <c r="C45" s="21"/>
-      <c r="D45" s="21"/>
-      <c r="E45" s="21"/>
-      <c r="F45" s="21"/>
-      <c r="G45" s="21"/>
-      <c r="I45" s="18" t="s">
+      <c r="C45" s="22"/>
+      <c r="D45" s="22"/>
+      <c r="E45" s="22"/>
+      <c r="F45" s="22"/>
+      <c r="G45" s="22"/>
+      <c r="I45" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="J45" s="19"/>
-      <c r="K45" s="19"/>
-      <c r="L45" s="19"/>
-      <c r="M45" s="19"/>
-      <c r="N45" s="20"/>
+      <c r="J45" s="20"/>
+      <c r="K45" s="20"/>
+      <c r="L45" s="20"/>
+      <c r="M45" s="20"/>
+      <c r="N45" s="21"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B46" s="3" t="s">
@@ -4462,14 +4579,14 @@
         <v>58</v>
       </c>
       <c r="H60" s="8"/>
-      <c r="I60" s="18" t="s">
+      <c r="I60" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="J60" s="19"/>
-      <c r="K60" s="19"/>
-      <c r="L60" s="19"/>
-      <c r="M60" s="19"/>
-      <c r="N60" s="20"/>
+      <c r="J60" s="20"/>
+      <c r="K60" s="20"/>
+      <c r="L60" s="20"/>
+      <c r="M60" s="20"/>
+      <c r="N60" s="21"/>
     </row>
     <row r="61" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B61" s="4">

--- a/Check-lists.xlsx
+++ b/Check-lists.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="999" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1166" uniqueCount="289">
   <si>
     <t>№ проверки</t>
   </si>
@@ -664,12 +664,649 @@
   <si>
     <t>Показывается "Не удалось изменить статус." ,badge и активная кнопка статуса не меняются.</t>
   </si>
+  <si>
+    <t>Удаление задачи</t>
+  </si>
+  <si>
+    <t>Успешное удаление задачи</t>
+  </si>
+  <si>
+    <t>Закрытие окна удаления через Escape</t>
+  </si>
+  <si>
+    <t>Закрытие окна удаления через "x"</t>
+  </si>
+  <si>
+    <t>Закрытие окна удаления по клику на backdrop</t>
+  </si>
+  <si>
+    <t>Удаление задачи с истёкшим токеном</t>
+  </si>
+  <si>
+    <t>Закрытие окна удаления через "Отмена"</t>
+  </si>
+  <si>
+    <t>Открытие окна удаления показывает название именно той задачи, которую собираемся удалить.</t>
+  </si>
+  <si>
+    <t>Задача удаляется, список задач обновляется, выходит уведомление об успешном удалении задачи</t>
+  </si>
+  <si>
+    <t>Окно удаления закрывается, пользователь остаётся на экране задач</t>
+  </si>
+  <si>
+    <t>Название задачи в окне подтверждения удаления соответствует удаляемой задаче</t>
+  </si>
+  <si>
+    <t>Задача не удаляется, происходит автологаут, выходит уведомление "Сессия истекла. Войдите снова."</t>
+  </si>
+  <si>
+    <t>Быстрый отбор по ключевым словам</t>
+  </si>
+  <si>
+    <t>Поиск по полному слову в названии задачи</t>
+  </si>
+  <si>
+    <t>Поиск по полному слову в описании задачи</t>
+  </si>
+  <si>
+    <t>Поиск по части слова</t>
+  </si>
+  <si>
+    <t>Поиск в разном регистре</t>
+  </si>
+  <si>
+    <t>Поиск по значению, которого нет ни в названии, ни в описании</t>
+  </si>
+  <si>
+    <t>Поиск с пустым значением</t>
+  </si>
+  <si>
+    <t>Поиск со значением с пробелами по краям</t>
+  </si>
+  <si>
+    <t>Применение поиска по Enter в поле поиска</t>
+  </si>
+  <si>
+    <t>Фильтр по статусу</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Фильтр </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Все задачи</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Фильтр </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Новые</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Фильтр </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>В работе</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Фильтр </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Готово</t>
+    </r>
+  </si>
+  <si>
+    <t>Переключение между статусами подряд</t>
+  </si>
+  <si>
+    <t>Поиск по ключевым словам + фильтру</t>
+  </si>
+  <si>
+    <t>Поиск + фильтр по статусу</t>
+  </si>
+  <si>
+    <t>Поиск совпадает, но статус не совпадает</t>
+  </si>
+  <si>
+    <t>Статус совпадает, но поиск не совпадает</t>
+  </si>
+  <si>
+    <t>Сортировка</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Сортировка </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Ближайший дедлайн</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Сортировка </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Высокий приоритет</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Сортировка </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Сначала новые</t>
+    </r>
+  </si>
+  <si>
+    <t>Смена сортировки при уже заданных поиске и статусе</t>
+  </si>
+  <si>
+    <t>Кнопка “Сбросить”</t>
+  </si>
+  <si>
+    <t>Сброс поиска</t>
+  </si>
+  <si>
+    <t>Сброс фильтра статуса</t>
+  </si>
+  <si>
+    <t>Сброс сортировки</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">После </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Сбросить</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> контролы синхронизируются визуально</t>
+    </r>
+  </si>
+  <si>
+    <t>Плашки активных фильтров</t>
+  </si>
+  <si>
+    <t>Удаление только плашки поиска</t>
+  </si>
+  <si>
+    <t>Удаление только плашки статуса</t>
+  </si>
+  <si>
+    <t>Удаление только плашки сортировки</t>
+  </si>
+  <si>
+    <t>Сводка результатов над списком задач</t>
+  </si>
+  <si>
+    <t>Сводка при непустой выборке</t>
+  </si>
+  <si>
+    <t>Сводка при пустой выборке без поиска</t>
+  </si>
+  <si>
+    <t>Сводка при пустой выборке с поиском</t>
+  </si>
+  <si>
+    <t>задачи находятся по частичному совпадению подстроки, а не только по полному слову.</t>
+  </si>
+  <si>
+    <t>результат поиска одинаковый</t>
+  </si>
+  <si>
+    <t>список пустой,выборка показывает, что по запросу ничего не найдено. Для пустой выборки по запросу выводится отдельный текст.</t>
+  </si>
+  <si>
+    <t>отображаются задачи без поискового ограничения.</t>
+  </si>
+  <si>
+    <t>пробелы по краям обрезаются, поиск применяется по очищенному значению</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">при нажатии </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Enter</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> фильтр применяется так же, как по кнопке </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Применить</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">в списке остаются только задачи со статусом </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>В работе.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">в списке остаются только задачи со статусом </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Новые.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">в списке остаются только задачи со статусом </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Готово.</t>
+    </r>
+  </si>
+  <si>
+    <t>список корректно перестраивается при каждом новом выборе статуса, без сохранения старой выборки.</t>
+  </si>
+  <si>
+    <t>остаются только задачи, которые одновременно подходят и по статусу, и по поисковому запросу. Логика сначала проверяет статус, потом поиск.</t>
+  </si>
+  <si>
+    <t>задача не отображается, потому что статусная фильтрация обязательна</t>
+  </si>
+  <si>
+    <t>задача не отображается, потому что поисковый фильтр тоже обязателен при заполненном поле поиска.</t>
+  </si>
+  <si>
+    <t>задачи сортируются по дедлайну по возрастанию; задачи без дедлайна уходят ниже задач с дедлайном</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">сначала показываются </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>high</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, затем </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>medium</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, затем </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>low</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. При равном приоритете действует дополнительная сортировка по дедлайну/дате создания.</t>
+    </r>
+  </si>
+  <si>
+    <t>первыми идут задачи с более поздним временем создания</t>
+  </si>
+  <si>
+    <t>меняется только порядок задач внутри текущей выборки, сами фильтры не сбрасываются.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">статус возвращается в </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Все задачи</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">поле поиска пустое, select статуса — </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Все задачи</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, select сортировки — </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Ближайший дедлайн</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">сортировка возвращается к </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Ближайший дедлайн</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">После </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Сбросить</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> метки активных фильтров исчезают</t>
+    </r>
+  </si>
+  <si>
+    <t>блок активных меток скрывается, если активных фильтров не осталось</t>
+  </si>
+  <si>
+    <t>очищается только поиск, остальные фильтры сохраняются</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">статус возвращается к </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Все задачи</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, поиск и сортировка остаются без изменений.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">сортировка возвращается к </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Ближайший дедлайн</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, остальные фильтры сохраняются</t>
+    </r>
+  </si>
+  <si>
+    <t>показывается количество задач и текущая выборка статуса; при наличии поиска — ещё и поисковая часть.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">отображается текст вида </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Сейчас нет задач в выборке ...</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">отображается текст вида </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>По запросу «... » ничего не найдено.</t>
+    </r>
+  </si>
+  <si>
+    <t>в списке остаются только задачи, у которых ключевое слово есть в заголовке. Поиск работает по названию задачи</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">в списке остаются только задачи, у которых ключевое слово есть в </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>описании</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. Поиск работает и по описанию.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>отображаются задачи всех статусов. Это дефолтное значение</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>поле поиска очищается, список перестраивается без поискового фильтра.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -692,6 +1329,11 @@
       <family val="2"/>
       <charset val="204"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
     </font>
   </fonts>
   <fills count="4">
@@ -789,7 +1431,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -833,6 +1475,15 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -840,9 +1491,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -853,6 +1501,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1134,8 +1785,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:G83"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B2:G131"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="59.42578125" customWidth="1"/>
@@ -1145,17 +1796,17 @@
     <col min="7" max="7" width="40.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B2" s="19" t="s">
+    <row r="2" spans="2:7">
+      <c r="B2" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="21"/>
-    </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="24"/>
+    </row>
+    <row r="3" spans="2:7">
       <c r="B3" s="3" t="s">
         <v>0</v>
       </c>
@@ -1175,7 +1826,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:7" ht="30">
       <c r="B4" s="10">
         <v>1</v>
       </c>
@@ -1195,7 +1846,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="5" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:7" ht="30">
       <c r="B5" s="10">
         <v>2</v>
       </c>
@@ -1215,7 +1866,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:7">
       <c r="B6" s="10">
         <v>3</v>
       </c>
@@ -1235,7 +1886,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="7" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:7" ht="30">
       <c r="B7" s="10">
         <v>4</v>
       </c>
@@ -1255,7 +1906,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:7" ht="30">
       <c r="B8" s="10">
         <v>5</v>
       </c>
@@ -1275,7 +1926,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="9" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:7" ht="30">
       <c r="B9" s="10">
         <v>6</v>
       </c>
@@ -1295,7 +1946,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="10" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:7" ht="30">
       <c r="B10" s="10">
         <v>7</v>
       </c>
@@ -1315,7 +1966,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="11" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:7" ht="30">
       <c r="B11" s="10">
         <v>8</v>
       </c>
@@ -1335,7 +1986,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="12" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:7" ht="30">
       <c r="B12" s="10">
         <v>9</v>
       </c>
@@ -1355,7 +2006,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:7">
       <c r="B13" s="10">
         <v>10</v>
       </c>
@@ -1375,7 +2026,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="14" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:7" ht="30">
       <c r="B14" s="10">
         <v>11</v>
       </c>
@@ -1395,7 +2046,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="15" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:7" ht="30">
       <c r="B15" s="10">
         <v>12</v>
       </c>
@@ -1415,7 +2066,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="16" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:7" ht="30">
       <c r="B16" s="10">
         <v>13</v>
       </c>
@@ -1435,7 +2086,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="17" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:7" ht="30">
       <c r="B17" s="10">
         <v>14</v>
       </c>
@@ -1455,7 +2106,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:7">
       <c r="B18" s="10">
         <v>15</v>
       </c>
@@ -1475,7 +2126,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:7">
       <c r="B19" s="10">
         <v>16</v>
       </c>
@@ -1495,7 +2146,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:7">
       <c r="B20" s="10">
         <v>17</v>
       </c>
@@ -1515,7 +2166,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:7">
       <c r="B21" s="10">
         <v>18</v>
       </c>
@@ -1535,18 +2186,18 @@
         <v>58</v>
       </c>
     </row>
-    <row r="22" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B23" s="22" t="s">
+    <row r="22" spans="2:7" ht="15.75" customHeight="1"/>
+    <row r="23" spans="2:7">
+      <c r="B23" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="C23" s="22"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="22"/>
-      <c r="F23" s="22"/>
-      <c r="G23" s="22"/>
-    </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C23" s="20"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="20"/>
+    </row>
+    <row r="24" spans="2:7">
       <c r="B24" s="3" t="s">
         <v>0</v>
       </c>
@@ -1566,7 +2217,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:7">
       <c r="B25" s="10">
         <v>1</v>
       </c>
@@ -1586,7 +2237,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:7">
       <c r="B26" s="10">
         <v>2</v>
       </c>
@@ -1606,7 +2257,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:7">
       <c r="B27" s="10">
         <v>3</v>
       </c>
@@ -1626,7 +2277,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="28" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:7">
       <c r="B28" s="10">
         <v>4</v>
       </c>
@@ -1646,7 +2297,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:7">
       <c r="B29" s="10">
         <v>5</v>
       </c>
@@ -1666,7 +2317,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:7">
       <c r="B30" s="10">
         <v>6</v>
       </c>
@@ -1686,7 +2337,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="31" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:7" ht="30">
       <c r="B31" s="10">
         <v>7</v>
       </c>
@@ -1706,7 +2357,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="32" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:7" ht="30">
       <c r="B32" s="10">
         <v>8</v>
       </c>
@@ -1726,7 +2377,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="33" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:7" ht="30">
       <c r="B33" s="10">
         <v>9</v>
       </c>
@@ -1746,7 +2397,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:7">
       <c r="B34" s="10">
         <v>10</v>
       </c>
@@ -1766,7 +2417,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="35" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:7">
       <c r="B35" s="10">
         <v>11</v>
       </c>
@@ -1786,17 +2437,17 @@
         <v>58</v>
       </c>
     </row>
-    <row r="37" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B37" s="19" t="s">
+    <row r="37" spans="2:7">
+      <c r="B37" s="22" t="s">
         <v>140</v>
       </c>
-      <c r="C37" s="20"/>
-      <c r="D37" s="20"/>
-      <c r="E37" s="20"/>
-      <c r="F37" s="20"/>
-      <c r="G37" s="21"/>
-    </row>
-    <row r="38" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C37" s="23"/>
+      <c r="D37" s="23"/>
+      <c r="E37" s="23"/>
+      <c r="F37" s="23"/>
+      <c r="G37" s="24"/>
+    </row>
+    <row r="38" spans="2:7">
       <c r="B38" s="3" t="s">
         <v>0</v>
       </c>
@@ -1816,7 +2467,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="39" spans="2:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:7" ht="45">
       <c r="B39" s="10">
         <v>1</v>
       </c>
@@ -1836,7 +2487,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="40" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:7">
       <c r="B40" s="10">
         <v>2</v>
       </c>
@@ -1856,7 +2507,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="41" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:7">
       <c r="B41" s="10">
         <v>3</v>
       </c>
@@ -1876,7 +2527,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="42" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:7">
       <c r="B42" s="10">
         <v>4</v>
       </c>
@@ -1896,7 +2547,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="43" spans="2:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:7" ht="45">
       <c r="B43" s="10">
         <v>5</v>
       </c>
@@ -1916,7 +2567,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="44" spans="2:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:7" ht="45">
       <c r="B44" s="10">
         <v>6</v>
       </c>
@@ -1936,7 +2587,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="45" spans="2:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:7" ht="45">
       <c r="B45" s="10">
         <v>7</v>
       </c>
@@ -1956,7 +2607,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="46" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:7" ht="30">
       <c r="B46" s="10">
         <v>8</v>
       </c>
@@ -1976,7 +2627,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="47" spans="2:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:7" ht="45">
       <c r="B47" s="10">
         <v>9</v>
       </c>
@@ -1996,7 +2647,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="48" spans="2:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:7" ht="45">
       <c r="B48" s="10">
         <v>10</v>
       </c>
@@ -2016,7 +2667,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="49" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:7">
       <c r="B49" s="10">
         <v>11</v>
       </c>
@@ -2036,7 +2687,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="50" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:7" ht="30">
       <c r="B50" s="10">
         <v>12</v>
       </c>
@@ -2056,7 +2707,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="51" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:7">
       <c r="B51" s="10">
         <v>13</v>
       </c>
@@ -2076,7 +2727,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="52" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:7">
       <c r="B52" s="10">
         <v>14</v>
       </c>
@@ -2096,20 +2747,20 @@
         <v>58</v>
       </c>
     </row>
-    <row r="53" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:7">
       <c r="C53" s="17"/>
     </row>
-    <row r="54" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B54" s="19" t="s">
+    <row r="54" spans="2:7">
+      <c r="B54" s="22" t="s">
         <v>176</v>
       </c>
-      <c r="C54" s="20"/>
-      <c r="D54" s="20"/>
-      <c r="E54" s="20"/>
-      <c r="F54" s="20"/>
-      <c r="G54" s="21"/>
-    </row>
-    <row r="55" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C54" s="23"/>
+      <c r="D54" s="23"/>
+      <c r="E54" s="23"/>
+      <c r="F54" s="23"/>
+      <c r="G54" s="24"/>
+    </row>
+    <row r="55" spans="2:7">
       <c r="B55" s="3" t="s">
         <v>0</v>
       </c>
@@ -2129,7 +2780,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="56" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:7" ht="30">
       <c r="B56" s="10">
         <v>1</v>
       </c>
@@ -2149,7 +2800,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="57" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:7">
       <c r="B57" s="10">
         <v>2</v>
       </c>
@@ -2169,7 +2820,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="58" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:7" ht="30">
       <c r="B58" s="10">
         <v>3</v>
       </c>
@@ -2189,7 +2840,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="59" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:7" ht="30">
       <c r="B59" s="10">
         <v>4</v>
       </c>
@@ -2209,7 +2860,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="60" spans="2:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:7" ht="45">
       <c r="B60" s="10">
         <v>5</v>
       </c>
@@ -2229,7 +2880,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="61" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:7" ht="30">
       <c r="B61" s="10">
         <v>6</v>
       </c>
@@ -2249,7 +2900,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="62" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:7" ht="30">
       <c r="B62" s="10">
         <v>7</v>
       </c>
@@ -2269,7 +2920,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="63" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:7" ht="30">
       <c r="B63" s="10">
         <v>8</v>
       </c>
@@ -2289,7 +2940,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="64" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:7" ht="30">
       <c r="B64" s="10">
         <v>9</v>
       </c>
@@ -2309,7 +2960,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="65" spans="2:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:7" ht="45">
       <c r="B65" s="10">
         <v>10</v>
       </c>
@@ -2329,7 +2980,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="66" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:7" ht="30">
       <c r="B66" s="10">
         <v>11</v>
       </c>
@@ -2349,7 +3000,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="67" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:7" ht="30">
       <c r="B67" s="10">
         <v>12</v>
       </c>
@@ -2369,7 +3020,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="68" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:7" ht="30">
       <c r="B68" s="10">
         <v>13</v>
       </c>
@@ -2389,7 +3040,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="69" spans="2:7" ht="75" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:7" ht="75">
       <c r="B69" s="10">
         <v>14</v>
       </c>
@@ -2409,7 +3060,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="70" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:7" ht="30">
       <c r="B70" s="10">
         <v>15</v>
       </c>
@@ -2429,7 +3080,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="71" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:7" ht="30">
       <c r="B71" s="10">
         <v>16</v>
       </c>
@@ -2449,7 +3100,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="72" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:7">
       <c r="B72" s="10">
         <v>17</v>
       </c>
@@ -2469,7 +3120,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="73" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:7" ht="30">
       <c r="B73" s="10">
         <v>18</v>
       </c>
@@ -2489,7 +3140,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="74" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:7" ht="30">
       <c r="B74" s="10">
         <v>19</v>
       </c>
@@ -2509,7 +3160,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="75" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:7" ht="30">
       <c r="B75" s="10">
         <v>20</v>
       </c>
@@ -2529,7 +3180,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="76" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:7" ht="30">
       <c r="B76" s="10">
         <v>21</v>
       </c>
@@ -2549,7 +3200,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="77" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:7" ht="30">
       <c r="B77" s="10">
         <v>22</v>
       </c>
@@ -2569,7 +3220,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="78" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:7" ht="30">
       <c r="B78" s="10">
         <v>23</v>
       </c>
@@ -2589,7 +3240,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="79" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:7" ht="30">
       <c r="B79" s="10">
         <v>24</v>
       </c>
@@ -2609,17 +3260,17 @@
         <v>58</v>
       </c>
     </row>
-    <row r="80" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B80" s="23" t="s">
+    <row r="80" spans="2:7">
+      <c r="B80" s="25" t="s">
         <v>201</v>
       </c>
-      <c r="C80" s="24"/>
-      <c r="D80" s="24"/>
-      <c r="E80" s="24"/>
-      <c r="F80" s="24"/>
-      <c r="G80" s="25"/>
-    </row>
-    <row r="81" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C80" s="26"/>
+      <c r="D80" s="26"/>
+      <c r="E80" s="26"/>
+      <c r="F80" s="26"/>
+      <c r="G80" s="27"/>
+    </row>
+    <row r="81" spans="2:7">
       <c r="B81" s="10">
         <v>25</v>
       </c>
@@ -2639,7 +3290,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="82" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:7">
       <c r="B82" s="10">
         <v>26</v>
       </c>
@@ -2659,7 +3310,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="83" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:7">
       <c r="B83" s="10">
         <v>27</v>
       </c>
@@ -2679,13 +3330,799 @@
         <v>58</v>
       </c>
     </row>
+    <row r="85" spans="2:7">
+      <c r="B85" s="21" t="s">
+        <v>208</v>
+      </c>
+      <c r="C85" s="21"/>
+      <c r="D85" s="21"/>
+      <c r="E85" s="21"/>
+      <c r="F85" s="21"/>
+      <c r="G85" s="21"/>
+    </row>
+    <row r="86" spans="2:7" ht="30">
+      <c r="B86" s="10">
+        <v>1</v>
+      </c>
+      <c r="C86" s="14" t="s">
+        <v>209</v>
+      </c>
+      <c r="D86" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G86" s="11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="87" spans="2:7" ht="30">
+      <c r="B87" s="10">
+        <v>2</v>
+      </c>
+      <c r="C87" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="D87" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G87" s="11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="88" spans="2:7" ht="30">
+      <c r="B88" s="10">
+        <v>3</v>
+      </c>
+      <c r="C88" s="14" t="s">
+        <v>211</v>
+      </c>
+      <c r="D88" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G88" s="11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="89" spans="2:7" ht="30">
+      <c r="B89" s="10">
+        <v>4</v>
+      </c>
+      <c r="C89" s="14" t="s">
+        <v>212</v>
+      </c>
+      <c r="D89" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G89" s="11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="90" spans="2:7" ht="30">
+      <c r="B90" s="10">
+        <v>5</v>
+      </c>
+      <c r="C90" s="14" t="s">
+        <v>214</v>
+      </c>
+      <c r="D90" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G90" s="11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="91" spans="2:7" ht="30">
+      <c r="B91" s="10">
+        <v>6</v>
+      </c>
+      <c r="C91" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="D91" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G91" s="11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="92" spans="2:7" ht="30">
+      <c r="B92" s="10">
+        <v>7</v>
+      </c>
+      <c r="C92" s="14" t="s">
+        <v>215</v>
+      </c>
+      <c r="D92" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G92" s="11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="94" spans="2:7">
+      <c r="B94" s="21" t="s">
+        <v>220</v>
+      </c>
+      <c r="C94" s="21"/>
+      <c r="D94" s="21"/>
+      <c r="E94" s="21"/>
+      <c r="F94" s="21"/>
+      <c r="G94" s="21"/>
+    </row>
+    <row r="95" spans="2:7" ht="30">
+      <c r="B95" s="10">
+        <v>1</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="D95" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G95" s="11"/>
+    </row>
+    <row r="96" spans="2:7" ht="30">
+      <c r="B96" s="10">
+        <v>2</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="D96" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G96" s="11"/>
+    </row>
+    <row r="97" spans="2:7" ht="30">
+      <c r="B97" s="10">
+        <v>3</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="D97" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G97" s="11"/>
+    </row>
+    <row r="98" spans="2:7">
+      <c r="B98" s="10">
+        <v>4</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="D98" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G98" s="11"/>
+    </row>
+    <row r="99" spans="2:7" ht="45">
+      <c r="B99" s="10">
+        <v>5</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="D99" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G99" s="11"/>
+    </row>
+    <row r="100" spans="2:7">
+      <c r="B100" s="10">
+        <v>6</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="D100" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G100" s="11"/>
+    </row>
+    <row r="101" spans="2:7" ht="30">
+      <c r="B101" s="10">
+        <v>7</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="D101" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G101" s="11"/>
+    </row>
+    <row r="102" spans="2:7" ht="30">
+      <c r="B102" s="10">
+        <v>8</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="D102" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G102" s="1"/>
+    </row>
+    <row r="103" spans="2:7">
+      <c r="B103" s="20" t="s">
+        <v>229</v>
+      </c>
+      <c r="C103" s="20"/>
+      <c r="D103" s="20"/>
+      <c r="E103" s="20"/>
+      <c r="F103" s="20"/>
+      <c r="G103" s="20"/>
+    </row>
+    <row r="104" spans="2:7" ht="30">
+      <c r="B104" s="10">
+        <v>9</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="D104" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G104" s="1"/>
+    </row>
+    <row r="105" spans="2:7">
+      <c r="B105" s="10">
+        <v>10</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="D105" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G105" s="1"/>
+    </row>
+    <row r="106" spans="2:7">
+      <c r="B106" s="10">
+        <v>11</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="D106" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G106" s="1"/>
+    </row>
+    <row r="107" spans="2:7">
+      <c r="B107" s="10">
+        <v>12</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="D107" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G107" s="1"/>
+    </row>
+    <row r="108" spans="2:7" ht="30">
+      <c r="B108" s="10">
+        <v>13</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="D108" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G108" s="1"/>
+    </row>
+    <row r="109" spans="2:7">
+      <c r="B109" s="20" t="s">
+        <v>235</v>
+      </c>
+      <c r="C109" s="20"/>
+      <c r="D109" s="20"/>
+      <c r="E109" s="20"/>
+      <c r="F109" s="20"/>
+      <c r="G109" s="20"/>
+    </row>
+    <row r="110" spans="2:7" ht="45">
+      <c r="B110" s="10">
+        <v>14</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="D110" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="F110" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G110" s="1"/>
+    </row>
+    <row r="111" spans="2:7" ht="30">
+      <c r="B111" s="10">
+        <v>15</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="D111" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="F111" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G111" s="1"/>
+    </row>
+    <row r="112" spans="2:7" ht="30">
+      <c r="B112" s="10">
+        <v>16</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="D112" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="E112" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="F112" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G112" s="1"/>
+    </row>
+    <row r="113" spans="2:7">
+      <c r="B113" s="20" t="s">
+        <v>239</v>
+      </c>
+      <c r="C113" s="20"/>
+      <c r="D113" s="20"/>
+      <c r="E113" s="20"/>
+      <c r="F113" s="20"/>
+      <c r="G113" s="20"/>
+    </row>
+    <row r="114" spans="2:7" ht="30">
+      <c r="B114" s="10">
+        <v>17</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="D114" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="F114" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G114" s="1"/>
+    </row>
+    <row r="115" spans="2:7" ht="45">
+      <c r="B115" s="10">
+        <v>18</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="D115" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="F115" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G115" s="1"/>
+    </row>
+    <row r="116" spans="2:7">
+      <c r="B116" s="10">
+        <v>19</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="D116" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="F116" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G116" s="1"/>
+    </row>
+    <row r="117" spans="2:7" ht="30">
+      <c r="B117" s="10">
+        <v>20</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="D117" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="E117" s="28" t="s">
+        <v>273</v>
+      </c>
+      <c r="F117" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G117" s="1"/>
+    </row>
+    <row r="118" spans="2:7">
+      <c r="B118" s="20" t="s">
+        <v>244</v>
+      </c>
+      <c r="C118" s="20"/>
+      <c r="D118" s="20"/>
+      <c r="E118" s="20"/>
+      <c r="F118" s="20"/>
+      <c r="G118" s="20"/>
+    </row>
+    <row r="119" spans="2:7" ht="30">
+      <c r="B119" s="19">
+        <v>21</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="D119" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="E119" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="F119" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G119" s="1"/>
+    </row>
+    <row r="120" spans="2:7">
+      <c r="B120" s="19">
+        <v>22</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="D120" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="E120" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="F120" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G120" s="1"/>
+    </row>
+    <row r="121" spans="2:7">
+      <c r="B121" s="19">
+        <v>23</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="D121" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="F121" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G121" s="1"/>
+    </row>
+    <row r="122" spans="2:7" ht="30">
+      <c r="B122" s="19">
+        <v>24</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="D122" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="E122" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="F122" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G122" s="1"/>
+    </row>
+    <row r="123" spans="2:7" ht="30">
+      <c r="B123" s="19">
+        <v>25</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="D123" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="E123" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="F123" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G123" s="1"/>
+    </row>
+    <row r="124" spans="2:7">
+      <c r="B124" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="C124" s="20"/>
+      <c r="D124" s="20"/>
+      <c r="E124" s="20"/>
+      <c r="F124" s="20"/>
+      <c r="G124" s="20"/>
+    </row>
+    <row r="125" spans="2:7">
+      <c r="B125" s="19">
+        <v>26</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="D125" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="E125" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="F125" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G125" s="1"/>
+    </row>
+    <row r="126" spans="2:7" ht="30">
+      <c r="B126" s="19">
+        <v>27</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="D126" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="E126" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="F126" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G126" s="1"/>
+    </row>
+    <row r="127" spans="2:7" ht="30">
+      <c r="B127" s="19">
+        <v>28</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="D127" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="E127" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="F127" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G127" s="1"/>
+    </row>
+    <row r="128" spans="2:7">
+      <c r="B128" s="20" t="s">
+        <v>253</v>
+      </c>
+      <c r="C128" s="20"/>
+      <c r="D128" s="20"/>
+      <c r="E128" s="20"/>
+      <c r="F128" s="20"/>
+      <c r="G128" s="20"/>
+    </row>
+    <row r="129" spans="2:7" ht="30">
+      <c r="B129" s="19">
+        <v>29</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="D129" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="E129" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="F129" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G129" s="1"/>
+    </row>
+    <row r="130" spans="2:7">
+      <c r="B130" s="19">
+        <v>30</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="D130" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="E130" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="F130" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G130" s="1"/>
+    </row>
+    <row r="131" spans="2:7">
+      <c r="B131" s="19">
+        <v>31</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="D131" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="E131" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="F131" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G131" s="1"/>
+    </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="13">
+    <mergeCell ref="B85:G85"/>
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="B23:G23"/>
     <mergeCell ref="B37:G37"/>
     <mergeCell ref="B54:G54"/>
     <mergeCell ref="B80:G80"/>
+    <mergeCell ref="B124:G124"/>
+    <mergeCell ref="B128:G128"/>
+    <mergeCell ref="B94:G94"/>
+    <mergeCell ref="B103:G103"/>
+    <mergeCell ref="B109:G109"/>
+    <mergeCell ref="B113:G113"/>
+    <mergeCell ref="B118:G118"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2696,13 +4133,13 @@
           <x14:formula1>
             <xm:f>'выпад списки'!$B$2:$B$5</xm:f>
           </x14:formula1>
-          <xm:sqref>D4:D21 D25:D35 D39:D52 D56:D79 D81:D83</xm:sqref>
+          <xm:sqref>D4:D21 D25:D35 D39:D52 D56:D79 D81:D83 D86:D92 D95:D102 D104:D108 D110:D112 D114:D117 D119:D123 D125:D127 D129:D131</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'выпад списки'!$F$2:$F$3</xm:f>
           </x14:formula1>
-          <xm:sqref>F25:F35 F4:F21 F39:F52 F56:F79 F81:F83</xm:sqref>
+          <xm:sqref>F25:F35 F4:F21 F39:F52 F56:F79 F81:F83 F86:F92 F95:F102 F104:F108 F110:F112 F114:F117 F119:F123 F125:F127 F129:F131</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -2713,7 +4150,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:N72"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="12.7109375" customWidth="1"/>
     <col min="3" max="3" width="36.28515625" customWidth="1"/>
@@ -2729,25 +4166,25 @@
     <col min="14" max="14" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="19" t="s">
+    <row r="2" spans="2:14" ht="29.25" customHeight="1">
+      <c r="B2" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="21"/>
-      <c r="I2" s="19" t="s">
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="24"/>
+      <c r="I2" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="J2" s="20"/>
-      <c r="K2" s="20"/>
-      <c r="L2" s="20"/>
-      <c r="M2" s="20"/>
-      <c r="N2" s="21"/>
-    </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="J2" s="23"/>
+      <c r="K2" s="23"/>
+      <c r="L2" s="23"/>
+      <c r="M2" s="23"/>
+      <c r="N2" s="24"/>
+    </row>
+    <row r="3" spans="2:14">
       <c r="B3" s="3" t="s">
         <v>0</v>
       </c>
@@ -2785,7 +4222,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="2:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:14" ht="45">
       <c r="B4" s="4">
         <v>1</v>
       </c>
@@ -2823,7 +4260,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="5" spans="2:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:14" ht="45">
       <c r="B5" s="4">
         <v>2</v>
       </c>
@@ -2861,7 +4298,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="6" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:14" ht="30">
       <c r="B6" s="4">
         <v>3</v>
       </c>
@@ -2899,7 +4336,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="7" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:14" ht="30">
       <c r="B7" s="4">
         <v>4</v>
       </c>
@@ -2937,7 +4374,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:14">
       <c r="B8" s="4">
         <v>5</v>
       </c>
@@ -2975,7 +4412,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:14">
       <c r="B9" s="4">
         <v>6</v>
       </c>
@@ -3013,7 +4450,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:14">
       <c r="B10" s="4">
         <v>7</v>
       </c>
@@ -3051,7 +4488,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="11" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:14" ht="30">
       <c r="B11" s="4">
         <v>8</v>
       </c>
@@ -3089,7 +4526,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="12" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:14" ht="30">
       <c r="B12" s="4">
         <v>9</v>
       </c>
@@ -3127,7 +4564,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="13" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:14" ht="30">
       <c r="B13" s="4">
         <v>10</v>
       </c>
@@ -3165,7 +4602,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="14" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:14" ht="30">
       <c r="B14" s="4">
         <v>11</v>
       </c>
@@ -3203,7 +4640,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="15" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:14" ht="30">
       <c r="B15" s="4">
         <v>12</v>
       </c>
@@ -3241,7 +4678,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="16" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:14" ht="30">
       <c r="B16" s="4">
         <v>13</v>
       </c>
@@ -3261,7 +4698,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="17" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:14" ht="30">
       <c r="B17" s="4">
         <v>14</v>
       </c>
@@ -3280,16 +4717,16 @@
       <c r="G17" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="I17" s="19" t="s">
+      <c r="I17" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="J17" s="20"/>
-      <c r="K17" s="20"/>
-      <c r="L17" s="20"/>
-      <c r="M17" s="20"/>
-      <c r="N17" s="21"/>
-    </row>
-    <row r="18" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="J17" s="23"/>
+      <c r="K17" s="23"/>
+      <c r="L17" s="23"/>
+      <c r="M17" s="23"/>
+      <c r="N17" s="24"/>
+    </row>
+    <row r="18" spans="2:14" ht="30">
       <c r="B18" s="4">
         <v>15</v>
       </c>
@@ -3327,7 +4764,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:14" ht="30">
       <c r="B19" s="4">
         <v>16</v>
       </c>
@@ -3365,7 +4802,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="20" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:14">
       <c r="B20" s="4">
         <v>17</v>
       </c>
@@ -3403,7 +4840,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="21" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:14">
       <c r="B21" s="4">
         <v>18</v>
       </c>
@@ -3441,7 +4878,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="22" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:14">
       <c r="I22" s="4">
         <v>4</v>
       </c>
@@ -3461,7 +4898,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="23" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:14">
       <c r="I23" s="4">
         <v>5</v>
       </c>
@@ -3481,15 +4918,15 @@
         <v>58</v>
       </c>
     </row>
-    <row r="24" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B24" s="22" t="s">
+    <row r="24" spans="2:14">
+      <c r="B24" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="C24" s="22"/>
-      <c r="D24" s="22"/>
-      <c r="E24" s="22"/>
-      <c r="F24" s="22"/>
-      <c r="G24" s="22"/>
+      <c r="C24" s="20"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="20"/>
+      <c r="G24" s="20"/>
       <c r="I24" s="4">
         <v>6</v>
       </c>
@@ -3509,7 +4946,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="25" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:14" ht="30">
       <c r="B25" s="3" t="s">
         <v>0</v>
       </c>
@@ -3547,7 +4984,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="26" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:14" ht="30">
       <c r="B26" s="4">
         <v>1</v>
       </c>
@@ -3585,7 +5022,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="27" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:14" ht="30">
       <c r="B27" s="4">
         <v>2</v>
       </c>
@@ -3623,7 +5060,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="28" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:14">
       <c r="B28" s="4">
         <v>3</v>
       </c>
@@ -3661,7 +5098,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="29" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:14" ht="30">
       <c r="B29" s="4">
         <v>4</v>
       </c>
@@ -3699,7 +5136,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="30" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:14">
       <c r="B30" s="4">
         <v>5</v>
       </c>
@@ -3737,7 +5174,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="31" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:14" ht="30">
       <c r="B31" s="4">
         <v>6</v>
       </c>
@@ -3775,7 +5212,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="32" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:14">
       <c r="B32" s="4">
         <v>7</v>
       </c>
@@ -3813,7 +5250,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:14">
       <c r="B33" s="4">
         <v>8</v>
       </c>
@@ -3851,7 +5288,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="34" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:14" ht="30">
       <c r="B34" s="4">
         <v>9</v>
       </c>
@@ -3889,7 +5326,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="35" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:14" ht="30">
       <c r="B35" s="4">
         <v>10</v>
       </c>
@@ -3927,7 +5364,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="36" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:14" ht="30">
       <c r="B36" s="4">
         <v>11</v>
       </c>
@@ -3965,7 +5402,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="37" spans="2:14" ht="90" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:14" ht="90">
       <c r="B37" s="4">
         <v>12</v>
       </c>
@@ -4003,7 +5440,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="38" spans="2:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:14" ht="45">
       <c r="B38" s="4">
         <v>13</v>
       </c>
@@ -4041,7 +5478,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="39" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:14" ht="30">
       <c r="B39" s="6"/>
       <c r="C39" s="7"/>
       <c r="D39" s="8"/>
@@ -4067,7 +5504,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="40" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:14" ht="30">
       <c r="I40" s="4">
         <v>22</v>
       </c>
@@ -4087,7 +5524,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:14">
       <c r="I41" s="4">
         <v>23</v>
       </c>
@@ -4107,25 +5544,25 @@
         <v>58</v>
       </c>
     </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B45" s="22" t="s">
+    <row r="45" spans="2:14">
+      <c r="B45" s="20" t="s">
         <v>97</v>
       </c>
-      <c r="C45" s="22"/>
-      <c r="D45" s="22"/>
-      <c r="E45" s="22"/>
-      <c r="F45" s="22"/>
-      <c r="G45" s="22"/>
-      <c r="I45" s="19" t="s">
+      <c r="C45" s="20"/>
+      <c r="D45" s="20"/>
+      <c r="E45" s="20"/>
+      <c r="F45" s="20"/>
+      <c r="G45" s="20"/>
+      <c r="I45" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="J45" s="20"/>
-      <c r="K45" s="20"/>
-      <c r="L45" s="20"/>
-      <c r="M45" s="20"/>
-      <c r="N45" s="21"/>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="J45" s="23"/>
+      <c r="K45" s="23"/>
+      <c r="L45" s="23"/>
+      <c r="M45" s="23"/>
+      <c r="N45" s="24"/>
+    </row>
+    <row r="46" spans="2:14">
       <c r="B46" s="3" t="s">
         <v>0</v>
       </c>
@@ -4163,7 +5600,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="47" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:14" ht="30">
       <c r="B47" s="4">
         <v>1</v>
       </c>
@@ -4201,7 +5638,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:14">
       <c r="B48" s="4">
         <v>2</v>
       </c>
@@ -4239,7 +5676,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="49" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:14">
       <c r="B49" s="4">
         <v>3</v>
       </c>
@@ -4277,7 +5714,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="50" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:14" ht="30">
       <c r="B50" s="4">
         <v>4</v>
       </c>
@@ -4315,7 +5752,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="51" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:14" ht="30">
       <c r="B51" s="4">
         <v>5</v>
       </c>
@@ -4353,7 +5790,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="52" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:14" ht="30">
       <c r="B52" s="4">
         <v>6</v>
       </c>
@@ -4391,7 +5828,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="53" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:14" ht="30">
       <c r="B53" s="4">
         <v>7</v>
       </c>
@@ -4429,7 +5866,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="54" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:14">
       <c r="B54" s="4">
         <v>8</v>
       </c>
@@ -4455,7 +5892,7 @@
       <c r="M54" s="8"/>
       <c r="N54" s="8"/>
     </row>
-    <row r="55" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:14">
       <c r="B55" s="4">
         <v>9</v>
       </c>
@@ -4475,7 +5912,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="56" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:14">
       <c r="B56" s="4">
         <v>10</v>
       </c>
@@ -4496,7 +5933,7 @@
       </c>
       <c r="H56" s="8"/>
     </row>
-    <row r="57" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:14">
       <c r="B57" s="4">
         <v>11</v>
       </c>
@@ -4517,7 +5954,7 @@
       </c>
       <c r="H57" s="8"/>
     </row>
-    <row r="58" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:14" ht="30">
       <c r="B58" s="4">
         <v>12</v>
       </c>
@@ -4538,7 +5975,7 @@
       </c>
       <c r="H58" s="8"/>
     </row>
-    <row r="59" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:14" ht="30">
       <c r="B59" s="4">
         <v>13</v>
       </c>
@@ -4559,7 +5996,7 @@
       </c>
       <c r="H59" s="8"/>
     </row>
-    <row r="60" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:14">
       <c r="B60" s="4">
         <v>14</v>
       </c>
@@ -4579,16 +6016,16 @@
         <v>58</v>
       </c>
       <c r="H60" s="8"/>
-      <c r="I60" s="19" t="s">
+      <c r="I60" s="22" t="s">
         <v>94</v>
       </c>
-      <c r="J60" s="20"/>
-      <c r="K60" s="20"/>
-      <c r="L60" s="20"/>
-      <c r="M60" s="20"/>
-      <c r="N60" s="21"/>
-    </row>
-    <row r="61" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="J60" s="23"/>
+      <c r="K60" s="23"/>
+      <c r="L60" s="23"/>
+      <c r="M60" s="23"/>
+      <c r="N60" s="24"/>
+    </row>
+    <row r="61" spans="2:14">
       <c r="B61" s="4">
         <v>15</v>
       </c>
@@ -4627,7 +6064,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="62" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:14">
       <c r="B62" s="4">
         <v>16</v>
       </c>
@@ -4665,7 +6102,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="63" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:14">
       <c r="B63" s="4">
         <v>17</v>
       </c>
@@ -4703,7 +6140,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="64" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:14">
       <c r="B64" s="4">
         <v>18</v>
       </c>
@@ -4741,7 +6178,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:14">
       <c r="B65" s="4">
         <v>19</v>
       </c>
@@ -4779,7 +6216,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="66" spans="2:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:14" ht="75">
       <c r="B66" s="4">
         <v>20</v>
       </c>
@@ -4817,7 +6254,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="67" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:14" ht="30">
       <c r="B67" s="4">
         <v>21</v>
       </c>
@@ -4855,7 +6292,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="68" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:14" ht="30">
       <c r="B68" s="4">
         <v>22</v>
       </c>
@@ -4893,7 +6330,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:14">
       <c r="B69" s="4">
         <v>23</v>
       </c>
@@ -4931,7 +6368,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="70" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:14" ht="30">
       <c r="B70" s="4">
         <v>24</v>
       </c>
@@ -4969,7 +6406,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:14">
       <c r="B71" s="4">
         <v>25</v>
       </c>
@@ -5007,7 +6444,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:14">
       <c r="B72" s="4">
         <v>26</v>
       </c>
@@ -5105,7 +6542,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:H11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
     <col min="4" max="4" width="27" bestFit="1" customWidth="1"/>
@@ -5113,7 +6550,7 @@
     <col min="8" max="8" width="29.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:8">
       <c r="B1" t="s">
         <v>6</v>
       </c>
@@ -5127,7 +6564,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8">
       <c r="B2" t="s">
         <v>1</v>
       </c>
@@ -5141,7 +6578,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:8">
       <c r="B3" t="s">
         <v>19</v>
       </c>
@@ -5152,7 +6589,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:8">
       <c r="B4" t="s">
         <v>16</v>
       </c>
@@ -5160,7 +6597,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:8">
       <c r="B5" t="s">
         <v>20</v>
       </c>
@@ -5168,32 +6605,32 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:8">
       <c r="D6" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:8">
       <c r="D7" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:8">
       <c r="D8" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:8">
       <c r="D9" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:8">
       <c r="D10" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:8">
       <c r="D11" t="s">
         <v>72</v>
       </c>
